--- a/public/data/GDM_Tracker_latest.xlsx
+++ b/public/data/GDM_Tracker_latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nationalgridplc.sharepoint.com/sites/GRP-INT-GasBusinessEnablement-DataManagement/Public Folder/Gas Data Modernization Journey/Report Migration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3263" documentId="13_ncr:1_{52745E9B-3AA1-4770-AAD3-E6166BFC13AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F201BFB7-AEC2-4682-89A0-0CB486F6F58A}"/>
+  <xr:revisionPtr revIDLastSave="3265" documentId="13_ncr:1_{52745E9B-3AA1-4770-AAD3-E6166BFC13AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C71BDCB-6DA3-430C-B367-09342452B28B}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="-21540" yWindow="4485" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27151,7 +27151,7 @@
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="56" customWidth="1"/>
     <col min="7" max="7" width="9.7109375" customWidth="1"/>
-    <col min="8" max="8" width="3.5703125" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" customWidth="1"/>
     <col min="9" max="9" width="17.7109375" customWidth="1"/>
     <col min="10" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="51.140625" bestFit="1" customWidth="1"/>

--- a/public/data/GDM_Tracker_latest.xlsx
+++ b/public/data/GDM_Tracker_latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nationalgridplc.sharepoint.com/sites/GRP-INT-GasBusinessEnablement-DataManagement/Public Folder/Gas Data Modernization Journey/Report Migration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3265" documentId="13_ncr:1_{52745E9B-3AA1-4770-AAD3-E6166BFC13AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C71BDCB-6DA3-430C-B367-09342452B28B}"/>
+  <xr:revisionPtr revIDLastSave="3331" documentId="13_ncr:1_{52745E9B-3AA1-4770-AAD3-E6166BFC13AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83406268-B8EA-46A8-B23B-8594C89345DB}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="-21540" yWindow="4485" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,11 +25,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dim Table'!$A$2:$C$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Fact Table'!$A$2:$J$156</definedName>
     <definedName name="A73A73">'Combined Delivery Data'!$A$73:$A$73</definedName>
-    <definedName name="DB_Dev_List">'Data Validation'!$B$3:$B$10</definedName>
+    <definedName name="B49B81">'Combined Delivery Data'!$B$49:$B$49</definedName>
+    <definedName name="DB_Dev_List">'Data Validation'!$B$3:$B$12</definedName>
     <definedName name="DPO_Approval_List">'Data Validation'!$K$3:$K$6</definedName>
     <definedName name="L2T2">'Rework Log'!$L$2:$L$2</definedName>
     <definedName name="PBI_Dev_List">'Data Validation'!$C$3:$C$5</definedName>
-    <definedName name="QA_List">'Data Validation'!$H$3:$H$6</definedName>
+    <definedName name="QA_List">'Data Validation'!$H$3:$H$7</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -228,7 +229,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3166" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3206" uniqueCount="467">
   <si>
     <t>Domain</t>
   </si>
@@ -714,7 +715,7 @@
     <t>RPT_02_GRO Monitor</t>
   </si>
   <si>
-    <t>PI2 - S3</t>
+    <t>PI2, S3</t>
   </si>
   <si>
     <t>Ready for review</t>
@@ -786,9 +787,6 @@
   </si>
   <si>
     <t>RPT_02_Fitting Work</t>
-  </si>
-  <si>
-    <t>hybrid</t>
   </si>
   <si>
     <t>RPT_02_Field Collector Report</t>
@@ -982,7 +980,7 @@
     <t>RPT_02_Emergency Response Statistics</t>
   </si>
   <si>
-    <t>RPT_02_Emergency Time Adjustments Log </t>
+    <t>RPT_02_Emergency Time Adjustments Log</t>
   </si>
   <si>
     <t>PI2, S6</t>
@@ -1000,7 +998,7 @@
     <t>RPT_02_Service Interruptions</t>
   </si>
   <si>
-    <t>RPT_02 Duty to Inspect</t>
+    <t>RPT_02_Duty to Inspect</t>
   </si>
   <si>
     <t>PI3,S2</t>
@@ -1291,7 +1289,7 @@
     <t>Resolved?</t>
   </si>
   <si>
-    <t>First Completed On (cut &amp; paste from main tab)</t>
+    <t>Fix Sent To</t>
   </si>
   <si>
     <t>Expected Fix Date</t>
@@ -1364,9 +1362,6 @@
   </si>
   <si>
     <t>Count mismatch for Elevated Pressure tab</t>
-  </si>
-  <si>
-    <t>RPT_Cut Out Orders</t>
   </si>
   <si>
     <t>Data last refresh showing incorrect for older data in the report</t>
@@ -1586,6 +1581,9 @@
   </si>
   <si>
     <t>Geetha.S1@nationalgrid.com</t>
+  </si>
+  <si>
+    <t>hybrid</t>
   </si>
   <si>
     <t>Did not pass re-test</t>
@@ -4089,7 +4087,7 @@
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Sent Back By"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="What Was Wrong"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Resolved?"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="First Completed On (cut &amp; paste from main tab)"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Fix Sent To"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Expected Fix Date"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Date Fixed"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="Fixed By"/>
@@ -7516,7 +7514,10 @@
       <c r="AJ33" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK33" s="72"/>
+      <c r="AK33" s="72" t="str">
+        <f>IF($B33="","",IF(AND(LEFT($AJ33,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B33)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ33,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B33)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ33="Yes – needs DB Dev to fix",M33&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B33)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ33="Yes – needs PBI Dev to fix",S33&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B33)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ33="Yes – needs QA to fix",Y33&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B33)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B33)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B33)&gt;0,"",IF(AND(V33&lt;&gt;"",K33&lt;&gt;"",V33&lt;K33),"QA target is before DB Dev target",IF(AND(V33&lt;&gt;"",Q33&lt;&gt;"",V33&lt;Q33),"QA target is before PBI Dev target",IF(AND(AA33&lt;&gt;"",V33&lt;&gt;"",AA33&lt;V33),"DPO Approval target is before QA target",IF(AND(AG33&lt;&gt;"",AA33&lt;&gt;"",AG33&lt;AA33),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL33" s="41" t="s">
         <v>141</v>
       </c>
@@ -8501,7 +8502,10 @@
       <c r="AJ42" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK42" s="47"/>
+      <c r="AK42" s="47" t="str">
+        <f>IF($B42="","",IF(AND(LEFT($AJ42,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B42)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ42,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B42)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ42="Yes – needs DB Dev to fix",M42&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B42)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ42="Yes – needs PBI Dev to fix",S42&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B42)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ42="Yes – needs QA to fix",Y42&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B42)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B42)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B42)&gt;0,"",IF(AND(V42&lt;&gt;"",K42&lt;&gt;"",V42&lt;K42),"QA target is before DB Dev target",IF(AND(V42&lt;&gt;"",Q42&lt;&gt;"",V42&lt;Q42),"QA target is before PBI Dev target",IF(AND(AA42&lt;&gt;"",V42&lt;&gt;"",AA42&lt;V42),"DPO Approval target is before QA target",IF(AND(AG42&lt;&gt;"",AA42&lt;&gt;"",AG42&lt;AA42),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL42" s="45" t="s">
         <v>162</v>
       </c>
@@ -8831,9 +8835,9 @@
       <c r="AL45" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="AM45" s="32" t="str" cm="1">
+      <c r="AM45" s="32" cm="1">
         <f t="array" ref="AM45">_xlfn.LET(_xlpm.rep,$B45,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
-        <v/>
+        <v>46268</v>
       </c>
       <c r="AN45" s="32" t="str" cm="1">
         <f t="array" ref="AN45">_xlfn.LET(_xlpm.rep,$B45,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"DPO*",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"DPO*",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,7)))</f>
@@ -9306,7 +9310,7 @@
         <v>46245</v>
       </c>
       <c r="N50" s="117" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="O50" s="117" t="s">
         <v>178</v>
@@ -9377,7 +9381,7 @@
         <v>126</v>
       </c>
       <c r="B51" s="33" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C51" s="33" t="s">
         <v>164</v>
@@ -9452,7 +9456,7 @@
       </c>
       <c r="AC51" s="36"/>
       <c r="AD51" s="33" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AE51" s="33" t="s">
         <v>72</v>
@@ -9485,10 +9489,10 @@
         <v>126</v>
       </c>
       <c r="B52" s="33" t="s">
+        <v>187</v>
+      </c>
+      <c r="C52" s="33" t="s">
         <v>188</v>
-      </c>
-      <c r="C52" s="33" t="s">
-        <v>189</v>
       </c>
       <c r="D52" t="str" cm="1">
         <f t="array" aca="1" ref="D52" ca="1">IF(AND(C52="Ready for Release in Prod",LEFT($AJ52,3)&lt;&gt;"Yes"),IF(AG52&lt;&gt;"","Delivered","On track"),IF($B52="","",IF(LEFT($AJ52,3)="Yes","Blocked - "&amp;MID($AJ52,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B52)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B52)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B52)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C52="NOT STARTED",IF(H52="","No plan date set",IF(H52&lt;TODAY(),"Review - planned start passed","On track")),IF(C52="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B52,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B52,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L52&lt;&gt;"",L52,K52)),_xlpm.act,IF(AND(M52&lt;&gt;"",M52&gt;=_xlpm.sent),M52,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C52="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B52,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B52,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R52&lt;&gt;"",R52,Q52)),_xlpm.act,IF(AND(S52&lt;&gt;"",S52&gt;=_xlpm.sent),S52,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C52="QA",_xlfn.LET(_xlpm.tgt,IF(AM52&lt;&gt;"",AM52,IF(W52&lt;&gt;"",W52,V52)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B52,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y52&lt;&gt;"",Y52&gt;=_xlpm.sent),Y52,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C52="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN52&lt;&gt;"",AN52,IF(AB52&lt;&gt;"",AB52,AA52)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B52,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC52&lt;&gt;"",AC52&gt;=_xlpm.sent),AC52,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C52="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -9558,7 +9562,7 @@
       </c>
       <c r="AC52" s="36"/>
       <c r="AD52" s="33" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AE52" s="33" t="s">
         <v>72</v>
@@ -9568,14 +9572,14 @@
       <c r="AH52" s="39"/>
       <c r="AI52" s="33"/>
       <c r="AJ52" s="40" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AK52" s="72" t="str">
         <f>IF($B52="","",IF(AND(LEFT($AJ52,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B52)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ52,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B52)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ52="Yes – needs DB Dev to fix",M52&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B52)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ52="Yes – needs PBI Dev to fix",S52&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B52)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ52="Yes – needs QA to fix",Y52&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B52)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B52)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B52)&gt;0,"",IF(AND(V52&lt;&gt;"",K52&lt;&gt;"",V52&lt;K52),"QA target is before DB Dev target",IF(AND(V52&lt;&gt;"",Q52&lt;&gt;"",V52&lt;Q52),"QA target is before PBI Dev target",IF(AND(AA52&lt;&gt;"",V52&lt;&gt;"",AA52&lt;V52),"DPO Approval target is before QA target",IF(AND(AG52&lt;&gt;"",AA52&lt;&gt;"",AG52&lt;AA52),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL52" s="79" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AM52" s="32" t="str" cm="1">
         <f t="array" ref="AM52">_xlfn.LET(_xlpm.rep,$B52,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -9591,7 +9595,7 @@
         <v>126</v>
       </c>
       <c r="B53" s="33" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C53" s="33" t="s">
         <v>164</v>
@@ -9626,7 +9630,7 @@
         <v>46251</v>
       </c>
       <c r="N53" s="36" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="O53" s="36" t="s">
         <v>131</v>
@@ -9697,7 +9701,7 @@
         <v>126</v>
       </c>
       <c r="B54" s="33" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C54" s="33" t="s">
         <v>164</v>
@@ -9772,7 +9776,7 @@
       </c>
       <c r="AC54" s="36"/>
       <c r="AD54" s="33" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AE54" s="33" t="s">
         <v>72</v>
@@ -9803,7 +9807,7 @@
         <v>126</v>
       </c>
       <c r="B55" s="33" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C55" s="33" t="s">
         <v>173</v>
@@ -9823,7 +9827,7 @@
         <v>46295</v>
       </c>
       <c r="I55" s="54" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J55" s="33" t="s">
         <v>76</v>
@@ -9839,7 +9843,7 @@
       </c>
       <c r="N55" s="36"/>
       <c r="O55" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P55" s="62" t="s">
         <v>77</v>
@@ -9854,7 +9858,7 @@
         <v>46267</v>
       </c>
       <c r="T55" s="68" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="U55" s="33" t="s">
         <v>47</v>
@@ -9876,7 +9880,7 @@
       <c r="AB55" s="36"/>
       <c r="AC55" s="36"/>
       <c r="AD55" s="33" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AE55" s="33" t="s">
         <v>49</v>
@@ -9893,7 +9897,7 @@
         <v/>
       </c>
       <c r="AL55" s="41" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AM55" s="32" cm="1">
         <f t="array" ref="AM55">_xlfn.LET(_xlpm.rep,$B55,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -9909,7 +9913,7 @@
         <v>126</v>
       </c>
       <c r="B56" s="33" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C56" s="33" t="s">
         <v>173</v>
@@ -9929,7 +9933,7 @@
         <v>46295</v>
       </c>
       <c r="I56" s="54" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J56" s="33" t="s">
         <v>76</v>
@@ -9944,10 +9948,10 @@
         <v>46253</v>
       </c>
       <c r="N56" s="36" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="O56" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P56" s="62" t="s">
         <v>60</v>
@@ -9962,10 +9966,10 @@
         <v>46266</v>
       </c>
       <c r="T56" s="68" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="U56" s="33" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="V56" s="58">
         <v>46276</v>
@@ -9984,7 +9988,7 @@
       <c r="AB56" s="36"/>
       <c r="AC56" s="36"/>
       <c r="AD56" s="33" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AE56" s="33" t="s">
         <v>49</v>
@@ -10001,7 +10005,7 @@
         <v/>
       </c>
       <c r="AL56" s="41" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AM56" s="32" t="str" cm="1">
         <f t="array" ref="AM56">_xlfn.LET(_xlpm.rep,$B56,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -10017,7 +10021,7 @@
         <v>126</v>
       </c>
       <c r="B57" s="33" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C57" s="33" t="s">
         <v>164</v>
@@ -10037,7 +10041,7 @@
         <v>46295</v>
       </c>
       <c r="I57" s="54" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J57" s="33" t="s">
         <v>65</v>
@@ -10053,7 +10057,7 @@
         <v>146</v>
       </c>
       <c r="O57" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P57" s="62" t="s">
         <v>46</v>
@@ -10068,7 +10072,7 @@
         <v>46268</v>
       </c>
       <c r="T57" s="68" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="U57" s="33" t="s">
         <v>47</v>
@@ -10109,7 +10113,7 @@
         <v/>
       </c>
       <c r="AL57" s="41" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM57" s="32" t="str" cm="1">
         <f t="array" ref="AM57">_xlfn.LET(_xlpm.rep,$B57,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -10125,10 +10129,10 @@
         <v>126</v>
       </c>
       <c r="B58" s="33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C58" s="33" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D58" t="str" cm="1">
         <f t="array" aca="1" ref="D58" ca="1">IF(AND(C58="Ready for Release in Prod",LEFT($AJ58,3)&lt;&gt;"Yes"),IF(AG58&lt;&gt;"","Delivered","On track"),IF($B58="","",IF(LEFT($AJ58,3)="Yes","Blocked - "&amp;MID($AJ58,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B58)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B58)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B58)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C58="NOT STARTED",IF(H58="","No plan date set",IF(H58&lt;TODAY(),"Review - planned start passed","On track")),IF(C58="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B58,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B58,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L58&lt;&gt;"",L58,K58)),_xlpm.act,IF(AND(M58&lt;&gt;"",M58&gt;=_xlpm.sent),M58,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C58="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B58,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B58,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R58&lt;&gt;"",R58,Q58)),_xlpm.act,IF(AND(S58&lt;&gt;"",S58&gt;=_xlpm.sent),S58,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C58="QA",_xlfn.LET(_xlpm.tgt,IF(AM58&lt;&gt;"",AM58,IF(W58&lt;&gt;"",W58,V58)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B58,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y58&lt;&gt;"",Y58&gt;=_xlpm.sent),Y58,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C58="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN58&lt;&gt;"",AN58,IF(AB58&lt;&gt;"",AB58,AA58)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B58,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC58&lt;&gt;"",AC58&gt;=_xlpm.sent),AC58,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C58="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -10145,7 +10149,7 @@
         <v>46295</v>
       </c>
       <c r="I58" s="54" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J58" s="33" t="s">
         <v>65</v>
@@ -10161,7 +10165,7 @@
         <v>146</v>
       </c>
       <c r="O58" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P58" s="62" t="s">
         <v>77</v>
@@ -10174,7 +10178,7 @@
       </c>
       <c r="S58" s="36"/>
       <c r="T58" s="68" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="U58" s="33"/>
       <c r="V58" s="58">
@@ -10207,7 +10211,7 @@
         <v>Blocked - log it on Rework Log</v>
       </c>
       <c r="AL58" s="41" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AM58" s="32" t="str" cm="1">
         <f t="array" ref="AM58">_xlfn.LET(_xlpm.rep,$B58,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -10223,7 +10227,7 @@
         <v>126</v>
       </c>
       <c r="B59" s="33" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C59" s="33" t="s">
         <v>182</v>
@@ -10243,7 +10247,7 @@
         <v>46295</v>
       </c>
       <c r="I59" s="54" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J59" s="33" t="s">
         <v>44</v>
@@ -10259,7 +10263,7 @@
       </c>
       <c r="N59" s="36"/>
       <c r="O59" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P59" s="62" t="s">
         <v>60</v>
@@ -10274,7 +10278,7 @@
         <v>46266</v>
       </c>
       <c r="T59" s="68" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="U59" s="33" t="s">
         <v>47</v>
@@ -10302,7 +10306,7 @@
       <c r="AH59" s="39"/>
       <c r="AI59" s="33"/>
       <c r="AJ59" s="40" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AK59" s="72" t="str">
         <f>IF($B59="","",IF(AND(LEFT($AJ59,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B59)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ59,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B59)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ59="Yes – needs DB Dev to fix",M59&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B59)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ59="Yes – needs PBI Dev to fix",S59&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B59)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ59="Yes – needs QA to fix",Y59&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B59)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B59)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B59)&gt;0,"",IF(AND(V59&lt;&gt;"",K59&lt;&gt;"",V59&lt;K59),"QA target is before DB Dev target",IF(AND(V59&lt;&gt;"",Q59&lt;&gt;"",V59&lt;Q59),"QA target is before PBI Dev target",IF(AND(AA59&lt;&gt;"",V59&lt;&gt;"",AA59&lt;V59),"DPO Approval target is before QA target",IF(AND(AG59&lt;&gt;"",AA59&lt;&gt;"",AG59&lt;AA59),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
@@ -10323,7 +10327,7 @@
         <v>126</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C60" s="33" t="s">
         <v>173</v>
@@ -10343,7 +10347,7 @@
         <v>46295</v>
       </c>
       <c r="I60" s="54" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J60" s="33" t="s">
         <v>154</v>
@@ -10358,10 +10362,10 @@
         <v>46255</v>
       </c>
       <c r="N60" s="36" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="O60" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P60" s="62" t="s">
         <v>46</v>
@@ -10376,7 +10380,7 @@
         <v>46273</v>
       </c>
       <c r="T60" s="68" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="U60" s="33" t="s">
         <v>47</v>
@@ -10394,7 +10398,7 @@
       <c r="AB60" s="36"/>
       <c r="AC60" s="36"/>
       <c r="AD60" s="33" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AE60" s="33" t="s">
         <v>72</v>
@@ -10425,7 +10429,7 @@
         <v>126</v>
       </c>
       <c r="B61" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C61" s="33" t="s">
         <v>173</v>
@@ -10445,7 +10449,7 @@
         <v>46295</v>
       </c>
       <c r="I61" s="54" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J61" s="33" t="s">
         <v>44</v>
@@ -10459,7 +10463,7 @@
       <c r="M61" s="36"/>
       <c r="N61" s="36"/>
       <c r="O61" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P61" s="62" t="s">
         <v>60</v>
@@ -10474,7 +10478,7 @@
         <v>46268</v>
       </c>
       <c r="T61" s="68" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="U61" s="33" t="s">
         <v>47</v>
@@ -10498,7 +10502,7 @@
       <c r="AB61" s="36"/>
       <c r="AC61" s="36"/>
       <c r="AD61" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AE61" s="33" t="s">
         <v>72</v>
@@ -10515,7 +10519,7 @@
         <v/>
       </c>
       <c r="AL61" s="41" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AM61" s="32" t="str" cm="1">
         <f t="array" ref="AM61">_xlfn.LET(_xlpm.rep,$B61,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -10531,7 +10535,7 @@
         <v>126</v>
       </c>
       <c r="B62" s="33" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C62" s="33" t="s">
         <v>173</v>
@@ -10551,7 +10555,7 @@
         <v>46295</v>
       </c>
       <c r="I62" s="54" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J62" s="33" t="s">
         <v>84</v>
@@ -10567,7 +10571,7 @@
       </c>
       <c r="N62" s="36"/>
       <c r="O62" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P62" s="62" t="s">
         <v>77</v>
@@ -10582,7 +10586,7 @@
         <v>46282</v>
       </c>
       <c r="T62" s="68" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="U62" s="33"/>
       <c r="V62" s="58">
@@ -10598,7 +10602,7 @@
       <c r="AB62" s="36"/>
       <c r="AC62" s="36"/>
       <c r="AD62" s="33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AE62" s="33" t="s">
         <v>72</v>
@@ -10629,7 +10633,7 @@
         <v>126</v>
       </c>
       <c r="B63" s="33" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C63" s="33" t="s">
         <v>173</v>
@@ -10649,7 +10653,7 @@
         <v>46295</v>
       </c>
       <c r="I63" s="54" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J63" s="33" t="s">
         <v>84</v>
@@ -10665,7 +10669,7 @@
       </c>
       <c r="N63" s="36"/>
       <c r="O63" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P63" s="62" t="s">
         <v>46</v>
@@ -10680,7 +10684,7 @@
         <v>46282</v>
       </c>
       <c r="T63" s="68" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="U63" s="33"/>
       <c r="V63" s="58">
@@ -10696,7 +10700,7 @@
       <c r="AB63" s="36"/>
       <c r="AC63" s="36"/>
       <c r="AD63" s="33" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AE63" s="33" t="s">
         <v>72</v>
@@ -10713,7 +10717,7 @@
         <v/>
       </c>
       <c r="AL63" s="41" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AM63" s="32" t="str" cm="1">
         <f t="array" ref="AM63">_xlfn.LET(_xlpm.rep,$B63,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -10729,7 +10733,7 @@
         <v>126</v>
       </c>
       <c r="B64" s="118" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C64" s="118" t="s">
         <v>173</v>
@@ -10749,7 +10753,7 @@
         <v>46295</v>
       </c>
       <c r="I64" s="122" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J64" s="118" t="s">
         <v>103</v>
@@ -10764,10 +10768,10 @@
         <v>46266</v>
       </c>
       <c r="N64" s="124" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="O64" s="124" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P64" s="125" t="s">
         <v>60</v>
@@ -10782,7 +10786,7 @@
         <v>46269</v>
       </c>
       <c r="T64" s="126" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="U64" s="118"/>
       <c r="V64" s="127">
@@ -10798,7 +10802,7 @@
       <c r="AB64" s="124"/>
       <c r="AC64" s="124"/>
       <c r="AD64" s="118" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AE64" s="118" t="s">
         <v>72</v>
@@ -10829,7 +10833,7 @@
         <v>126</v>
       </c>
       <c r="B65" s="33" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C65" s="33" t="s">
         <v>173</v>
@@ -10849,7 +10853,7 @@
         <v>46295</v>
       </c>
       <c r="I65" s="54" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J65" s="33" t="s">
         <v>154</v>
@@ -10867,7 +10871,7 @@
         <v>45</v>
       </c>
       <c r="O65" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P65" s="62" t="s">
         <v>77</v>
@@ -10882,10 +10886,10 @@
         <v>46273</v>
       </c>
       <c r="T65" s="68" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="U65" s="33" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="V65" s="58">
         <v>46290</v>
@@ -10933,10 +10937,10 @@
         <v>126</v>
       </c>
       <c r="B66" s="157" t="s">
+        <v>223</v>
+      </c>
+      <c r="C66" s="157" t="s">
         <v>224</v>
-      </c>
-      <c r="C66" s="157" t="s">
-        <v>225</v>
       </c>
       <c r="D66" s="136" t="str" cm="1">
         <f t="array" aca="1" ref="D66" ca="1">IF(AND(C66="Ready for Release in Prod",LEFT($AJ66,3)&lt;&gt;"Yes"),IF(AG66&lt;&gt;"","Delivered","On track"),IF($B66="","",IF(LEFT($AJ66,3)="Yes","Blocked - "&amp;MID($AJ66,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B66)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B66)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B66)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C66="NOT STARTED",IF(H66="","No plan date set",IF(H66&lt;TODAY(),"Review - planned start passed","On track")),IF(C66="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B66,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B66,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L66&lt;&gt;"",L66,K66)),_xlpm.act,IF(AND(M66&lt;&gt;"",M66&gt;=_xlpm.sent),M66,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C66="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B66,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B66,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R66&lt;&gt;"",R66,Q66)),_xlpm.act,IF(AND(S66&lt;&gt;"",S66&gt;=_xlpm.sent),S66,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C66="QA",_xlfn.LET(_xlpm.tgt,IF(AM66&lt;&gt;"",AM66,IF(W66&lt;&gt;"",W66,V66)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B66,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y66&lt;&gt;"",Y66&gt;=_xlpm.sent),Y66,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C66="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN66&lt;&gt;"",AN66,IF(AB66&lt;&gt;"",AB66,AA66)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B66,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC66&lt;&gt;"",AC66&gt;=_xlpm.sent),AC66,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C66="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -10953,7 +10957,7 @@
         <v>46295</v>
       </c>
       <c r="I66" s="159" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J66" s="157" t="s">
         <v>44</v>
@@ -10965,7 +10969,7 @@
       <c r="M66" s="145"/>
       <c r="N66" s="145"/>
       <c r="O66" s="145" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P66" s="161" t="s">
         <v>46</v>
@@ -10978,7 +10982,7 @@
       </c>
       <c r="S66" s="145"/>
       <c r="T66" s="162" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="U66" s="157"/>
       <c r="V66" s="144">
@@ -10994,7 +10998,7 @@
       <c r="AB66" s="145"/>
       <c r="AC66" s="145"/>
       <c r="AD66" s="157" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AE66" s="157" t="s">
         <v>94</v>
@@ -11025,7 +11029,7 @@
         <v>126</v>
       </c>
       <c r="B67" s="33" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C67" s="33" t="s">
         <v>173</v>
@@ -11045,7 +11049,7 @@
         <v>46295</v>
       </c>
       <c r="I67" s="54" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J67" s="33" t="s">
         <v>44</v>
@@ -11061,7 +11065,7 @@
       </c>
       <c r="N67" s="36"/>
       <c r="O67" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P67" s="62" t="s">
         <v>60</v>
@@ -11076,7 +11080,7 @@
         <v>46254</v>
       </c>
       <c r="T67" s="68" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="U67" s="33"/>
       <c r="V67" s="58">
@@ -11096,7 +11100,7 @@
       </c>
       <c r="AC67" s="36"/>
       <c r="AD67" s="33" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AE67" s="33" t="s">
         <v>94</v>
@@ -11127,10 +11131,10 @@
         <v>126</v>
       </c>
       <c r="B68" s="77" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C68" s="80" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D68" s="81" t="str" cm="1">
         <f t="array" aca="1" ref="D68" ca="1">IF(AND(C68="Ready for Release in Prod",LEFT($AJ68,3)&lt;&gt;"Yes"),IF(AG68&lt;&gt;"","Delivered","On track"),IF($B68="","",IF(LEFT($AJ68,3)="Yes","Blocked - "&amp;MID($AJ68,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B68)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B68)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B68)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C68="NOT STARTED",IF(H68="","No plan date set",IF(H68&lt;TODAY(),"Review - planned start passed","On track")),IF(C68="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B68,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B68,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L68&lt;&gt;"",L68,K68)),_xlpm.act,IF(AND(M68&lt;&gt;"",M68&gt;=_xlpm.sent),M68,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C68="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B68,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B68,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R68&lt;&gt;"",R68,Q68)),_xlpm.act,IF(AND(S68&lt;&gt;"",S68&gt;=_xlpm.sent),S68,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C68="QA",_xlfn.LET(_xlpm.tgt,IF(AM68&lt;&gt;"",AM68,IF(W68&lt;&gt;"",W68,V68)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B68,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y68&lt;&gt;"",Y68&gt;=_xlpm.sent),Y68,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C68="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN68&lt;&gt;"",AN68,IF(AB68&lt;&gt;"",AB68,AA68)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B68,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC68&lt;&gt;"",AC68&gt;=_xlpm.sent),AC68,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C68="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -11147,10 +11151,10 @@
         <v>46295</v>
       </c>
       <c r="I68" s="84" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J68" s="80" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K68" s="85">
         <v>46276</v>
@@ -11163,7 +11167,7 @@
       </c>
       <c r="N68" s="86"/>
       <c r="O68" s="86" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P68" s="87" t="s">
         <v>77</v>
@@ -11174,7 +11178,7 @@
       <c r="R68" s="86"/>
       <c r="S68" s="86"/>
       <c r="T68" s="88" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U68" s="80"/>
       <c r="V68" s="89">
@@ -11190,7 +11194,7 @@
       <c r="AB68" s="86"/>
       <c r="AC68" s="86"/>
       <c r="AD68" s="77" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AE68" s="80" t="s">
         <v>72</v>
@@ -11207,7 +11211,7 @@
         <v/>
       </c>
       <c r="AL68" s="95" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AM68" s="96" t="str" cm="1">
         <f t="array" ref="AM68">_xlfn.LET(_xlpm.rep,$B68,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -11223,10 +11227,10 @@
         <v>126</v>
       </c>
       <c r="B69" s="78" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C69" s="97" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D69" s="98" t="str" cm="1">
         <f t="array" aca="1" ref="D69" ca="1">IF(AND(C69="Ready for Release in Prod",LEFT($AJ69,3)&lt;&gt;"Yes"),IF(AG69&lt;&gt;"","Delivered","On track"),IF($B69="","",IF(LEFT($AJ69,3)="Yes","Blocked - "&amp;MID($AJ69,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B69)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B69)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B69)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C69="NOT STARTED",IF(H69="","No plan date set",IF(H69&lt;TODAY(),"Review - planned start passed","On track")),IF(C69="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B69,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B69,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L69&lt;&gt;"",L69,K69)),_xlpm.act,IF(AND(M69&lt;&gt;"",M69&gt;=_xlpm.sent),M69,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C69="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B69,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B69,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R69&lt;&gt;"",R69,Q69)),_xlpm.act,IF(AND(S69&lt;&gt;"",S69&gt;=_xlpm.sent),S69,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C69="QA",_xlfn.LET(_xlpm.tgt,IF(AM69&lt;&gt;"",AM69,IF(W69&lt;&gt;"",W69,V69)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B69,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y69&lt;&gt;"",Y69&gt;=_xlpm.sent),Y69,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C69="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN69&lt;&gt;"",AN69,IF(AB69&lt;&gt;"",AB69,AA69)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B69,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC69&lt;&gt;"",AC69&gt;=_xlpm.sent),AC69,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C69="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -11243,7 +11247,7 @@
         <v>46295</v>
       </c>
       <c r="I69" s="101" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J69" s="97" t="s">
         <v>59</v>
@@ -11255,7 +11259,7 @@
       <c r="M69" s="103"/>
       <c r="N69" s="103"/>
       <c r="O69" s="103" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P69" s="104" t="s">
         <v>46</v>
@@ -11266,7 +11270,7 @@
       <c r="R69" s="103"/>
       <c r="S69" s="103"/>
       <c r="T69" s="105" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U69" s="97"/>
       <c r="V69" s="106">
@@ -11282,7 +11286,7 @@
       <c r="AB69" s="103"/>
       <c r="AC69" s="103"/>
       <c r="AD69" s="78" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AE69" s="97" t="s">
         <v>72</v>
@@ -11299,7 +11303,7 @@
         <v/>
       </c>
       <c r="AL69" s="112" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AM69" s="113" t="str" cm="1">
         <f t="array" ref="AM69">_xlfn.LET(_xlpm.rep,$B69,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -11315,10 +11319,10 @@
         <v>126</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C70" s="33" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D70" t="str" cm="1">
         <f t="array" aca="1" ref="D70" ca="1">IF(AND(C70="Ready for Release in Prod",LEFT($AJ70,3)&lt;&gt;"Yes"),IF(AG70&lt;&gt;"","Delivered","On track"),IF($B70="","",IF(LEFT($AJ70,3)="Yes","Blocked - "&amp;MID($AJ70,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B70)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B70)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B70)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C70="NOT STARTED",IF(H70="","No plan date set",IF(H70&lt;TODAY(),"Review - planned start passed","On track")),IF(C70="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B70,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B70,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L70&lt;&gt;"",L70,K70)),_xlpm.act,IF(AND(M70&lt;&gt;"",M70&gt;=_xlpm.sent),M70,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C70="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B70,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B70,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R70&lt;&gt;"",R70,Q70)),_xlpm.act,IF(AND(S70&lt;&gt;"",S70&gt;=_xlpm.sent),S70,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C70="QA",_xlfn.LET(_xlpm.tgt,IF(AM70&lt;&gt;"",AM70,IF(W70&lt;&gt;"",W70,V70)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B70,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y70&lt;&gt;"",Y70&gt;=_xlpm.sent),Y70,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C70="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN70&lt;&gt;"",AN70,IF(AB70&lt;&gt;"",AB70,AA70)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B70,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC70&lt;&gt;"",AC70&gt;=_xlpm.sent),AC70,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C70="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -11335,7 +11339,7 @@
         <v>46295</v>
       </c>
       <c r="I70" s="54" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J70" s="33" t="s">
         <v>65</v>
@@ -11353,7 +11357,7 @@
         <v>146</v>
       </c>
       <c r="O70" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P70" s="62" t="s">
         <v>46</v>
@@ -11366,7 +11370,7 @@
       </c>
       <c r="S70" s="36"/>
       <c r="T70" s="68" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U70" s="33"/>
       <c r="V70" s="58">
@@ -11413,7 +11417,7 @@
         <v>126</v>
       </c>
       <c r="B71" s="33" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C71" s="33" t="s">
         <v>182</v>
@@ -11433,7 +11437,7 @@
         <v>46295</v>
       </c>
       <c r="I71" s="54" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J71" s="33" t="s">
         <v>44</v>
@@ -11449,7 +11453,7 @@
       </c>
       <c r="N71" s="36"/>
       <c r="O71" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P71" s="62" t="s">
         <v>60</v>
@@ -11464,7 +11468,7 @@
         <v>46281</v>
       </c>
       <c r="T71" s="68" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U71" s="33" t="s">
         <v>47</v>
@@ -11482,7 +11486,7 @@
       <c r="AB71" s="36"/>
       <c r="AC71" s="36"/>
       <c r="AD71" s="33" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AE71" s="33" t="s">
         <v>94</v>
@@ -11499,7 +11503,7 @@
         <v/>
       </c>
       <c r="AL71" s="41" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AM71" s="32" t="str" cm="1">
         <f t="array" ref="AM71">_xlfn.LET(_xlpm.rep,$B71,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -11515,7 +11519,7 @@
         <v>126</v>
       </c>
       <c r="B72" s="33" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C72" s="33" t="s">
         <v>164</v>
@@ -11535,7 +11539,7 @@
         <v>46295</v>
       </c>
       <c r="I72" s="54" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J72" s="33" t="s">
         <v>76</v>
@@ -11553,7 +11557,7 @@
         <v>45</v>
       </c>
       <c r="O72" s="36" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P72" s="62" t="s">
         <v>77</v>
@@ -11568,7 +11572,7 @@
         <v>46276</v>
       </c>
       <c r="T72" s="68" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="U72" s="33" t="s">
         <v>47</v>
@@ -11623,10 +11627,10 @@
         <v>126</v>
       </c>
       <c r="B73" s="31" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C73" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D73" t="str" cm="1">
         <f t="array" aca="1" ref="D73" ca="1">IF(AND(C73="Ready for Release in Prod",LEFT($AJ73,3)&lt;&gt;"Yes"),IF(AG73&lt;&gt;"","Delivered","On track"),IF($B73="","",IF(LEFT($AJ73,3)="Yes","Blocked - "&amp;MID($AJ73,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B73)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B73)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B73)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C73="NOT STARTED",IF(H73="","No plan date set",IF(H73&lt;TODAY(),"Review - planned start passed","On track")),IF(C73="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B73,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B73,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L73&lt;&gt;"",L73,K73)),_xlpm.act,IF(AND(M73&lt;&gt;"",M73&gt;=_xlpm.sent),M73,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C73="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B73,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B73,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R73&lt;&gt;"",R73,Q73)),_xlpm.act,IF(AND(S73&lt;&gt;"",S73&gt;=_xlpm.sent),S73,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C73="QA",_xlfn.LET(_xlpm.tgt,IF(AM73&lt;&gt;"",AM73,IF(W73&lt;&gt;"",W73,V73)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B73,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y73&lt;&gt;"",Y73&gt;=_xlpm.sent),Y73,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C73="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN73&lt;&gt;"",AN73,IF(AB73&lt;&gt;"",AB73,AA73)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B73,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC73&lt;&gt;"",AC73&gt;=_xlpm.sent),AC73,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C73="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -11643,7 +11647,7 @@
         <v>46325</v>
       </c>
       <c r="I73" s="55" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J73" s="31" t="s">
         <v>76</v>
@@ -11661,7 +11665,7 @@
         <v>45</v>
       </c>
       <c r="O73" s="44" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P73" s="65" t="s">
         <v>77</v>
@@ -11672,7 +11676,7 @@
       <c r="R73" s="43"/>
       <c r="S73" s="44"/>
       <c r="T73" s="69" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="U73" s="31"/>
       <c r="V73" s="28">
@@ -11688,7 +11692,7 @@
       <c r="AB73" s="43"/>
       <c r="AC73" s="43"/>
       <c r="AD73" s="31" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AE73" s="31" t="s">
         <v>72</v>
@@ -11698,7 +11702,10 @@
       <c r="AH73" s="31"/>
       <c r="AI73" s="31"/>
       <c r="AJ73" s="31"/>
-      <c r="AK73" s="31"/>
+      <c r="AK73" s="31" t="str">
+        <f>IF($B73="","",IF(AND(LEFT($AJ73,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B73)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ73,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B73)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ73="Yes – needs DB Dev to fix",M73&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B73)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ73="Yes – needs PBI Dev to fix",S73&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B73)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ73="Yes – needs QA to fix",Y73&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B73)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B73)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B73)&gt;0,"",IF(AND(V73&lt;&gt;"",K73&lt;&gt;"",V73&lt;K73),"QA target is before DB Dev target",IF(AND(V73&lt;&gt;"",Q73&lt;&gt;"",V73&lt;Q73),"QA target is before PBI Dev target",IF(AND(AA73&lt;&gt;"",V73&lt;&gt;"",AA73&lt;V73),"DPO Approval target is before QA target",IF(AND(AG73&lt;&gt;"",AA73&lt;&gt;"",AG73&lt;AA73),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL73" s="31"/>
       <c r="AM73" s="32" t="str" cm="1">
         <f t="array" ref="AM73">_xlfn.LET(_xlpm.rep,$B73,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -11714,10 +11721,10 @@
         <v>126</v>
       </c>
       <c r="B74" s="31" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C74" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D74" t="str" cm="1">
         <f t="array" aca="1" ref="D74" ca="1">IF(AND(C74="Ready for Release in Prod",LEFT($AJ74,3)&lt;&gt;"Yes"),IF(AG74&lt;&gt;"","Delivered","On track"),IF($B74="","",IF(LEFT($AJ74,3)="Yes","Blocked - "&amp;MID($AJ74,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B74)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B74)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B74)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C74="NOT STARTED",IF(H74="","No plan date set",IF(H74&lt;TODAY(),"Review - planned start passed","On track")),IF(C74="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B74,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B74,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L74&lt;&gt;"",L74,K74)),_xlpm.act,IF(AND(M74&lt;&gt;"",M74&gt;=_xlpm.sent),M74,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C74="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B74,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B74,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R74&lt;&gt;"",R74,Q74)),_xlpm.act,IF(AND(S74&lt;&gt;"",S74&gt;=_xlpm.sent),S74,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C74="QA",_xlfn.LET(_xlpm.tgt,IF(AM74&lt;&gt;"",AM74,IF(W74&lt;&gt;"",W74,V74)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B74,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y74&lt;&gt;"",Y74&gt;=_xlpm.sent),Y74,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C74="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN74&lt;&gt;"",AN74,IF(AB74&lt;&gt;"",AB74,AA74)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B74,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC74&lt;&gt;"",AC74&gt;=_xlpm.sent),AC74,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C74="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -11734,10 +11741,10 @@
         <v>46325</v>
       </c>
       <c r="I74" s="55" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J74" s="53" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K74" s="43">
         <v>46304</v>
@@ -11750,7 +11757,7 @@
       </c>
       <c r="N74" s="44"/>
       <c r="O74" s="44" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P74" s="74" t="s">
         <v>77</v>
@@ -11761,7 +11768,7 @@
       <c r="R74" s="43"/>
       <c r="S74" s="44"/>
       <c r="T74" s="69" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="U74" s="46"/>
       <c r="V74" s="28">
@@ -11787,7 +11794,10 @@
       <c r="AH74" s="31"/>
       <c r="AI74" s="31"/>
       <c r="AJ74" s="31"/>
-      <c r="AK74" s="31"/>
+      <c r="AK74" s="31" t="str">
+        <f>IF($B74="","",IF(AND(LEFT($AJ74,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B74)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ74,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B74)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ74="Yes – needs DB Dev to fix",M74&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B74)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ74="Yes – needs PBI Dev to fix",S74&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B74)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ74="Yes – needs QA to fix",Y74&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B74)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B74)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B74)&gt;0,"",IF(AND(V74&lt;&gt;"",K74&lt;&gt;"",V74&lt;K74),"QA target is before DB Dev target",IF(AND(V74&lt;&gt;"",Q74&lt;&gt;"",V74&lt;Q74),"QA target is before PBI Dev target",IF(AND(AA74&lt;&gt;"",V74&lt;&gt;"",AA74&lt;V74),"DPO Approval target is before QA target",IF(AND(AG74&lt;&gt;"",AA74&lt;&gt;"",AG74&lt;AA74),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL74" s="31"/>
       <c r="AM74" s="32" t="str" cm="1">
         <f t="array" ref="AM74">_xlfn.LET(_xlpm.rep,$B74,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -11803,10 +11813,10 @@
         <v>126</v>
       </c>
       <c r="B75" s="135" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C75" s="135" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D75" s="136" t="str" cm="1">
         <f t="array" aca="1" ref="D75" ca="1">IF(AND(C75="Ready for Release in Prod",LEFT($AJ75,3)&lt;&gt;"Yes"),IF(AG75&lt;&gt;"","Delivered","On track"),IF($B75="","",IF(LEFT($AJ75,3)="Yes","Blocked - "&amp;MID($AJ75,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B75)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B75)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B75)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C75="NOT STARTED",IF(H75="","No plan date set",IF(H75&lt;TODAY(),"Review - planned start passed","On track")),IF(C75="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B75,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B75,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L75&lt;&gt;"",L75,K75)),_xlpm.act,IF(AND(M75&lt;&gt;"",M75&gt;=_xlpm.sent),M75,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C75="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B75,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B75,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R75&lt;&gt;"",R75,Q75)),_xlpm.act,IF(AND(S75&lt;&gt;"",S75&gt;=_xlpm.sent),S75,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C75="QA",_xlfn.LET(_xlpm.tgt,IF(AM75&lt;&gt;"",AM75,IF(W75&lt;&gt;"",W75,V75)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B75,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y75&lt;&gt;"",Y75&gt;=_xlpm.sent),Y75,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C75="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN75&lt;&gt;"",AN75,IF(AB75&lt;&gt;"",AB75,AA75)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B75,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC75&lt;&gt;"",AC75&gt;=_xlpm.sent),AC75,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C75="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -11821,7 +11831,7 @@
         <v>46325</v>
       </c>
       <c r="I75" s="138" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J75" s="135" t="s">
         <v>59</v>
@@ -11833,7 +11843,7 @@
       <c r="M75" s="140"/>
       <c r="N75" s="140"/>
       <c r="O75" s="140" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P75" s="141"/>
       <c r="Q75" s="139">
@@ -11842,7 +11852,7 @@
       <c r="R75" s="139"/>
       <c r="S75" s="140"/>
       <c r="T75" s="142" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="U75" s="143"/>
       <c r="V75" s="144">
@@ -11858,7 +11868,7 @@
       <c r="AB75" s="139"/>
       <c r="AC75" s="139"/>
       <c r="AD75" s="135" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AE75" s="135" t="s">
         <v>94</v>
@@ -11868,7 +11878,10 @@
       <c r="AH75" s="135"/>
       <c r="AI75" s="135"/>
       <c r="AJ75" s="135"/>
-      <c r="AK75" s="135"/>
+      <c r="AK75" s="135" t="str">
+        <f>IF($B75="","",IF(AND(LEFT($AJ75,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B75)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ75,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B75)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ75="Yes – needs DB Dev to fix",M75&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B75)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ75="Yes – needs PBI Dev to fix",S75&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B75)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ75="Yes – needs QA to fix",Y75&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B75)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B75)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B75)&gt;0,"",IF(AND(V75&lt;&gt;"",K75&lt;&gt;"",V75&lt;K75),"QA target is before DB Dev target",IF(AND(V75&lt;&gt;"",Q75&lt;&gt;"",V75&lt;Q75),"QA target is before PBI Dev target",IF(AND(AA75&lt;&gt;"",V75&lt;&gt;"",AA75&lt;V75),"DPO Approval target is before QA target",IF(AND(AG75&lt;&gt;"",AA75&lt;&gt;"",AG75&lt;AA75),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL75" s="135"/>
       <c r="AM75" s="143" t="str" cm="1">
         <f t="array" ref="AM75">_xlfn.LET(_xlpm.rep,$B75,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -11884,10 +11897,10 @@
         <v>126</v>
       </c>
       <c r="B76" s="135" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C76" s="135" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D76" s="136" t="str" cm="1">
         <f t="array" aca="1" ref="D76" ca="1">IF(AND(C76="Ready for Release in Prod",LEFT($AJ76,3)&lt;&gt;"Yes"),IF(AG76&lt;&gt;"","Delivered","On track"),IF($B76="","",IF(LEFT($AJ76,3)="Yes","Blocked - "&amp;MID($AJ76,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B76)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B76)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B76)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C76="NOT STARTED",IF(H76="","No plan date set",IF(H76&lt;TODAY(),"Review - planned start passed","On track")),IF(C76="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B76,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B76,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L76&lt;&gt;"",L76,K76)),_xlpm.act,IF(AND(M76&lt;&gt;"",M76&gt;=_xlpm.sent),M76,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C76="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B76,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B76,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R76&lt;&gt;"",R76,Q76)),_xlpm.act,IF(AND(S76&lt;&gt;"",S76&gt;=_xlpm.sent),S76,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C76="QA",_xlfn.LET(_xlpm.tgt,IF(AM76&lt;&gt;"",AM76,IF(W76&lt;&gt;"",W76,V76)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B76,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y76&lt;&gt;"",Y76&gt;=_xlpm.sent),Y76,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C76="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN76&lt;&gt;"",AN76,IF(AB76&lt;&gt;"",AB76,AA76)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B76,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC76&lt;&gt;"",AC76&gt;=_xlpm.sent),AC76,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C76="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -11902,7 +11915,7 @@
         <v>46325</v>
       </c>
       <c r="I76" s="138" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J76" s="135" t="s">
         <v>59</v>
@@ -11914,7 +11927,7 @@
       <c r="M76" s="140"/>
       <c r="N76" s="140"/>
       <c r="O76" s="140" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P76" s="141"/>
       <c r="Q76" s="139">
@@ -11923,7 +11936,7 @@
       <c r="R76" s="139"/>
       <c r="S76" s="140"/>
       <c r="T76" s="142" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="U76" s="143"/>
       <c r="V76" s="144">
@@ -11939,7 +11952,7 @@
       <c r="AB76" s="139"/>
       <c r="AC76" s="139"/>
       <c r="AD76" s="135" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AE76" s="135" t="s">
         <v>94</v>
@@ -11949,7 +11962,10 @@
       <c r="AH76" s="135"/>
       <c r="AI76" s="135"/>
       <c r="AJ76" s="135"/>
-      <c r="AK76" s="135"/>
+      <c r="AK76" s="135" t="str">
+        <f>IF($B76="","",IF(AND(LEFT($AJ76,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B76)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ76,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B76)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ76="Yes – needs DB Dev to fix",M76&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B76)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ76="Yes – needs PBI Dev to fix",S76&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B76)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ76="Yes – needs QA to fix",Y76&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B76)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B76)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B76)&gt;0,"",IF(AND(V76&lt;&gt;"",K76&lt;&gt;"",V76&lt;K76),"QA target is before DB Dev target",IF(AND(V76&lt;&gt;"",Q76&lt;&gt;"",V76&lt;Q76),"QA target is before PBI Dev target",IF(AND(AA76&lt;&gt;"",V76&lt;&gt;"",AA76&lt;V76),"DPO Approval target is before QA target",IF(AND(AG76&lt;&gt;"",AA76&lt;&gt;"",AG76&lt;AA76),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL76" s="135"/>
       <c r="AM76" s="143" t="str" cm="1">
         <f t="array" ref="AM76">_xlfn.LET(_xlpm.rep,$B76,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -11965,10 +11981,10 @@
         <v>126</v>
       </c>
       <c r="B77" s="135" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C77" s="135" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D77" s="136" t="str" cm="1">
         <f t="array" aca="1" ref="D77" ca="1">IF(AND(C77="Ready for Release in Prod",LEFT($AJ77,3)&lt;&gt;"Yes"),IF(AG77&lt;&gt;"","Delivered","On track"),IF($B77="","",IF(LEFT($AJ77,3)="Yes","Blocked - "&amp;MID($AJ77,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B77)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B77)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B77)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C77="NOT STARTED",IF(H77="","No plan date set",IF(H77&lt;TODAY(),"Review - planned start passed","On track")),IF(C77="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B77,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B77,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L77&lt;&gt;"",L77,K77)),_xlpm.act,IF(AND(M77&lt;&gt;"",M77&gt;=_xlpm.sent),M77,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C77="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B77,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B77,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R77&lt;&gt;"",R77,Q77)),_xlpm.act,IF(AND(S77&lt;&gt;"",S77&gt;=_xlpm.sent),S77,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C77="QA",_xlfn.LET(_xlpm.tgt,IF(AM77&lt;&gt;"",AM77,IF(W77&lt;&gt;"",W77,V77)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B77,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y77&lt;&gt;"",Y77&gt;=_xlpm.sent),Y77,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C77="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN77&lt;&gt;"",AN77,IF(AB77&lt;&gt;"",AB77,AA77)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B77,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC77&lt;&gt;"",AC77&gt;=_xlpm.sent),AC77,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C77="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -11983,7 +11999,7 @@
         <v>46325</v>
       </c>
       <c r="I77" s="138" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J77" s="135" t="s">
         <v>154</v>
@@ -11995,7 +12011,7 @@
       <c r="M77" s="140"/>
       <c r="N77" s="140"/>
       <c r="O77" s="140" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P77" s="141"/>
       <c r="Q77" s="139">
@@ -12004,7 +12020,7 @@
       <c r="R77" s="139"/>
       <c r="S77" s="140"/>
       <c r="T77" s="142" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="U77" s="143"/>
       <c r="V77" s="144">
@@ -12020,7 +12036,7 @@
       <c r="AB77" s="139"/>
       <c r="AC77" s="139"/>
       <c r="AD77" s="135" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AE77" s="135" t="s">
         <v>94</v>
@@ -12030,7 +12046,10 @@
       <c r="AH77" s="135"/>
       <c r="AI77" s="135"/>
       <c r="AJ77" s="135"/>
-      <c r="AK77" s="135"/>
+      <c r="AK77" s="135" t="str">
+        <f>IF($B77="","",IF(AND(LEFT($AJ77,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B77)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ77,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B77)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ77="Yes – needs DB Dev to fix",M77&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B77)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ77="Yes – needs PBI Dev to fix",S77&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B77)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ77="Yes – needs QA to fix",Y77&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B77)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B77)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B77)&gt;0,"",IF(AND(V77&lt;&gt;"",K77&lt;&gt;"",V77&lt;K77),"QA target is before DB Dev target",IF(AND(V77&lt;&gt;"",Q77&lt;&gt;"",V77&lt;Q77),"QA target is before PBI Dev target",IF(AND(AA77&lt;&gt;"",V77&lt;&gt;"",AA77&lt;V77),"DPO Approval target is before QA target",IF(AND(AG77&lt;&gt;"",AA77&lt;&gt;"",AG77&lt;AA77),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL77" s="135"/>
       <c r="AM77" s="143" t="str" cm="1">
         <f t="array" ref="AM77">_xlfn.LET(_xlpm.rep,$B77,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -12046,10 +12065,10 @@
         <v>126</v>
       </c>
       <c r="B78" s="146" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C78" s="146" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D78" s="147" t="str" cm="1">
         <f t="array" aca="1" ref="D78" ca="1">IF(AND(C78="Ready for Release in Prod",LEFT($AJ78,3)&lt;&gt;"Yes"),IF(AG78&lt;&gt;"","Delivered","On track"),IF($B78="","",IF(LEFT($AJ78,3)="Yes","Blocked - "&amp;MID($AJ78,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B78)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B78)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B78)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C78="NOT STARTED",IF(H78="","No plan date set",IF(H78&lt;TODAY(),"Review - planned start passed","On track")),IF(C78="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B78,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B78,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L78&lt;&gt;"",L78,K78)),_xlpm.act,IF(AND(M78&lt;&gt;"",M78&gt;=_xlpm.sent),M78,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C78="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B78,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B78,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R78&lt;&gt;"",R78,Q78)),_xlpm.act,IF(AND(S78&lt;&gt;"",S78&gt;=_xlpm.sent),S78,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C78="QA",_xlfn.LET(_xlpm.tgt,IF(AM78&lt;&gt;"",AM78,IF(W78&lt;&gt;"",W78,V78)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B78,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y78&lt;&gt;"",Y78&gt;=_xlpm.sent),Y78,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C78="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN78&lt;&gt;"",AN78,IF(AB78&lt;&gt;"",AB78,AA78)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B78,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC78&lt;&gt;"",AC78&gt;=_xlpm.sent),AC78,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C78="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -12066,7 +12085,7 @@
         <v>46325</v>
       </c>
       <c r="I78" s="149" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J78" s="146" t="s">
         <v>44</v>
@@ -12078,7 +12097,7 @@
       <c r="M78" s="151"/>
       <c r="N78" s="151"/>
       <c r="O78" s="151" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P78" s="152" t="s">
         <v>60</v>
@@ -12089,7 +12108,7 @@
       <c r="R78" s="150"/>
       <c r="S78" s="151"/>
       <c r="T78" s="153" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="U78" s="154"/>
       <c r="V78" s="155">
@@ -12105,7 +12124,7 @@
       <c r="AB78" s="150"/>
       <c r="AC78" s="150"/>
       <c r="AD78" s="146" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AE78" s="146" t="s">
         <v>94</v>
@@ -12115,7 +12134,10 @@
       <c r="AH78" s="146"/>
       <c r="AI78" s="146"/>
       <c r="AJ78" s="146"/>
-      <c r="AK78" s="146"/>
+      <c r="AK78" s="146" t="str">
+        <f>IF($B78="","",IF(AND(LEFT($AJ78,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B78)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ78,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B78)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ78="Yes – needs DB Dev to fix",M78&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B78)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ78="Yes – needs PBI Dev to fix",S78&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B78)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ78="Yes – needs QA to fix",Y78&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B78)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B78)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B78)&gt;0,"",IF(AND(V78&lt;&gt;"",K78&lt;&gt;"",V78&lt;K78),"QA target is before DB Dev target",IF(AND(V78&lt;&gt;"",Q78&lt;&gt;"",V78&lt;Q78),"QA target is before PBI Dev target",IF(AND(AA78&lt;&gt;"",V78&lt;&gt;"",AA78&lt;V78),"DPO Approval target is before QA target",IF(AND(AG78&lt;&gt;"",AA78&lt;&gt;"",AG78&lt;AA78),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL78" s="146"/>
       <c r="AM78" s="154" t="str" cm="1">
         <f t="array" ref="AM78">_xlfn.LET(_xlpm.rep,$B78,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -12131,10 +12153,10 @@
         <v>126</v>
       </c>
       <c r="B79" s="31" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C79" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D79" t="str" cm="1">
         <f t="array" aca="1" ref="D79" ca="1">IF(AND(C79="Ready for Release in Prod",LEFT($AJ79,3)&lt;&gt;"Yes"),IF(AG79&lt;&gt;"","Delivered","On track"),IF($B79="","",IF(LEFT($AJ79,3)="Yes","Blocked - "&amp;MID($AJ79,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B79)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B79)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B79)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C79="NOT STARTED",IF(H79="","No plan date set",IF(H79&lt;TODAY(),"Review - planned start passed","On track")),IF(C79="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B79,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B79,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L79&lt;&gt;"",L79,K79)),_xlpm.act,IF(AND(M79&lt;&gt;"",M79&gt;=_xlpm.sent),M79,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C79="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B79,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B79,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R79&lt;&gt;"",R79,Q79)),_xlpm.act,IF(AND(S79&lt;&gt;"",S79&gt;=_xlpm.sent),S79,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C79="QA",_xlfn.LET(_xlpm.tgt,IF(AM79&lt;&gt;"",AM79,IF(W79&lt;&gt;"",W79,V79)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B79,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y79&lt;&gt;"",Y79&gt;=_xlpm.sent),Y79,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C79="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN79&lt;&gt;"",AN79,IF(AB79&lt;&gt;"",AB79,AA79)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B79,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC79&lt;&gt;"",AC79&gt;=_xlpm.sent),AC79,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C79="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -12151,7 +12173,7 @@
         <v>46326</v>
       </c>
       <c r="I79" s="55" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J79" s="53" t="s">
         <v>76</v>
@@ -12166,10 +12188,10 @@
         <v>46266</v>
       </c>
       <c r="N79" s="44" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O79" s="44" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P79" s="74" t="s">
         <v>46</v>
@@ -12180,7 +12202,7 @@
       <c r="R79" s="43"/>
       <c r="S79" s="44"/>
       <c r="T79" s="69" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="U79" s="46"/>
       <c r="V79" s="28">
@@ -12196,7 +12218,7 @@
       <c r="AB79" s="43"/>
       <c r="AC79" s="43"/>
       <c r="AD79" s="31" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AE79" s="31" t="s">
         <v>94</v>
@@ -12206,7 +12228,10 @@
       <c r="AH79" s="31"/>
       <c r="AI79" s="31"/>
       <c r="AJ79" s="31"/>
-      <c r="AK79" s="31"/>
+      <c r="AK79" s="31" t="str">
+        <f>IF($B79="","",IF(AND(LEFT($AJ79,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B79)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ79,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B79)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ79="Yes – needs DB Dev to fix",M79&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B79)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ79="Yes – needs PBI Dev to fix",S79&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B79)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ79="Yes – needs QA to fix",Y79&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B79)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B79)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B79)&gt;0,"",IF(AND(V79&lt;&gt;"",K79&lt;&gt;"",V79&lt;K79),"QA target is before DB Dev target",IF(AND(V79&lt;&gt;"",Q79&lt;&gt;"",V79&lt;Q79),"QA target is before PBI Dev target",IF(AND(AA79&lt;&gt;"",V79&lt;&gt;"",AA79&lt;V79),"DPO Approval target is before QA target",IF(AND(AG79&lt;&gt;"",AA79&lt;&gt;"",AG79&lt;AA79),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL79" s="31"/>
       <c r="AM79" s="32" t="str" cm="1">
         <f t="array" ref="AM79">_xlfn.LET(_xlpm.rep,$B79,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -12222,10 +12247,10 @@
         <v>126</v>
       </c>
       <c r="B80" s="31" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C80" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D80" t="str" cm="1">
         <f t="array" aca="1" ref="D80" ca="1">IF(AND(C80="Ready for Release in Prod",LEFT($AJ80,3)&lt;&gt;"Yes"),IF(AG80&lt;&gt;"","Delivered","On track"),IF($B80="","",IF(LEFT($AJ80,3)="Yes","Blocked - "&amp;MID($AJ80,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B80)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B80)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B80)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C80="NOT STARTED",IF(H80="","No plan date set",IF(H80&lt;TODAY(),"Review - planned start passed","On track")),IF(C80="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B80,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B80,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L80&lt;&gt;"",L80,K80)),_xlpm.act,IF(AND(M80&lt;&gt;"",M80&gt;=_xlpm.sent),M80,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C80="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B80,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B80,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R80&lt;&gt;"",R80,Q80)),_xlpm.act,IF(AND(S80&lt;&gt;"",S80&gt;=_xlpm.sent),S80,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C80="QA",_xlfn.LET(_xlpm.tgt,IF(AM80&lt;&gt;"",AM80,IF(W80&lt;&gt;"",W80,V80)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B80,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y80&lt;&gt;"",Y80&gt;=_xlpm.sent),Y80,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C80="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN80&lt;&gt;"",AN80,IF(AB80&lt;&gt;"",AB80,AA80)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B80,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC80&lt;&gt;"",AC80&gt;=_xlpm.sent),AC80,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C80="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -12242,7 +12267,7 @@
         <v>46325</v>
       </c>
       <c r="I80" s="55" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J80" s="33" t="s">
         <v>103</v>
@@ -12260,7 +12285,7 @@
         <v>45</v>
       </c>
       <c r="O80" s="44" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P80" s="74" t="s">
         <v>60</v>
@@ -12271,7 +12296,7 @@
       <c r="R80" s="43"/>
       <c r="S80" s="44"/>
       <c r="T80" s="69" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="U80" s="46"/>
       <c r="V80" s="28">
@@ -12287,7 +12312,7 @@
       <c r="AB80" s="43"/>
       <c r="AC80" s="43"/>
       <c r="AD80" s="31" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AE80" s="31" t="s">
         <v>94</v>
@@ -12297,7 +12322,10 @@
       <c r="AH80" s="31"/>
       <c r="AI80" s="31"/>
       <c r="AJ80" s="31"/>
-      <c r="AK80" s="31"/>
+      <c r="AK80" s="31" t="str">
+        <f>IF($B80="","",IF(AND(LEFT($AJ80,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B80)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ80,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B80)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ80="Yes – needs DB Dev to fix",M80&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B80)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ80="Yes – needs PBI Dev to fix",S80&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B80)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ80="Yes – needs QA to fix",Y80&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B80)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B80)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B80)&gt;0,"",IF(AND(V80&lt;&gt;"",K80&lt;&gt;"",V80&lt;K80),"QA target is before DB Dev target",IF(AND(V80&lt;&gt;"",Q80&lt;&gt;"",V80&lt;Q80),"QA target is before PBI Dev target",IF(AND(AA80&lt;&gt;"",V80&lt;&gt;"",AA80&lt;V80),"DPO Approval target is before QA target",IF(AND(AG80&lt;&gt;"",AA80&lt;&gt;"",AG80&lt;AA80),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL80" s="31"/>
       <c r="AM80" s="32" t="str" cm="1">
         <f t="array" ref="AM80">_xlfn.LET(_xlpm.rep,$B80,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -12313,10 +12341,10 @@
         <v>126</v>
       </c>
       <c r="B81" s="146" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C81" s="146" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D81" s="147" t="str" cm="1">
         <f t="array" aca="1" ref="D81" ca="1">IF(AND(C81="Ready for Release in Prod",LEFT($AJ81,3)&lt;&gt;"Yes"),IF(AG81&lt;&gt;"","Delivered","On track"),IF($B81="","",IF(LEFT($AJ81,3)="Yes","Blocked - "&amp;MID($AJ81,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B81)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B81)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B81)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C81="NOT STARTED",IF(H81="","No plan date set",IF(H81&lt;TODAY(),"Review - planned start passed","On track")),IF(C81="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B81,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B81,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L81&lt;&gt;"",L81,K81)),_xlpm.act,IF(AND(M81&lt;&gt;"",M81&gt;=_xlpm.sent),M81,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C81="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B81,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B81,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R81&lt;&gt;"",R81,Q81)),_xlpm.act,IF(AND(S81&lt;&gt;"",S81&gt;=_xlpm.sent),S81,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C81="QA",_xlfn.LET(_xlpm.tgt,IF(AM81&lt;&gt;"",AM81,IF(W81&lt;&gt;"",W81,V81)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B81,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y81&lt;&gt;"",Y81&gt;=_xlpm.sent),Y81,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C81="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN81&lt;&gt;"",AN81,IF(AB81&lt;&gt;"",AB81,AA81)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B81,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC81&lt;&gt;"",AC81&gt;=_xlpm.sent),AC81,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C81="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -12333,7 +12361,7 @@
         <v>46325</v>
       </c>
       <c r="I81" s="149" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J81" s="33" t="s">
         <v>103</v>
@@ -12345,7 +12373,7 @@
       <c r="M81" s="151"/>
       <c r="N81" s="151"/>
       <c r="O81" s="151" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P81" s="152" t="s">
         <v>60</v>
@@ -12356,7 +12384,7 @@
       <c r="R81" s="150"/>
       <c r="S81" s="151"/>
       <c r="T81" s="169" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="U81" s="154"/>
       <c r="V81" s="155">
@@ -12372,7 +12400,7 @@
       <c r="AB81" s="150"/>
       <c r="AC81" s="150"/>
       <c r="AD81" s="146" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AE81" s="146" t="s">
         <v>94</v>
@@ -12382,7 +12410,10 @@
       <c r="AH81" s="146"/>
       <c r="AI81" s="146"/>
       <c r="AJ81" s="146"/>
-      <c r="AK81" s="146"/>
+      <c r="AK81" s="146" t="str">
+        <f>IF($B81="","",IF(AND(LEFT($AJ81,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B81)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ81,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B81)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ81="Yes – needs DB Dev to fix",M81&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B81)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ81="Yes – needs PBI Dev to fix",S81&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B81)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ81="Yes – needs QA to fix",Y81&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B81)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B81)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B81)&gt;0,"",IF(AND(V81&lt;&gt;"",K81&lt;&gt;"",V81&lt;K81),"QA target is before DB Dev target",IF(AND(V81&lt;&gt;"",Q81&lt;&gt;"",V81&lt;Q81),"QA target is before PBI Dev target",IF(AND(AA81&lt;&gt;"",V81&lt;&gt;"",AA81&lt;V81),"DPO Approval target is before QA target",IF(AND(AG81&lt;&gt;"",AA81&lt;&gt;"",AG81&lt;AA81),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL81" s="146"/>
       <c r="AM81" s="154" t="str" cm="1">
         <f t="array" ref="AM81">_xlfn.LET(_xlpm.rep,$B81,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -12398,7 +12429,7 @@
         <v>126</v>
       </c>
       <c r="B82" s="31" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C82" s="31" t="s">
         <v>182</v>
@@ -12418,7 +12449,7 @@
         <v>46325</v>
       </c>
       <c r="I82" s="55" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J82" s="53" t="s">
         <v>154</v>
@@ -12434,7 +12465,7 @@
         <v>146</v>
       </c>
       <c r="O82" s="44" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P82" s="74" t="s">
         <v>46</v>
@@ -12445,7 +12476,7 @@
       <c r="R82" s="43"/>
       <c r="S82" s="44"/>
       <c r="T82" s="68" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="U82" s="46"/>
       <c r="V82" s="28">
@@ -12461,7 +12492,7 @@
       <c r="AB82" s="43"/>
       <c r="AC82" s="43"/>
       <c r="AD82" s="31" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AE82" s="31" t="s">
         <v>94</v>
@@ -12471,7 +12502,10 @@
       <c r="AH82" s="31"/>
       <c r="AI82" s="31"/>
       <c r="AJ82" s="31"/>
-      <c r="AK82" s="31"/>
+      <c r="AK82" s="31" t="str">
+        <f>IF($B82="","",IF(AND(LEFT($AJ82,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B82)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ82,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B82)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ82="Yes – needs DB Dev to fix",M82&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B82)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ82="Yes – needs PBI Dev to fix",S82&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B82)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ82="Yes – needs QA to fix",Y82&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B82)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B82)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B82)&gt;0,"",IF(AND(V82&lt;&gt;"",K82&lt;&gt;"",V82&lt;K82),"QA target is before DB Dev target",IF(AND(V82&lt;&gt;"",Q82&lt;&gt;"",V82&lt;Q82),"QA target is before PBI Dev target",IF(AND(AA82&lt;&gt;"",V82&lt;&gt;"",AA82&lt;V82),"DPO Approval target is before QA target",IF(AND(AG82&lt;&gt;"",AA82&lt;&gt;"",AG82&lt;AA82),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL82" s="31"/>
       <c r="AM82" s="32" t="str" cm="1">
         <f t="array" ref="AM82">_xlfn.LET(_xlpm.rep,$B82,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -12487,10 +12521,10 @@
         <v>126</v>
       </c>
       <c r="B83" s="31" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C83" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D83" t="str" cm="1">
         <f t="array" aca="1" ref="D83" ca="1">IF(AND(C83="Ready for Release in Prod",LEFT($AJ83,3)&lt;&gt;"Yes"),IF(AG83&lt;&gt;"","Delivered","On track"),IF($B83="","",IF(LEFT($AJ83,3)="Yes","Blocked - "&amp;MID($AJ83,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B83)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B83)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B83)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C83="NOT STARTED",IF(H83="","No plan date set",IF(H83&lt;TODAY(),"Review - planned start passed","On track")),IF(C83="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B83,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B83,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L83&lt;&gt;"",L83,K83)),_xlpm.act,IF(AND(M83&lt;&gt;"",M83&gt;=_xlpm.sent),M83,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C83="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B83,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B83,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R83&lt;&gt;"",R83,Q83)),_xlpm.act,IF(AND(S83&lt;&gt;"",S83&gt;=_xlpm.sent),S83,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C83="QA",_xlfn.LET(_xlpm.tgt,IF(AM83&lt;&gt;"",AM83,IF(W83&lt;&gt;"",W83,V83)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B83,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y83&lt;&gt;"",Y83&gt;=_xlpm.sent),Y83,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C83="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN83&lt;&gt;"",AN83,IF(AB83&lt;&gt;"",AB83,AA83)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B83,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC83&lt;&gt;"",AC83&gt;=_xlpm.sent),AC83,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C83="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -12507,7 +12541,7 @@
         <v>46325</v>
       </c>
       <c r="I83" s="55" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J83" s="53" t="s">
         <v>76</v>
@@ -12522,10 +12556,10 @@
         <v>46268</v>
       </c>
       <c r="N83" s="44" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O83" s="44" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P83" s="74" t="s">
         <v>77</v>
@@ -12536,7 +12570,7 @@
       <c r="R83" s="43"/>
       <c r="S83" s="44"/>
       <c r="T83" s="68" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="U83" s="46"/>
       <c r="V83" s="28">
@@ -12552,7 +12586,7 @@
       <c r="AB83" s="43"/>
       <c r="AC83" s="43"/>
       <c r="AD83" s="31" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AE83" s="31" t="s">
         <v>94</v>
@@ -12562,7 +12596,10 @@
       <c r="AH83" s="31"/>
       <c r="AI83" s="31"/>
       <c r="AJ83" s="31"/>
-      <c r="AK83" s="31"/>
+      <c r="AK83" s="31" t="str">
+        <f>IF($B83="","",IF(AND(LEFT($AJ83,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B83)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ83,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B83)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ83="Yes – needs DB Dev to fix",M83&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B83)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ83="Yes – needs PBI Dev to fix",S83&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B83)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ83="Yes – needs QA to fix",Y83&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B83)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B83)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B83)&gt;0,"",IF(AND(V83&lt;&gt;"",K83&lt;&gt;"",V83&lt;K83),"QA target is before DB Dev target",IF(AND(V83&lt;&gt;"",Q83&lt;&gt;"",V83&lt;Q83),"QA target is before PBI Dev target",IF(AND(AA83&lt;&gt;"",V83&lt;&gt;"",AA83&lt;V83),"DPO Approval target is before QA target",IF(AND(AG83&lt;&gt;"",AA83&lt;&gt;"",AG83&lt;AA83),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL83" s="31"/>
       <c r="AM83" s="32" t="str" cm="1">
         <f t="array" ref="AM83">_xlfn.LET(_xlpm.rep,$B83,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -12578,7 +12615,7 @@
         <v>126</v>
       </c>
       <c r="B84" s="31" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C84" s="31" t="s">
         <v>182</v>
@@ -12598,7 +12635,7 @@
         <v>46325</v>
       </c>
       <c r="I84" s="55" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J84" s="53" t="s">
         <v>76</v>
@@ -12609,10 +12646,10 @@
       <c r="L84" s="43"/>
       <c r="M84" s="44"/>
       <c r="N84" s="44" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="O84" s="44" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P84" s="74" t="s">
         <v>46</v>
@@ -12623,7 +12660,7 @@
       <c r="R84" s="43"/>
       <c r="S84" s="44"/>
       <c r="T84" s="68" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="U84" s="46"/>
       <c r="V84" s="28">
@@ -12649,7 +12686,10 @@
       <c r="AH84" s="31"/>
       <c r="AI84" s="31"/>
       <c r="AJ84" s="31"/>
-      <c r="AK84" s="31"/>
+      <c r="AK84" s="31" t="str">
+        <f>IF($B84="","",IF(AND(LEFT($AJ84,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B84)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ84,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B84)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ84="Yes – needs DB Dev to fix",M84&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B84)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ84="Yes – needs PBI Dev to fix",S84&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B84)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ84="Yes – needs QA to fix",Y84&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B84)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B84)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B84)&gt;0,"",IF(AND(V84&lt;&gt;"",K84&lt;&gt;"",V84&lt;K84),"QA target is before DB Dev target",IF(AND(V84&lt;&gt;"",Q84&lt;&gt;"",V84&lt;Q84),"QA target is before PBI Dev target",IF(AND(AA84&lt;&gt;"",V84&lt;&gt;"",AA84&lt;V84),"DPO Approval target is before QA target",IF(AND(AG84&lt;&gt;"",AA84&lt;&gt;"",AG84&lt;AA84),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL84" s="31"/>
       <c r="AM84" s="32" t="str" cm="1">
         <f t="array" ref="AM84">_xlfn.LET(_xlpm.rep,$B84,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -12665,17 +12705,17 @@
         <v>126</v>
       </c>
       <c r="B85" s="31" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C85" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D85" t="str" cm="1">
         <f t="array" aca="1" ref="D85" ca="1">IF(AND(C85="Ready for Release in Prod",LEFT($AJ85,3)&lt;&gt;"Yes"),IF(AG85&lt;&gt;"","Delivered","On track"),IF($B85="","",IF(LEFT($AJ85,3)="Yes","Blocked - "&amp;MID($AJ85,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B85)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B85)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B85)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C85="NOT STARTED",IF(H85="","No plan date set",IF(H85&lt;TODAY(),"Review - planned start passed","On track")),IF(C85="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B85,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B85,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L85&lt;&gt;"",L85,K85)),_xlpm.act,IF(AND(M85&lt;&gt;"",M85&gt;=_xlpm.sent),M85,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C85="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B85,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B85,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R85&lt;&gt;"",R85,Q85)),_xlpm.act,IF(AND(S85&lt;&gt;"",S85&gt;=_xlpm.sent),S85,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C85="QA",_xlfn.LET(_xlpm.tgt,IF(AM85&lt;&gt;"",AM85,IF(W85&lt;&gt;"",W85,V85)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B85,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y85&lt;&gt;"",Y85&gt;=_xlpm.sent),Y85,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C85="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN85&lt;&gt;"",AN85,IF(AB85&lt;&gt;"",AB85,AA85)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B85,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC85&lt;&gt;"",AC85&gt;=_xlpm.sent),AC85,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C85="RELEASED IN PROD","Delivered","")))))))))</f>
         <v>On track</v>
       </c>
       <c r="E85" s="31" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F85" s="31" t="s">
         <v>143</v>
@@ -12685,7 +12725,7 @@
         <v>46325</v>
       </c>
       <c r="I85" s="55" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="J85" s="53" t="s">
         <v>44</v>
@@ -12697,7 +12737,7 @@
       <c r="M85" s="44"/>
       <c r="N85" s="44"/>
       <c r="O85" s="44" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P85" s="74" t="s">
         <v>60</v>
@@ -12708,7 +12748,7 @@
       <c r="R85" s="43"/>
       <c r="S85" s="44"/>
       <c r="T85" s="68" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="U85" s="46"/>
       <c r="V85" s="28">
@@ -12724,7 +12764,7 @@
       <c r="AB85" s="43"/>
       <c r="AC85" s="43"/>
       <c r="AD85" s="31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AE85" s="31" t="s">
         <v>94</v>
@@ -12734,7 +12774,10 @@
       <c r="AH85" s="31"/>
       <c r="AI85" s="31"/>
       <c r="AJ85" s="31"/>
-      <c r="AK85" s="31"/>
+      <c r="AK85" s="31" t="str">
+        <f>IF($B85="","",IF(AND(LEFT($AJ85,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B85)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ85,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B85)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ85="Yes – needs DB Dev to fix",M85&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B85)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ85="Yes – needs PBI Dev to fix",S85&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B85)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ85="Yes – needs QA to fix",Y85&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B85)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B85)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B85)&gt;0,"",IF(AND(V85&lt;&gt;"",K85&lt;&gt;"",V85&lt;K85),"QA target is before DB Dev target",IF(AND(V85&lt;&gt;"",Q85&lt;&gt;"",V85&lt;Q85),"QA target is before PBI Dev target",IF(AND(AA85&lt;&gt;"",V85&lt;&gt;"",AA85&lt;V85),"DPO Approval target is before QA target",IF(AND(AG85&lt;&gt;"",AA85&lt;&gt;"",AG85&lt;AA85),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL85" s="31"/>
       <c r="AM85" s="32" t="str" cm="1">
         <f t="array" ref="AM85">_xlfn.LET(_xlpm.rep,$B85,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -12750,10 +12793,10 @@
         <v>126</v>
       </c>
       <c r="B86" s="31" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C86" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D86" t="str" cm="1">
         <f t="array" aca="1" ref="D86" ca="1">IF(AND(C86="Ready for Release in Prod",LEFT($AJ86,3)&lt;&gt;"Yes"),IF(AG86&lt;&gt;"","Delivered","On track"),IF($B86="","",IF(LEFT($AJ86,3)="Yes","Blocked - "&amp;MID($AJ86,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B86)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B86)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B86)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C86="NOT STARTED",IF(H86="","No plan date set",IF(H86&lt;TODAY(),"Review - planned start passed","On track")),IF(C86="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B86,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B86,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L86&lt;&gt;"",L86,K86)),_xlpm.act,IF(AND(M86&lt;&gt;"",M86&gt;=_xlpm.sent),M86,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C86="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B86,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B86,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R86&lt;&gt;"",R86,Q86)),_xlpm.act,IF(AND(S86&lt;&gt;"",S86&gt;=_xlpm.sent),S86,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C86="QA",_xlfn.LET(_xlpm.tgt,IF(AM86&lt;&gt;"",AM86,IF(W86&lt;&gt;"",W86,V86)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B86,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y86&lt;&gt;"",Y86&gt;=_xlpm.sent),Y86,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C86="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN86&lt;&gt;"",AN86,IF(AB86&lt;&gt;"",AB86,AA86)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B86,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC86&lt;&gt;"",AC86&gt;=_xlpm.sent),AC86,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C86="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -12770,7 +12813,7 @@
         <v>46356</v>
       </c>
       <c r="I86" s="55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J86" s="53" t="s">
         <v>84</v>
@@ -12782,7 +12825,7 @@
       <c r="M86" s="44"/>
       <c r="N86" s="44"/>
       <c r="O86" s="44" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P86" s="74"/>
       <c r="Q86" s="49">
@@ -12791,7 +12834,7 @@
       <c r="R86" s="43"/>
       <c r="S86" s="44"/>
       <c r="T86" s="68" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="U86" s="46"/>
       <c r="V86" s="28">
@@ -12807,7 +12850,7 @@
       <c r="AB86" s="43"/>
       <c r="AC86" s="43"/>
       <c r="AD86" s="31" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AE86" s="31" t="s">
         <v>49</v>
@@ -12817,7 +12860,10 @@
       <c r="AH86" s="31"/>
       <c r="AI86" s="31"/>
       <c r="AJ86" s="31"/>
-      <c r="AK86" s="31"/>
+      <c r="AK86" s="31" t="str">
+        <f>IF($B86="","",IF(AND(LEFT($AJ86,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B86)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ86,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B86)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ86="Yes – needs DB Dev to fix",M86&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B86)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ86="Yes – needs PBI Dev to fix",S86&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B86)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ86="Yes – needs QA to fix",Y86&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B86)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B86)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B86)&gt;0,"",IF(AND(V86&lt;&gt;"",K86&lt;&gt;"",V86&lt;K86),"QA target is before DB Dev target",IF(AND(V86&lt;&gt;"",Q86&lt;&gt;"",V86&lt;Q86),"QA target is before PBI Dev target",IF(AND(AA86&lt;&gt;"",V86&lt;&gt;"",AA86&lt;V86),"DPO Approval target is before QA target",IF(AND(AG86&lt;&gt;"",AA86&lt;&gt;"",AG86&lt;AA86),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL86" s="31"/>
       <c r="AM86" s="32" t="str" cm="1">
         <f t="array" ref="AM86">_xlfn.LET(_xlpm.rep,$B86,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -12833,10 +12879,10 @@
         <v>126</v>
       </c>
       <c r="B87" s="31" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C87" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D87" t="str" cm="1">
         <f t="array" aca="1" ref="D87" ca="1">IF(AND(C87="Ready for Release in Prod",LEFT($AJ87,3)&lt;&gt;"Yes"),IF(AG87&lt;&gt;"","Delivered","On track"),IF($B87="","",IF(LEFT($AJ87,3)="Yes","Blocked - "&amp;MID($AJ87,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B87)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B87)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B87)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C87="NOT STARTED",IF(H87="","No plan date set",IF(H87&lt;TODAY(),"Review - planned start passed","On track")),IF(C87="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B87,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B87,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L87&lt;&gt;"",L87,K87)),_xlpm.act,IF(AND(M87&lt;&gt;"",M87&gt;=_xlpm.sent),M87,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C87="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B87,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B87,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R87&lt;&gt;"",R87,Q87)),_xlpm.act,IF(AND(S87&lt;&gt;"",S87&gt;=_xlpm.sent),S87,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C87="QA",_xlfn.LET(_xlpm.tgt,IF(AM87&lt;&gt;"",AM87,IF(W87&lt;&gt;"",W87,V87)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B87,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y87&lt;&gt;"",Y87&gt;=_xlpm.sent),Y87,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C87="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN87&lt;&gt;"",AN87,IF(AB87&lt;&gt;"",AB87,AA87)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B87,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC87&lt;&gt;"",AC87&gt;=_xlpm.sent),AC87,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C87="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -12853,7 +12899,7 @@
         <v>46356</v>
       </c>
       <c r="I87" s="55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J87" s="53" t="s">
         <v>59</v>
@@ -12865,7 +12911,7 @@
       <c r="M87" s="44"/>
       <c r="N87" s="44"/>
       <c r="O87" s="44" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P87" s="74"/>
       <c r="Q87" s="49">
@@ -12874,7 +12920,7 @@
       <c r="R87" s="43"/>
       <c r="S87" s="44"/>
       <c r="T87" s="68" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="U87" s="46"/>
       <c r="V87" s="28">
@@ -12900,7 +12946,10 @@
       <c r="AH87" s="31"/>
       <c r="AI87" s="31"/>
       <c r="AJ87" s="31"/>
-      <c r="AK87" s="31"/>
+      <c r="AK87" s="31" t="str">
+        <f>IF($B87="","",IF(AND(LEFT($AJ87,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B87)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ87,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B87)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ87="Yes – needs DB Dev to fix",M87&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B87)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ87="Yes – needs PBI Dev to fix",S87&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B87)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ87="Yes – needs QA to fix",Y87&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B87)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B87)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B87)&gt;0,"",IF(AND(V87&lt;&gt;"",K87&lt;&gt;"",V87&lt;K87),"QA target is before DB Dev target",IF(AND(V87&lt;&gt;"",Q87&lt;&gt;"",V87&lt;Q87),"QA target is before PBI Dev target",IF(AND(AA87&lt;&gt;"",V87&lt;&gt;"",AA87&lt;V87),"DPO Approval target is before QA target",IF(AND(AG87&lt;&gt;"",AA87&lt;&gt;"",AG87&lt;AA87),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL87" s="31"/>
       <c r="AM87" s="32" t="str" cm="1">
         <f t="array" ref="AM87">_xlfn.LET(_xlpm.rep,$B87,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -12916,10 +12965,10 @@
         <v>126</v>
       </c>
       <c r="B88" s="31" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C88" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D88" t="str" cm="1">
         <f t="array" aca="1" ref="D88" ca="1">IF(AND(C88="Ready for Release in Prod",LEFT($AJ88,3)&lt;&gt;"Yes"),IF(AG88&lt;&gt;"","Delivered","On track"),IF($B88="","",IF(LEFT($AJ88,3)="Yes","Blocked - "&amp;MID($AJ88,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B88)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B88)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B88)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C88="NOT STARTED",IF(H88="","No plan date set",IF(H88&lt;TODAY(),"Review - planned start passed","On track")),IF(C88="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B88,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B88,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L88&lt;&gt;"",L88,K88)),_xlpm.act,IF(AND(M88&lt;&gt;"",M88&gt;=_xlpm.sent),M88,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C88="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B88,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B88,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R88&lt;&gt;"",R88,Q88)),_xlpm.act,IF(AND(S88&lt;&gt;"",S88&gt;=_xlpm.sent),S88,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C88="QA",_xlfn.LET(_xlpm.tgt,IF(AM88&lt;&gt;"",AM88,IF(W88&lt;&gt;"",W88,V88)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B88,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y88&lt;&gt;"",Y88&gt;=_xlpm.sent),Y88,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C88="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN88&lt;&gt;"",AN88,IF(AB88&lt;&gt;"",AB88,AA88)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B88,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC88&lt;&gt;"",AC88&gt;=_xlpm.sent),AC88,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C88="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -12936,7 +12985,7 @@
         <v>46356</v>
       </c>
       <c r="I88" s="55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J88" s="53" t="s">
         <v>59</v>
@@ -12948,7 +12997,7 @@
       <c r="M88" s="44"/>
       <c r="N88" s="44"/>
       <c r="O88" s="44" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P88" s="74"/>
       <c r="Q88" s="49">
@@ -12957,7 +13006,7 @@
       <c r="R88" s="43"/>
       <c r="S88" s="44"/>
       <c r="T88" s="68" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="U88" s="46"/>
       <c r="V88" s="28">
@@ -12983,7 +13032,10 @@
       <c r="AH88" s="31"/>
       <c r="AI88" s="31"/>
       <c r="AJ88" s="31"/>
-      <c r="AK88" s="31"/>
+      <c r="AK88" s="31" t="str">
+        <f>IF($B88="","",IF(AND(LEFT($AJ88,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B88)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ88,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B88)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ88="Yes – needs DB Dev to fix",M88&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B88)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ88="Yes – needs PBI Dev to fix",S88&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B88)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ88="Yes – needs QA to fix",Y88&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B88)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B88)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B88)&gt;0,"",IF(AND(V88&lt;&gt;"",K88&lt;&gt;"",V88&lt;K88),"QA target is before DB Dev target",IF(AND(V88&lt;&gt;"",Q88&lt;&gt;"",V88&lt;Q88),"QA target is before PBI Dev target",IF(AND(AA88&lt;&gt;"",V88&lt;&gt;"",AA88&lt;V88),"DPO Approval target is before QA target",IF(AND(AG88&lt;&gt;"",AA88&lt;&gt;"",AG88&lt;AA88),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL88" s="31"/>
       <c r="AM88" s="32" t="str" cm="1">
         <f t="array" ref="AM88">_xlfn.LET(_xlpm.rep,$B88,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -12999,10 +13051,10 @@
         <v>126</v>
       </c>
       <c r="B89" s="31" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C89" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D89" t="str" cm="1">
         <f t="array" aca="1" ref="D89" ca="1">IF(AND(C89="Ready for Release in Prod",LEFT($AJ89,3)&lt;&gt;"Yes"),IF(AG89&lt;&gt;"","Delivered","On track"),IF($B89="","",IF(LEFT($AJ89,3)="Yes","Blocked - "&amp;MID($AJ89,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B89)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B89)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B89)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C89="NOT STARTED",IF(H89="","No plan date set",IF(H89&lt;TODAY(),"Review - planned start passed","On track")),IF(C89="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B89,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B89,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L89&lt;&gt;"",L89,K89)),_xlpm.act,IF(AND(M89&lt;&gt;"",M89&gt;=_xlpm.sent),M89,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C89="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B89,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B89,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R89&lt;&gt;"",R89,Q89)),_xlpm.act,IF(AND(S89&lt;&gt;"",S89&gt;=_xlpm.sent),S89,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C89="QA",_xlfn.LET(_xlpm.tgt,IF(AM89&lt;&gt;"",AM89,IF(W89&lt;&gt;"",W89,V89)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B89,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y89&lt;&gt;"",Y89&gt;=_xlpm.sent),Y89,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C89="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN89&lt;&gt;"",AN89,IF(AB89&lt;&gt;"",AB89,AA89)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B89,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC89&lt;&gt;"",AC89&gt;=_xlpm.sent),AC89,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C89="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -13019,10 +13071,10 @@
         <v>46356</v>
       </c>
       <c r="I89" s="55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J89" s="53" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K89" s="49">
         <v>46332</v>
@@ -13035,7 +13087,7 @@
       </c>
       <c r="N89" s="44"/>
       <c r="O89" s="44" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P89" s="74"/>
       <c r="Q89" s="49">
@@ -13044,7 +13096,7 @@
       <c r="R89" s="43"/>
       <c r="S89" s="44"/>
       <c r="T89" s="68" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="U89" s="46"/>
       <c r="V89" s="28">
@@ -13070,7 +13122,10 @@
       <c r="AH89" s="31"/>
       <c r="AI89" s="31"/>
       <c r="AJ89" s="31"/>
-      <c r="AK89" s="31"/>
+      <c r="AK89" s="31" t="str">
+        <f>IF($B89="","",IF(AND(LEFT($AJ89,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B89)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ89,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B89)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ89="Yes – needs DB Dev to fix",M89&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B89)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ89="Yes – needs PBI Dev to fix",S89&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B89)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ89="Yes – needs QA to fix",Y89&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B89)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B89)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B89)&gt;0,"",IF(AND(V89&lt;&gt;"",K89&lt;&gt;"",V89&lt;K89),"QA target is before DB Dev target",IF(AND(V89&lt;&gt;"",Q89&lt;&gt;"",V89&lt;Q89),"QA target is before PBI Dev target",IF(AND(AA89&lt;&gt;"",V89&lt;&gt;"",AA89&lt;V89),"DPO Approval target is before QA target",IF(AND(AG89&lt;&gt;"",AA89&lt;&gt;"",AG89&lt;AA89),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL89" s="31"/>
       <c r="AM89" s="32" t="str" cm="1">
         <f t="array" ref="AM89">_xlfn.LET(_xlpm.rep,$B89,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -13086,10 +13141,10 @@
         <v>126</v>
       </c>
       <c r="B90" s="31" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C90" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D90" t="str" cm="1">
         <f t="array" aca="1" ref="D90" ca="1">IF(AND(C90="Ready for Release in Prod",LEFT($AJ90,3)&lt;&gt;"Yes"),IF(AG90&lt;&gt;"","Delivered","On track"),IF($B90="","",IF(LEFT($AJ90,3)="Yes","Blocked - "&amp;MID($AJ90,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B90)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B90)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B90)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C90="NOT STARTED",IF(H90="","No plan date set",IF(H90&lt;TODAY(),"Review - planned start passed","On track")),IF(C90="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B90,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B90,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L90&lt;&gt;"",L90,K90)),_xlpm.act,IF(AND(M90&lt;&gt;"",M90&gt;=_xlpm.sent),M90,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C90="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B90,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B90,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R90&lt;&gt;"",R90,Q90)),_xlpm.act,IF(AND(S90&lt;&gt;"",S90&gt;=_xlpm.sent),S90,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C90="QA",_xlfn.LET(_xlpm.tgt,IF(AM90&lt;&gt;"",AM90,IF(W90&lt;&gt;"",W90,V90)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B90,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y90&lt;&gt;"",Y90&gt;=_xlpm.sent),Y90,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C90="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN90&lt;&gt;"",AN90,IF(AB90&lt;&gt;"",AB90,AA90)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B90,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC90&lt;&gt;"",AC90&gt;=_xlpm.sent),AC90,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C90="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -13106,7 +13161,7 @@
         <v>46356</v>
       </c>
       <c r="I90" s="55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J90" s="53"/>
       <c r="K90" s="49">
@@ -13116,7 +13171,7 @@
       <c r="M90" s="44"/>
       <c r="N90" s="44"/>
       <c r="O90" s="36" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P90" s="74"/>
       <c r="Q90" s="49">
@@ -13125,7 +13180,7 @@
       <c r="R90" s="43"/>
       <c r="S90" s="44"/>
       <c r="T90" s="68" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="U90" s="46"/>
       <c r="V90" s="28">
@@ -13151,7 +13206,10 @@
       <c r="AH90" s="31"/>
       <c r="AI90" s="31"/>
       <c r="AJ90" s="31"/>
-      <c r="AK90" s="31"/>
+      <c r="AK90" s="31" t="str">
+        <f>IF($B90="","",IF(AND(LEFT($AJ90,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B90)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ90,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B90)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ90="Yes – needs DB Dev to fix",M90&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B90)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ90="Yes – needs PBI Dev to fix",S90&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B90)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ90="Yes – needs QA to fix",Y90&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B90)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B90)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B90)&gt;0,"",IF(AND(V90&lt;&gt;"",K90&lt;&gt;"",V90&lt;K90),"QA target is before DB Dev target",IF(AND(V90&lt;&gt;"",Q90&lt;&gt;"",V90&lt;Q90),"QA target is before PBI Dev target",IF(AND(AA90&lt;&gt;"",V90&lt;&gt;"",AA90&lt;V90),"DPO Approval target is before QA target",IF(AND(AG90&lt;&gt;"",AA90&lt;&gt;"",AG90&lt;AA90),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL90" s="31"/>
       <c r="AM90" s="32" t="str" cm="1">
         <f t="array" ref="AM90">_xlfn.LET(_xlpm.rep,$B90,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -13167,10 +13225,10 @@
         <v>126</v>
       </c>
       <c r="B91" s="31" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C91" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D91" t="str" cm="1">
         <f t="array" aca="1" ref="D91" ca="1">IF(AND(C91="Ready for Release in Prod",LEFT($AJ91,3)&lt;&gt;"Yes"),IF(AG91&lt;&gt;"","Delivered","On track"),IF($B91="","",IF(LEFT($AJ91,3)="Yes","Blocked - "&amp;MID($AJ91,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B91)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B91)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B91)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C91="NOT STARTED",IF(H91="","No plan date set",IF(H91&lt;TODAY(),"Review - planned start passed","On track")),IF(C91="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B91,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B91,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L91&lt;&gt;"",L91,K91)),_xlpm.act,IF(AND(M91&lt;&gt;"",M91&gt;=_xlpm.sent),M91,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C91="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B91,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B91,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R91&lt;&gt;"",R91,Q91)),_xlpm.act,IF(AND(S91&lt;&gt;"",S91&gt;=_xlpm.sent),S91,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C91="QA",_xlfn.LET(_xlpm.tgt,IF(AM91&lt;&gt;"",AM91,IF(W91&lt;&gt;"",W91,V91)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B91,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y91&lt;&gt;"",Y91&gt;=_xlpm.sent),Y91,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C91="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN91&lt;&gt;"",AN91,IF(AB91&lt;&gt;"",AB91,AA91)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B91,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC91&lt;&gt;"",AC91&gt;=_xlpm.sent),AC91,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C91="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -13187,7 +13245,7 @@
         <v>46356</v>
       </c>
       <c r="I91" s="55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J91" s="53" t="s">
         <v>65</v>
@@ -13205,7 +13263,7 @@
         <v>146</v>
       </c>
       <c r="O91" s="44" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P91" s="74"/>
       <c r="Q91" s="49">
@@ -13214,7 +13272,7 @@
       <c r="R91" s="43"/>
       <c r="S91" s="44"/>
       <c r="T91" s="68" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="U91" s="46"/>
       <c r="V91" s="28">
@@ -13230,7 +13288,7 @@
       <c r="AB91" s="43"/>
       <c r="AC91" s="43"/>
       <c r="AD91" s="31" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AE91" s="31" t="s">
         <v>72</v>
@@ -13240,9 +13298,12 @@
       <c r="AH91" s="31"/>
       <c r="AI91" s="31"/>
       <c r="AJ91" s="31"/>
-      <c r="AK91" s="31"/>
+      <c r="AK91" s="31" t="str">
+        <f>IF($B91="","",IF(AND(LEFT($AJ91,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B91)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ91,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B91)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ91="Yes – needs DB Dev to fix",M91&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B91)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ91="Yes – needs PBI Dev to fix",S91&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B91)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ91="Yes – needs QA to fix",Y91&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B91)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B91)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B91)&gt;0,"",IF(AND(V91&lt;&gt;"",K91&lt;&gt;"",V91&lt;K91),"QA target is before DB Dev target",IF(AND(V91&lt;&gt;"",Q91&lt;&gt;"",V91&lt;Q91),"QA target is before PBI Dev target",IF(AND(AA91&lt;&gt;"",V91&lt;&gt;"",AA91&lt;V91),"DPO Approval target is before QA target",IF(AND(AG91&lt;&gt;"",AA91&lt;&gt;"",AG91&lt;AA91),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL91" s="31" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="AM91" s="32" t="str" cm="1">
         <f t="array" ref="AM91">_xlfn.LET(_xlpm.rep,$B91,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -13258,10 +13319,10 @@
         <v>126</v>
       </c>
       <c r="B92" s="31" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C92" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D92" t="str" cm="1">
         <f t="array" aca="1" ref="D92" ca="1">IF(AND(C92="Ready for Release in Prod",LEFT($AJ92,3)&lt;&gt;"Yes"),IF(AG92&lt;&gt;"","Delivered","On track"),IF($B92="","",IF(LEFT($AJ92,3)="Yes","Blocked - "&amp;MID($AJ92,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B92)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B92)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B92)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C92="NOT STARTED",IF(H92="","No plan date set",IF(H92&lt;TODAY(),"Review - planned start passed","On track")),IF(C92="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B92,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B92,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L92&lt;&gt;"",L92,K92)),_xlpm.act,IF(AND(M92&lt;&gt;"",M92&gt;=_xlpm.sent),M92,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C92="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B92,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B92,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R92&lt;&gt;"",R92,Q92)),_xlpm.act,IF(AND(S92&lt;&gt;"",S92&gt;=_xlpm.sent),S92,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C92="QA",_xlfn.LET(_xlpm.tgt,IF(AM92&lt;&gt;"",AM92,IF(W92&lt;&gt;"",W92,V92)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B92,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y92&lt;&gt;"",Y92&gt;=_xlpm.sent),Y92,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C92="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN92&lt;&gt;"",AN92,IF(AB92&lt;&gt;"",AB92,AA92)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B92,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC92&lt;&gt;"",AC92&gt;=_xlpm.sent),AC92,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C92="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -13278,7 +13339,7 @@
         <v>46356</v>
       </c>
       <c r="I92" s="55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J92" s="53" t="s">
         <v>84</v>
@@ -13294,7 +13355,7 @@
       </c>
       <c r="N92" s="44"/>
       <c r="O92" s="44" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P92" s="74"/>
       <c r="Q92" s="49">
@@ -13303,7 +13364,7 @@
       <c r="R92" s="43"/>
       <c r="S92" s="44"/>
       <c r="T92" s="68" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="U92" s="46"/>
       <c r="V92" s="28">
@@ -13329,9 +13390,12 @@
       <c r="AH92" s="31"/>
       <c r="AI92" s="31"/>
       <c r="AJ92" s="31"/>
-      <c r="AK92" s="31"/>
+      <c r="AK92" s="31" t="str">
+        <f>IF($B92="","",IF(AND(LEFT($AJ92,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B92)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ92,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B92)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ92="Yes – needs DB Dev to fix",M92&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B92)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ92="Yes – needs PBI Dev to fix",S92&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B92)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ92="Yes – needs QA to fix",Y92&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B92)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B92)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B92)&gt;0,"",IF(AND(V92&lt;&gt;"",K92&lt;&gt;"",V92&lt;K92),"QA target is before DB Dev target",IF(AND(V92&lt;&gt;"",Q92&lt;&gt;"",V92&lt;Q92),"QA target is before PBI Dev target",IF(AND(AA92&lt;&gt;"",V92&lt;&gt;"",AA92&lt;V92),"DPO Approval target is before QA target",IF(AND(AG92&lt;&gt;"",AA92&lt;&gt;"",AG92&lt;AA92),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL92" s="31" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AM92" s="32" t="str" cm="1">
         <f t="array" ref="AM92">_xlfn.LET(_xlpm.rep,$B92,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -13347,10 +13411,10 @@
         <v>126</v>
       </c>
       <c r="B93" s="31" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C93" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D93" t="str" cm="1">
         <f t="array" aca="1" ref="D93" ca="1">IF(AND(C93="Ready for Release in Prod",LEFT($AJ93,3)&lt;&gt;"Yes"),IF(AG93&lt;&gt;"","Delivered","On track"),IF($B93="","",IF(LEFT($AJ93,3)="Yes","Blocked - "&amp;MID($AJ93,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B93)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B93)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B93)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C93="NOT STARTED",IF(H93="","No plan date set",IF(H93&lt;TODAY(),"Review - planned start passed","On track")),IF(C93="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B93,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B93,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L93&lt;&gt;"",L93,K93)),_xlpm.act,IF(AND(M93&lt;&gt;"",M93&gt;=_xlpm.sent),M93,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C93="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B93,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B93,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R93&lt;&gt;"",R93,Q93)),_xlpm.act,IF(AND(S93&lt;&gt;"",S93&gt;=_xlpm.sent),S93,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C93="QA",_xlfn.LET(_xlpm.tgt,IF(AM93&lt;&gt;"",AM93,IF(W93&lt;&gt;"",W93,V93)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B93,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y93&lt;&gt;"",Y93&gt;=_xlpm.sent),Y93,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C93="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN93&lt;&gt;"",AN93,IF(AB93&lt;&gt;"",AB93,AA93)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B93,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC93&lt;&gt;"",AC93&gt;=_xlpm.sent),AC93,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C93="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -13367,7 +13431,7 @@
         <v>46356</v>
       </c>
       <c r="I93" s="55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J93" s="53"/>
       <c r="K93" s="49">
@@ -13377,7 +13441,7 @@
       <c r="M93" s="44"/>
       <c r="N93" s="44"/>
       <c r="O93" s="36" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P93" s="74"/>
       <c r="Q93" s="49">
@@ -13386,7 +13450,7 @@
       <c r="R93" s="43"/>
       <c r="S93" s="44"/>
       <c r="T93" s="68" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="U93" s="46"/>
       <c r="V93" s="28">
@@ -13402,7 +13466,7 @@
       <c r="AB93" s="43"/>
       <c r="AC93" s="43"/>
       <c r="AD93" s="31" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AE93" s="31" t="s">
         <v>94</v>
@@ -13412,7 +13476,10 @@
       <c r="AH93" s="31"/>
       <c r="AI93" s="31"/>
       <c r="AJ93" s="31"/>
-      <c r="AK93" s="31"/>
+      <c r="AK93" s="31" t="str">
+        <f>IF($B93="","",IF(AND(LEFT($AJ93,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B93)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ93,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B93)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ93="Yes – needs DB Dev to fix",M93&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B93)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ93="Yes – needs PBI Dev to fix",S93&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B93)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ93="Yes – needs QA to fix",Y93&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B93)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B93)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B93)&gt;0,"",IF(AND(V93&lt;&gt;"",K93&lt;&gt;"",V93&lt;K93),"QA target is before DB Dev target",IF(AND(V93&lt;&gt;"",Q93&lt;&gt;"",V93&lt;Q93),"QA target is before PBI Dev target",IF(AND(AA93&lt;&gt;"",V93&lt;&gt;"",AA93&lt;V93),"DPO Approval target is before QA target",IF(AND(AG93&lt;&gt;"",AA93&lt;&gt;"",AG93&lt;AA93),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL93" s="31"/>
       <c r="AM93" s="32" t="str" cm="1">
         <f t="array" ref="AM93">_xlfn.LET(_xlpm.rep,$B93,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -13428,10 +13495,10 @@
         <v>126</v>
       </c>
       <c r="B94" s="31" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C94" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D94" t="str" cm="1">
         <f t="array" aca="1" ref="D94" ca="1">IF(AND(C94="Ready for Release in Prod",LEFT($AJ94,3)&lt;&gt;"Yes"),IF(AG94&lt;&gt;"","Delivered","On track"),IF($B94="","",IF(LEFT($AJ94,3)="Yes","Blocked - "&amp;MID($AJ94,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B94)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B94)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B94)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C94="NOT STARTED",IF(H94="","No plan date set",IF(H94&lt;TODAY(),"Review - planned start passed","On track")),IF(C94="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B94,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B94,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L94&lt;&gt;"",L94,K94)),_xlpm.act,IF(AND(M94&lt;&gt;"",M94&gt;=_xlpm.sent),M94,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C94="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B94,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B94,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R94&lt;&gt;"",R94,Q94)),_xlpm.act,IF(AND(S94&lt;&gt;"",S94&gt;=_xlpm.sent),S94,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C94="QA",_xlfn.LET(_xlpm.tgt,IF(AM94&lt;&gt;"",AM94,IF(W94&lt;&gt;"",W94,V94)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B94,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y94&lt;&gt;"",Y94&gt;=_xlpm.sent),Y94,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C94="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN94&lt;&gt;"",AN94,IF(AB94&lt;&gt;"",AB94,AA94)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B94,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC94&lt;&gt;"",AC94&gt;=_xlpm.sent),AC94,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C94="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -13448,7 +13515,7 @@
         <v>46356</v>
       </c>
       <c r="I94" s="55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J94" s="53"/>
       <c r="K94" s="49">
@@ -13458,7 +13525,7 @@
       <c r="M94" s="44"/>
       <c r="N94" s="44"/>
       <c r="O94" s="36" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P94" s="74"/>
       <c r="Q94" s="49">
@@ -13467,7 +13534,7 @@
       <c r="R94" s="43"/>
       <c r="S94" s="44"/>
       <c r="T94" s="68" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="U94" s="46"/>
       <c r="V94" s="28">
@@ -13493,7 +13560,10 @@
       <c r="AH94" s="31"/>
       <c r="AI94" s="31"/>
       <c r="AJ94" s="31"/>
-      <c r="AK94" s="31"/>
+      <c r="AK94" s="31" t="str">
+        <f>IF($B94="","",IF(AND(LEFT($AJ94,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B94)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ94,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B94)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ94="Yes – needs DB Dev to fix",M94&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B94)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ94="Yes – needs PBI Dev to fix",S94&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B94)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ94="Yes – needs QA to fix",Y94&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B94)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B94)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B94)&gt;0,"",IF(AND(V94&lt;&gt;"",K94&lt;&gt;"",V94&lt;K94),"QA target is before DB Dev target",IF(AND(V94&lt;&gt;"",Q94&lt;&gt;"",V94&lt;Q94),"QA target is before PBI Dev target",IF(AND(AA94&lt;&gt;"",V94&lt;&gt;"",AA94&lt;V94),"DPO Approval target is before QA target",IF(AND(AG94&lt;&gt;"",AA94&lt;&gt;"",AG94&lt;AA94),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL94" s="31"/>
       <c r="AM94" s="32" t="str" cm="1">
         <f t="array" ref="AM94">_xlfn.LET(_xlpm.rep,$B94,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -13509,10 +13579,10 @@
         <v>126</v>
       </c>
       <c r="B95" s="31" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C95" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D95" t="str" cm="1">
         <f t="array" aca="1" ref="D95" ca="1">IF(AND(C95="Ready for Release in Prod",LEFT($AJ95,3)&lt;&gt;"Yes"),IF(AG95&lt;&gt;"","Delivered","On track"),IF($B95="","",IF(LEFT($AJ95,3)="Yes","Blocked - "&amp;MID($AJ95,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B95)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B95)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B95)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C95="NOT STARTED",IF(H95="","No plan date set",IF(H95&lt;TODAY(),"Review - planned start passed","On track")),IF(C95="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B95,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B95,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L95&lt;&gt;"",L95,K95)),_xlpm.act,IF(AND(M95&lt;&gt;"",M95&gt;=_xlpm.sent),M95,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C95="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B95,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B95,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R95&lt;&gt;"",R95,Q95)),_xlpm.act,IF(AND(S95&lt;&gt;"",S95&gt;=_xlpm.sent),S95,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C95="QA",_xlfn.LET(_xlpm.tgt,IF(AM95&lt;&gt;"",AM95,IF(W95&lt;&gt;"",W95,V95)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B95,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y95&lt;&gt;"",Y95&gt;=_xlpm.sent),Y95,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C95="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN95&lt;&gt;"",AN95,IF(AB95&lt;&gt;"",AB95,AA95)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B95,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC95&lt;&gt;"",AC95&gt;=_xlpm.sent),AC95,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C95="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -13529,7 +13599,7 @@
         <v>46356</v>
       </c>
       <c r="I95" s="55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J95" s="53" t="s">
         <v>76</v>
@@ -13541,7 +13611,7 @@
       <c r="M95" s="44"/>
       <c r="N95" s="44"/>
       <c r="O95" s="36" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P95" s="74"/>
       <c r="Q95" s="49">
@@ -13550,7 +13620,7 @@
       <c r="R95" s="43"/>
       <c r="S95" s="44"/>
       <c r="T95" s="68" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="U95" s="46"/>
       <c r="V95" s="28">
@@ -13566,7 +13636,7 @@
       <c r="AB95" s="43"/>
       <c r="AC95" s="43"/>
       <c r="AD95" s="31" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AE95" s="31" t="s">
         <v>72</v>
@@ -13576,7 +13646,10 @@
       <c r="AH95" s="31"/>
       <c r="AI95" s="31"/>
       <c r="AJ95" s="31"/>
-      <c r="AK95" s="31"/>
+      <c r="AK95" s="31" t="str">
+        <f>IF($B95="","",IF(AND(LEFT($AJ95,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B95)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ95,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B95)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ95="Yes – needs DB Dev to fix",M95&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B95)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ95="Yes – needs PBI Dev to fix",S95&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B95)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ95="Yes – needs QA to fix",Y95&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B95)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B95)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B95)&gt;0,"",IF(AND(V95&lt;&gt;"",K95&lt;&gt;"",V95&lt;K95),"QA target is before DB Dev target",IF(AND(V95&lt;&gt;"",Q95&lt;&gt;"",V95&lt;Q95),"QA target is before PBI Dev target",IF(AND(AA95&lt;&gt;"",V95&lt;&gt;"",AA95&lt;V95),"DPO Approval target is before QA target",IF(AND(AG95&lt;&gt;"",AA95&lt;&gt;"",AG95&lt;AA95),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL95" s="31"/>
       <c r="AM95" s="32" t="str" cm="1">
         <f t="array" ref="AM95">_xlfn.LET(_xlpm.rep,$B95,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -13592,10 +13665,10 @@
         <v>126</v>
       </c>
       <c r="B96" s="31" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C96" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D96" t="str" cm="1">
         <f t="array" aca="1" ref="D96" ca="1">IF(AND(C96="Ready for Release in Prod",LEFT($AJ96,3)&lt;&gt;"Yes"),IF(AG96&lt;&gt;"","Delivered","On track"),IF($B96="","",IF(LEFT($AJ96,3)="Yes","Blocked - "&amp;MID($AJ96,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B96)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B96)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B96)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C96="NOT STARTED",IF(H96="","No plan date set",IF(H96&lt;TODAY(),"Review - planned start passed","On track")),IF(C96="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B96,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B96,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L96&lt;&gt;"",L96,K96)),_xlpm.act,IF(AND(M96&lt;&gt;"",M96&gt;=_xlpm.sent),M96,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C96="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B96,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B96,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R96&lt;&gt;"",R96,Q96)),_xlpm.act,IF(AND(S96&lt;&gt;"",S96&gt;=_xlpm.sent),S96,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C96="QA",_xlfn.LET(_xlpm.tgt,IF(AM96&lt;&gt;"",AM96,IF(W96&lt;&gt;"",W96,V96)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B96,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y96&lt;&gt;"",Y96&gt;=_xlpm.sent),Y96,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C96="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN96&lt;&gt;"",AN96,IF(AB96&lt;&gt;"",AB96,AA96)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B96,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC96&lt;&gt;"",AC96&gt;=_xlpm.sent),AC96,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C96="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -13612,7 +13685,7 @@
         <v>46356</v>
       </c>
       <c r="I96" s="55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J96" s="53" t="s">
         <v>76</v>
@@ -13624,7 +13697,7 @@
       <c r="M96" s="44"/>
       <c r="N96" s="44"/>
       <c r="O96" s="36" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="P96" s="74"/>
       <c r="Q96" s="49">
@@ -13633,7 +13706,7 @@
       <c r="R96" s="43"/>
       <c r="S96" s="44"/>
       <c r="T96" s="68" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="U96" s="46"/>
       <c r="V96" s="28">
@@ -13649,7 +13722,7 @@
       <c r="AB96" s="43"/>
       <c r="AC96" s="43"/>
       <c r="AD96" s="31" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AE96" s="31" t="s">
         <v>72</v>
@@ -13659,7 +13732,10 @@
       <c r="AH96" s="31"/>
       <c r="AI96" s="31"/>
       <c r="AJ96" s="31"/>
-      <c r="AK96" s="31"/>
+      <c r="AK96" s="31" t="str">
+        <f>IF($B96="","",IF(AND(LEFT($AJ96,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B96)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ96,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B96)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ96="Yes – needs DB Dev to fix",M96&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B96)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ96="Yes – needs PBI Dev to fix",S96&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B96)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ96="Yes – needs QA to fix",Y96&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B96)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B96)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B96)&gt;0,"",IF(AND(V96&lt;&gt;"",K96&lt;&gt;"",V96&lt;K96),"QA target is before DB Dev target",IF(AND(V96&lt;&gt;"",Q96&lt;&gt;"",V96&lt;Q96),"QA target is before PBI Dev target",IF(AND(AA96&lt;&gt;"",V96&lt;&gt;"",AA96&lt;V96),"DPO Approval target is before QA target",IF(AND(AG96&lt;&gt;"",AA96&lt;&gt;"",AG96&lt;AA96),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL96" s="31"/>
       <c r="AM96" s="32" t="str" cm="1">
         <f t="array" ref="AM96">_xlfn.LET(_xlpm.rep,$B96,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -13675,10 +13751,10 @@
         <v>126</v>
       </c>
       <c r="B97" s="31" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C97" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D97" t="str" cm="1">
         <f t="array" aca="1" ref="D97" ca="1">IF(AND(C97="Ready for Release in Prod",LEFT($AJ97,3)&lt;&gt;"Yes"),IF(AG97&lt;&gt;"","Delivered","On track"),IF($B97="","",IF(LEFT($AJ97,3)="Yes","Blocked - "&amp;MID($AJ97,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B97)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B97)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B97)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C97="NOT STARTED",IF(H97="","No plan date set",IF(H97&lt;TODAY(),"Review - planned start passed","On track")),IF(C97="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B97,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B97,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L97&lt;&gt;"",L97,K97)),_xlpm.act,IF(AND(M97&lt;&gt;"",M97&gt;=_xlpm.sent),M97,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C97="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B97,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B97,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R97&lt;&gt;"",R97,Q97)),_xlpm.act,IF(AND(S97&lt;&gt;"",S97&gt;=_xlpm.sent),S97,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C97="QA",_xlfn.LET(_xlpm.tgt,IF(AM97&lt;&gt;"",AM97,IF(W97&lt;&gt;"",W97,V97)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B97,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y97&lt;&gt;"",Y97&gt;=_xlpm.sent),Y97,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C97="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN97&lt;&gt;"",AN97,IF(AB97&lt;&gt;"",AB97,AA97)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B97,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC97&lt;&gt;"",AC97&gt;=_xlpm.sent),AC97,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C97="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -13695,7 +13771,7 @@
         <v>46356</v>
       </c>
       <c r="I97" s="55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J97" s="53"/>
       <c r="K97" s="49">
@@ -13705,7 +13781,7 @@
       <c r="M97" s="44"/>
       <c r="N97" s="44"/>
       <c r="O97" s="36" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P97" s="74"/>
       <c r="Q97" s="49">
@@ -13714,7 +13790,7 @@
       <c r="R97" s="43"/>
       <c r="S97" s="44"/>
       <c r="T97" s="68" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="U97" s="46"/>
       <c r="V97" s="28">
@@ -13730,7 +13806,7 @@
       <c r="AB97" s="43"/>
       <c r="AC97" s="43"/>
       <c r="AD97" s="31" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AE97" s="31" t="s">
         <v>72</v>
@@ -13740,7 +13816,10 @@
       <c r="AH97" s="31"/>
       <c r="AI97" s="31"/>
       <c r="AJ97" s="31"/>
-      <c r="AK97" s="31"/>
+      <c r="AK97" s="31" t="str">
+        <f>IF($B97="","",IF(AND(LEFT($AJ97,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B97)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ97,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B97)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ97="Yes – needs DB Dev to fix",M97&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B97)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ97="Yes – needs PBI Dev to fix",S97&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B97)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ97="Yes – needs QA to fix",Y97&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B97)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B97)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B97)&gt;0,"",IF(AND(V97&lt;&gt;"",K97&lt;&gt;"",V97&lt;K97),"QA target is before DB Dev target",IF(AND(V97&lt;&gt;"",Q97&lt;&gt;"",V97&lt;Q97),"QA target is before PBI Dev target",IF(AND(AA97&lt;&gt;"",V97&lt;&gt;"",AA97&lt;V97),"DPO Approval target is before QA target",IF(AND(AG97&lt;&gt;"",AA97&lt;&gt;"",AG97&lt;AA97),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL97" s="31"/>
       <c r="AM97" s="32" t="str" cm="1">
         <f t="array" ref="AM97">_xlfn.LET(_xlpm.rep,$B97,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -13756,10 +13835,10 @@
         <v>126</v>
       </c>
       <c r="B98" s="31" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C98" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D98" t="str" cm="1">
         <f t="array" aca="1" ref="D98" ca="1">IF(AND(C98="Ready for Release in Prod",LEFT($AJ98,3)&lt;&gt;"Yes"),IF(AG98&lt;&gt;"","Delivered","On track"),IF($B98="","",IF(LEFT($AJ98,3)="Yes","Blocked - "&amp;MID($AJ98,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B98)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B98)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B98)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C98="NOT STARTED",IF(H98="","No plan date set",IF(H98&lt;TODAY(),"Review - planned start passed","On track")),IF(C98="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B98,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B98,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L98&lt;&gt;"",L98,K98)),_xlpm.act,IF(AND(M98&lt;&gt;"",M98&gt;=_xlpm.sent),M98,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C98="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B98,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B98,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R98&lt;&gt;"",R98,Q98)),_xlpm.act,IF(AND(S98&lt;&gt;"",S98&gt;=_xlpm.sent),S98,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C98="QA",_xlfn.LET(_xlpm.tgt,IF(AM98&lt;&gt;"",AM98,IF(W98&lt;&gt;"",W98,V98)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B98,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y98&lt;&gt;"",Y98&gt;=_xlpm.sent),Y98,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C98="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN98&lt;&gt;"",AN98,IF(AB98&lt;&gt;"",AB98,AA98)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B98,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC98&lt;&gt;"",AC98&gt;=_xlpm.sent),AC98,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C98="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -13776,7 +13855,7 @@
         <v>46356</v>
       </c>
       <c r="I98" s="55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J98" s="53"/>
       <c r="K98" s="49">
@@ -13786,7 +13865,7 @@
       <c r="M98" s="44"/>
       <c r="N98" s="44"/>
       <c r="O98" s="36" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P98" s="74"/>
       <c r="Q98" s="49">
@@ -13795,7 +13874,7 @@
       <c r="R98" s="43"/>
       <c r="S98" s="44"/>
       <c r="T98" s="68" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="U98" s="46"/>
       <c r="V98" s="28">
@@ -13821,7 +13900,10 @@
       <c r="AH98" s="31"/>
       <c r="AI98" s="31"/>
       <c r="AJ98" s="31"/>
-      <c r="AK98" s="31"/>
+      <c r="AK98" s="31" t="str">
+        <f>IF($B98="","",IF(AND(LEFT($AJ98,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B98)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ98,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B98)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ98="Yes – needs DB Dev to fix",M98&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B98)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ98="Yes – needs PBI Dev to fix",S98&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B98)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ98="Yes – needs QA to fix",Y98&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B98)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B98)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B98)&gt;0,"",IF(AND(V98&lt;&gt;"",K98&lt;&gt;"",V98&lt;K98),"QA target is before DB Dev target",IF(AND(V98&lt;&gt;"",Q98&lt;&gt;"",V98&lt;Q98),"QA target is before PBI Dev target",IF(AND(AA98&lt;&gt;"",V98&lt;&gt;"",AA98&lt;V98),"DPO Approval target is before QA target",IF(AND(AG98&lt;&gt;"",AA98&lt;&gt;"",AG98&lt;AA98),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL98" s="31"/>
       <c r="AM98" s="32" t="str" cm="1">
         <f t="array" ref="AM98">_xlfn.LET(_xlpm.rep,$B98,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -13837,17 +13919,17 @@
         <v>126</v>
       </c>
       <c r="B99" s="31" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C99" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D99" t="str" cm="1">
         <f t="array" aca="1" ref="D99" ca="1">IF(AND(C99="Ready for Release in Prod",LEFT($AJ99,3)&lt;&gt;"Yes"),IF(AG99&lt;&gt;"","Delivered","On track"),IF($B99="","",IF(LEFT($AJ99,3)="Yes","Blocked - "&amp;MID($AJ99,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B99)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B99)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B99)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C99="NOT STARTED",IF(H99="","No plan date set",IF(H99&lt;TODAY(),"Review - planned start passed","On track")),IF(C99="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B99,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B99,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L99&lt;&gt;"",L99,K99)),_xlpm.act,IF(AND(M99&lt;&gt;"",M99&gt;=_xlpm.sent),M99,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C99="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B99,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B99,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R99&lt;&gt;"",R99,Q99)),_xlpm.act,IF(AND(S99&lt;&gt;"",S99&gt;=_xlpm.sent),S99,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C99="QA",_xlfn.LET(_xlpm.tgt,IF(AM99&lt;&gt;"",AM99,IF(W99&lt;&gt;"",W99,V99)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B99,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y99&lt;&gt;"",Y99&gt;=_xlpm.sent),Y99,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C99="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN99&lt;&gt;"",AN99,IF(AB99&lt;&gt;"",AB99,AA99)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B99,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC99&lt;&gt;"",AC99&gt;=_xlpm.sent),AC99,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C99="RELEASED IN PROD","Delivered","")))))))))</f>
         <v>On track</v>
       </c>
       <c r="E99" s="31" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F99" s="31" t="s">
         <v>129</v>
@@ -13857,7 +13939,7 @@
         <v>46356</v>
       </c>
       <c r="I99" s="55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J99" s="53" t="s">
         <v>65</v>
@@ -13869,7 +13951,7 @@
       <c r="M99" s="44"/>
       <c r="N99" s="44"/>
       <c r="O99" s="44" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P99" s="74"/>
       <c r="Q99" s="49">
@@ -13878,7 +13960,7 @@
       <c r="R99" s="43"/>
       <c r="S99" s="44"/>
       <c r="T99" s="68" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="U99" s="46"/>
       <c r="V99" s="28">
@@ -13894,7 +13976,7 @@
       <c r="AB99" s="43"/>
       <c r="AC99" s="43"/>
       <c r="AD99" s="31" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AE99" s="31" t="s">
         <v>94</v>
@@ -13904,7 +13986,10 @@
       <c r="AH99" s="31"/>
       <c r="AI99" s="31"/>
       <c r="AJ99" s="31"/>
-      <c r="AK99" s="31"/>
+      <c r="AK99" s="31" t="str">
+        <f>IF($B99="","",IF(AND(LEFT($AJ99,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B99)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ99,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B99)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ99="Yes – needs DB Dev to fix",M99&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B99)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ99="Yes – needs PBI Dev to fix",S99&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B99)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ99="Yes – needs QA to fix",Y99&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B99)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B99)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B99)&gt;0,"",IF(AND(V99&lt;&gt;"",K99&lt;&gt;"",V99&lt;K99),"QA target is before DB Dev target",IF(AND(V99&lt;&gt;"",Q99&lt;&gt;"",V99&lt;Q99),"QA target is before PBI Dev target",IF(AND(AA99&lt;&gt;"",V99&lt;&gt;"",AA99&lt;V99),"DPO Approval target is before QA target",IF(AND(AG99&lt;&gt;"",AA99&lt;&gt;"",AG99&lt;AA99),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL99" s="31"/>
       <c r="AM99" s="32" t="str" cm="1">
         <f t="array" ref="AM99">_xlfn.LET(_xlpm.rep,$B99,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -13920,10 +14005,10 @@
         <v>126</v>
       </c>
       <c r="B100" s="31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C100" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D100" t="str" cm="1">
         <f t="array" aca="1" ref="D100" ca="1">IF(AND(C100="Ready for Release in Prod",LEFT($AJ100,3)&lt;&gt;"Yes"),IF(AG100&lt;&gt;"","Delivered","On track"),IF($B100="","",IF(LEFT($AJ100,3)="Yes","Blocked - "&amp;MID($AJ100,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B100)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B100)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B100)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C100="NOT STARTED",IF(H100="","No plan date set",IF(H100&lt;TODAY(),"Review - planned start passed","On track")),IF(C100="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B100,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B100,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L100&lt;&gt;"",L100,K100)),_xlpm.act,IF(AND(M100&lt;&gt;"",M100&gt;=_xlpm.sent),M100,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C100="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B100,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B100,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R100&lt;&gt;"",R100,Q100)),_xlpm.act,IF(AND(S100&lt;&gt;"",S100&gt;=_xlpm.sent),S100,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C100="QA",_xlfn.LET(_xlpm.tgt,IF(AM100&lt;&gt;"",AM100,IF(W100&lt;&gt;"",W100,V100)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B100,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y100&lt;&gt;"",Y100&gt;=_xlpm.sent),Y100,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C100="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN100&lt;&gt;"",AN100,IF(AB100&lt;&gt;"",AB100,AA100)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B100,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC100&lt;&gt;"",AC100&gt;=_xlpm.sent),AC100,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C100="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -13940,7 +14025,7 @@
         <v>46356</v>
       </c>
       <c r="I100" s="55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J100" s="53"/>
       <c r="K100" s="49">
@@ -13950,7 +14035,7 @@
       <c r="M100" s="44"/>
       <c r="N100" s="44"/>
       <c r="O100" s="36" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P100" s="74"/>
       <c r="Q100" s="49">
@@ -13959,7 +14044,7 @@
       <c r="R100" s="43"/>
       <c r="S100" s="44"/>
       <c r="T100" s="68" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="U100" s="46"/>
       <c r="V100" s="28">
@@ -13975,7 +14060,7 @@
       <c r="AB100" s="43"/>
       <c r="AC100" s="43"/>
       <c r="AD100" s="31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AE100" s="31" t="s">
         <v>72</v>
@@ -13985,7 +14070,10 @@
       <c r="AH100" s="31"/>
       <c r="AI100" s="31"/>
       <c r="AJ100" s="31"/>
-      <c r="AK100" s="31"/>
+      <c r="AK100" s="31" t="str">
+        <f>IF($B100="","",IF(AND(LEFT($AJ100,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B100)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ100,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B100)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ100="Yes – needs DB Dev to fix",M100&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B100)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ100="Yes – needs PBI Dev to fix",S100&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B100)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ100="Yes – needs QA to fix",Y100&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B100)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B100)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B100)&gt;0,"",IF(AND(V100&lt;&gt;"",K100&lt;&gt;"",V100&lt;K100),"QA target is before DB Dev target",IF(AND(V100&lt;&gt;"",Q100&lt;&gt;"",V100&lt;Q100),"QA target is before PBI Dev target",IF(AND(AA100&lt;&gt;"",V100&lt;&gt;"",AA100&lt;V100),"DPO Approval target is before QA target",IF(AND(AG100&lt;&gt;"",AA100&lt;&gt;"",AG100&lt;AA100),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL100" s="31"/>
       <c r="AM100" s="32" t="str" cm="1">
         <f t="array" ref="AM100">_xlfn.LET(_xlpm.rep,$B100,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -13998,13 +14086,13 @@
     </row>
     <row r="101" spans="1:40" ht="14.45" hidden="1">
       <c r="A101" s="31" t="s">
+        <v>294</v>
+      </c>
+      <c r="B101" s="31" t="s">
         <v>295</v>
       </c>
-      <c r="B101" s="31" t="s">
-        <v>296</v>
-      </c>
       <c r="C101" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D101" t="str" cm="1">
         <f t="array" aca="1" ref="D101" ca="1">IF(AND(C101="Ready for Release in Prod",LEFT($AJ101,3)&lt;&gt;"Yes"),IF(AG101&lt;&gt;"","Delivered","On track"),IF($B101="","",IF(LEFT($AJ101,3)="Yes","Blocked - "&amp;MID($AJ101,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B101)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B101)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B101)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C101="NOT STARTED",IF(H101="","No plan date set",IF(H101&lt;TODAY(),"Review - planned start passed","On track")),IF(C101="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B101,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B101,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L101&lt;&gt;"",L101,K101)),_xlpm.act,IF(AND(M101&lt;&gt;"",M101&gt;=_xlpm.sent),M101,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C101="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B101,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B101,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R101&lt;&gt;"",R101,Q101)),_xlpm.act,IF(AND(S101&lt;&gt;"",S101&gt;=_xlpm.sent),S101,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C101="QA",_xlfn.LET(_xlpm.tgt,IF(AM101&lt;&gt;"",AM101,IF(W101&lt;&gt;"",W101,V101)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B101,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y101&lt;&gt;"",Y101&gt;=_xlpm.sent),Y101,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C101="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN101&lt;&gt;"",AN101,IF(AB101&lt;&gt;"",AB101,AA101)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B101,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC101&lt;&gt;"",AC101&gt;=_xlpm.sent),AC101,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C101="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -14021,7 +14109,7 @@
         <v>46387</v>
       </c>
       <c r="I101" s="55" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J101" s="53"/>
       <c r="K101" s="28">
@@ -14031,7 +14119,7 @@
       <c r="M101" s="31"/>
       <c r="N101" s="31"/>
       <c r="O101" s="36" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P101" s="74"/>
       <c r="Q101" s="28">
@@ -14040,7 +14128,7 @@
       <c r="R101" s="43"/>
       <c r="S101" s="31"/>
       <c r="T101" s="68" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="U101" s="46"/>
       <c r="V101" s="28">
@@ -14056,7 +14144,7 @@
       <c r="AB101" s="43"/>
       <c r="AC101" s="43"/>
       <c r="AD101" s="31" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AE101" s="31" t="s">
         <v>94</v>
@@ -14079,13 +14167,13 @@
     </row>
     <row r="102" spans="1:40" ht="14.45" hidden="1">
       <c r="A102" s="31" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B102" s="31" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C102" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D102" t="str" cm="1">
         <f t="array" aca="1" ref="D102" ca="1">IF(AND(C102="Ready for Release in Prod",LEFT($AJ102,3)&lt;&gt;"Yes"),IF(AG102&lt;&gt;"","Delivered","On track"),IF($B102="","",IF(LEFT($AJ102,3)="Yes","Blocked - "&amp;MID($AJ102,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B102)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B102)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B102)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C102="NOT STARTED",IF(H102="","No plan date set",IF(H102&lt;TODAY(),"Review - planned start passed","On track")),IF(C102="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B102,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B102,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L102&lt;&gt;"",L102,K102)),_xlpm.act,IF(AND(M102&lt;&gt;"",M102&gt;=_xlpm.sent),M102,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C102="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B102,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B102,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R102&lt;&gt;"",R102,Q102)),_xlpm.act,IF(AND(S102&lt;&gt;"",S102&gt;=_xlpm.sent),S102,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C102="QA",_xlfn.LET(_xlpm.tgt,IF(AM102&lt;&gt;"",AM102,IF(W102&lt;&gt;"",W102,V102)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B102,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y102&lt;&gt;"",Y102&gt;=_xlpm.sent),Y102,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C102="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN102&lt;&gt;"",AN102,IF(AB102&lt;&gt;"",AB102,AA102)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B102,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC102&lt;&gt;"",AC102&gt;=_xlpm.sent),AC102,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C102="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -14102,7 +14190,7 @@
         <v>46387</v>
       </c>
       <c r="I102" s="55" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J102" s="53"/>
       <c r="K102" s="28">
@@ -14112,7 +14200,7 @@
       <c r="M102" s="31"/>
       <c r="N102" s="31"/>
       <c r="O102" s="36" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P102" s="74"/>
       <c r="Q102" s="28">
@@ -14121,7 +14209,7 @@
       <c r="R102" s="43"/>
       <c r="S102" s="31"/>
       <c r="T102" s="68" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="U102" s="46"/>
       <c r="V102" s="28">
@@ -14137,7 +14225,7 @@
       <c r="AB102" s="43"/>
       <c r="AC102" s="43"/>
       <c r="AD102" s="31" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AE102" s="31" t="s">
         <v>94</v>
@@ -14160,13 +14248,13 @@
     </row>
     <row r="103" spans="1:40" ht="14.45" hidden="1">
       <c r="A103" s="31" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B103" s="31" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C103" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D103" t="str" cm="1">
         <f t="array" aca="1" ref="D103" ca="1">IF(AND(C103="Ready for Release in Prod",LEFT($AJ103,3)&lt;&gt;"Yes"),IF(AG103&lt;&gt;"","Delivered","On track"),IF($B103="","",IF(LEFT($AJ103,3)="Yes","Blocked - "&amp;MID($AJ103,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B103)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B103)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B103)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C103="NOT STARTED",IF(H103="","No plan date set",IF(H103&lt;TODAY(),"Review - planned start passed","On track")),IF(C103="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B103,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B103,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L103&lt;&gt;"",L103,K103)),_xlpm.act,IF(AND(M103&lt;&gt;"",M103&gt;=_xlpm.sent),M103,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C103="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B103,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B103,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R103&lt;&gt;"",R103,Q103)),_xlpm.act,IF(AND(S103&lt;&gt;"",S103&gt;=_xlpm.sent),S103,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C103="QA",_xlfn.LET(_xlpm.tgt,IF(AM103&lt;&gt;"",AM103,IF(W103&lt;&gt;"",W103,V103)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B103,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y103&lt;&gt;"",Y103&gt;=_xlpm.sent),Y103,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C103="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN103&lt;&gt;"",AN103,IF(AB103&lt;&gt;"",AB103,AA103)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B103,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC103&lt;&gt;"",AC103&gt;=_xlpm.sent),AC103,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C103="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -14183,7 +14271,7 @@
         <v>46387</v>
       </c>
       <c r="I103" s="55" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J103" s="53"/>
       <c r="K103" s="28">
@@ -14193,7 +14281,7 @@
       <c r="M103" s="31"/>
       <c r="N103" s="31"/>
       <c r="O103" s="36" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P103" s="74"/>
       <c r="Q103" s="28">
@@ -14202,7 +14290,7 @@
       <c r="R103" s="43"/>
       <c r="S103" s="31"/>
       <c r="T103" s="68" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="U103" s="46"/>
       <c r="V103" s="28">
@@ -14218,7 +14306,7 @@
       <c r="AB103" s="43"/>
       <c r="AC103" s="43"/>
       <c r="AD103" s="31" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AE103" s="31" t="s">
         <v>94</v>
@@ -14241,13 +14329,13 @@
     </row>
     <row r="104" spans="1:40" ht="14.45" hidden="1">
       <c r="A104" s="31" t="s">
+        <v>304</v>
+      </c>
+      <c r="B104" s="31" t="s">
         <v>305</v>
       </c>
-      <c r="B104" s="31" t="s">
-        <v>306</v>
-      </c>
       <c r="C104" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D104" t="str" cm="1">
         <f t="array" aca="1" ref="D104" ca="1">IF(AND(C104="Ready for Release in Prod",LEFT($AJ104,3)&lt;&gt;"Yes"),IF(AG104&lt;&gt;"","Delivered","On track"),IF($B104="","",IF(LEFT($AJ104,3)="Yes","Blocked - "&amp;MID($AJ104,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B104)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B104)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B104)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C104="NOT STARTED",IF(H104="","No plan date set",IF(H104&lt;TODAY(),"Review - planned start passed","On track")),IF(C104="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B104,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B104,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L104&lt;&gt;"",L104,K104)),_xlpm.act,IF(AND(M104&lt;&gt;"",M104&gt;=_xlpm.sent),M104,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C104="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B104,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B104,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R104&lt;&gt;"",R104,Q104)),_xlpm.act,IF(AND(S104&lt;&gt;"",S104&gt;=_xlpm.sent),S104,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C104="QA",_xlfn.LET(_xlpm.tgt,IF(AM104&lt;&gt;"",AM104,IF(W104&lt;&gt;"",W104,V104)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B104,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y104&lt;&gt;"",Y104&gt;=_xlpm.sent),Y104,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C104="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN104&lt;&gt;"",AN104,IF(AB104&lt;&gt;"",AB104,AA104)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B104,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC104&lt;&gt;"",AC104&gt;=_xlpm.sent),AC104,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C104="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -14264,7 +14352,7 @@
         <v>46387</v>
       </c>
       <c r="I104" s="55" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J104" s="53"/>
       <c r="K104" s="28">
@@ -14274,7 +14362,7 @@
       <c r="M104" s="31"/>
       <c r="N104" s="31"/>
       <c r="O104" s="36" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P104" s="74"/>
       <c r="Q104" s="28">
@@ -14283,7 +14371,7 @@
       <c r="R104" s="43"/>
       <c r="S104" s="31"/>
       <c r="T104" s="68" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="U104" s="46"/>
       <c r="V104" s="28">
@@ -14299,7 +14387,7 @@
       <c r="AB104" s="43"/>
       <c r="AC104" s="43"/>
       <c r="AD104" s="31" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AE104" s="31" t="s">
         <v>49</v>
@@ -14322,13 +14410,13 @@
     </row>
     <row r="105" spans="1:40" ht="14.45" hidden="1">
       <c r="A105" s="31" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B105" s="31" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C105" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D105" t="str" cm="1">
         <f t="array" aca="1" ref="D105" ca="1">IF(AND(C105="Ready for Release in Prod",LEFT($AJ105,3)&lt;&gt;"Yes"),IF(AG105&lt;&gt;"","Delivered","On track"),IF($B105="","",IF(LEFT($AJ105,3)="Yes","Blocked - "&amp;MID($AJ105,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B105)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B105)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B105)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C105="NOT STARTED",IF(H105="","No plan date set",IF(H105&lt;TODAY(),"Review - planned start passed","On track")),IF(C105="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B105,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B105,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L105&lt;&gt;"",L105,K105)),_xlpm.act,IF(AND(M105&lt;&gt;"",M105&gt;=_xlpm.sent),M105,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C105="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B105,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B105,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R105&lt;&gt;"",R105,Q105)),_xlpm.act,IF(AND(S105&lt;&gt;"",S105&gt;=_xlpm.sent),S105,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C105="QA",_xlfn.LET(_xlpm.tgt,IF(AM105&lt;&gt;"",AM105,IF(W105&lt;&gt;"",W105,V105)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B105,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y105&lt;&gt;"",Y105&gt;=_xlpm.sent),Y105,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C105="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN105&lt;&gt;"",AN105,IF(AB105&lt;&gt;"",AB105,AA105)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B105,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC105&lt;&gt;"",AC105&gt;=_xlpm.sent),AC105,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C105="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -14345,7 +14433,7 @@
         <v>46387</v>
       </c>
       <c r="I105" s="55" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J105" s="53"/>
       <c r="K105" s="28">
@@ -14355,7 +14443,7 @@
       <c r="M105" s="31"/>
       <c r="N105" s="31"/>
       <c r="O105" s="36" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P105" s="74"/>
       <c r="Q105" s="28">
@@ -14364,7 +14452,7 @@
       <c r="R105" s="43"/>
       <c r="S105" s="31"/>
       <c r="T105" s="68" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="U105" s="46"/>
       <c r="V105" s="28">
@@ -14380,7 +14468,7 @@
       <c r="AB105" s="43"/>
       <c r="AC105" s="43"/>
       <c r="AD105" s="31" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AE105" s="31" t="s">
         <v>72</v>
@@ -14403,13 +14491,13 @@
     </row>
     <row r="106" spans="1:40" ht="14.45" hidden="1">
       <c r="A106" s="31" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B106" s="31" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C106" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D106" t="str" cm="1">
         <f t="array" aca="1" ref="D106" ca="1">IF(AND(C106="Ready for Release in Prod",LEFT($AJ106,3)&lt;&gt;"Yes"),IF(AG106&lt;&gt;"","Delivered","On track"),IF($B106="","",IF(LEFT($AJ106,3)="Yes","Blocked - "&amp;MID($AJ106,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B106)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B106)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B106)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C106="NOT STARTED",IF(H106="","No plan date set",IF(H106&lt;TODAY(),"Review - planned start passed","On track")),IF(C106="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B106,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B106,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L106&lt;&gt;"",L106,K106)),_xlpm.act,IF(AND(M106&lt;&gt;"",M106&gt;=_xlpm.sent),M106,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C106="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B106,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B106,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R106&lt;&gt;"",R106,Q106)),_xlpm.act,IF(AND(S106&lt;&gt;"",S106&gt;=_xlpm.sent),S106,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C106="QA",_xlfn.LET(_xlpm.tgt,IF(AM106&lt;&gt;"",AM106,IF(W106&lt;&gt;"",W106,V106)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B106,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y106&lt;&gt;"",Y106&gt;=_xlpm.sent),Y106,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C106="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN106&lt;&gt;"",AN106,IF(AB106&lt;&gt;"",AB106,AA106)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B106,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC106&lt;&gt;"",AC106&gt;=_xlpm.sent),AC106,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C106="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -14426,7 +14514,7 @@
         <v>46387</v>
       </c>
       <c r="I106" s="55" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J106" s="53"/>
       <c r="K106" s="28">
@@ -14436,7 +14524,7 @@
       <c r="M106" s="31"/>
       <c r="N106" s="31"/>
       <c r="O106" s="36" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P106" s="74"/>
       <c r="Q106" s="28">
@@ -14445,7 +14533,7 @@
       <c r="R106" s="43"/>
       <c r="S106" s="31"/>
       <c r="T106" s="68" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="U106" s="46"/>
       <c r="V106" s="28">
@@ -14461,7 +14549,7 @@
       <c r="AB106" s="43"/>
       <c r="AC106" s="43"/>
       <c r="AD106" s="31" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AE106" s="31" t="s">
         <v>72</v>
@@ -14484,13 +14572,13 @@
     </row>
     <row r="107" spans="1:40" ht="14.45" hidden="1">
       <c r="A107" s="31" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B107" s="31" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C107" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D107" t="str" cm="1">
         <f t="array" aca="1" ref="D107" ca="1">IF(AND(C107="Ready for Release in Prod",LEFT($AJ107,3)&lt;&gt;"Yes"),IF(AG107&lt;&gt;"","Delivered","On track"),IF($B107="","",IF(LEFT($AJ107,3)="Yes","Blocked - "&amp;MID($AJ107,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B107)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B107)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B107)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C107="NOT STARTED",IF(H107="","No plan date set",IF(H107&lt;TODAY(),"Review - planned start passed","On track")),IF(C107="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B107,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B107,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L107&lt;&gt;"",L107,K107)),_xlpm.act,IF(AND(M107&lt;&gt;"",M107&gt;=_xlpm.sent),M107,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C107="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B107,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B107,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R107&lt;&gt;"",R107,Q107)),_xlpm.act,IF(AND(S107&lt;&gt;"",S107&gt;=_xlpm.sent),S107,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C107="QA",_xlfn.LET(_xlpm.tgt,IF(AM107&lt;&gt;"",AM107,IF(W107&lt;&gt;"",W107,V107)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B107,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y107&lt;&gt;"",Y107&gt;=_xlpm.sent),Y107,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C107="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN107&lt;&gt;"",AN107,IF(AB107&lt;&gt;"",AB107,AA107)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B107,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC107&lt;&gt;"",AC107&gt;=_xlpm.sent),AC107,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C107="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -14507,7 +14595,7 @@
         <v>46387</v>
       </c>
       <c r="I107" s="55" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J107" s="53"/>
       <c r="K107" s="28">
@@ -14517,7 +14605,7 @@
       <c r="M107" s="31"/>
       <c r="N107" s="31"/>
       <c r="O107" s="36" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P107" s="74"/>
       <c r="Q107" s="28">
@@ -14526,7 +14614,7 @@
       <c r="R107" s="43"/>
       <c r="S107" s="31"/>
       <c r="T107" s="68" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="U107" s="46"/>
       <c r="V107" s="28">
@@ -14542,7 +14630,7 @@
       <c r="AB107" s="43"/>
       <c r="AC107" s="43"/>
       <c r="AD107" s="31" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AE107" s="31" t="s">
         <v>72</v>
@@ -14565,13 +14653,13 @@
     </row>
     <row r="108" spans="1:40" ht="14.45" hidden="1">
       <c r="A108" s="31" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B108" s="31" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C108" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D108" t="str" cm="1">
         <f t="array" aca="1" ref="D108" ca="1">IF(AND(C108="Ready for Release in Prod",LEFT($AJ108,3)&lt;&gt;"Yes"),IF(AG108&lt;&gt;"","Delivered","On track"),IF($B108="","",IF(LEFT($AJ108,3)="Yes","Blocked - "&amp;MID($AJ108,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B108)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B108)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B108)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C108="NOT STARTED",IF(H108="","No plan date set",IF(H108&lt;TODAY(),"Review - planned start passed","On track")),IF(C108="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B108,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B108,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L108&lt;&gt;"",L108,K108)),_xlpm.act,IF(AND(M108&lt;&gt;"",M108&gt;=_xlpm.sent),M108,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C108="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B108,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B108,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R108&lt;&gt;"",R108,Q108)),_xlpm.act,IF(AND(S108&lt;&gt;"",S108&gt;=_xlpm.sent),S108,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C108="QA",_xlfn.LET(_xlpm.tgt,IF(AM108&lt;&gt;"",AM108,IF(W108&lt;&gt;"",W108,V108)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B108,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y108&lt;&gt;"",Y108&gt;=_xlpm.sent),Y108,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C108="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN108&lt;&gt;"",AN108,IF(AB108&lt;&gt;"",AB108,AA108)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B108,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC108&lt;&gt;"",AC108&gt;=_xlpm.sent),AC108,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C108="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -14588,7 +14676,7 @@
         <v>46387</v>
       </c>
       <c r="I108" s="55" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J108" s="53"/>
       <c r="K108" s="28">
@@ -14598,7 +14686,7 @@
       <c r="M108" s="31"/>
       <c r="N108" s="31"/>
       <c r="O108" s="36" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P108" s="74"/>
       <c r="Q108" s="28">
@@ -14607,7 +14695,7 @@
       <c r="R108" s="43"/>
       <c r="S108" s="31"/>
       <c r="T108" s="68" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="U108" s="46"/>
       <c r="V108" s="28">
@@ -14623,7 +14711,7 @@
       <c r="AB108" s="43"/>
       <c r="AC108" s="43"/>
       <c r="AD108" s="31" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AE108" s="31" t="s">
         <v>72</v>
@@ -14646,13 +14734,13 @@
     </row>
     <row r="109" spans="1:40" ht="14.45" hidden="1">
       <c r="A109" s="31" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B109" s="31" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C109" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D109" t="str" cm="1">
         <f t="array" aca="1" ref="D109" ca="1">IF(AND(C109="Ready for Release in Prod",LEFT($AJ109,3)&lt;&gt;"Yes"),IF(AG109&lt;&gt;"","Delivered","On track"),IF($B109="","",IF(LEFT($AJ109,3)="Yes","Blocked - "&amp;MID($AJ109,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B109)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B109)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B109)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C109="NOT STARTED",IF(H109="","No plan date set",IF(H109&lt;TODAY(),"Review - planned start passed","On track")),IF(C109="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B109,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B109,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L109&lt;&gt;"",L109,K109)),_xlpm.act,IF(AND(M109&lt;&gt;"",M109&gt;=_xlpm.sent),M109,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C109="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B109,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B109,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R109&lt;&gt;"",R109,Q109)),_xlpm.act,IF(AND(S109&lt;&gt;"",S109&gt;=_xlpm.sent),S109,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C109="QA",_xlfn.LET(_xlpm.tgt,IF(AM109&lt;&gt;"",AM109,IF(W109&lt;&gt;"",W109,V109)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B109,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y109&lt;&gt;"",Y109&gt;=_xlpm.sent),Y109,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C109="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN109&lt;&gt;"",AN109,IF(AB109&lt;&gt;"",AB109,AA109)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B109,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC109&lt;&gt;"",AC109&gt;=_xlpm.sent),AC109,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C109="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -14669,7 +14757,7 @@
         <v>46387</v>
       </c>
       <c r="I109" s="55" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J109" s="53"/>
       <c r="K109" s="28">
@@ -14679,7 +14767,7 @@
       <c r="M109" s="31"/>
       <c r="N109" s="31"/>
       <c r="O109" s="36" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P109" s="74"/>
       <c r="Q109" s="28">
@@ -14688,7 +14776,7 @@
       <c r="R109" s="43"/>
       <c r="S109" s="31"/>
       <c r="T109" s="68" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="U109" s="46"/>
       <c r="V109" s="28">
@@ -14704,7 +14792,7 @@
       <c r="AB109" s="43"/>
       <c r="AC109" s="43"/>
       <c r="AD109" s="31" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AE109" s="31" t="s">
         <v>72</v>
@@ -14727,13 +14815,13 @@
     </row>
     <row r="110" spans="1:40" ht="14.45" hidden="1">
       <c r="A110" s="31" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B110" s="31" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C110" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D110" t="str" cm="1">
         <f t="array" aca="1" ref="D110" ca="1">IF(AND(C110="Ready for Release in Prod",LEFT($AJ110,3)&lt;&gt;"Yes"),IF(AG110&lt;&gt;"","Delivered","On track"),IF($B110="","",IF(LEFT($AJ110,3)="Yes","Blocked - "&amp;MID($AJ110,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B110)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B110)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B110)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C110="NOT STARTED",IF(H110="","No plan date set",IF(H110&lt;TODAY(),"Review - planned start passed","On track")),IF(C110="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B110,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B110,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L110&lt;&gt;"",L110,K110)),_xlpm.act,IF(AND(M110&lt;&gt;"",M110&gt;=_xlpm.sent),M110,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C110="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B110,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B110,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R110&lt;&gt;"",R110,Q110)),_xlpm.act,IF(AND(S110&lt;&gt;"",S110&gt;=_xlpm.sent),S110,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C110="QA",_xlfn.LET(_xlpm.tgt,IF(AM110&lt;&gt;"",AM110,IF(W110&lt;&gt;"",W110,V110)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B110,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y110&lt;&gt;"",Y110&gt;=_xlpm.sent),Y110,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C110="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN110&lt;&gt;"",AN110,IF(AB110&lt;&gt;"",AB110,AA110)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B110,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC110&lt;&gt;"",AC110&gt;=_xlpm.sent),AC110,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C110="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -14750,7 +14838,7 @@
         <v>46387</v>
       </c>
       <c r="I110" s="55" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J110" s="53"/>
       <c r="K110" s="28">
@@ -14760,7 +14848,7 @@
       <c r="M110" s="31"/>
       <c r="N110" s="31"/>
       <c r="O110" s="36" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P110" s="74"/>
       <c r="Q110" s="28">
@@ -14769,7 +14857,7 @@
       <c r="R110" s="43"/>
       <c r="S110" s="31"/>
       <c r="T110" s="68" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="U110" s="46"/>
       <c r="V110" s="28">
@@ -14785,7 +14873,7 @@
       <c r="AB110" s="43"/>
       <c r="AC110" s="43"/>
       <c r="AD110" s="31" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AE110" s="31" t="s">
         <v>72</v>
@@ -14808,13 +14896,13 @@
     </row>
     <row r="111" spans="1:40" ht="14.45" hidden="1">
       <c r="A111" s="31" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B111" s="31" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C111" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D111" t="str" cm="1">
         <f t="array" aca="1" ref="D111" ca="1">IF(AND(C111="Ready for Release in Prod",LEFT($AJ111,3)&lt;&gt;"Yes"),IF(AG111&lt;&gt;"","Delivered","On track"),IF($B111="","",IF(LEFT($AJ111,3)="Yes","Blocked - "&amp;MID($AJ111,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B111)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B111)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B111)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C111="NOT STARTED",IF(H111="","No plan date set",IF(H111&lt;TODAY(),"Review - planned start passed","On track")),IF(C111="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B111,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B111,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L111&lt;&gt;"",L111,K111)),_xlpm.act,IF(AND(M111&lt;&gt;"",M111&gt;=_xlpm.sent),M111,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C111="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B111,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B111,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R111&lt;&gt;"",R111,Q111)),_xlpm.act,IF(AND(S111&lt;&gt;"",S111&gt;=_xlpm.sent),S111,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C111="QA",_xlfn.LET(_xlpm.tgt,IF(AM111&lt;&gt;"",AM111,IF(W111&lt;&gt;"",W111,V111)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B111,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y111&lt;&gt;"",Y111&gt;=_xlpm.sent),Y111,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C111="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN111&lt;&gt;"",AN111,IF(AB111&lt;&gt;"",AB111,AA111)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B111,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC111&lt;&gt;"",AC111&gt;=_xlpm.sent),AC111,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C111="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -14831,7 +14919,7 @@
         <v>46387</v>
       </c>
       <c r="I111" s="55" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J111" s="53"/>
       <c r="K111" s="28">
@@ -14841,7 +14929,7 @@
       <c r="M111" s="31"/>
       <c r="N111" s="31"/>
       <c r="O111" s="36" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P111" s="74"/>
       <c r="Q111" s="28">
@@ -14850,7 +14938,7 @@
       <c r="R111" s="43"/>
       <c r="S111" s="31"/>
       <c r="T111" s="68" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="U111" s="46"/>
       <c r="V111" s="28">
@@ -14866,7 +14954,7 @@
       <c r="AB111" s="43"/>
       <c r="AC111" s="43"/>
       <c r="AD111" s="31" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AE111" s="31" t="s">
         <v>72</v>
@@ -14889,13 +14977,13 @@
     </row>
     <row r="112" spans="1:40" ht="14.45" hidden="1">
       <c r="A112" s="31" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B112" s="31" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C112" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D112" t="str" cm="1">
         <f t="array" aca="1" ref="D112" ca="1">IF(AND(C112="Ready for Release in Prod",LEFT($AJ112,3)&lt;&gt;"Yes"),IF(AG112&lt;&gt;"","Delivered","On track"),IF($B112="","",IF(LEFT($AJ112,3)="Yes","Blocked - "&amp;MID($AJ112,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B112)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B112)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B112)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C112="NOT STARTED",IF(H112="","No plan date set",IF(H112&lt;TODAY(),"Review - planned start passed","On track")),IF(C112="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B112,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B112,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L112&lt;&gt;"",L112,K112)),_xlpm.act,IF(AND(M112&lt;&gt;"",M112&gt;=_xlpm.sent),M112,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C112="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B112,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B112,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R112&lt;&gt;"",R112,Q112)),_xlpm.act,IF(AND(S112&lt;&gt;"",S112&gt;=_xlpm.sent),S112,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C112="QA",_xlfn.LET(_xlpm.tgt,IF(AM112&lt;&gt;"",AM112,IF(W112&lt;&gt;"",W112,V112)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B112,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y112&lt;&gt;"",Y112&gt;=_xlpm.sent),Y112,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C112="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN112&lt;&gt;"",AN112,IF(AB112&lt;&gt;"",AB112,AA112)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B112,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC112&lt;&gt;"",AC112&gt;=_xlpm.sent),AC112,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C112="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -14912,7 +15000,7 @@
         <v>46387</v>
       </c>
       <c r="I112" s="55" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J112" s="53"/>
       <c r="K112" s="28">
@@ -14922,7 +15010,7 @@
       <c r="M112" s="31"/>
       <c r="N112" s="31"/>
       <c r="O112" s="36" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P112" s="74"/>
       <c r="Q112" s="28">
@@ -14931,7 +15019,7 @@
       <c r="R112" s="43"/>
       <c r="S112" s="31"/>
       <c r="T112" s="68" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="U112" s="46"/>
       <c r="V112" s="28">
@@ -14947,7 +15035,7 @@
       <c r="AB112" s="43"/>
       <c r="AC112" s="43"/>
       <c r="AD112" s="31" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AE112" s="31" t="s">
         <v>72</v>
@@ -14970,13 +15058,13 @@
     </row>
     <row r="113" spans="1:40" ht="14.45" hidden="1">
       <c r="A113" s="31" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B113" s="31" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C113" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D113" t="str" cm="1">
         <f t="array" aca="1" ref="D113" ca="1">IF(AND(C113="Ready for Release in Prod",LEFT($AJ113,3)&lt;&gt;"Yes"),IF(AG113&lt;&gt;"","Delivered","On track"),IF($B113="","",IF(LEFT($AJ113,3)="Yes","Blocked - "&amp;MID($AJ113,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B113)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B113)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B113)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C113="NOT STARTED",IF(H113="","No plan date set",IF(H113&lt;TODAY(),"Review - planned start passed","On track")),IF(C113="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B113,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B113,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L113&lt;&gt;"",L113,K113)),_xlpm.act,IF(AND(M113&lt;&gt;"",M113&gt;=_xlpm.sent),M113,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C113="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B113,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B113,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R113&lt;&gt;"",R113,Q113)),_xlpm.act,IF(AND(S113&lt;&gt;"",S113&gt;=_xlpm.sent),S113,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C113="QA",_xlfn.LET(_xlpm.tgt,IF(AM113&lt;&gt;"",AM113,IF(W113&lt;&gt;"",W113,V113)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B113,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y113&lt;&gt;"",Y113&gt;=_xlpm.sent),Y113,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C113="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN113&lt;&gt;"",AN113,IF(AB113&lt;&gt;"",AB113,AA113)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B113,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC113&lt;&gt;"",AC113&gt;=_xlpm.sent),AC113,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C113="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -14993,7 +15081,7 @@
         <v>46387</v>
       </c>
       <c r="I113" s="55" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J113" s="53"/>
       <c r="K113" s="28">
@@ -15003,7 +15091,7 @@
       <c r="M113" s="31"/>
       <c r="N113" s="31"/>
       <c r="O113" s="36" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="P113" s="74"/>
       <c r="Q113" s="28">
@@ -15012,7 +15100,7 @@
       <c r="R113" s="43"/>
       <c r="S113" s="31"/>
       <c r="T113" s="68" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="U113" s="46"/>
       <c r="V113" s="28">
@@ -15028,7 +15116,7 @@
       <c r="AB113" s="43"/>
       <c r="AC113" s="43"/>
       <c r="AD113" s="31" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AE113" s="31" t="s">
         <v>72</v>
@@ -15051,13 +15139,13 @@
     </row>
     <row r="114" spans="1:40" ht="14.45" hidden="1">
       <c r="A114" s="31" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B114" s="31" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C114" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D114" t="str" cm="1">
         <f t="array" aca="1" ref="D114" ca="1">IF(AND(C114="Ready for Release in Prod",LEFT($AJ114,3)&lt;&gt;"Yes"),IF(AG114&lt;&gt;"","Delivered","On track"),IF($B114="","",IF(LEFT($AJ114,3)="Yes","Blocked - "&amp;MID($AJ114,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B114)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B114)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B114)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C114="NOT STARTED",IF(H114="","No plan date set",IF(H114&lt;TODAY(),"Review - planned start passed","On track")),IF(C114="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B114,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B114,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L114&lt;&gt;"",L114,K114)),_xlpm.act,IF(AND(M114&lt;&gt;"",M114&gt;=_xlpm.sent),M114,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C114="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B114,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B114,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R114&lt;&gt;"",R114,Q114)),_xlpm.act,IF(AND(S114&lt;&gt;"",S114&gt;=_xlpm.sent),S114,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C114="QA",_xlfn.LET(_xlpm.tgt,IF(AM114&lt;&gt;"",AM114,IF(W114&lt;&gt;"",W114,V114)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B114,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y114&lt;&gt;"",Y114&gt;=_xlpm.sent),Y114,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C114="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN114&lt;&gt;"",AN114,IF(AB114&lt;&gt;"",AB114,AA114)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B114,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC114&lt;&gt;"",AC114&gt;=_xlpm.sent),AC114,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C114="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -15074,7 +15162,7 @@
         <v>46387</v>
       </c>
       <c r="I114" s="55" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J114" s="53"/>
       <c r="K114" s="28">
@@ -15084,7 +15172,7 @@
       <c r="M114" s="31"/>
       <c r="N114" s="31"/>
       <c r="O114" s="36" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P114" s="74"/>
       <c r="Q114" s="28">
@@ -15093,7 +15181,7 @@
       <c r="R114" s="43"/>
       <c r="S114" s="31"/>
       <c r="T114" s="68" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="U114" s="46"/>
       <c r="V114" s="28">
@@ -15109,7 +15197,7 @@
       <c r="AB114" s="43"/>
       <c r="AC114" s="43"/>
       <c r="AD114" s="31" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AE114" s="31" t="s">
         <v>72</v>
@@ -15132,13 +15220,13 @@
     </row>
     <row r="115" spans="1:40" ht="21" hidden="1" customHeight="1">
       <c r="A115" s="31" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B115" s="31" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C115" s="31" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D115" t="str" cm="1">
         <f t="array" aca="1" ref="D115" ca="1">IF(AND(C115="Ready for Release in Prod",LEFT($AJ115,3)&lt;&gt;"Yes"),IF(AG115&lt;&gt;"","Delivered","On track"),IF($B115="","",IF(LEFT($AJ115,3)="Yes","Blocked - "&amp;MID($AJ115,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B115)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B115)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B115)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C115="NOT STARTED",IF(H115="","No plan date set",IF(H115&lt;TODAY(),"Review - planned start passed","On track")),IF(C115="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B115,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B115,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L115&lt;&gt;"",L115,K115)),_xlpm.act,IF(AND(M115&lt;&gt;"",M115&gt;=_xlpm.sent),M115,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C115="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B115,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B115,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R115&lt;&gt;"",R115,Q115)),_xlpm.act,IF(AND(S115&lt;&gt;"",S115&gt;=_xlpm.sent),S115,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C115="QA",_xlfn.LET(_xlpm.tgt,IF(AM115&lt;&gt;"",AM115,IF(W115&lt;&gt;"",W115,V115)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B115,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y115&lt;&gt;"",Y115&gt;=_xlpm.sent),Y115,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C115="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN115&lt;&gt;"",AN115,IF(AB115&lt;&gt;"",AB115,AA115)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B115,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC115&lt;&gt;"",AC115&gt;=_xlpm.sent),AC115,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C115="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -15155,7 +15243,7 @@
         <v>46387</v>
       </c>
       <c r="I115" s="55" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J115" s="53"/>
       <c r="K115" s="28">
@@ -15165,7 +15253,7 @@
       <c r="M115" s="31"/>
       <c r="N115" s="31"/>
       <c r="O115" s="36" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P115" s="74"/>
       <c r="Q115" s="28">
@@ -15174,7 +15262,7 @@
       <c r="R115" s="43"/>
       <c r="S115" s="31"/>
       <c r="T115" s="68" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="U115" s="46"/>
       <c r="V115" s="28">
@@ -15190,7 +15278,7 @@
       <c r="AB115" s="43"/>
       <c r="AC115" s="43"/>
       <c r="AD115" s="31" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AE115" s="31" t="s">
         <v>72</v>
@@ -26672,7 +26760,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation type="date" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Real date only" error="This column only accepts real dates. Put notes in Comments instead." sqref="W101:Y527 AG2:AG72 AB2:AB72 AC5:AC72 S2:S28 S30:S64 V2:V115 AA2:AA115 AC2:AC3 Q2:R64 Q65 Y2:Y72 H2:H527 Q66:S527 X2:X115 W2:W72 K2:M527" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="date" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Real date only" error="This column only accepts real dates. Put notes in Comments instead." sqref="W101:Y527 AG2:AG72 AB2:AB72 AC5:AC72 S2:S28 S30:S64 V2:V115 AA2:AA115 AC2:AC3 Q2:R64 Q65 Y2:Y72 H2:H527 Q66:S527 K2:M527 W2:W72 X2:X72 X101:X115" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>DATE(2020,1,1)</formula1>
     </dataValidation>
     <dataValidation type="list" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Real date only" error="This column only accepts real dates. Put notes in Comments instead." sqref="AC4" xr:uid="{AB5B7243-367B-48A5-B4E6-E66C038D2D60}">
@@ -26682,7 +26770,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AC116:AC1048576 AE2:AE115" xr:uid="{DA68FF9D-BD58-4B66-BD0E-CEC5E83F324E}">
       <formula1>$T$2:$T$4</formula1>
     </dataValidation>
-    <dataValidation operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Real date only" error="This column only accepts real dates. Put notes in Comments instead." sqref="O1:P1048568" xr:uid="{DAD9BD11-4282-4C05-A84B-0F51450196AD}"/>
+    <dataValidation operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="Real date only" error="This column only accepts real dates. Put notes in Comments instead." sqref="P1:P1048568" xr:uid="{DAD9BD11-4282-4C05-A84B-0F51450196AD}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J1:J1048568" xr:uid="{21F3A93D-2A33-4A7C-9F45-C528B522B74E}">
       <formula1>"Fetwi,Siva,Sreevasha,Siddu,Sree,Rupa,Greeta,Nick,Mejo,Michael"</formula1>
     </dataValidation>
@@ -26701,18 +26789,18 @@
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="9">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="10">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Confirmed Deployed?" prompt="Confirmed live in production? Yes/No." xr:uid="{00000000-0002-0000-0100-000007000000}">
           <x14:formula1>
             <xm:f>'Data Validation'!$E$3:$E$4</xm:f>
           </x14:formula1>
-          <xm:sqref>AF2:AF72 W73:Y100 X116:X527 U116:V527</xm:sqref>
+          <xm:sqref>AF2:AF72 U116:V527 X116:X527</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Blocked?" prompt="Is this report blocked, and if so, does a previous stage need to fix something? Pick from the list. Log details on Rework Log." xr:uid="{00000000-0002-0000-0100-000008000000}">
           <x14:formula1>
             <xm:f>'Data Validation'!$I$3:$I$8</xm:f>
           </x14:formula1>
-          <xm:sqref>AJ2:AJ115 AF73:AF100 X116:X527</xm:sqref>
+          <xm:sqref>AJ2:AJ115 X116:X527</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="QA Tester" prompt="Pick from the list, or type a new name." xr:uid="{00000000-0002-0000-0100-000006000000}">
           <x14:formula1>
@@ -26756,6 +26844,12 @@
           </x14:formula1>
           <xm:sqref>U2:U115</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DE28ABC5-7592-4DD3-8CAA-C21F555A62CA}">
+          <x14:formula1>
+            <xm:f>'Data Validation'!$E$3:$E$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>AF73:AF100</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -26776,17 +26870,17 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1">
       <c r="A1" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="21.95" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B4" s="174"/>
       <c r="C4" s="175"/>
@@ -26807,7 +26901,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="42" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B7" s="172" t="str">
         <f>IF($B$4="","",IFERROR(INDEX('Combined Delivery Data'!$C:$C,MATCH($B$4,'Combined Delivery Data'!$B:$B,0)),""))</f>
@@ -26891,7 +26985,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="42" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B14" s="171" t="str">
         <f>IF($B$4="","",IFERROR(INDEX('Combined Delivery Data'!$K:$K,MATCH($B$4,'Combined Delivery Data'!$B:$B,0)),""))</f>
@@ -26903,7 +26997,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="42" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B15" s="171" t="str">
         <f>IF($B$4="","",IFERROR(INDEX('Combined Delivery Data'!$L:$L,MATCH($B$4,'Combined Delivery Data'!$B:$B,0)),""))</f>
@@ -26915,7 +27009,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="42" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B16" s="171" t="str">
         <f>IF($B$4="","",IFERROR(INDEX('Combined Delivery Data'!$M:$M,MATCH($B$4,'Combined Delivery Data'!$B:$B,0)),""))</f>
@@ -26927,7 +27021,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="42" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B17" s="171" t="str">
         <f>IF($B$4="","",IFERROR(INDEX('Combined Delivery Data'!$O:$O,MATCH($B$4,'Combined Delivery Data'!$B:$B,0)),""))</f>
@@ -26939,7 +27033,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="42" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B18" s="171" t="str">
         <f>IF($B$4="","",IFERROR(INDEX('Combined Delivery Data'!$Q:$Q,MATCH($B$4,'Combined Delivery Data'!$B:$B,0)),""))</f>
@@ -26951,7 +27045,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="42" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B19" s="171" t="str">
         <f>IF($B$4="","",IFERROR(INDEX('Combined Delivery Data'!$R:$R,MATCH($B$4,'Combined Delivery Data'!$B:$B,0)),""))</f>
@@ -26963,7 +27057,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="42" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B20" s="171" t="str">
         <f>IF($B$4="","",IFERROR(INDEX('Combined Delivery Data'!$S:$S,MATCH($B$4,'Combined Delivery Data'!$B:$B,0)),""))</f>
@@ -27035,7 +27129,7 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="42" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B26" s="172" t="str">
         <f>IF($B$4="","",IFERROR(INDEX('Rework Log'!$Q:$Q,MATCH($B$4,'Rework Log'!$P:$P,0)),""))</f>
@@ -27047,7 +27141,7 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="42" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B27" s="172" t="str">
         <f>IF($B$4="","",IFERROR(INDEX('Rework Log'!$R:$R,MATCH($B$4,'Rework Log'!$P:$P,0)),""))</f>
@@ -27059,7 +27153,7 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="42" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B28" s="172" t="str">
         <f>IF($B$4="","",IFERROR(INDEX('Rework Log'!$S:$S,MATCH($B$4,'Rework Log'!$P:$P,0)),""))</f>
@@ -27071,7 +27165,7 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="42" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B29" s="172" t="str">
         <f>IF($B$4="","",IFERROR(INDEX('Rework Log'!$T:$T,MATCH($B$4,'Rework Log'!$P:$P,0)),""))</f>
@@ -27165,7 +27259,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="75.95" hidden="1" customHeight="1">
       <c r="A1" s="173" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B1" s="173"/>
       <c r="C1" s="173"/>
@@ -27180,7 +27274,7 @@
       <c r="L1" s="173"/>
       <c r="M1" s="173"/>
       <c r="P1" s="179" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q1" s="179"/>
       <c r="R1" s="179"/>
@@ -27192,58 +27286,58 @@
         <v>1</v>
       </c>
       <c r="B2" s="17" t="s">
+        <v>345</v>
+      </c>
+      <c r="C2" s="17" t="s">
         <v>346</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="D2" s="17" t="s">
         <v>347</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="E2" s="17" t="s">
         <v>348</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="F2" s="17" t="s">
         <v>349</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="G2" s="17" t="s">
         <v>350</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="H2" s="30" t="s">
         <v>351</v>
       </c>
-      <c r="H2" s="30" t="s">
+      <c r="I2" s="30" t="s">
         <v>352</v>
       </c>
-      <c r="I2" s="30" t="s">
+      <c r="J2" s="30" t="s">
         <v>353</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="K2" s="30" t="s">
         <v>354</v>
       </c>
-      <c r="K2" s="30" t="s">
+      <c r="L2" s="30" t="s">
         <v>355</v>
       </c>
-      <c r="L2" s="30" t="s">
+      <c r="M2" s="21" t="s">
         <v>356</v>
       </c>
-      <c r="M2" s="21" t="s">
+      <c r="N2" s="21" t="s">
         <v>357</v>
-      </c>
-      <c r="N2" s="21" t="s">
-        <v>358</v>
       </c>
       <c r="P2" s="13" t="s">
         <v>1</v>
       </c>
       <c r="Q2" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="R2" s="13" t="s">
         <v>340</v>
       </c>
-      <c r="R2" s="13" t="s">
+      <c r="S2" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="S2" s="13" t="s">
+      <c r="T2" s="13" t="s">
         <v>342</v>
-      </c>
-      <c r="T2" s="13" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -27263,12 +27357,14 @@
         <v>143</v>
       </c>
       <c r="F3" s="33" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G3" s="33" t="s">
         <v>50</v>
       </c>
-      <c r="H3" s="36"/>
+      <c r="H3" s="36" t="s">
+        <v>84</v>
+      </c>
       <c r="I3" s="52"/>
       <c r="J3" s="52">
         <v>46247</v>
@@ -27320,12 +27416,14 @@
         <v>143</v>
       </c>
       <c r="F4" s="31" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G4" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H4" s="32"/>
+      <c r="H4" s="32" t="s">
+        <v>154</v>
+      </c>
       <c r="I4" s="32"/>
       <c r="J4" s="32">
         <v>46247</v>
@@ -27334,7 +27432,7 @@
         <v>60</v>
       </c>
       <c r="L4" s="31" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="M4" s="3" t="str">
         <f t="shared" ref="M4:M65" ca="1" si="4">IF($A4="","",IF($G4="Did not pass re-test","Sent back again",IF(NOT(ISNUMBER($B4)),"Missing sent-back date",IF($J4&lt;&gt;"","Fixed",IF($I4="","UNCLAIMED "&amp;(TODAY()-$B4)&amp;" d",IF(TODAY()&gt;$I4,(TODAY()-$I4)&amp;" d LATE","Open "&amp;(TODAY()-$B4)&amp;" d"))))))</f>
@@ -27381,12 +27479,14 @@
         <v>129</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G5" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="32"/>
+      <c r="H5" s="32" t="s">
+        <v>76</v>
+      </c>
       <c r="I5" s="32"/>
       <c r="J5" s="32">
         <v>46245</v>
@@ -27438,12 +27538,14 @@
         <v>129</v>
       </c>
       <c r="F6" s="31" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G6" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="32"/>
+      <c r="H6" s="32" t="s">
+        <v>103</v>
+      </c>
       <c r="I6" s="32"/>
       <c r="J6" s="32">
         <v>46251</v>
@@ -27495,12 +27597,14 @@
         <v>129</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G7" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H7" s="32"/>
+      <c r="H7" s="32" t="s">
+        <v>65</v>
+      </c>
       <c r="I7" s="32"/>
       <c r="J7" s="32">
         <v>46251</v>
@@ -27552,12 +27656,14 @@
         <v>129</v>
       </c>
       <c r="F8" s="31" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G8" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H8" s="32"/>
+      <c r="H8" s="32" t="s">
+        <v>65</v>
+      </c>
       <c r="I8" s="32"/>
       <c r="J8" s="32">
         <v>46251</v>
@@ -27569,7 +27675,7 @@
         <v>Fixed</v>
       </c>
       <c r="N8" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="P8" t="str">
         <f>'Combined Delivery Data'!B10</f>
@@ -27609,12 +27715,14 @@
         <v>143</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G9" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H9" s="32"/>
+      <c r="H9" s="32" t="s">
+        <v>154</v>
+      </c>
       <c r="I9" s="32"/>
       <c r="J9" s="32">
         <v>46254</v>
@@ -27626,7 +27734,7 @@
         <v>Fixed</v>
       </c>
       <c r="N9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="P9" t="str">
         <f>'Combined Delivery Data'!B11</f>
@@ -27666,12 +27774,14 @@
         <v>143</v>
       </c>
       <c r="F10" s="31" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G10" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H10" s="32"/>
+      <c r="H10" s="32" t="s">
+        <v>84</v>
+      </c>
       <c r="I10" s="32"/>
       <c r="J10" s="32">
         <v>46252</v>
@@ -27683,7 +27793,7 @@
         <v>Fixed</v>
       </c>
       <c r="N10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="P10" t="str">
         <f>'Combined Delivery Data'!B12</f>
@@ -27723,12 +27833,14 @@
         <v>129</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G11" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H11" s="32"/>
+      <c r="H11" s="32" t="s">
+        <v>65</v>
+      </c>
       <c r="I11" s="32"/>
       <c r="J11" s="32">
         <v>46255</v>
@@ -27780,12 +27892,14 @@
         <v>143</v>
       </c>
       <c r="F12" s="31" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G12" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H12" s="32"/>
+      <c r="H12" s="32" t="s">
+        <v>84</v>
+      </c>
       <c r="I12" s="32"/>
       <c r="J12" s="32">
         <v>46255</v>
@@ -27797,7 +27911,7 @@
         <v>Fixed</v>
       </c>
       <c r="N12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P12" t="str">
         <f>'Combined Delivery Data'!B14</f>
@@ -27837,12 +27951,14 @@
         <v>129</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G13" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H13" s="32"/>
+      <c r="H13" s="32" t="s">
+        <v>59</v>
+      </c>
       <c r="I13" s="32"/>
       <c r="J13" s="32">
         <v>46258</v>
@@ -27888,18 +28004,20 @@
         <v>173</v>
       </c>
       <c r="D14" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E14" s="31" t="s">
         <v>143</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G14" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H14" s="32"/>
+      <c r="H14" s="32" t="s">
+        <v>46</v>
+      </c>
       <c r="I14" s="32"/>
       <c r="J14" s="32">
         <v>46258</v>
@@ -27945,18 +28063,20 @@
         <v>173</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E15" s="31" t="s">
         <v>143</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G15" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H15" s="32"/>
+      <c r="H15" s="32" t="s">
+        <v>77</v>
+      </c>
       <c r="I15" s="32"/>
       <c r="J15" s="32">
         <v>46258</v>
@@ -28008,12 +28128,14 @@
         <v>143</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G16" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H16" s="32"/>
+      <c r="H16" s="32" t="s">
+        <v>65</v>
+      </c>
       <c r="I16" s="32"/>
       <c r="J16" s="32">
         <v>46258</v>
@@ -28025,7 +28147,7 @@
         <v>Fixed</v>
       </c>
       <c r="N16" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P16" t="str">
         <f>'Combined Delivery Data'!B10</f>
@@ -28059,18 +28181,20 @@
         <v>173</v>
       </c>
       <c r="D17" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E17" s="31" t="s">
         <v>143</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G17" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H17" s="32"/>
+      <c r="H17" s="32" t="s">
+        <v>46</v>
+      </c>
       <c r="I17" s="32"/>
       <c r="J17" s="32"/>
       <c r="K17" s="31"/>
@@ -28095,12 +28219,14 @@
         <v>129</v>
       </c>
       <c r="F18" s="31" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G18" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H18" s="32"/>
+      <c r="H18" s="32" t="s">
+        <v>154</v>
+      </c>
       <c r="I18" s="32"/>
       <c r="J18" s="32">
         <v>46261</v>
@@ -28148,18 +28274,20 @@
         <v>173</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E19" s="31" t="s">
         <v>143</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G19" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H19" s="32"/>
+      <c r="H19" s="32" t="s">
+        <v>46</v>
+      </c>
       <c r="I19" s="32"/>
       <c r="J19" s="32">
         <v>46266</v>
@@ -28171,7 +28299,7 @@
         <v>Fixed</v>
       </c>
       <c r="N19" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="P19" t="str">
         <f>'Combined Delivery Data'!B13</f>
@@ -28196,7 +28324,7 @@
     </row>
     <row r="20" spans="1:20">
       <c r="A20" s="31" t="s">
-        <v>377</v>
+        <v>172</v>
       </c>
       <c r="B20" s="32">
         <v>46265</v>
@@ -28205,18 +28333,20 @@
         <v>173</v>
       </c>
       <c r="D20" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E20" s="31" t="s">
         <v>47</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G20" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H20" s="32"/>
+      <c r="H20" s="32" t="s">
+        <v>77</v>
+      </c>
       <c r="I20" s="32">
         <v>46265</v>
       </c>
@@ -28227,14 +28357,14 @@
         <v>77</v>
       </c>
       <c r="L20" s="31" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="M20" s="3" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>Fixed</v>
       </c>
       <c r="N20" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P20" t="str">
         <f>'Combined Delivery Data'!B14</f>
@@ -28274,12 +28404,14 @@
         <v>47</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="G21" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H21" s="32"/>
+      <c r="H21" s="32" t="s">
+        <v>84</v>
+      </c>
       <c r="I21" s="32">
         <v>46266</v>
       </c>
@@ -28288,7 +28420,7 @@
       </c>
       <c r="K21" s="31"/>
       <c r="L21" s="31" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="M21" s="3" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -28335,12 +28467,14 @@
         <v>129</v>
       </c>
       <c r="F22" s="31" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="G22" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H22" s="32"/>
+      <c r="H22" s="32" t="s">
+        <v>59</v>
+      </c>
       <c r="I22" s="32"/>
       <c r="J22" s="32">
         <v>46266</v>
@@ -28354,7 +28488,7 @@
         <v>Fixed</v>
       </c>
       <c r="N22" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P22" t="str">
         <f>'Combined Delivery Data'!B21</f>
@@ -28388,18 +28522,20 @@
         <v>173</v>
       </c>
       <c r="D23" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E23" s="31" t="s">
         <v>47</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="G23" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H23" s="32"/>
+      <c r="H23" s="32" t="s">
+        <v>46</v>
+      </c>
       <c r="I23" s="32">
         <v>46267</v>
       </c>
@@ -28410,7 +28546,7 @@
         <v>46</v>
       </c>
       <c r="L23" s="31" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="M23" s="3" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -28451,18 +28587,20 @@
         <v>173</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E24" s="31" t="s">
         <v>47</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G24" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H24" s="32"/>
+      <c r="H24" s="32" t="s">
+        <v>46</v>
+      </c>
       <c r="I24" s="170">
         <v>46267</v>
       </c>
@@ -28473,14 +28611,14 @@
         <v>46</v>
       </c>
       <c r="L24" s="31" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="M24" s="3" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>Fixed</v>
       </c>
       <c r="N24" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P24" t="str">
         <f>'Combined Delivery Data'!B23</f>
@@ -28514,18 +28652,20 @@
         <v>173</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E25" s="31" t="s">
         <v>47</v>
       </c>
       <c r="F25" s="76" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="G25" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H25" s="32"/>
+      <c r="H25" s="32" t="s">
+        <v>46</v>
+      </c>
       <c r="I25" s="32">
         <v>46267</v>
       </c>
@@ -28536,14 +28676,14 @@
         <v>46</v>
       </c>
       <c r="L25" s="31" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="M25" s="3" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>Fixed</v>
       </c>
       <c r="N25" s="33" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P25" t="str">
         <f>'Combined Delivery Data'!B24</f>
@@ -28568,7 +28708,7 @@
     </row>
     <row r="26" spans="1:20">
       <c r="A26" s="53" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B26" s="32">
         <v>46267</v>
@@ -28577,18 +28717,20 @@
         <v>173</v>
       </c>
       <c r="D26" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E26" s="31" t="s">
         <v>129</v>
       </c>
       <c r="F26" s="31" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G26" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H26" s="32"/>
+      <c r="H26" s="32" t="s">
+        <v>46</v>
+      </c>
       <c r="I26" s="32"/>
       <c r="J26" s="32"/>
       <c r="K26" s="31"/>
@@ -28638,12 +28780,14 @@
         <v>129</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G27" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H27" s="32"/>
+      <c r="H27" s="32" t="s">
+        <v>154</v>
+      </c>
       <c r="I27" s="32"/>
       <c r="J27" s="32">
         <v>46267</v>
@@ -28657,7 +28801,7 @@
         <v>Fixed</v>
       </c>
       <c r="N27" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P27" t="str">
         <f>'Combined Delivery Data'!B26</f>
@@ -28691,18 +28835,20 @@
         <v>173</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E28" s="31" t="s">
         <v>143</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G28" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H28" s="32"/>
+      <c r="H28" s="32" t="s">
+        <v>77</v>
+      </c>
       <c r="I28" s="32"/>
       <c r="J28" s="32">
         <v>46267</v>
@@ -28711,14 +28857,14 @@
         <v>77</v>
       </c>
       <c r="L28" s="31" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="M28" s="3" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>Fixed</v>
       </c>
       <c r="N28" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P28" t="str">
         <f>'Combined Delivery Data'!B27</f>
@@ -28752,18 +28898,20 @@
         <v>173</v>
       </c>
       <c r="D29" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E29" s="31" t="s">
         <v>129</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G29" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H29" s="32"/>
+      <c r="H29" s="32" t="s">
+        <v>77</v>
+      </c>
       <c r="I29" s="32"/>
       <c r="J29" s="32">
         <v>46267</v>
@@ -28772,7 +28920,7 @@
         <v>77</v>
       </c>
       <c r="L29" s="114" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="M29" s="3" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -28813,18 +28961,20 @@
         <v>173</v>
       </c>
       <c r="D30" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E30" s="31" t="s">
         <v>129</v>
       </c>
       <c r="F30" s="31" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="G30" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H30" s="32"/>
+      <c r="H30" s="32" t="s">
+        <v>77</v>
+      </c>
       <c r="I30" s="32"/>
       <c r="J30" s="32">
         <v>46267</v>
@@ -28833,7 +28983,7 @@
         <v>77</v>
       </c>
       <c r="L30" s="114" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="M30" s="3" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -28880,12 +29030,14 @@
         <v>129</v>
       </c>
       <c r="F31" s="31" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G31" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H31" s="32"/>
+      <c r="H31" s="32" t="s">
+        <v>154</v>
+      </c>
       <c r="I31" s="32"/>
       <c r="J31" s="32">
         <v>46267</v>
@@ -28899,7 +29051,7 @@
         <v>Fixed</v>
       </c>
       <c r="N31" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P31" t="str">
         <f>'Combined Delivery Data'!B30</f>
@@ -28939,12 +29091,14 @@
         <v>47</v>
       </c>
       <c r="F32" s="31" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G32" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H32" s="32"/>
+      <c r="H32" s="32" t="s">
+        <v>103</v>
+      </c>
       <c r="I32" s="32">
         <v>46269</v>
       </c>
@@ -28953,7 +29107,7 @@
       </c>
       <c r="K32" s="31"/>
       <c r="L32" s="31" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="M32" s="3" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -28997,15 +29151,17 @@
         <v>182</v>
       </c>
       <c r="E33" s="31" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F33" s="31" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="G33" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H33" s="32"/>
+      <c r="H33" s="32" t="s">
+        <v>44</v>
+      </c>
       <c r="I33" s="32"/>
       <c r="J33" s="32">
         <v>46268</v>
@@ -29057,12 +29213,14 @@
         <v>47</v>
       </c>
       <c r="F34" s="31" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G34" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H34" s="32"/>
+      <c r="H34" s="32" t="s">
+        <v>103</v>
+      </c>
       <c r="I34" s="32">
         <v>46274</v>
       </c>
@@ -29071,7 +29229,7 @@
       </c>
       <c r="K34" s="31"/>
       <c r="L34" s="31" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="M34" s="3" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -29103,7 +29261,7 @@
     </row>
     <row r="35" spans="1:20" ht="25.5" customHeight="1">
       <c r="A35" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B35" s="32">
         <v>46274</v>
@@ -29112,18 +29270,20 @@
         <v>173</v>
       </c>
       <c r="D35" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E35" s="31" t="s">
         <v>47</v>
       </c>
       <c r="F35" s="76" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G35" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H35" s="32"/>
+      <c r="H35" s="32" t="s">
+        <v>77</v>
+      </c>
       <c r="I35" s="32">
         <v>46275</v>
       </c>
@@ -29134,7 +29294,7 @@
         <v>77</v>
       </c>
       <c r="L35" s="31" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="M35" s="3" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -29181,12 +29341,14 @@
         <v>129</v>
       </c>
       <c r="F36" s="31" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="G36" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H36" s="32"/>
+      <c r="H36" s="32" t="s">
+        <v>154</v>
+      </c>
       <c r="I36" s="32"/>
       <c r="J36" s="32">
         <v>46276</v>
@@ -29200,7 +29362,7 @@
         <v>Fixed</v>
       </c>
       <c r="N36" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P36" t="str">
         <f>'Combined Delivery Data'!B36</f>
@@ -29225,7 +29387,7 @@
     </row>
     <row r="37" spans="1:20">
       <c r="A37" s="33" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B37" s="32">
         <v>46275</v>
@@ -29240,12 +29402,14 @@
         <v>129</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G37" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="H37" s="32"/>
+      <c r="H37" s="32" t="s">
+        <v>65</v>
+      </c>
       <c r="I37" s="32"/>
       <c r="J37" s="32"/>
       <c r="K37" s="31"/>
@@ -29292,12 +29456,14 @@
         <v>129</v>
       </c>
       <c r="F38" s="31" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="G38" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="H38" s="32"/>
+      <c r="H38" s="32" t="s">
+        <v>154</v>
+      </c>
       <c r="I38" s="32"/>
       <c r="J38" s="32"/>
       <c r="K38" s="31"/>
@@ -29307,7 +29473,7 @@
         <v>UNCLAIMED 3 d</v>
       </c>
       <c r="N38" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P38" t="str">
         <f>'Combined Delivery Data'!B38</f>
@@ -29332,7 +29498,7 @@
     </row>
     <row r="39" spans="1:20">
       <c r="A39" s="31" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B39" s="32">
         <v>46279</v>
@@ -29341,18 +29507,20 @@
         <v>173</v>
       </c>
       <c r="D39" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E39" s="31" t="s">
         <v>143</v>
       </c>
       <c r="F39" s="31" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G39" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H39" s="32"/>
+      <c r="H39" s="32" t="s">
+        <v>77</v>
+      </c>
       <c r="I39" s="32">
         <v>46281</v>
       </c>
@@ -29363,7 +29531,7 @@
         <v>77</v>
       </c>
       <c r="L39" s="31" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="M39" s="3" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -29395,7 +29563,7 @@
     </row>
     <row r="40" spans="1:20">
       <c r="A40" s="31" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B40" s="32">
         <v>46280</v>
@@ -29410,12 +29578,14 @@
         <v>47</v>
       </c>
       <c r="F40" s="31" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G40" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="H40" s="32"/>
+      <c r="H40" s="32" t="s">
+        <v>44</v>
+      </c>
       <c r="I40" s="32"/>
       <c r="J40" s="32"/>
       <c r="K40" s="31"/>
@@ -29450,7 +29620,7 @@
     </row>
     <row r="41" spans="1:20">
       <c r="A41" s="31" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B41" s="32">
         <v>46281</v>
@@ -29459,18 +29629,20 @@
         <v>173</v>
       </c>
       <c r="D41" s="31" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E41" s="31" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G41" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H41" s="32"/>
+      <c r="H41" s="32" t="s">
+        <v>46</v>
+      </c>
       <c r="I41" s="32"/>
       <c r="J41" s="32"/>
       <c r="K41" s="31"/>
@@ -29502,7 +29674,7 @@
     </row>
     <row r="42" spans="1:20">
       <c r="A42" s="31" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B42" s="32">
         <v>46282</v>
@@ -29517,12 +29689,14 @@
         <v>47</v>
       </c>
       <c r="F42" s="31" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="G42" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="H42" s="32"/>
+      <c r="H42" s="32" t="s">
+        <v>154</v>
+      </c>
       <c r="I42" s="32"/>
       <c r="J42" s="32"/>
       <c r="K42" s="31"/>
@@ -29663,19 +29837,19 @@
       </c>
       <c r="Q45">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="S45" s="28" t="str">
+      <c r="S45" s="28">
         <f t="shared" si="7"/>
-        <v/>
+        <v>46265</v>
       </c>
       <c r="T45" t="str">
         <f t="shared" si="8"/>
-        <v/>
+        <v>QA -&gt; PBI Dev</v>
       </c>
     </row>
     <row r="46" spans="1:20">
@@ -47604,8 +47778,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Fixed By" prompt="Pick the To Stage first - list shows that stage's people." sqref="K3:K498" xr:uid="{00000000-0002-0000-0300-000005000000}">
       <formula1>INDIRECT(SUBSTITUTE($D3," ","_")&amp;"_List")</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Real date only" error="This column only accepts real dates." promptTitle="First Completed On" prompt="Fixer, at pickup: CUT your old completion date from the main tab, PASTE it here." sqref="H3:H498" xr:uid="{00000000-0002-0000-0300-000007000000}">
-      <formula1>DATE(2020,1,1)</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H498" xr:uid="{DAF77D53-E6E7-426A-A654-9ADBF3CB2CB1}">
+      <formula1>INDIRECT(SUBSTITUTE($D3," ","_")&amp;"_List")</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -47619,12 +47793,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Report Name" prompt="Pick the report. Ctrl+; enters today in date cells." xr:uid="{00000000-0002-0000-0300-000000000000}">
-          <x14:formula1>
-            <xm:f>'Combined Delivery Data'!$B$2:$B$527</xm:f>
-          </x14:formula1>
-          <xm:sqref>A3:A4 A9:A10 A19:A21 A14:A17 A12 A23:A25 A28:A30 A32:A35 A39:A498</xm:sqref>
-        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="From Stage" prompt="Which stage found the problem?" xr:uid="{00000000-0002-0000-0300-000001000000}">
           <x14:formula1>
             <xm:f>'Data Validation'!$J$3:$J$6</xm:f>
@@ -47649,6 +47817,12 @@
           </x14:formula1>
           <xm:sqref>G3:G498</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{43BE092B-93A8-43E9-B519-EB5F441FF52C}">
+          <x14:formula1>
+            <xm:f>'Combined Delivery Data'!$B$29:$B$100</xm:f>
+          </x14:formula1>
+          <xm:sqref>A3:A498</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -47672,7 +47846,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" hidden="1" customHeight="1">
       <c r="A1" s="180" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B1" s="175"/>
       <c r="C1" s="175"/>
@@ -47682,22 +47856,22 @@
         <v>0</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="E2" t="s">
         <v>404</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="F2" t="s">
         <v>405</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>406</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>407</v>
-      </c>
-      <c r="G2" t="s">
-        <v>408</v>
-      </c>
-      <c r="H2" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="14.25" customHeight="1">
@@ -47711,7 +47885,7 @@
         <v>46142</v>
       </c>
       <c r="E3" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F3" s="28">
         <v>46233</v>
@@ -47731,7 +47905,7 @@
         <v>46172</v>
       </c>
       <c r="E4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="F4" s="28">
         <v>46264</v>
@@ -47751,7 +47925,7 @@
         <v>46203</v>
       </c>
       <c r="E5" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F5" s="28">
         <v>46295</v>
@@ -47771,7 +47945,7 @@
         <v>46233</v>
       </c>
       <c r="E6" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F6" s="28">
         <v>46325</v>
@@ -47791,7 +47965,7 @@
         <v>46264</v>
       </c>
       <c r="E7" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="F7" s="28">
         <v>46356</v>
@@ -47811,7 +47985,7 @@
         <v>46295</v>
       </c>
       <c r="E8" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F8" s="28">
         <v>46387</v>
@@ -47831,7 +48005,7 @@
         <v>46325</v>
       </c>
       <c r="E9" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F9" s="28">
         <v>46417</v>
@@ -47851,7 +48025,7 @@
         <v>46356</v>
       </c>
       <c r="E10" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F10" s="28">
         <v>46446</v>
@@ -47862,7 +48036,7 @@
     </row>
     <row r="11" spans="1:8" ht="14.25" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B11" s="11">
         <v>18</v>
@@ -47871,7 +48045,7 @@
         <v>46417</v>
       </c>
       <c r="E11" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F11" s="28">
         <v>46477</v>
@@ -47882,7 +48056,7 @@
     </row>
     <row r="12" spans="1:8" ht="14.25" customHeight="1">
       <c r="A12" s="11" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B12" s="11">
         <v>18</v>
@@ -47893,7 +48067,7 @@
     </row>
     <row r="13" spans="1:8" ht="14.25" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B13" s="11">
         <v>19</v>
@@ -47904,7 +48078,7 @@
     </row>
     <row r="14" spans="1:8" ht="14.25" customHeight="1">
       <c r="A14" s="11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B14" s="11">
         <v>9</v>
@@ -47915,7 +48089,7 @@
     </row>
     <row r="15" spans="1:8" ht="14.25" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B15" s="11">
         <v>8</v>
@@ -47960,7 +48134,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.25" customHeight="1">
       <c r="A1" s="181" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B1" s="175"/>
       <c r="C1" s="175"/>
@@ -47977,16 +48151,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>6</v>
@@ -47995,13 +48169,13 @@
         <v>5</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="14.25" customHeight="1">
@@ -48035,7 +48209,7 @@
         <v>40</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
@@ -48163,7 +48337,7 @@
         <v>40</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>55</v>
@@ -48268,10 +48442,10 @@
         <v>182</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>46</v>
@@ -48291,13 +48465,13 @@
         <v>40</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>46</v>
@@ -48322,10 +48496,10 @@
         <v>173</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>46</v>
@@ -48350,10 +48524,10 @@
         <v>164</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>46</v>
@@ -48374,10 +48548,10 @@
         <v>42</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>46</v>
@@ -48419,7 +48593,7 @@
         <v>40</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>58</v>
@@ -48527,7 +48701,7 @@
         <v>64</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>46</v>
@@ -48547,13 +48721,13 @@
         <v>40</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>64</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>46</v>
@@ -48581,7 +48755,7 @@
         <v>64</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>46</v>
@@ -48609,7 +48783,7 @@
         <v>64</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>46</v>
@@ -48633,7 +48807,7 @@
         <v>64</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>46</v>
@@ -48675,7 +48849,7 @@
         <v>40</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>69</v>
@@ -48783,7 +48957,7 @@
         <v>70</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>60</v>
@@ -48803,13 +48977,13 @@
         <v>40</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>70</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>60</v>
@@ -48837,7 +49011,7 @@
         <v>70</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>60</v>
@@ -48865,7 +49039,7 @@
         <v>70</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>60</v>
@@ -48889,7 +49063,7 @@
         <v>70</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>60</v>
@@ -48931,7 +49105,7 @@
         <v>40</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C39" s="9" t="s">
         <v>71</v>
@@ -49059,7 +49233,7 @@
         <v>40</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C44" s="9" t="s">
         <v>73</v>
@@ -49167,7 +49341,7 @@
         <v>97</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>60</v>
@@ -49183,13 +49357,13 @@
         <v>40</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C49" s="9" t="s">
         <v>97</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>60</v>
@@ -49215,7 +49389,7 @@
         <v>97</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E50" s="9" t="s">
         <v>60</v>
@@ -49243,7 +49417,7 @@
         <v>97</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>60</v>
@@ -49267,7 +49441,7 @@
         <v>97</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E52" s="9" t="s">
         <v>60</v>
@@ -49289,7 +49463,7 @@
         <v>98</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>60</v>
@@ -49305,13 +49479,13 @@
         <v>40</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C54" s="9" t="s">
         <v>98</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>60</v>
@@ -49337,7 +49511,7 @@
         <v>98</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>60</v>
@@ -49365,7 +49539,7 @@
         <v>98</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>60</v>
@@ -49389,7 +49563,7 @@
         <v>98</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>60</v>
@@ -49411,7 +49585,7 @@
         <v>99</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>46</v>
@@ -49427,13 +49601,13 @@
         <v>40</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C59" s="9" t="s">
         <v>99</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>46</v>
@@ -49459,7 +49633,7 @@
         <v>99</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>46</v>
@@ -49487,7 +49661,7 @@
         <v>99</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>46</v>
@@ -49511,7 +49685,7 @@
         <v>99</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E62" s="9" t="s">
         <v>46</v>
@@ -49549,7 +49723,7 @@
         <v>40</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C64" s="9" t="s">
         <v>100</v>
@@ -49675,7 +49849,7 @@
         <v>40</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C69" s="9" t="s">
         <v>74</v>
@@ -49797,7 +49971,7 @@
         <v>40</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C74" s="9" t="s">
         <v>80</v>
@@ -49919,7 +50093,7 @@
         <v>40</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C79" s="9" t="s">
         <v>83</v>
@@ -50041,7 +50215,7 @@
         <v>40</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C84" s="9" t="s">
         <v>87</v>
@@ -50163,7 +50337,7 @@
         <v>40</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C89" s="9" t="s">
         <v>90</v>
@@ -50293,7 +50467,7 @@
         <v>40</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C94" s="9" t="s">
         <v>93</v>
@@ -50425,7 +50599,7 @@
         <v>40</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C99" s="9" t="s">
         <v>101</v>
@@ -50553,7 +50727,7 @@
         <v>40</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C104" s="9" t="s">
         <v>105</v>
@@ -50681,7 +50855,7 @@
         <v>40</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C109" s="9" t="s">
         <v>108</v>
@@ -50809,7 +50983,7 @@
         <v>40</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C114" s="9" t="s">
         <v>109</v>
@@ -50941,7 +51115,7 @@
         <v>40</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C119" s="9" t="s">
         <v>113</v>
@@ -51023,7 +51197,7 @@
         <v>40</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C122" s="9" t="s">
         <v>116</v>
@@ -51151,7 +51325,7 @@
         <v>40</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C127" s="9" t="s">
         <v>117</v>
@@ -51279,7 +51453,7 @@
         <v>40</v>
       </c>
       <c r="B132" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C132" s="9" t="s">
         <v>121</v>
@@ -51411,7 +51585,7 @@
         <v>40</v>
       </c>
       <c r="B137" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C137" s="9" t="s">
         <v>123</v>
@@ -51537,7 +51711,7 @@
         <v>126</v>
       </c>
       <c r="B142" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C142" s="9" t="s">
         <v>127</v>
@@ -51619,7 +51793,7 @@
         <v>126</v>
       </c>
       <c r="B145" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C145" s="9" t="s">
         <v>134</v>
@@ -51701,7 +51875,7 @@
         <v>126</v>
       </c>
       <c r="B148" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C148" s="9" t="s">
         <v>136</v>
@@ -51783,7 +51957,7 @@
         <v>126</v>
       </c>
       <c r="B151" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C151" s="9" t="s">
         <v>138</v>
@@ -51865,7 +52039,7 @@
         <v>126</v>
       </c>
       <c r="B154" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C154" s="9" t="s">
         <v>140</v>
@@ -51995,7 +52169,7 @@
         <v>126</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C159" s="3" t="s">
         <v>148</v>
@@ -52077,7 +52251,7 @@
         <v>126</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>149</v>
@@ -52159,7 +52333,7 @@
         <v>126</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C165" s="3" t="s">
         <v>152</v>
@@ -52241,7 +52415,7 @@
         <v>126</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C168" s="3" t="s">
         <v>155</v>
@@ -52323,7 +52497,7 @@
         <v>126</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C171" s="3" t="s">
         <v>156</v>
@@ -52405,7 +52579,7 @@
         <v>126</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C174" s="3" t="s">
         <v>158</v>
@@ -52487,7 +52661,7 @@
         <v>126</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C177" s="3" t="s">
         <v>160</v>
@@ -52565,7 +52739,7 @@
         <v>126</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C180" s="3" t="s">
         <v>163</v>
@@ -52625,7 +52799,7 @@
         <v>126</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C183" s="3" t="s">
         <v>175</v>
@@ -52707,13 +52881,13 @@
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>20</v>
@@ -52722,72 +52896,72 @@
         <v>35</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>164</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="R1" t="s">
         <v>13</v>
       </c>
       <c r="T1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="13.5" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" t="s">
         <v>438</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" t="s">
         <v>439</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>440</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" s="29" t="s">
         <v>441</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" s="29" t="s">
         <v>442</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="L2" s="29" t="s">
         <v>443</v>
-      </c>
-      <c r="K2" s="29" t="s">
-        <v>444</v>
-      </c>
-      <c r="L2" s="29" t="s">
-        <v>445</v>
       </c>
       <c r="M2" t="s">
         <v>143</v>
       </c>
       <c r="N2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="R2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="T2" t="s">
         <v>49</v>
@@ -52810,7 +52984,7 @@
         <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G3" t="s">
         <v>44</v>
@@ -52834,7 +53008,7 @@
         <v>44</v>
       </c>
       <c r="N3" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="R3" t="s">
         <v>45</v>
@@ -52872,7 +53046,7 @@
         <v>183</v>
       </c>
       <c r="J4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L4" t="s">
         <v>50</v>
@@ -52881,10 +53055,10 @@
         <v>103</v>
       </c>
       <c r="N4" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="R4" t="s">
-        <v>185</v>
+        <v>447</v>
       </c>
       <c r="T4" t="s">
         <v>72</v>
@@ -52892,42 +53066,42 @@
     </row>
     <row r="5" spans="1:20" ht="15" customHeight="1">
       <c r="A5" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B5" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C5" t="s">
         <v>77</v>
       </c>
       <c r="F5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G5" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="H5" t="s">
         <v>129</v>
       </c>
       <c r="I5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J5" t="s">
         <v>173</v>
       </c>
       <c r="L5" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="M5" t="s">
         <v>88</v>
       </c>
       <c r="N5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="15" customHeight="1">
       <c r="A6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B6" t="s">
         <v>84</v>
@@ -52942,7 +53116,7 @@
         <v>143</v>
       </c>
       <c r="I6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J6" t="s">
         <v>164</v>
@@ -52951,12 +53125,12 @@
         <v>48</v>
       </c>
       <c r="N6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="15" customHeight="1">
       <c r="A7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
@@ -52968,16 +53142,16 @@
         <v>65</v>
       </c>
       <c r="H7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="M7" t="s">
         <v>129</v>
       </c>
       <c r="N7" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="15" customHeight="1">
@@ -52991,13 +53165,13 @@
         <v>76</v>
       </c>
       <c r="I8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="M8" t="s">
         <v>60</v>
       </c>
       <c r="N8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15" customHeight="1">
@@ -53011,13 +53185,13 @@
         <v>103</v>
       </c>
       <c r="I9" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="M9" t="s">
         <v>154</v>
       </c>
       <c r="N9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15" customHeight="1">
@@ -53031,12 +53205,12 @@
         <v>47</v>
       </c>
       <c r="N10" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="B11" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G11" t="s">
         <v>60</v>
@@ -53045,12 +53219,12 @@
         <v>76</v>
       </c>
       <c r="N11" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="B12" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G12" t="s">
         <v>46</v>
@@ -53059,7 +53233,7 @@
         <v>46</v>
       </c>
       <c r="N12" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -53070,7 +53244,7 @@
         <v>77</v>
       </c>
       <c r="N13" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -53078,7 +53252,7 @@
         <v>84</v>
       </c>
       <c r="N14" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -53086,7 +53260,7 @@
         <v>59</v>
       </c>
       <c r="N15" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -53094,31 +53268,31 @@
         <v>65</v>
       </c>
       <c r="N16" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="17" spans="13:14">
       <c r="M17" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="N17" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="18" spans="13:14">
       <c r="M18" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="N18" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="19" spans="13:14">
       <c r="M19" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N19" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/GDM_Tracker_latest.xlsx
+++ b/public/data/GDM_Tracker_latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nationalgridplc.sharepoint.com/sites/GRP-INT-GasBusinessEnablement-DataManagement/Public Folder/Gas Data Modernization Journey/Report Migration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3331" documentId="13_ncr:1_{52745E9B-3AA1-4770-AAD3-E6166BFC13AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83406268-B8EA-46A8-B23B-8594C89345DB}"/>
+  <xr:revisionPtr revIDLastSave="3334" documentId="13_ncr:1_{52745E9B-3AA1-4770-AAD3-E6166BFC13AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA9446D7-8765-49AA-B397-8D6039EF1B4E}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="-21540" yWindow="4485" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27303,7 +27303,7 @@
       <c r="G2" s="17" t="s">
         <v>350</v>
       </c>
-      <c r="H2" s="30" t="s">
+      <c r="H2" s="17" t="s">
         <v>351</v>
       </c>
       <c r="I2" s="30" t="s">
@@ -27340,7 +27340,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:20" ht="15">
       <c r="A3" s="33" t="s">
         <v>142</v>
       </c>
@@ -27399,7 +27399,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:20" ht="15">
       <c r="A4" s="31" t="s">
         <v>152</v>
       </c>
@@ -27462,7 +27462,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:20" ht="15">
       <c r="A5" s="53" t="s">
         <v>127</v>
       </c>
@@ -27521,7 +27521,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:20" ht="15">
       <c r="A6" s="53" t="s">
         <v>140</v>
       </c>
@@ -27580,7 +27580,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:20" ht="15">
       <c r="A7" s="53" t="s">
         <v>134</v>
       </c>
@@ -27639,7 +27639,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:20" ht="15">
       <c r="A8" s="53" t="s">
         <v>134</v>
       </c>
@@ -27698,7 +27698,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:20" ht="15">
       <c r="A9" s="31" t="s">
         <v>152</v>
       </c>
@@ -27757,7 +27757,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:20" ht="15">
       <c r="A10" s="31" t="s">
         <v>142</v>
       </c>
@@ -27816,7 +27816,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:20" ht="15">
       <c r="A11" s="53" t="s">
         <v>134</v>
       </c>
@@ -27875,7 +27875,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:20" ht="15">
       <c r="A12" s="53" t="s">
         <v>149</v>
       </c>
@@ -27934,7 +27934,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:20" ht="15">
       <c r="A13" s="53" t="s">
         <v>138</v>
       </c>
@@ -27993,7 +27993,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:20" ht="15">
       <c r="A14" s="31" t="s">
         <v>145</v>
       </c>
@@ -28052,7 +28052,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:20" ht="15">
       <c r="A15" s="31" t="s">
         <v>155</v>
       </c>
@@ -28111,7 +28111,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:20" ht="15">
       <c r="A16" s="31" t="s">
         <v>148</v>
       </c>
@@ -28170,7 +28170,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:20" ht="15">
       <c r="A17" s="31" t="s">
         <v>145</v>
       </c>
@@ -28202,7 +28202,7 @@
       <c r="M17" s="3"/>
       <c r="S17" s="28"/>
     </row>
-    <row r="18" spans="1:20">
+    <row r="18" spans="1:20" ht="15">
       <c r="A18" s="33" t="s">
         <v>181</v>
       </c>
@@ -28263,7 +28263,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" spans="1:20" ht="15">
       <c r="A19" s="31" t="s">
         <v>145</v>
       </c>
@@ -28322,7 +28322,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:20">
+    <row r="20" spans="1:20" ht="15">
       <c r="A20" s="31" t="s">
         <v>172</v>
       </c>
@@ -28387,7 +28387,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:20">
+    <row r="21" spans="1:20" ht="15">
       <c r="A21" s="31" t="s">
         <v>175</v>
       </c>
@@ -28450,7 +28450,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:20" ht="15">
       <c r="A22" s="53" t="s">
         <v>138</v>
       </c>
@@ -28511,7 +28511,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:20">
+    <row r="23" spans="1:20" ht="15">
       <c r="A23" s="31" t="s">
         <v>169</v>
       </c>
@@ -28576,7 +28576,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="1:20" ht="15">
       <c r="A24" s="31" t="s">
         <v>169</v>
       </c>
@@ -28706,7 +28706,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:20">
+    <row r="26" spans="1:20" ht="15">
       <c r="A26" s="53" t="s">
         <v>187</v>
       </c>
@@ -28763,7 +28763,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:20">
+    <row r="27" spans="1:20" ht="15">
       <c r="A27" s="53" t="s">
         <v>181</v>
       </c>
@@ -28824,7 +28824,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:20">
+    <row r="28" spans="1:20" ht="15">
       <c r="A28" s="31" t="s">
         <v>155</v>
       </c>
@@ -28887,7 +28887,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:20">
+    <row r="29" spans="1:20" ht="15">
       <c r="A29" s="31" t="s">
         <v>136</v>
       </c>
@@ -28950,7 +28950,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:20">
+    <row r="30" spans="1:20" ht="15">
       <c r="A30" s="31" t="s">
         <v>156</v>
       </c>
@@ -29013,7 +29013,7 @@
         <v>QA -&gt; DB Dev</v>
       </c>
     </row>
-    <row r="31" spans="1:20">
+    <row r="31" spans="1:20" ht="15">
       <c r="A31" s="53" t="s">
         <v>181</v>
       </c>
@@ -29074,7 +29074,7 @@
         <v>QA -&gt; DB Dev</v>
       </c>
     </row>
-    <row r="32" spans="1:20">
+    <row r="32" spans="1:20" ht="15">
       <c r="A32" s="31" t="s">
         <v>163</v>
       </c>
@@ -29137,7 +29137,7 @@
         <v>QA -&gt; PBI Dev</v>
       </c>
     </row>
-    <row r="33" spans="1:20">
+    <row r="33" spans="1:20" ht="15">
       <c r="A33" s="31" t="s">
         <v>184</v>
       </c>
@@ -29196,7 +29196,7 @@
         <v>QA -&gt; DB Dev</v>
       </c>
     </row>
-    <row r="34" spans="1:20">
+    <row r="34" spans="1:20" ht="15">
       <c r="A34" s="31" t="s">
         <v>163</v>
       </c>
@@ -29324,7 +29324,7 @@
         <v>QA -&gt; DB Dev</v>
       </c>
     </row>
-    <row r="36" spans="1:20">
+    <row r="36" spans="1:20" ht="15">
       <c r="A36" s="33" t="s">
         <v>181</v>
       </c>
@@ -29385,7 +29385,7 @@
         <v>QA -&gt; DB Dev</v>
       </c>
     </row>
-    <row r="37" spans="1:20">
+    <row r="37" spans="1:20" ht="15">
       <c r="A37" s="33" t="s">
         <v>187</v>
       </c>
@@ -29439,7 +29439,7 @@
         <v>QA -&gt; DB Dev</v>
       </c>
     </row>
-    <row r="38" spans="1:20">
+    <row r="38" spans="1:20" ht="15">
       <c r="A38" s="33" t="s">
         <v>181</v>
       </c>
@@ -29496,7 +29496,7 @@
         <v>QA -&gt; DB Dev</v>
       </c>
     </row>
-    <row r="39" spans="1:20">
+    <row r="39" spans="1:20" ht="15">
       <c r="A39" s="31" t="s">
         <v>192</v>
       </c>
@@ -29561,7 +29561,7 @@
         <v>QA -&gt; PBI Dev</v>
       </c>
     </row>
-    <row r="40" spans="1:20">
+    <row r="40" spans="1:20" ht="15">
       <c r="A40" s="31" t="s">
         <v>209</v>
       </c>
@@ -29618,7 +29618,7 @@
         <v>QA -&gt; PBI Dev</v>
       </c>
     </row>
-    <row r="41" spans="1:20">
+    <row r="41" spans="1:20" ht="15">
       <c r="A41" s="31" t="s">
         <v>205</v>
       </c>
@@ -29672,7 +29672,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:20">
+    <row r="42" spans="1:20" ht="15">
       <c r="A42" s="31" t="s">
         <v>211</v>
       </c>
@@ -29726,7 +29726,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:20">
+    <row r="43" spans="1:20" ht="15">
       <c r="A43" s="31"/>
       <c r="B43" s="32"/>
       <c r="C43" s="31" t="s">
@@ -29768,7 +29768,7 @@
         <v>QA -&gt; DB Dev</v>
       </c>
     </row>
-    <row r="44" spans="1:20">
+    <row r="44" spans="1:20" ht="15">
       <c r="A44" s="31"/>
       <c r="B44" s="32"/>
       <c r="C44" s="31" t="s">
@@ -29810,7 +29810,7 @@
         <v>QA -&gt; PBI Dev</v>
       </c>
     </row>
-    <row r="45" spans="1:20">
+    <row r="45" spans="1:20" ht="15">
       <c r="A45" s="31"/>
       <c r="B45" s="32"/>
       <c r="C45" s="31" t="s">
@@ -29852,7 +29852,7 @@
         <v>QA -&gt; PBI Dev</v>
       </c>
     </row>
-    <row r="46" spans="1:20">
+    <row r="46" spans="1:20" ht="15">
       <c r="A46" s="31"/>
       <c r="B46" s="32"/>
       <c r="C46" s="31" t="s">
@@ -29894,7 +29894,7 @@
         <v>QA -&gt; DB Dev</v>
       </c>
     </row>
-    <row r="47" spans="1:20">
+    <row r="47" spans="1:20" ht="15">
       <c r="A47" s="31"/>
       <c r="B47" s="32"/>
       <c r="C47" s="31" t="s">
@@ -29936,7 +29936,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:20">
+    <row r="48" spans="1:20" ht="15">
       <c r="A48" s="31"/>
       <c r="B48" s="32"/>
       <c r="C48" s="31" t="s">
@@ -29978,7 +29978,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:20">
+    <row r="49" spans="1:20" ht="15">
       <c r="A49" s="31"/>
       <c r="B49" s="32"/>
       <c r="C49" s="31" t="s">
@@ -30020,7 +30020,7 @@
         <v>QA -&gt; DB Dev</v>
       </c>
     </row>
-    <row r="50" spans="1:20">
+    <row r="50" spans="1:20" ht="15">
       <c r="A50" s="31"/>
       <c r="B50" s="32"/>
       <c r="C50" s="31" t="s">
@@ -30062,7 +30062,7 @@
         <v>QA -&gt; DB Dev</v>
       </c>
     </row>
-    <row r="51" spans="1:20">
+    <row r="51" spans="1:20" ht="15">
       <c r="A51" s="31"/>
       <c r="B51" s="32"/>
       <c r="C51" s="31" t="s">
@@ -30104,7 +30104,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:20">
+    <row r="52" spans="1:20" ht="15">
       <c r="A52" s="31"/>
       <c r="B52" s="32"/>
       <c r="C52" s="31" t="s">
@@ -30146,7 +30146,7 @@
         <v>QA -&gt; DB Dev</v>
       </c>
     </row>
-    <row r="53" spans="1:20">
+    <row r="53" spans="1:20" ht="15">
       <c r="A53" s="31"/>
       <c r="B53" s="32"/>
       <c r="C53" s="31" t="s">
@@ -30188,7 +30188,7 @@
         <v>QA -&gt; PBI Dev</v>
       </c>
     </row>
-    <row r="54" spans="1:20">
+    <row r="54" spans="1:20" ht="15">
       <c r="A54" s="31"/>
       <c r="B54" s="32"/>
       <c r="C54" s="31" t="s">
@@ -30230,7 +30230,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:20">
+    <row r="55" spans="1:20" ht="15">
       <c r="A55" s="31"/>
       <c r="B55" s="32"/>
       <c r="C55" s="31" t="s">
@@ -30272,7 +30272,7 @@
         <v>QA -&gt; PBI Dev</v>
       </c>
     </row>
-    <row r="56" spans="1:20">
+    <row r="56" spans="1:20" ht="15">
       <c r="A56" s="31"/>
       <c r="B56" s="32"/>
       <c r="C56" s="31" t="s">
@@ -30314,7 +30314,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:20">
+    <row r="57" spans="1:20" ht="15">
       <c r="A57" s="31"/>
       <c r="B57" s="32"/>
       <c r="C57" s="31" t="s">
@@ -30356,7 +30356,7 @@
         <v>QA -&gt; PBI Dev</v>
       </c>
     </row>
-    <row r="58" spans="1:20">
+    <row r="58" spans="1:20" ht="15">
       <c r="A58" s="31"/>
       <c r="B58" s="32"/>
       <c r="C58" s="31" t="s">
@@ -30398,7 +30398,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:20">
+    <row r="59" spans="1:20" ht="15">
       <c r="A59" s="31"/>
       <c r="B59" s="32"/>
       <c r="C59" s="31" t="s">
@@ -30440,7 +30440,7 @@
         <v>QA -&gt; DB Dev</v>
       </c>
     </row>
-    <row r="60" spans="1:20">
+    <row r="60" spans="1:20" ht="15">
       <c r="A60" s="31"/>
       <c r="B60" s="32"/>
       <c r="C60" s="31" t="s">
@@ -30482,7 +30482,7 @@
         <v>QA -&gt; DB Dev</v>
       </c>
     </row>
-    <row r="61" spans="1:20">
+    <row r="61" spans="1:20" ht="15">
       <c r="A61" s="31"/>
       <c r="B61" s="32"/>
       <c r="C61" s="31" t="s">
@@ -30524,7 +30524,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:20">
+    <row r="62" spans="1:20" ht="15">
       <c r="A62" s="31"/>
       <c r="B62" s="32"/>
       <c r="C62" s="31" t="s">
@@ -30566,7 +30566,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:20">
+    <row r="63" spans="1:20" ht="15">
       <c r="A63" s="31"/>
       <c r="B63" s="32"/>
       <c r="C63" s="31" t="s">
@@ -30608,7 +30608,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:20">
+    <row r="64" spans="1:20" ht="15">
       <c r="A64" s="31"/>
       <c r="B64" s="32"/>
       <c r="C64" s="31" t="s">
@@ -30650,7 +30650,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:20">
+    <row r="65" spans="1:20" ht="15">
       <c r="A65" s="31"/>
       <c r="B65" s="32"/>
       <c r="C65" s="31" t="s">
@@ -30692,7 +30692,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:20">
+    <row r="66" spans="1:20" ht="15">
       <c r="A66" s="31"/>
       <c r="B66" s="32"/>
       <c r="C66" s="31" t="s">
@@ -30734,7 +30734,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:20">
+    <row r="67" spans="1:20" ht="15">
       <c r="A67" s="31"/>
       <c r="B67" s="32"/>
       <c r="C67" s="31" t="s">
@@ -30776,7 +30776,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:20">
+    <row r="68" spans="1:20" ht="15">
       <c r="A68" s="31"/>
       <c r="B68" s="32"/>
       <c r="C68" s="31" t="s">
@@ -30818,7 +30818,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:20">
+    <row r="69" spans="1:20" ht="15">
       <c r="A69" s="31"/>
       <c r="B69" s="32"/>
       <c r="C69" s="31" t="s">
@@ -30860,7 +30860,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:20">
+    <row r="70" spans="1:20" ht="15">
       <c r="A70" s="31"/>
       <c r="B70" s="32"/>
       <c r="C70" s="31" t="s">
@@ -30902,7 +30902,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:20">
+    <row r="71" spans="1:20" ht="15">
       <c r="A71" s="31"/>
       <c r="B71" s="32"/>
       <c r="C71" s="31" t="s">
@@ -30944,7 +30944,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:20">
+    <row r="72" spans="1:20" ht="15">
       <c r="A72" s="31"/>
       <c r="B72" s="32"/>
       <c r="C72" s="31" t="s">
@@ -30986,7 +30986,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:20">
+    <row r="73" spans="1:20" ht="15">
       <c r="A73" s="31"/>
       <c r="B73" s="32"/>
       <c r="C73" s="31" t="s">
@@ -31028,7 +31028,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:20">
+    <row r="74" spans="1:20" ht="15">
       <c r="A74" s="31"/>
       <c r="B74" s="32"/>
       <c r="C74" s="31" t="s">
@@ -31070,7 +31070,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:20">
+    <row r="75" spans="1:20" ht="15">
       <c r="A75" s="31"/>
       <c r="B75" s="32"/>
       <c r="C75" s="31" t="s">
@@ -31112,7 +31112,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:20">
+    <row r="76" spans="1:20" ht="15">
       <c r="A76" s="31"/>
       <c r="B76" s="32"/>
       <c r="C76" s="31" t="s">
@@ -31154,7 +31154,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:20">
+    <row r="77" spans="1:20" ht="15">
       <c r="A77" s="31"/>
       <c r="B77" s="32"/>
       <c r="C77" s="31" t="s">
@@ -31196,7 +31196,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:20">
+    <row r="78" spans="1:20" ht="15">
       <c r="A78" s="31"/>
       <c r="B78" s="32"/>
       <c r="C78" s="31" t="s">
@@ -31238,7 +31238,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:20">
+    <row r="79" spans="1:20" ht="15">
       <c r="A79" s="31"/>
       <c r="B79" s="32"/>
       <c r="C79" s="31" t="s">
@@ -31280,7 +31280,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:20">
+    <row r="80" spans="1:20" ht="15">
       <c r="A80" s="31"/>
       <c r="B80" s="32"/>
       <c r="C80" s="31" t="s">
@@ -31322,7 +31322,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:20">
+    <row r="81" spans="1:20" ht="15">
       <c r="A81" s="31"/>
       <c r="B81" s="32"/>
       <c r="C81" s="31" t="s">
@@ -31364,7 +31364,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:20">
+    <row r="82" spans="1:20" ht="15">
       <c r="A82" s="31"/>
       <c r="B82" s="32"/>
       <c r="C82" s="31" t="s">
@@ -31406,7 +31406,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:20">
+    <row r="83" spans="1:20" ht="15">
       <c r="A83" s="31"/>
       <c r="B83" s="32"/>
       <c r="C83" s="31" t="s">
@@ -31448,7 +31448,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:20">
+    <row r="84" spans="1:20" ht="15">
       <c r="A84" s="31"/>
       <c r="B84" s="32"/>
       <c r="C84" s="31" t="s">
@@ -31490,7 +31490,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:20">
+    <row r="85" spans="1:20" ht="15">
       <c r="A85" s="31"/>
       <c r="B85" s="32"/>
       <c r="C85" s="31" t="s">
@@ -31532,7 +31532,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:20">
+    <row r="86" spans="1:20" ht="15">
       <c r="A86" s="31"/>
       <c r="B86" s="32"/>
       <c r="C86" s="31" t="s">
@@ -31574,7 +31574,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:20">
+    <row r="87" spans="1:20" ht="15">
       <c r="A87" s="31"/>
       <c r="B87" s="32"/>
       <c r="C87" s="31" t="s">
@@ -31616,7 +31616,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:20">
+    <row r="88" spans="1:20" ht="15">
       <c r="A88" s="31"/>
       <c r="B88" s="32"/>
       <c r="C88" s="31" t="s">
@@ -31658,7 +31658,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:20">
+    <row r="89" spans="1:20" ht="15">
       <c r="A89" s="31"/>
       <c r="B89" s="32"/>
       <c r="C89" s="31" t="s">
@@ -31700,7 +31700,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="90" spans="1:20">
+    <row r="90" spans="1:20" ht="15">
       <c r="A90" s="31"/>
       <c r="B90" s="32"/>
       <c r="C90" s="31" t="s">
@@ -31742,7 +31742,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="91" spans="1:20">
+    <row r="91" spans="1:20" ht="15">
       <c r="A91" s="31"/>
       <c r="B91" s="32"/>
       <c r="C91" s="31" t="s">
@@ -31784,7 +31784,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="92" spans="1:20">
+    <row r="92" spans="1:20" ht="15">
       <c r="A92" s="31"/>
       <c r="B92" s="32"/>
       <c r="C92" s="31" t="s">
@@ -31826,7 +31826,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="93" spans="1:20">
+    <row r="93" spans="1:20" ht="15">
       <c r="A93" s="31"/>
       <c r="B93" s="32"/>
       <c r="C93" s="31" t="s">
@@ -31868,7 +31868,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="94" spans="1:20">
+    <row r="94" spans="1:20" ht="15">
       <c r="A94" s="31"/>
       <c r="B94" s="32"/>
       <c r="C94" s="31" t="s">
@@ -31910,7 +31910,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="95" spans="1:20">
+    <row r="95" spans="1:20" ht="15">
       <c r="A95" s="31"/>
       <c r="B95" s="32"/>
       <c r="C95" s="31" t="s">
@@ -31952,7 +31952,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="96" spans="1:20">
+    <row r="96" spans="1:20" ht="15">
       <c r="A96" s="31"/>
       <c r="B96" s="32"/>
       <c r="C96" s="31" t="s">
@@ -31994,7 +31994,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="97" spans="1:20">
+    <row r="97" spans="1:20" ht="15">
       <c r="A97" s="31"/>
       <c r="B97" s="32"/>
       <c r="C97" s="31" t="s">
@@ -32036,7 +32036,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="98" spans="1:20">
+    <row r="98" spans="1:20" ht="15">
       <c r="A98" s="31"/>
       <c r="B98" s="32"/>
       <c r="C98" s="31" t="s">
@@ -32078,7 +32078,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="99" spans="1:20">
+    <row r="99" spans="1:20" ht="15">
       <c r="A99" s="31"/>
       <c r="B99" s="32"/>
       <c r="C99" s="31" t="s">
@@ -32120,7 +32120,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="100" spans="1:20">
+    <row r="100" spans="1:20" ht="15">
       <c r="A100" s="31"/>
       <c r="B100" s="32"/>
       <c r="C100" s="31" t="s">
@@ -32162,7 +32162,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="101" spans="1:20">
+    <row r="101" spans="1:20" ht="15">
       <c r="A101" s="31"/>
       <c r="B101" s="32"/>
       <c r="C101" s="31" t="s">
@@ -32204,7 +32204,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="102" spans="1:20">
+    <row r="102" spans="1:20" ht="15">
       <c r="A102" s="31"/>
       <c r="B102" s="32"/>
       <c r="C102" s="31" t="s">
@@ -32246,7 +32246,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="103" spans="1:20">
+    <row r="103" spans="1:20" ht="15">
       <c r="A103" s="31"/>
       <c r="B103" s="32"/>
       <c r="C103" s="31" t="s">
@@ -32288,7 +32288,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="104" spans="1:20">
+    <row r="104" spans="1:20" ht="15">
       <c r="A104" s="31"/>
       <c r="B104" s="32"/>
       <c r="C104" s="31" t="s">
@@ -32330,7 +32330,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="105" spans="1:20">
+    <row r="105" spans="1:20" ht="15">
       <c r="A105" s="31"/>
       <c r="B105" s="32"/>
       <c r="C105" s="31" t="s">
@@ -32372,7 +32372,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="106" spans="1:20">
+    <row r="106" spans="1:20" ht="15">
       <c r="A106" s="31"/>
       <c r="B106" s="32"/>
       <c r="C106" s="31" t="s">
@@ -32414,7 +32414,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="107" spans="1:20">
+    <row r="107" spans="1:20" ht="15">
       <c r="A107" s="31"/>
       <c r="B107" s="32"/>
       <c r="C107" s="31" t="s">
@@ -32456,7 +32456,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="108" spans="1:20">
+    <row r="108" spans="1:20" ht="15">
       <c r="A108" s="31"/>
       <c r="B108" s="32"/>
       <c r="C108" s="31" t="s">
@@ -32498,7 +32498,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="109" spans="1:20">
+    <row r="109" spans="1:20" ht="15">
       <c r="A109" s="31"/>
       <c r="B109" s="32"/>
       <c r="C109" s="31" t="s">
@@ -32540,7 +32540,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="110" spans="1:20">
+    <row r="110" spans="1:20" ht="15">
       <c r="A110" s="31"/>
       <c r="B110" s="32"/>
       <c r="C110" s="31" t="s">
@@ -32582,7 +32582,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="111" spans="1:20">
+    <row r="111" spans="1:20" ht="15">
       <c r="A111" s="31"/>
       <c r="B111" s="32"/>
       <c r="C111" s="31" t="s">
@@ -32624,7 +32624,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="112" spans="1:20">
+    <row r="112" spans="1:20" ht="15">
       <c r="A112" s="31"/>
       <c r="B112" s="32"/>
       <c r="C112" s="31" t="s">
@@ -32666,7 +32666,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="113" spans="1:20">
+    <row r="113" spans="1:20" ht="15">
       <c r="A113" s="31"/>
       <c r="B113" s="32"/>
       <c r="C113" s="31" t="s">
@@ -32708,7 +32708,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="114" spans="1:20">
+    <row r="114" spans="1:20" ht="15">
       <c r="A114" s="31"/>
       <c r="B114" s="32"/>
       <c r="C114" s="31" t="s">
@@ -32750,7 +32750,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="115" spans="1:20">
+    <row r="115" spans="1:20" ht="15">
       <c r="A115" s="31"/>
       <c r="B115" s="32"/>
       <c r="C115" s="31" t="s">
@@ -32792,7 +32792,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="116" spans="1:20">
+    <row r="116" spans="1:20" ht="15">
       <c r="A116" s="31"/>
       <c r="B116" s="32"/>
       <c r="C116" s="31" t="s">
@@ -32834,7 +32834,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="117" spans="1:20">
+    <row r="117" spans="1:20" ht="15">
       <c r="A117" s="31"/>
       <c r="B117" s="32"/>
       <c r="C117" s="31" t="s">
@@ -32876,7 +32876,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="118" spans="1:20">
+    <row r="118" spans="1:20" ht="15">
       <c r="A118" s="31"/>
       <c r="B118" s="32"/>
       <c r="C118" s="31" t="s">
@@ -32918,7 +32918,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="119" spans="1:20">
+    <row r="119" spans="1:20" ht="15">
       <c r="A119" s="31"/>
       <c r="B119" s="32"/>
       <c r="C119" s="31" t="s">
@@ -32960,7 +32960,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="120" spans="1:20">
+    <row r="120" spans="1:20" ht="15">
       <c r="A120" s="31"/>
       <c r="B120" s="32"/>
       <c r="C120" s="31" t="s">
@@ -33002,7 +33002,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="121" spans="1:20">
+    <row r="121" spans="1:20" ht="15">
       <c r="A121" s="31"/>
       <c r="B121" s="32"/>
       <c r="C121" s="31" t="s">
@@ -33044,7 +33044,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="122" spans="1:20">
+    <row r="122" spans="1:20" ht="15">
       <c r="A122" s="31"/>
       <c r="B122" s="32"/>
       <c r="C122" s="31" t="s">
@@ -33086,7 +33086,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="123" spans="1:20">
+    <row r="123" spans="1:20" ht="15">
       <c r="A123" s="31"/>
       <c r="B123" s="32"/>
       <c r="C123" s="31" t="s">
@@ -33128,7 +33128,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="124" spans="1:20">
+    <row r="124" spans="1:20" ht="15">
       <c r="A124" s="31"/>
       <c r="B124" s="32"/>
       <c r="C124" s="31" t="s">
@@ -33170,7 +33170,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="125" spans="1:20">
+    <row r="125" spans="1:20" ht="15">
       <c r="A125" s="31"/>
       <c r="B125" s="32"/>
       <c r="C125" s="31" t="s">
@@ -33212,7 +33212,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="126" spans="1:20">
+    <row r="126" spans="1:20" ht="15">
       <c r="A126" s="31"/>
       <c r="B126" s="32"/>
       <c r="C126" s="31" t="s">
@@ -33254,7 +33254,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="127" spans="1:20">
+    <row r="127" spans="1:20" ht="15">
       <c r="A127" s="31"/>
       <c r="B127" s="32"/>
       <c r="C127" s="31" t="s">
@@ -33296,7 +33296,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="128" spans="1:20">
+    <row r="128" spans="1:20" ht="15">
       <c r="A128" s="31"/>
       <c r="B128" s="32"/>
       <c r="C128" s="31" t="s">
@@ -33338,7 +33338,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="129" spans="1:20">
+    <row r="129" spans="1:20" ht="15">
       <c r="A129" s="31"/>
       <c r="B129" s="32"/>
       <c r="C129" s="31" t="s">
@@ -33380,7 +33380,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="130" spans="1:20">
+    <row r="130" spans="1:20" ht="15">
       <c r="A130" s="31"/>
       <c r="B130" s="32"/>
       <c r="C130" s="31" t="s">
@@ -33422,7 +33422,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="131" spans="1:20">
+    <row r="131" spans="1:20" ht="15">
       <c r="A131" s="31"/>
       <c r="B131" s="32"/>
       <c r="C131" s="31" t="s">
@@ -33464,7 +33464,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="132" spans="1:20">
+    <row r="132" spans="1:20" ht="15">
       <c r="A132" s="31"/>
       <c r="B132" s="32"/>
       <c r="C132" s="31" t="s">
@@ -33506,7 +33506,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="133" spans="1:20">
+    <row r="133" spans="1:20" ht="15">
       <c r="A133" s="31"/>
       <c r="B133" s="32"/>
       <c r="C133" s="31" t="s">
@@ -33548,7 +33548,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="134" spans="1:20">
+    <row r="134" spans="1:20" ht="15">
       <c r="A134" s="31"/>
       <c r="B134" s="32"/>
       <c r="C134" s="31" t="s">
@@ -33590,7 +33590,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="135" spans="1:20">
+    <row r="135" spans="1:20" ht="15">
       <c r="A135" s="31"/>
       <c r="B135" s="32"/>
       <c r="C135" s="31" t="s">
@@ -33632,7 +33632,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="136" spans="1:20">
+    <row r="136" spans="1:20" ht="15">
       <c r="A136" s="31"/>
       <c r="B136" s="32"/>
       <c r="C136" s="31" t="s">
@@ -33674,7 +33674,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="137" spans="1:20">
+    <row r="137" spans="1:20" ht="15">
       <c r="A137" s="31"/>
       <c r="B137" s="32"/>
       <c r="C137" s="31" t="s">
@@ -33716,7 +33716,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="138" spans="1:20">
+    <row r="138" spans="1:20" ht="15">
       <c r="A138" s="31"/>
       <c r="B138" s="32"/>
       <c r="C138" s="31" t="s">
@@ -33758,7 +33758,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="139" spans="1:20">
+    <row r="139" spans="1:20" ht="15">
       <c r="A139" s="31"/>
       <c r="B139" s="32"/>
       <c r="C139" s="31" t="s">
@@ -33800,7 +33800,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="140" spans="1:20">
+    <row r="140" spans="1:20" ht="15">
       <c r="A140" s="31"/>
       <c r="B140" s="32"/>
       <c r="C140" s="31" t="s">
@@ -33842,7 +33842,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="141" spans="1:20">
+    <row r="141" spans="1:20" ht="15">
       <c r="A141" s="31"/>
       <c r="B141" s="32"/>
       <c r="C141" s="31" t="s">
@@ -33884,7 +33884,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="142" spans="1:20">
+    <row r="142" spans="1:20" ht="15">
       <c r="A142" s="31"/>
       <c r="B142" s="32"/>
       <c r="C142" s="31" t="s">
@@ -33926,7 +33926,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="143" spans="1:20">
+    <row r="143" spans="1:20" ht="15">
       <c r="A143" s="31"/>
       <c r="B143" s="32"/>
       <c r="C143" s="31" t="s">
@@ -33968,7 +33968,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="144" spans="1:20">
+    <row r="144" spans="1:20" ht="15">
       <c r="A144" s="31"/>
       <c r="B144" s="32"/>
       <c r="C144" s="31" t="s">
@@ -34010,7 +34010,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="145" spans="1:20">
+    <row r="145" spans="1:20" ht="15">
       <c r="A145" s="31"/>
       <c r="B145" s="32"/>
       <c r="C145" s="31" t="s">
@@ -34052,7 +34052,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="146" spans="1:20">
+    <row r="146" spans="1:20" ht="15">
       <c r="A146" s="31"/>
       <c r="B146" s="32"/>
       <c r="C146" s="31" t="s">
@@ -34094,7 +34094,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="147" spans="1:20">
+    <row r="147" spans="1:20" ht="15">
       <c r="A147" s="31"/>
       <c r="B147" s="32"/>
       <c r="C147" s="31" t="s">
@@ -34136,7 +34136,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="148" spans="1:20">
+    <row r="148" spans="1:20" ht="15">
       <c r="A148" s="31"/>
       <c r="B148" s="32"/>
       <c r="C148" s="31" t="s">
@@ -34178,7 +34178,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="149" spans="1:20">
+    <row r="149" spans="1:20" ht="15">
       <c r="A149" s="31"/>
       <c r="B149" s="32"/>
       <c r="C149" s="31" t="s">
@@ -34220,7 +34220,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="150" spans="1:20">
+    <row r="150" spans="1:20" ht="15">
       <c r="A150" s="31"/>
       <c r="B150" s="32"/>
       <c r="C150" s="31" t="s">
@@ -34262,7 +34262,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="151" spans="1:20">
+    <row r="151" spans="1:20" ht="15">
       <c r="A151" s="31"/>
       <c r="B151" s="32"/>
       <c r="C151" s="31" t="s">
@@ -34304,7 +34304,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="152" spans="1:20">
+    <row r="152" spans="1:20" ht="15">
       <c r="A152" s="31"/>
       <c r="B152" s="32"/>
       <c r="C152" s="31" t="s">
@@ -34346,7 +34346,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="153" spans="1:20">
+    <row r="153" spans="1:20" ht="15">
       <c r="A153" s="31"/>
       <c r="B153" s="32"/>
       <c r="C153" s="31" t="s">
@@ -34388,7 +34388,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="154" spans="1:20">
+    <row r="154" spans="1:20" ht="15">
       <c r="A154" s="31"/>
       <c r="B154" s="32"/>
       <c r="C154" s="31" t="s">
@@ -34430,7 +34430,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="155" spans="1:20">
+    <row r="155" spans="1:20" ht="15">
       <c r="A155" s="31"/>
       <c r="B155" s="32"/>
       <c r="C155" s="31" t="s">
@@ -34472,7 +34472,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="156" spans="1:20">
+    <row r="156" spans="1:20" ht="15">
       <c r="A156" s="31"/>
       <c r="B156" s="32"/>
       <c r="C156" s="31" t="s">
@@ -34514,7 +34514,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="157" spans="1:20">
+    <row r="157" spans="1:20" ht="15">
       <c r="A157" s="31"/>
       <c r="B157" s="32"/>
       <c r="C157" s="31" t="s">
@@ -34556,7 +34556,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="158" spans="1:20">
+    <row r="158" spans="1:20" ht="15">
       <c r="A158" s="31"/>
       <c r="B158" s="32"/>
       <c r="C158" s="31" t="s">
@@ -34598,7 +34598,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="159" spans="1:20">
+    <row r="159" spans="1:20" ht="15">
       <c r="A159" s="31"/>
       <c r="B159" s="32"/>
       <c r="C159" s="31" t="s">
@@ -34640,7 +34640,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="160" spans="1:20">
+    <row r="160" spans="1:20" ht="15">
       <c r="A160" s="31"/>
       <c r="B160" s="32"/>
       <c r="C160" s="31" t="s">
@@ -34682,7 +34682,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="161" spans="1:20">
+    <row r="161" spans="1:20" ht="15">
       <c r="A161" s="31"/>
       <c r="B161" s="32"/>
       <c r="C161" s="31" t="s">
@@ -34724,7 +34724,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="162" spans="1:20">
+    <row r="162" spans="1:20" ht="15">
       <c r="A162" s="31"/>
       <c r="B162" s="32"/>
       <c r="C162" s="31" t="s">
@@ -34766,7 +34766,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="163" spans="1:20">
+    <row r="163" spans="1:20" ht="15">
       <c r="A163" s="31"/>
       <c r="B163" s="32"/>
       <c r="C163" s="31" t="s">
@@ -34808,7 +34808,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="164" spans="1:20">
+    <row r="164" spans="1:20" ht="15">
       <c r="A164" s="31"/>
       <c r="B164" s="32"/>
       <c r="C164" s="31" t="s">
@@ -34850,7 +34850,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="165" spans="1:20">
+    <row r="165" spans="1:20" ht="15">
       <c r="A165" s="31"/>
       <c r="B165" s="32"/>
       <c r="C165" s="31" t="s">
@@ -34892,7 +34892,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="166" spans="1:20">
+    <row r="166" spans="1:20" ht="15">
       <c r="A166" s="31"/>
       <c r="B166" s="32"/>
       <c r="C166" s="31" t="s">
@@ -34934,7 +34934,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="167" spans="1:20">
+    <row r="167" spans="1:20" ht="15">
       <c r="A167" s="31"/>
       <c r="B167" s="32"/>
       <c r="C167" s="31" t="s">
@@ -34976,7 +34976,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="168" spans="1:20">
+    <row r="168" spans="1:20" ht="15">
       <c r="A168" s="31"/>
       <c r="B168" s="32"/>
       <c r="C168" s="31" t="s">
@@ -35018,7 +35018,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="169" spans="1:20">
+    <row r="169" spans="1:20" ht="15">
       <c r="A169" s="31"/>
       <c r="B169" s="32"/>
       <c r="C169" s="31" t="s">
@@ -35060,7 +35060,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="170" spans="1:20">
+    <row r="170" spans="1:20" ht="15">
       <c r="A170" s="31"/>
       <c r="B170" s="32"/>
       <c r="C170" s="31" t="s">
@@ -35102,7 +35102,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="171" spans="1:20">
+    <row r="171" spans="1:20" ht="15">
       <c r="A171" s="31"/>
       <c r="B171" s="32"/>
       <c r="C171" s="31" t="s">
@@ -35144,7 +35144,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="172" spans="1:20">
+    <row r="172" spans="1:20" ht="15">
       <c r="A172" s="31"/>
       <c r="B172" s="32"/>
       <c r="C172" s="31" t="s">
@@ -35186,7 +35186,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="173" spans="1:20">
+    <row r="173" spans="1:20" ht="15">
       <c r="A173" s="31"/>
       <c r="B173" s="32"/>
       <c r="C173" s="31" t="s">
@@ -35228,7 +35228,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="174" spans="1:20">
+    <row r="174" spans="1:20" ht="15">
       <c r="A174" s="31"/>
       <c r="B174" s="32"/>
       <c r="C174" s="31" t="s">
@@ -35270,7 +35270,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="175" spans="1:20">
+    <row r="175" spans="1:20" ht="15">
       <c r="A175" s="31"/>
       <c r="B175" s="32"/>
       <c r="C175" s="31" t="s">
@@ -35312,7 +35312,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="176" spans="1:20">
+    <row r="176" spans="1:20" ht="15">
       <c r="A176" s="31"/>
       <c r="B176" s="32"/>
       <c r="C176" s="31" t="s">
@@ -35354,7 +35354,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="177" spans="1:20">
+    <row r="177" spans="1:20" ht="15">
       <c r="A177" s="31"/>
       <c r="B177" s="32"/>
       <c r="C177" s="31" t="s">
@@ -35396,7 +35396,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="178" spans="1:20">
+    <row r="178" spans="1:20" ht="15">
       <c r="A178" s="31"/>
       <c r="B178" s="32"/>
       <c r="C178" s="31" t="s">
@@ -35438,7 +35438,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="179" spans="1:20">
+    <row r="179" spans="1:20" ht="15">
       <c r="A179" s="31"/>
       <c r="B179" s="32"/>
       <c r="C179" s="31" t="s">
@@ -35480,7 +35480,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="180" spans="1:20">
+    <row r="180" spans="1:20" ht="15">
       <c r="A180" s="31"/>
       <c r="B180" s="32"/>
       <c r="C180" s="31" t="s">
@@ -35522,7 +35522,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="181" spans="1:20">
+    <row r="181" spans="1:20" ht="15">
       <c r="A181" s="31"/>
       <c r="B181" s="32"/>
       <c r="C181" s="31" t="s">
@@ -35564,7 +35564,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="182" spans="1:20">
+    <row r="182" spans="1:20" ht="15">
       <c r="A182" s="31"/>
       <c r="B182" s="32"/>
       <c r="C182" s="31" t="s">
@@ -35606,7 +35606,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="183" spans="1:20">
+    <row r="183" spans="1:20" ht="15">
       <c r="A183" s="31"/>
       <c r="B183" s="32"/>
       <c r="C183" s="31" t="s">
@@ -35648,7 +35648,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="184" spans="1:20">
+    <row r="184" spans="1:20" ht="15">
       <c r="A184" s="31"/>
       <c r="B184" s="32"/>
       <c r="C184" s="31" t="s">
@@ -35690,7 +35690,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="185" spans="1:20">
+    <row r="185" spans="1:20" ht="15">
       <c r="A185" s="31"/>
       <c r="B185" s="32"/>
       <c r="C185" s="31" t="s">
@@ -35732,7 +35732,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="186" spans="1:20">
+    <row r="186" spans="1:20" ht="15">
       <c r="A186" s="31"/>
       <c r="B186" s="32"/>
       <c r="C186" s="31" t="s">
@@ -35774,7 +35774,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="187" spans="1:20">
+    <row r="187" spans="1:20" ht="15">
       <c r="A187" s="31"/>
       <c r="B187" s="32"/>
       <c r="C187" s="31" t="s">
@@ -35816,7 +35816,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="188" spans="1:20">
+    <row r="188" spans="1:20" ht="15">
       <c r="A188" s="31"/>
       <c r="B188" s="32"/>
       <c r="C188" s="31" t="s">
@@ -35858,7 +35858,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="189" spans="1:20">
+    <row r="189" spans="1:20" ht="15">
       <c r="A189" s="31"/>
       <c r="B189" s="32"/>
       <c r="C189" s="31" t="s">
@@ -35900,7 +35900,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="190" spans="1:20">
+    <row r="190" spans="1:20" ht="15">
       <c r="A190" s="31"/>
       <c r="B190" s="32"/>
       <c r="C190" s="31" t="s">
@@ -35942,7 +35942,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="191" spans="1:20">
+    <row r="191" spans="1:20" ht="15">
       <c r="A191" s="31"/>
       <c r="B191" s="32"/>
       <c r="C191" s="31" t="s">
@@ -35984,7 +35984,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="192" spans="1:20">
+    <row r="192" spans="1:20" ht="15">
       <c r="A192" s="31"/>
       <c r="B192" s="32"/>
       <c r="C192" s="31" t="s">
@@ -36026,7 +36026,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="193" spans="1:20">
+    <row r="193" spans="1:20" ht="15">
       <c r="A193" s="31"/>
       <c r="B193" s="32"/>
       <c r="C193" s="31" t="s">
@@ -36068,7 +36068,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="194" spans="1:20">
+    <row r="194" spans="1:20" ht="15">
       <c r="A194" s="31"/>
       <c r="B194" s="32"/>
       <c r="C194" s="31" t="s">
@@ -36110,7 +36110,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="195" spans="1:20">
+    <row r="195" spans="1:20" ht="15">
       <c r="A195" s="31"/>
       <c r="B195" s="32"/>
       <c r="C195" s="31" t="s">
@@ -36152,7 +36152,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="196" spans="1:20">
+    <row r="196" spans="1:20" ht="15">
       <c r="A196" s="31"/>
       <c r="B196" s="32"/>
       <c r="C196" s="31" t="s">
@@ -36194,7 +36194,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="197" spans="1:20">
+    <row r="197" spans="1:20" ht="15">
       <c r="A197" s="31"/>
       <c r="B197" s="32"/>
       <c r="C197" s="31" t="s">
@@ -36236,7 +36236,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="198" spans="1:20">
+    <row r="198" spans="1:20" ht="15">
       <c r="A198" s="31"/>
       <c r="B198" s="32"/>
       <c r="C198" s="31" t="s">
@@ -36278,7 +36278,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="199" spans="1:20">
+    <row r="199" spans="1:20" ht="15">
       <c r="A199" s="31"/>
       <c r="B199" s="32"/>
       <c r="C199" s="31"/>
@@ -36316,7 +36316,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="200" spans="1:20">
+    <row r="200" spans="1:20" ht="15">
       <c r="A200" s="31"/>
       <c r="B200" s="32"/>
       <c r="C200" s="31"/>
@@ -36354,7 +36354,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="201" spans="1:20">
+    <row r="201" spans="1:20" ht="15">
       <c r="A201" s="31"/>
       <c r="B201" s="32"/>
       <c r="C201" s="31"/>
@@ -36392,7 +36392,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="202" spans="1:20">
+    <row r="202" spans="1:20" ht="15">
       <c r="A202" s="31"/>
       <c r="B202" s="32"/>
       <c r="C202" s="31"/>
@@ -36430,7 +36430,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="203" spans="1:20">
+    <row r="203" spans="1:20" ht="15">
       <c r="A203" s="31"/>
       <c r="B203" s="32"/>
       <c r="C203" s="31"/>
@@ -36468,7 +36468,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="204" spans="1:20">
+    <row r="204" spans="1:20" ht="15">
       <c r="A204" s="31"/>
       <c r="B204" s="32"/>
       <c r="C204" s="31"/>
@@ -36506,7 +36506,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="205" spans="1:20">
+    <row r="205" spans="1:20" ht="15">
       <c r="A205" s="31"/>
       <c r="B205" s="32"/>
       <c r="C205" s="31"/>
@@ -36544,7 +36544,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="206" spans="1:20">
+    <row r="206" spans="1:20" ht="15">
       <c r="A206" s="31"/>
       <c r="B206" s="32"/>
       <c r="C206" s="31"/>
@@ -36582,7 +36582,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="207" spans="1:20">
+    <row r="207" spans="1:20" ht="15">
       <c r="A207" s="31"/>
       <c r="B207" s="32"/>
       <c r="C207" s="31"/>
@@ -36620,7 +36620,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="208" spans="1:20">
+    <row r="208" spans="1:20" ht="15">
       <c r="A208" s="31"/>
       <c r="B208" s="32"/>
       <c r="C208" s="31"/>
@@ -36658,7 +36658,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="209" spans="1:20">
+    <row r="209" spans="1:20" ht="15">
       <c r="A209" s="31"/>
       <c r="B209" s="32"/>
       <c r="C209" s="31"/>
@@ -36696,7 +36696,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="210" spans="1:20">
+    <row r="210" spans="1:20" ht="15">
       <c r="A210" s="31"/>
       <c r="B210" s="32"/>
       <c r="C210" s="31"/>
@@ -36734,7 +36734,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="211" spans="1:20">
+    <row r="211" spans="1:20" ht="15">
       <c r="A211" s="31"/>
       <c r="B211" s="32"/>
       <c r="C211" s="31"/>
@@ -36772,7 +36772,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="212" spans="1:20">
+    <row r="212" spans="1:20" ht="15">
       <c r="A212" s="31"/>
       <c r="B212" s="32"/>
       <c r="C212" s="31"/>
@@ -36810,7 +36810,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="213" spans="1:20">
+    <row r="213" spans="1:20" ht="15">
       <c r="A213" s="31"/>
       <c r="B213" s="32"/>
       <c r="C213" s="31"/>
@@ -36848,7 +36848,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="214" spans="1:20">
+    <row r="214" spans="1:20" ht="15">
       <c r="A214" s="31"/>
       <c r="B214" s="32"/>
       <c r="C214" s="31"/>
@@ -36886,7 +36886,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="215" spans="1:20">
+    <row r="215" spans="1:20" ht="15">
       <c r="A215" s="31"/>
       <c r="B215" s="32"/>
       <c r="C215" s="31"/>
@@ -36924,7 +36924,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="216" spans="1:20">
+    <row r="216" spans="1:20" ht="15">
       <c r="A216" s="31"/>
       <c r="B216" s="32"/>
       <c r="C216" s="31"/>
@@ -36962,7 +36962,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="217" spans="1:20">
+    <row r="217" spans="1:20" ht="15">
       <c r="A217" s="31"/>
       <c r="B217" s="32"/>
       <c r="C217" s="31"/>
@@ -37000,7 +37000,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="218" spans="1:20">
+    <row r="218" spans="1:20" ht="15">
       <c r="A218" s="31"/>
       <c r="B218" s="32"/>
       <c r="C218" s="31"/>
@@ -37038,7 +37038,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="219" spans="1:20">
+    <row r="219" spans="1:20" ht="15">
       <c r="A219" s="31"/>
       <c r="B219" s="32"/>
       <c r="C219" s="31"/>
@@ -37076,7 +37076,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="220" spans="1:20">
+    <row r="220" spans="1:20" ht="15">
       <c r="A220" s="31"/>
       <c r="B220" s="32"/>
       <c r="C220" s="31"/>
@@ -37114,7 +37114,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="221" spans="1:20">
+    <row r="221" spans="1:20" ht="15">
       <c r="A221" s="31"/>
       <c r="B221" s="32"/>
       <c r="C221" s="31"/>
@@ -37152,7 +37152,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="222" spans="1:20">
+    <row r="222" spans="1:20" ht="15">
       <c r="A222" s="31"/>
       <c r="B222" s="32"/>
       <c r="C222" s="31"/>
@@ -37190,7 +37190,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="223" spans="1:20">
+    <row r="223" spans="1:20" ht="15">
       <c r="A223" s="31"/>
       <c r="B223" s="32"/>
       <c r="C223" s="31"/>
@@ -37228,7 +37228,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="224" spans="1:20">
+    <row r="224" spans="1:20" ht="15">
       <c r="A224" s="31"/>
       <c r="B224" s="32"/>
       <c r="C224" s="31"/>
@@ -37266,7 +37266,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="225" spans="1:20">
+    <row r="225" spans="1:20" ht="15">
       <c r="A225" s="31"/>
       <c r="B225" s="32"/>
       <c r="C225" s="31"/>
@@ -37304,7 +37304,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="226" spans="1:20">
+    <row r="226" spans="1:20" ht="15">
       <c r="A226" s="31"/>
       <c r="B226" s="32"/>
       <c r="C226" s="31"/>
@@ -37342,7 +37342,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="227" spans="1:20">
+    <row r="227" spans="1:20" ht="15">
       <c r="A227" s="31"/>
       <c r="B227" s="32"/>
       <c r="C227" s="31"/>
@@ -37380,7 +37380,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="228" spans="1:20">
+    <row r="228" spans="1:20" ht="15">
       <c r="A228" s="31"/>
       <c r="B228" s="32"/>
       <c r="C228" s="31"/>
@@ -37418,7 +37418,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="229" spans="1:20">
+    <row r="229" spans="1:20" ht="15">
       <c r="A229" s="31"/>
       <c r="B229" s="32"/>
       <c r="C229" s="31"/>
@@ -37456,7 +37456,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="230" spans="1:20">
+    <row r="230" spans="1:20" ht="15">
       <c r="A230" s="31"/>
       <c r="B230" s="32"/>
       <c r="C230" s="31"/>
@@ -37494,7 +37494,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="231" spans="1:20">
+    <row r="231" spans="1:20" ht="15">
       <c r="A231" s="31"/>
       <c r="B231" s="32"/>
       <c r="C231" s="31"/>
@@ -37532,7 +37532,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="232" spans="1:20">
+    <row r="232" spans="1:20" ht="15">
       <c r="A232" s="31"/>
       <c r="B232" s="32"/>
       <c r="C232" s="31"/>
@@ -37570,7 +37570,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="233" spans="1:20">
+    <row r="233" spans="1:20" ht="15">
       <c r="A233" s="31"/>
       <c r="B233" s="32"/>
       <c r="C233" s="31"/>
@@ -37608,7 +37608,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="234" spans="1:20">
+    <row r="234" spans="1:20" ht="15">
       <c r="A234" s="31"/>
       <c r="B234" s="32"/>
       <c r="C234" s="31"/>
@@ -37646,7 +37646,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="235" spans="1:20">
+    <row r="235" spans="1:20" ht="15">
       <c r="A235" s="31"/>
       <c r="B235" s="32"/>
       <c r="C235" s="31"/>
@@ -37684,7 +37684,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="236" spans="1:20">
+    <row r="236" spans="1:20" ht="15">
       <c r="A236" s="31"/>
       <c r="B236" s="32"/>
       <c r="C236" s="31"/>
@@ -37722,7 +37722,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="237" spans="1:20">
+    <row r="237" spans="1:20" ht="15">
       <c r="A237" s="31"/>
       <c r="B237" s="32"/>
       <c r="C237" s="31"/>
@@ -37760,7 +37760,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="238" spans="1:20">
+    <row r="238" spans="1:20" ht="15">
       <c r="A238" s="31"/>
       <c r="B238" s="32"/>
       <c r="C238" s="31"/>
@@ -37798,7 +37798,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="239" spans="1:20">
+    <row r="239" spans="1:20" ht="15">
       <c r="A239" s="31"/>
       <c r="B239" s="32"/>
       <c r="C239" s="31"/>
@@ -37836,7 +37836,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="240" spans="1:20">
+    <row r="240" spans="1:20" ht="15">
       <c r="A240" s="31"/>
       <c r="B240" s="32"/>
       <c r="C240" s="31"/>
@@ -37874,7 +37874,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="241" spans="1:20">
+    <row r="241" spans="1:20" ht="15">
       <c r="A241" s="31"/>
       <c r="B241" s="32"/>
       <c r="C241" s="31"/>
@@ -37912,7 +37912,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="242" spans="1:20">
+    <row r="242" spans="1:20" ht="15">
       <c r="A242" s="31"/>
       <c r="B242" s="32"/>
       <c r="C242" s="31"/>
@@ -37950,7 +37950,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="243" spans="1:20">
+    <row r="243" spans="1:20" ht="15">
       <c r="A243" s="31"/>
       <c r="B243" s="32"/>
       <c r="C243" s="31"/>
@@ -37988,7 +37988,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="244" spans="1:20">
+    <row r="244" spans="1:20" ht="15">
       <c r="A244" s="31"/>
       <c r="B244" s="32"/>
       <c r="C244" s="31"/>
@@ -38026,7 +38026,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="245" spans="1:20">
+    <row r="245" spans="1:20" ht="15">
       <c r="A245" s="31"/>
       <c r="B245" s="32"/>
       <c r="C245" s="31"/>
@@ -38064,7 +38064,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="246" spans="1:20">
+    <row r="246" spans="1:20" ht="15">
       <c r="A246" s="31"/>
       <c r="B246" s="32"/>
       <c r="C246" s="31"/>
@@ -38102,7 +38102,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="247" spans="1:20">
+    <row r="247" spans="1:20" ht="15">
       <c r="A247" s="31"/>
       <c r="B247" s="32"/>
       <c r="C247" s="31"/>
@@ -38140,7 +38140,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="248" spans="1:20">
+    <row r="248" spans="1:20" ht="15">
       <c r="A248" s="31"/>
       <c r="B248" s="32"/>
       <c r="C248" s="31"/>
@@ -38178,7 +38178,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="249" spans="1:20">
+    <row r="249" spans="1:20" ht="15">
       <c r="A249" s="31"/>
       <c r="B249" s="32"/>
       <c r="C249" s="31"/>
@@ -38216,7 +38216,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="250" spans="1:20">
+    <row r="250" spans="1:20" ht="15">
       <c r="A250" s="31"/>
       <c r="B250" s="32"/>
       <c r="C250" s="31"/>
@@ -38254,7 +38254,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="251" spans="1:20">
+    <row r="251" spans="1:20" ht="15">
       <c r="A251" s="31"/>
       <c r="B251" s="32"/>
       <c r="C251" s="31"/>
@@ -38292,7 +38292,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="252" spans="1:20">
+    <row r="252" spans="1:20" ht="15">
       <c r="A252" s="31"/>
       <c r="B252" s="32"/>
       <c r="C252" s="31"/>
@@ -38330,7 +38330,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="253" spans="1:20">
+    <row r="253" spans="1:20" ht="15">
       <c r="A253" s="31"/>
       <c r="B253" s="32"/>
       <c r="C253" s="31"/>
@@ -38368,7 +38368,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="254" spans="1:20">
+    <row r="254" spans="1:20" ht="15">
       <c r="A254" s="31"/>
       <c r="B254" s="32"/>
       <c r="C254" s="31"/>
@@ -38406,7 +38406,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="255" spans="1:20">
+    <row r="255" spans="1:20" ht="15">
       <c r="A255" s="31"/>
       <c r="B255" s="32"/>
       <c r="C255" s="31"/>
@@ -38444,7 +38444,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="256" spans="1:20">
+    <row r="256" spans="1:20" ht="15">
       <c r="A256" s="31"/>
       <c r="B256" s="32"/>
       <c r="C256" s="31"/>
@@ -38482,7 +38482,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="257" spans="1:20">
+    <row r="257" spans="1:20" ht="15">
       <c r="A257" s="31"/>
       <c r="B257" s="32"/>
       <c r="C257" s="31"/>
@@ -38520,7 +38520,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="258" spans="1:20">
+    <row r="258" spans="1:20" ht="15">
       <c r="A258" s="31"/>
       <c r="B258" s="32"/>
       <c r="C258" s="31"/>
@@ -38558,7 +38558,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="259" spans="1:20">
+    <row r="259" spans="1:20" ht="15">
       <c r="A259" s="31"/>
       <c r="B259" s="32"/>
       <c r="C259" s="31"/>
@@ -38596,7 +38596,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="260" spans="1:20">
+    <row r="260" spans="1:20" ht="15">
       <c r="A260" s="31"/>
       <c r="B260" s="32"/>
       <c r="C260" s="31"/>
@@ -38634,7 +38634,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="261" spans="1:20">
+    <row r="261" spans="1:20" ht="15">
       <c r="A261" s="31"/>
       <c r="B261" s="32"/>
       <c r="C261" s="31"/>
@@ -38672,7 +38672,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="262" spans="1:20">
+    <row r="262" spans="1:20" ht="15">
       <c r="A262" s="31"/>
       <c r="B262" s="32"/>
       <c r="C262" s="31"/>
@@ -38710,7 +38710,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="263" spans="1:20">
+    <row r="263" spans="1:20" ht="15">
       <c r="A263" s="31"/>
       <c r="B263" s="32"/>
       <c r="C263" s="31"/>
@@ -38748,7 +38748,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="264" spans="1:20">
+    <row r="264" spans="1:20" ht="15">
       <c r="A264" s="31"/>
       <c r="B264" s="32"/>
       <c r="C264" s="31"/>
@@ -38786,7 +38786,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="265" spans="1:20">
+    <row r="265" spans="1:20" ht="15">
       <c r="A265" s="31"/>
       <c r="B265" s="32"/>
       <c r="C265" s="31"/>
@@ -38824,7 +38824,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="266" spans="1:20">
+    <row r="266" spans="1:20" ht="15">
       <c r="A266" s="31"/>
       <c r="B266" s="32"/>
       <c r="C266" s="31"/>
@@ -38862,7 +38862,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="267" spans="1:20">
+    <row r="267" spans="1:20" ht="15">
       <c r="A267" s="31"/>
       <c r="B267" s="32"/>
       <c r="C267" s="31"/>
@@ -38900,7 +38900,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="268" spans="1:20">
+    <row r="268" spans="1:20" ht="15">
       <c r="A268" s="31"/>
       <c r="B268" s="32"/>
       <c r="C268" s="31"/>
@@ -38938,7 +38938,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="269" spans="1:20">
+    <row r="269" spans="1:20" ht="15">
       <c r="A269" s="31"/>
       <c r="B269" s="32"/>
       <c r="C269" s="31"/>
@@ -38976,7 +38976,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="270" spans="1:20">
+    <row r="270" spans="1:20" ht="15">
       <c r="A270" s="31"/>
       <c r="B270" s="32"/>
       <c r="C270" s="31"/>
@@ -39014,7 +39014,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="271" spans="1:20">
+    <row r="271" spans="1:20" ht="15">
       <c r="A271" s="31"/>
       <c r="B271" s="32"/>
       <c r="C271" s="31"/>
@@ -39052,7 +39052,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="272" spans="1:20">
+    <row r="272" spans="1:20" ht="15">
       <c r="A272" s="31"/>
       <c r="B272" s="32"/>
       <c r="C272" s="31"/>
@@ -39090,7 +39090,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="273" spans="1:20">
+    <row r="273" spans="1:20" ht="15">
       <c r="A273" s="31"/>
       <c r="B273" s="32"/>
       <c r="C273" s="31"/>
@@ -39128,7 +39128,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="274" spans="1:20">
+    <row r="274" spans="1:20" ht="15">
       <c r="A274" s="31"/>
       <c r="B274" s="32"/>
       <c r="C274" s="31"/>
@@ -39166,7 +39166,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="275" spans="1:20">
+    <row r="275" spans="1:20" ht="15">
       <c r="A275" s="31"/>
       <c r="B275" s="32"/>
       <c r="C275" s="31"/>
@@ -39204,7 +39204,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="276" spans="1:20">
+    <row r="276" spans="1:20" ht="15">
       <c r="A276" s="31"/>
       <c r="B276" s="32"/>
       <c r="C276" s="31"/>
@@ -39242,7 +39242,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="277" spans="1:20">
+    <row r="277" spans="1:20" ht="15">
       <c r="A277" s="31"/>
       <c r="B277" s="32"/>
       <c r="C277" s="31"/>
@@ -39280,7 +39280,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="278" spans="1:20">
+    <row r="278" spans="1:20" ht="15">
       <c r="A278" s="31"/>
       <c r="B278" s="32"/>
       <c r="C278" s="31"/>
@@ -39318,7 +39318,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="279" spans="1:20">
+    <row r="279" spans="1:20" ht="15">
       <c r="A279" s="31"/>
       <c r="B279" s="32"/>
       <c r="C279" s="31"/>
@@ -39356,7 +39356,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="280" spans="1:20">
+    <row r="280" spans="1:20" ht="15">
       <c r="A280" s="31"/>
       <c r="B280" s="32"/>
       <c r="C280" s="31"/>
@@ -39394,7 +39394,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="281" spans="1:20">
+    <row r="281" spans="1:20" ht="15">
       <c r="A281" s="31"/>
       <c r="B281" s="32"/>
       <c r="C281" s="31"/>
@@ -39432,7 +39432,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="282" spans="1:20">
+    <row r="282" spans="1:20" ht="15">
       <c r="A282" s="31"/>
       <c r="B282" s="32"/>
       <c r="C282" s="31"/>
@@ -39470,7 +39470,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="283" spans="1:20">
+    <row r="283" spans="1:20" ht="15">
       <c r="A283" s="31"/>
       <c r="B283" s="32"/>
       <c r="C283" s="31"/>
@@ -39508,7 +39508,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="284" spans="1:20">
+    <row r="284" spans="1:20" ht="15">
       <c r="A284" s="31"/>
       <c r="B284" s="32"/>
       <c r="C284" s="31"/>
@@ -39546,7 +39546,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="285" spans="1:20">
+    <row r="285" spans="1:20" ht="15">
       <c r="A285" s="31"/>
       <c r="B285" s="32"/>
       <c r="C285" s="31"/>
@@ -39584,7 +39584,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="286" spans="1:20">
+    <row r="286" spans="1:20" ht="15">
       <c r="A286" s="31"/>
       <c r="B286" s="32"/>
       <c r="C286" s="31"/>
@@ -39622,7 +39622,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="287" spans="1:20">
+    <row r="287" spans="1:20" ht="15">
       <c r="A287" s="31"/>
       <c r="B287" s="32"/>
       <c r="C287" s="31"/>
@@ -39660,7 +39660,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="288" spans="1:20">
+    <row r="288" spans="1:20" ht="15">
       <c r="A288" s="31"/>
       <c r="B288" s="32"/>
       <c r="C288" s="31"/>
@@ -39698,7 +39698,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="289" spans="1:20">
+    <row r="289" spans="1:20" ht="15">
       <c r="A289" s="31"/>
       <c r="B289" s="32"/>
       <c r="C289" s="31"/>
@@ -39736,7 +39736,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="290" spans="1:20">
+    <row r="290" spans="1:20" ht="15">
       <c r="A290" s="31"/>
       <c r="B290" s="32"/>
       <c r="C290" s="31"/>
@@ -39774,7 +39774,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="291" spans="1:20">
+    <row r="291" spans="1:20" ht="15">
       <c r="A291" s="31"/>
       <c r="B291" s="32"/>
       <c r="C291" s="31"/>
@@ -39812,7 +39812,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="292" spans="1:20">
+    <row r="292" spans="1:20" ht="15">
       <c r="A292" s="31"/>
       <c r="B292" s="32"/>
       <c r="C292" s="31"/>
@@ -39850,7 +39850,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="293" spans="1:20">
+    <row r="293" spans="1:20" ht="15">
       <c r="A293" s="31"/>
       <c r="B293" s="32"/>
       <c r="C293" s="31"/>
@@ -39888,7 +39888,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="294" spans="1:20">
+    <row r="294" spans="1:20" ht="15">
       <c r="A294" s="31"/>
       <c r="B294" s="32"/>
       <c r="C294" s="31"/>
@@ -39926,7 +39926,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="295" spans="1:20">
+    <row r="295" spans="1:20" ht="15">
       <c r="A295" s="31"/>
       <c r="B295" s="32"/>
       <c r="C295" s="31"/>
@@ -39964,7 +39964,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="296" spans="1:20">
+    <row r="296" spans="1:20" ht="15">
       <c r="A296" s="31"/>
       <c r="B296" s="32"/>
       <c r="C296" s="31"/>
@@ -40002,7 +40002,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="297" spans="1:20">
+    <row r="297" spans="1:20" ht="15">
       <c r="A297" s="31"/>
       <c r="B297" s="32"/>
       <c r="C297" s="31"/>
@@ -40040,7 +40040,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="298" spans="1:20">
+    <row r="298" spans="1:20" ht="15">
       <c r="A298" s="31"/>
       <c r="B298" s="32"/>
       <c r="C298" s="31"/>
@@ -40078,7 +40078,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="299" spans="1:20">
+    <row r="299" spans="1:20" ht="15">
       <c r="A299" s="31"/>
       <c r="B299" s="32"/>
       <c r="C299" s="31"/>
@@ -40116,7 +40116,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="300" spans="1:20">
+    <row r="300" spans="1:20" ht="15">
       <c r="A300" s="31"/>
       <c r="B300" s="32"/>
       <c r="C300" s="31"/>
@@ -40154,7 +40154,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="301" spans="1:20">
+    <row r="301" spans="1:20" ht="15">
       <c r="A301" s="31"/>
       <c r="B301" s="32"/>
       <c r="C301" s="31"/>
@@ -40192,7 +40192,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="302" spans="1:20">
+    <row r="302" spans="1:20" ht="15">
       <c r="A302" s="31"/>
       <c r="B302" s="32"/>
       <c r="C302" s="31"/>
@@ -40230,7 +40230,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="303" spans="1:20">
+    <row r="303" spans="1:20" ht="15">
       <c r="A303" s="31"/>
       <c r="B303" s="32"/>
       <c r="C303" s="31"/>
@@ -40268,7 +40268,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="304" spans="1:20">
+    <row r="304" spans="1:20" ht="15">
       <c r="A304" s="31"/>
       <c r="B304" s="32"/>
       <c r="C304" s="31"/>
@@ -40306,7 +40306,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="305" spans="1:20">
+    <row r="305" spans="1:20" ht="15">
       <c r="A305" s="31"/>
       <c r="B305" s="32"/>
       <c r="C305" s="31"/>
@@ -40344,7 +40344,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="306" spans="1:20">
+    <row r="306" spans="1:20" ht="15">
       <c r="A306" s="31"/>
       <c r="B306" s="32"/>
       <c r="C306" s="31"/>
@@ -40382,7 +40382,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="307" spans="1:20">
+    <row r="307" spans="1:20" ht="15">
       <c r="A307" s="31"/>
       <c r="B307" s="32"/>
       <c r="C307" s="31"/>
@@ -40420,7 +40420,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="308" spans="1:20">
+    <row r="308" spans="1:20" ht="15">
       <c r="A308" s="31"/>
       <c r="B308" s="32"/>
       <c r="C308" s="31"/>
@@ -40458,7 +40458,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="309" spans="1:20">
+    <row r="309" spans="1:20" ht="15">
       <c r="A309" s="31"/>
       <c r="B309" s="32"/>
       <c r="C309" s="31"/>
@@ -40496,7 +40496,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="310" spans="1:20">
+    <row r="310" spans="1:20" ht="15">
       <c r="A310" s="31"/>
       <c r="B310" s="32"/>
       <c r="C310" s="31"/>
@@ -40534,7 +40534,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="311" spans="1:20">
+    <row r="311" spans="1:20" ht="15">
       <c r="A311" s="31"/>
       <c r="B311" s="32"/>
       <c r="C311" s="31"/>
@@ -40572,7 +40572,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="312" spans="1:20">
+    <row r="312" spans="1:20" ht="15">
       <c r="A312" s="31"/>
       <c r="B312" s="32"/>
       <c r="C312" s="31"/>
@@ -40610,7 +40610,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="313" spans="1:20">
+    <row r="313" spans="1:20" ht="15">
       <c r="A313" s="31"/>
       <c r="B313" s="32"/>
       <c r="C313" s="31"/>
@@ -40648,7 +40648,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="314" spans="1:20">
+    <row r="314" spans="1:20" ht="15">
       <c r="A314" s="31"/>
       <c r="B314" s="32"/>
       <c r="C314" s="31"/>
@@ -40686,7 +40686,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="315" spans="1:20">
+    <row r="315" spans="1:20" ht="15">
       <c r="A315" s="31"/>
       <c r="B315" s="32"/>
       <c r="C315" s="31"/>
@@ -40724,7 +40724,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="316" spans="1:20">
+    <row r="316" spans="1:20" ht="15">
       <c r="A316" s="31"/>
       <c r="B316" s="32"/>
       <c r="C316" s="31"/>
@@ -40762,7 +40762,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="317" spans="1:20">
+    <row r="317" spans="1:20" ht="15">
       <c r="A317" s="31"/>
       <c r="B317" s="32"/>
       <c r="C317" s="31"/>
@@ -40800,7 +40800,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="318" spans="1:20">
+    <row r="318" spans="1:20" ht="15">
       <c r="A318" s="31"/>
       <c r="B318" s="32"/>
       <c r="C318" s="31"/>
@@ -40838,7 +40838,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="319" spans="1:20">
+    <row r="319" spans="1:20" ht="15">
       <c r="A319" s="31"/>
       <c r="B319" s="32"/>
       <c r="C319" s="31"/>
@@ -40876,7 +40876,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="320" spans="1:20">
+    <row r="320" spans="1:20" ht="15">
       <c r="A320" s="31"/>
       <c r="B320" s="32"/>
       <c r="C320" s="31"/>
@@ -40914,7 +40914,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="321" spans="1:20">
+    <row r="321" spans="1:20" ht="15">
       <c r="A321" s="31"/>
       <c r="B321" s="32"/>
       <c r="C321" s="31"/>
@@ -40952,7 +40952,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="322" spans="1:20">
+    <row r="322" spans="1:20" ht="15">
       <c r="A322" s="31"/>
       <c r="B322" s="32"/>
       <c r="C322" s="31"/>
@@ -40990,7 +40990,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="323" spans="1:20">
+    <row r="323" spans="1:20" ht="15">
       <c r="A323" s="31"/>
       <c r="B323" s="32"/>
       <c r="C323" s="31"/>
@@ -41028,7 +41028,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="324" spans="1:20">
+    <row r="324" spans="1:20" ht="15">
       <c r="A324" s="31"/>
       <c r="B324" s="32"/>
       <c r="C324" s="31"/>
@@ -41066,7 +41066,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="325" spans="1:20">
+    <row r="325" spans="1:20" ht="15">
       <c r="A325" s="31"/>
       <c r="B325" s="32"/>
       <c r="C325" s="31"/>
@@ -41104,7 +41104,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="326" spans="1:20">
+    <row r="326" spans="1:20" ht="15">
       <c r="A326" s="31"/>
       <c r="B326" s="32"/>
       <c r="C326" s="31"/>
@@ -41142,7 +41142,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="327" spans="1:20">
+    <row r="327" spans="1:20" ht="15">
       <c r="A327" s="31"/>
       <c r="B327" s="32"/>
       <c r="C327" s="31"/>
@@ -41180,7 +41180,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="328" spans="1:20">
+    <row r="328" spans="1:20" ht="15">
       <c r="A328" s="31"/>
       <c r="B328" s="32"/>
       <c r="C328" s="31"/>
@@ -41218,7 +41218,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="329" spans="1:20">
+    <row r="329" spans="1:20" ht="15">
       <c r="A329" s="31"/>
       <c r="B329" s="32"/>
       <c r="C329" s="31"/>
@@ -41256,7 +41256,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="330" spans="1:20">
+    <row r="330" spans="1:20" ht="15">
       <c r="A330" s="31"/>
       <c r="B330" s="32"/>
       <c r="C330" s="31"/>
@@ -41294,7 +41294,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="331" spans="1:20">
+    <row r="331" spans="1:20" ht="15">
       <c r="A331" s="31"/>
       <c r="B331" s="32"/>
       <c r="C331" s="31"/>
@@ -41332,7 +41332,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="332" spans="1:20">
+    <row r="332" spans="1:20" ht="15">
       <c r="A332" s="31"/>
       <c r="B332" s="32"/>
       <c r="C332" s="31"/>
@@ -41370,7 +41370,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="333" spans="1:20">
+    <row r="333" spans="1:20" ht="15">
       <c r="A333" s="31"/>
       <c r="B333" s="32"/>
       <c r="C333" s="31"/>
@@ -41408,7 +41408,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="334" spans="1:20">
+    <row r="334" spans="1:20" ht="15">
       <c r="A334" s="31"/>
       <c r="B334" s="32"/>
       <c r="C334" s="31"/>
@@ -41446,7 +41446,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="335" spans="1:20">
+    <row r="335" spans="1:20" ht="15">
       <c r="A335" s="31"/>
       <c r="B335" s="32"/>
       <c r="C335" s="31"/>
@@ -41484,7 +41484,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="336" spans="1:20">
+    <row r="336" spans="1:20" ht="15">
       <c r="A336" s="31"/>
       <c r="B336" s="32"/>
       <c r="C336" s="31"/>
@@ -41522,7 +41522,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="337" spans="1:20">
+    <row r="337" spans="1:20" ht="15">
       <c r="A337" s="31"/>
       <c r="B337" s="32"/>
       <c r="C337" s="31"/>
@@ -41560,7 +41560,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="338" spans="1:20">
+    <row r="338" spans="1:20" ht="15">
       <c r="A338" s="31"/>
       <c r="B338" s="32"/>
       <c r="C338" s="31"/>
@@ -41598,7 +41598,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="339" spans="1:20">
+    <row r="339" spans="1:20" ht="15">
       <c r="A339" s="31"/>
       <c r="B339" s="32"/>
       <c r="C339" s="31"/>
@@ -41636,7 +41636,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="340" spans="1:20">
+    <row r="340" spans="1:20" ht="15">
       <c r="A340" s="31"/>
       <c r="B340" s="32"/>
       <c r="C340" s="31"/>
@@ -41674,7 +41674,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="341" spans="1:20">
+    <row r="341" spans="1:20" ht="15">
       <c r="A341" s="31"/>
       <c r="B341" s="32"/>
       <c r="C341" s="31"/>
@@ -41712,7 +41712,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="342" spans="1:20">
+    <row r="342" spans="1:20" ht="15">
       <c r="A342" s="31"/>
       <c r="B342" s="32"/>
       <c r="C342" s="31"/>
@@ -41750,7 +41750,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="343" spans="1:20">
+    <row r="343" spans="1:20" ht="15">
       <c r="A343" s="31"/>
       <c r="B343" s="32"/>
       <c r="C343" s="31"/>
@@ -41788,7 +41788,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="344" spans="1:20">
+    <row r="344" spans="1:20" ht="15">
       <c r="A344" s="31"/>
       <c r="B344" s="32"/>
       <c r="C344" s="31"/>
@@ -41826,7 +41826,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="345" spans="1:20">
+    <row r="345" spans="1:20" ht="15">
       <c r="A345" s="31"/>
       <c r="B345" s="32"/>
       <c r="C345" s="31"/>
@@ -41864,7 +41864,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="346" spans="1:20">
+    <row r="346" spans="1:20" ht="15">
       <c r="A346" s="31"/>
       <c r="B346" s="32"/>
       <c r="C346" s="31"/>
@@ -41902,7 +41902,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="347" spans="1:20">
+    <row r="347" spans="1:20" ht="15">
       <c r="A347" s="31"/>
       <c r="B347" s="32"/>
       <c r="C347" s="31"/>
@@ -41940,7 +41940,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="348" spans="1:20">
+    <row r="348" spans="1:20" ht="15">
       <c r="A348" s="31"/>
       <c r="B348" s="32"/>
       <c r="C348" s="31"/>
@@ -41978,7 +41978,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="349" spans="1:20">
+    <row r="349" spans="1:20" ht="15">
       <c r="A349" s="31"/>
       <c r="B349" s="32"/>
       <c r="C349" s="31"/>
@@ -42016,7 +42016,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="350" spans="1:20">
+    <row r="350" spans="1:20" ht="15">
       <c r="A350" s="31"/>
       <c r="B350" s="32"/>
       <c r="C350" s="31"/>
@@ -42054,7 +42054,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="351" spans="1:20">
+    <row r="351" spans="1:20" ht="15">
       <c r="A351" s="31"/>
       <c r="B351" s="32"/>
       <c r="C351" s="31"/>
@@ -42092,7 +42092,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="352" spans="1:20">
+    <row r="352" spans="1:20" ht="15">
       <c r="A352" s="31"/>
       <c r="B352" s="32"/>
       <c r="C352" s="31"/>
@@ -42130,7 +42130,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="353" spans="1:20">
+    <row r="353" spans="1:20" ht="15">
       <c r="A353" s="31"/>
       <c r="B353" s="32"/>
       <c r="C353" s="31"/>
@@ -42168,7 +42168,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="354" spans="1:20">
+    <row r="354" spans="1:20" ht="15">
       <c r="A354" s="31"/>
       <c r="B354" s="32"/>
       <c r="C354" s="31"/>
@@ -42206,7 +42206,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="355" spans="1:20">
+    <row r="355" spans="1:20" ht="15">
       <c r="A355" s="31"/>
       <c r="B355" s="32"/>
       <c r="C355" s="31"/>
@@ -42244,7 +42244,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="356" spans="1:20">
+    <row r="356" spans="1:20" ht="15">
       <c r="A356" s="31"/>
       <c r="B356" s="32"/>
       <c r="C356" s="31"/>
@@ -42282,7 +42282,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="357" spans="1:20">
+    <row r="357" spans="1:20" ht="15">
       <c r="A357" s="31"/>
       <c r="B357" s="32"/>
       <c r="C357" s="31"/>
@@ -42320,7 +42320,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="358" spans="1:20">
+    <row r="358" spans="1:20" ht="15">
       <c r="A358" s="31"/>
       <c r="B358" s="32"/>
       <c r="C358" s="31"/>
@@ -42358,7 +42358,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="359" spans="1:20">
+    <row r="359" spans="1:20" ht="15">
       <c r="A359" s="31"/>
       <c r="B359" s="32"/>
       <c r="C359" s="31"/>
@@ -42396,7 +42396,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="360" spans="1:20">
+    <row r="360" spans="1:20" ht="15">
       <c r="A360" s="31"/>
       <c r="B360" s="32"/>
       <c r="C360" s="31"/>
@@ -42434,7 +42434,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="361" spans="1:20">
+    <row r="361" spans="1:20" ht="15">
       <c r="A361" s="31"/>
       <c r="B361" s="32"/>
       <c r="C361" s="31"/>
@@ -42472,7 +42472,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="362" spans="1:20">
+    <row r="362" spans="1:20" ht="15">
       <c r="A362" s="31"/>
       <c r="B362" s="32"/>
       <c r="C362" s="31"/>
@@ -42510,7 +42510,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="363" spans="1:20">
+    <row r="363" spans="1:20" ht="15">
       <c r="A363" s="31"/>
       <c r="B363" s="32"/>
       <c r="C363" s="31"/>
@@ -42548,7 +42548,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="364" spans="1:20">
+    <row r="364" spans="1:20" ht="15">
       <c r="A364" s="31"/>
       <c r="B364" s="32"/>
       <c r="C364" s="31"/>
@@ -42586,7 +42586,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="365" spans="1:20">
+    <row r="365" spans="1:20" ht="15">
       <c r="A365" s="31"/>
       <c r="B365" s="32"/>
       <c r="C365" s="31"/>
@@ -42624,7 +42624,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="366" spans="1:20">
+    <row r="366" spans="1:20" ht="15">
       <c r="A366" s="31"/>
       <c r="B366" s="32"/>
       <c r="C366" s="31"/>
@@ -42662,7 +42662,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="367" spans="1:20">
+    <row r="367" spans="1:20" ht="15">
       <c r="A367" s="31"/>
       <c r="B367" s="32"/>
       <c r="C367" s="31"/>
@@ -42700,7 +42700,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="368" spans="1:20">
+    <row r="368" spans="1:20" ht="15">
       <c r="A368" s="31"/>
       <c r="B368" s="32"/>
       <c r="C368" s="31"/>
@@ -42738,7 +42738,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="369" spans="1:20">
+    <row r="369" spans="1:20" ht="15">
       <c r="A369" s="31"/>
       <c r="B369" s="32"/>
       <c r="C369" s="31"/>
@@ -42776,7 +42776,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="370" spans="1:20">
+    <row r="370" spans="1:20" ht="15">
       <c r="A370" s="31"/>
       <c r="B370" s="32"/>
       <c r="C370" s="31"/>
@@ -42814,7 +42814,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="371" spans="1:20">
+    <row r="371" spans="1:20" ht="15">
       <c r="A371" s="31"/>
       <c r="B371" s="32"/>
       <c r="C371" s="31"/>
@@ -42852,7 +42852,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="372" spans="1:20">
+    <row r="372" spans="1:20" ht="15">
       <c r="A372" s="31"/>
       <c r="B372" s="32"/>
       <c r="C372" s="31"/>
@@ -42890,7 +42890,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="373" spans="1:20">
+    <row r="373" spans="1:20" ht="15">
       <c r="A373" s="31"/>
       <c r="B373" s="32"/>
       <c r="C373" s="31"/>
@@ -42928,7 +42928,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="374" spans="1:20">
+    <row r="374" spans="1:20" ht="15">
       <c r="A374" s="31"/>
       <c r="B374" s="32"/>
       <c r="C374" s="31"/>
@@ -42966,7 +42966,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="375" spans="1:20">
+    <row r="375" spans="1:20" ht="15">
       <c r="A375" s="31"/>
       <c r="B375" s="32"/>
       <c r="C375" s="31"/>
@@ -43004,7 +43004,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="376" spans="1:20">
+    <row r="376" spans="1:20" ht="15">
       <c r="A376" s="31"/>
       <c r="B376" s="32"/>
       <c r="C376" s="31"/>
@@ -43042,7 +43042,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="377" spans="1:20">
+    <row r="377" spans="1:20" ht="15">
       <c r="A377" s="31"/>
       <c r="B377" s="32"/>
       <c r="C377" s="31"/>
@@ -43080,7 +43080,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="378" spans="1:20">
+    <row r="378" spans="1:20" ht="15">
       <c r="A378" s="31"/>
       <c r="B378" s="32"/>
       <c r="C378" s="31"/>
@@ -43118,7 +43118,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="379" spans="1:20">
+    <row r="379" spans="1:20" ht="15">
       <c r="A379" s="31"/>
       <c r="B379" s="32"/>
       <c r="C379" s="31"/>
@@ -43156,7 +43156,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="380" spans="1:20">
+    <row r="380" spans="1:20" ht="15">
       <c r="A380" s="31"/>
       <c r="B380" s="32"/>
       <c r="C380" s="31"/>
@@ -43194,7 +43194,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="381" spans="1:20">
+    <row r="381" spans="1:20" ht="15">
       <c r="A381" s="31"/>
       <c r="B381" s="32"/>
       <c r="C381" s="31"/>
@@ -43232,7 +43232,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="382" spans="1:20">
+    <row r="382" spans="1:20" ht="15">
       <c r="A382" s="31"/>
       <c r="B382" s="32"/>
       <c r="C382" s="31"/>
@@ -43270,7 +43270,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="383" spans="1:20">
+    <row r="383" spans="1:20" ht="15">
       <c r="A383" s="31"/>
       <c r="B383" s="32"/>
       <c r="C383" s="31"/>
@@ -43308,7 +43308,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="384" spans="1:20">
+    <row r="384" spans="1:20" ht="15">
       <c r="A384" s="31"/>
       <c r="B384" s="32"/>
       <c r="C384" s="31"/>
@@ -43346,7 +43346,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="385" spans="1:20">
+    <row r="385" spans="1:20" ht="15">
       <c r="A385" s="31"/>
       <c r="B385" s="32"/>
       <c r="C385" s="31"/>
@@ -43384,7 +43384,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="386" spans="1:20">
+    <row r="386" spans="1:20" ht="15">
       <c r="A386" s="31"/>
       <c r="B386" s="32"/>
       <c r="C386" s="31"/>
@@ -43422,7 +43422,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="387" spans="1:20">
+    <row r="387" spans="1:20" ht="15">
       <c r="A387" s="31"/>
       <c r="B387" s="32"/>
       <c r="C387" s="31"/>
@@ -43460,7 +43460,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="388" spans="1:20">
+    <row r="388" spans="1:20" ht="15">
       <c r="A388" s="31"/>
       <c r="B388" s="32"/>
       <c r="C388" s="31"/>
@@ -43498,7 +43498,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="389" spans="1:20">
+    <row r="389" spans="1:20" ht="15">
       <c r="A389" s="31"/>
       <c r="B389" s="32"/>
       <c r="C389" s="31"/>
@@ -43536,7 +43536,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="390" spans="1:20">
+    <row r="390" spans="1:20" ht="15">
       <c r="A390" s="31"/>
       <c r="B390" s="32"/>
       <c r="C390" s="31"/>
@@ -43574,7 +43574,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="391" spans="1:20">
+    <row r="391" spans="1:20" ht="15">
       <c r="A391" s="31"/>
       <c r="B391" s="32"/>
       <c r="C391" s="31"/>
@@ -43612,7 +43612,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="392" spans="1:20">
+    <row r="392" spans="1:20" ht="15">
       <c r="A392" s="31"/>
       <c r="B392" s="32"/>
       <c r="C392" s="31"/>
@@ -43650,7 +43650,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="393" spans="1:20">
+    <row r="393" spans="1:20" ht="15">
       <c r="A393" s="31"/>
       <c r="B393" s="32"/>
       <c r="C393" s="31"/>
@@ -43688,7 +43688,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="394" spans="1:20">
+    <row r="394" spans="1:20" ht="15">
       <c r="A394" s="31"/>
       <c r="B394" s="32"/>
       <c r="C394" s="31"/>
@@ -43726,7 +43726,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="395" spans="1:20">
+    <row r="395" spans="1:20" ht="15">
       <c r="A395" s="31"/>
       <c r="B395" s="32"/>
       <c r="C395" s="31"/>
@@ -43764,7 +43764,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="396" spans="1:20">
+    <row r="396" spans="1:20" ht="15">
       <c r="A396" s="31"/>
       <c r="B396" s="32"/>
       <c r="C396" s="31"/>
@@ -43802,7 +43802,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="397" spans="1:20">
+    <row r="397" spans="1:20" ht="15">
       <c r="A397" s="31"/>
       <c r="B397" s="32"/>
       <c r="C397" s="31"/>
@@ -43840,7 +43840,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="398" spans="1:20">
+    <row r="398" spans="1:20" ht="15">
       <c r="A398" s="31"/>
       <c r="B398" s="32"/>
       <c r="C398" s="31"/>
@@ -43878,7 +43878,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="399" spans="1:20">
+    <row r="399" spans="1:20" ht="15">
       <c r="A399" s="31"/>
       <c r="B399" s="32"/>
       <c r="C399" s="31"/>
@@ -43916,7 +43916,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="400" spans="1:20">
+    <row r="400" spans="1:20" ht="15">
       <c r="A400" s="31"/>
       <c r="B400" s="32"/>
       <c r="C400" s="31"/>
@@ -43954,7 +43954,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="401" spans="1:20">
+    <row r="401" spans="1:20" ht="15">
       <c r="A401" s="31"/>
       <c r="B401" s="32"/>
       <c r="C401" s="31"/>
@@ -43992,7 +43992,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="402" spans="1:20">
+    <row r="402" spans="1:20" ht="15">
       <c r="A402" s="31"/>
       <c r="B402" s="32"/>
       <c r="C402" s="31"/>
@@ -44030,7 +44030,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="403" spans="1:20">
+    <row r="403" spans="1:20" ht="15">
       <c r="A403" s="31"/>
       <c r="B403" s="32"/>
       <c r="C403" s="31"/>
@@ -44068,7 +44068,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="404" spans="1:20">
+    <row r="404" spans="1:20" ht="15">
       <c r="A404" s="31"/>
       <c r="B404" s="32"/>
       <c r="C404" s="31"/>
@@ -44106,7 +44106,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="405" spans="1:20">
+    <row r="405" spans="1:20" ht="15">
       <c r="A405" s="31"/>
       <c r="B405" s="32"/>
       <c r="C405" s="31"/>
@@ -44144,7 +44144,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="406" spans="1:20">
+    <row r="406" spans="1:20" ht="15">
       <c r="A406" s="31"/>
       <c r="B406" s="32"/>
       <c r="C406" s="31"/>
@@ -44182,7 +44182,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="407" spans="1:20">
+    <row r="407" spans="1:20" ht="15">
       <c r="A407" s="31"/>
       <c r="B407" s="32"/>
       <c r="C407" s="31"/>
@@ -44220,7 +44220,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="408" spans="1:20">
+    <row r="408" spans="1:20" ht="15">
       <c r="A408" s="31"/>
       <c r="B408" s="32"/>
       <c r="C408" s="31"/>
@@ -44258,7 +44258,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="409" spans="1:20">
+    <row r="409" spans="1:20" ht="15">
       <c r="A409" s="31"/>
       <c r="B409" s="32"/>
       <c r="C409" s="31"/>
@@ -44296,7 +44296,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="410" spans="1:20">
+    <row r="410" spans="1:20" ht="15">
       <c r="A410" s="31"/>
       <c r="B410" s="32"/>
       <c r="C410" s="31"/>
@@ -44334,7 +44334,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="411" spans="1:20">
+    <row r="411" spans="1:20" ht="15">
       <c r="A411" s="31"/>
       <c r="B411" s="32"/>
       <c r="C411" s="31"/>
@@ -44372,7 +44372,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="412" spans="1:20">
+    <row r="412" spans="1:20" ht="15">
       <c r="A412" s="31"/>
       <c r="B412" s="32"/>
       <c r="C412" s="31"/>
@@ -44410,7 +44410,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="413" spans="1:20">
+    <row r="413" spans="1:20" ht="15">
       <c r="A413" s="31"/>
       <c r="B413" s="32"/>
       <c r="C413" s="31"/>
@@ -44448,7 +44448,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="414" spans="1:20">
+    <row r="414" spans="1:20" ht="15">
       <c r="A414" s="31"/>
       <c r="B414" s="32"/>
       <c r="C414" s="31"/>
@@ -44486,7 +44486,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="415" spans="1:20">
+    <row r="415" spans="1:20" ht="15">
       <c r="A415" s="31"/>
       <c r="B415" s="32"/>
       <c r="C415" s="31"/>
@@ -44524,7 +44524,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="416" spans="1:20">
+    <row r="416" spans="1:20" ht="15">
       <c r="A416" s="31"/>
       <c r="B416" s="32"/>
       <c r="C416" s="31"/>
@@ -44562,7 +44562,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="417" spans="1:20">
+    <row r="417" spans="1:20" ht="15">
       <c r="A417" s="31"/>
       <c r="B417" s="32"/>
       <c r="C417" s="31"/>
@@ -44600,7 +44600,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="418" spans="1:20">
+    <row r="418" spans="1:20" ht="15">
       <c r="A418" s="31"/>
       <c r="B418" s="32"/>
       <c r="C418" s="31"/>
@@ -44638,7 +44638,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="419" spans="1:20">
+    <row r="419" spans="1:20" ht="15">
       <c r="A419" s="31"/>
       <c r="B419" s="32"/>
       <c r="C419" s="31"/>
@@ -44676,7 +44676,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="420" spans="1:20">
+    <row r="420" spans="1:20" ht="15">
       <c r="A420" s="31"/>
       <c r="B420" s="32"/>
       <c r="C420" s="31"/>
@@ -44714,7 +44714,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="421" spans="1:20">
+    <row r="421" spans="1:20" ht="15">
       <c r="A421" s="31"/>
       <c r="B421" s="32"/>
       <c r="C421" s="31"/>
@@ -44752,7 +44752,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="422" spans="1:20">
+    <row r="422" spans="1:20" ht="15">
       <c r="A422" s="31"/>
       <c r="B422" s="32"/>
       <c r="C422" s="31"/>
@@ -44790,7 +44790,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="423" spans="1:20">
+    <row r="423" spans="1:20" ht="15">
       <c r="A423" s="31"/>
       <c r="B423" s="32"/>
       <c r="C423" s="31"/>
@@ -44828,7 +44828,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="424" spans="1:20">
+    <row r="424" spans="1:20" ht="15">
       <c r="A424" s="31"/>
       <c r="B424" s="32"/>
       <c r="C424" s="31"/>
@@ -44866,7 +44866,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="425" spans="1:20">
+    <row r="425" spans="1:20" ht="15">
       <c r="A425" s="31"/>
       <c r="B425" s="32"/>
       <c r="C425" s="31"/>
@@ -44904,7 +44904,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="426" spans="1:20">
+    <row r="426" spans="1:20" ht="15">
       <c r="A426" s="31"/>
       <c r="B426" s="32"/>
       <c r="C426" s="31"/>
@@ -44942,7 +44942,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="427" spans="1:20">
+    <row r="427" spans="1:20" ht="15">
       <c r="A427" s="31"/>
       <c r="B427" s="32"/>
       <c r="C427" s="31"/>
@@ -44980,7 +44980,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="428" spans="1:20">
+    <row r="428" spans="1:20" ht="15">
       <c r="A428" s="31"/>
       <c r="B428" s="32"/>
       <c r="C428" s="31"/>
@@ -45018,7 +45018,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="429" spans="1:20">
+    <row r="429" spans="1:20" ht="15">
       <c r="A429" s="31"/>
       <c r="B429" s="32"/>
       <c r="C429" s="31"/>
@@ -45056,7 +45056,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="430" spans="1:20">
+    <row r="430" spans="1:20" ht="15">
       <c r="A430" s="31"/>
       <c r="B430" s="32"/>
       <c r="C430" s="31"/>
@@ -45094,7 +45094,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="431" spans="1:20">
+    <row r="431" spans="1:20" ht="15">
       <c r="A431" s="31"/>
       <c r="B431" s="32"/>
       <c r="C431" s="31"/>
@@ -45132,7 +45132,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="432" spans="1:20">
+    <row r="432" spans="1:20" ht="15">
       <c r="A432" s="31"/>
       <c r="B432" s="32"/>
       <c r="C432" s="31"/>
@@ -45170,7 +45170,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="433" spans="1:20">
+    <row r="433" spans="1:20" ht="15">
       <c r="A433" s="31"/>
       <c r="B433" s="32"/>
       <c r="C433" s="31"/>
@@ -45208,7 +45208,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="434" spans="1:20">
+    <row r="434" spans="1:20" ht="15">
       <c r="A434" s="31"/>
       <c r="B434" s="32"/>
       <c r="C434" s="31"/>
@@ -45246,7 +45246,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="435" spans="1:20">
+    <row r="435" spans="1:20" ht="15">
       <c r="A435" s="31"/>
       <c r="B435" s="32"/>
       <c r="C435" s="31"/>
@@ -45284,7 +45284,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="436" spans="1:20">
+    <row r="436" spans="1:20" ht="15">
       <c r="A436" s="31"/>
       <c r="B436" s="32"/>
       <c r="C436" s="31"/>
@@ -45322,7 +45322,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="437" spans="1:20">
+    <row r="437" spans="1:20" ht="15">
       <c r="A437" s="31"/>
       <c r="B437" s="32"/>
       <c r="C437" s="31"/>
@@ -45360,7 +45360,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="438" spans="1:20">
+    <row r="438" spans="1:20" ht="15">
       <c r="A438" s="31"/>
       <c r="B438" s="32"/>
       <c r="C438" s="31"/>
@@ -45398,7 +45398,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="439" spans="1:20">
+    <row r="439" spans="1:20" ht="15">
       <c r="A439" s="31"/>
       <c r="B439" s="32"/>
       <c r="C439" s="31"/>
@@ -45436,7 +45436,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="440" spans="1:20">
+    <row r="440" spans="1:20" ht="15">
       <c r="A440" s="31"/>
       <c r="B440" s="32"/>
       <c r="C440" s="31"/>
@@ -45474,7 +45474,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="441" spans="1:20">
+    <row r="441" spans="1:20" ht="15">
       <c r="A441" s="31"/>
       <c r="B441" s="32"/>
       <c r="C441" s="31"/>
@@ -45512,7 +45512,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="442" spans="1:20">
+    <row r="442" spans="1:20" ht="15">
       <c r="A442" s="31"/>
       <c r="B442" s="32"/>
       <c r="C442" s="31"/>
@@ -45550,7 +45550,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="443" spans="1:20">
+    <row r="443" spans="1:20" ht="15">
       <c r="A443" s="31"/>
       <c r="B443" s="32"/>
       <c r="C443" s="31"/>
@@ -45588,7 +45588,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="444" spans="1:20">
+    <row r="444" spans="1:20" ht="15">
       <c r="A444" s="31"/>
       <c r="B444" s="32"/>
       <c r="C444" s="31"/>
@@ -45626,7 +45626,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="445" spans="1:20">
+    <row r="445" spans="1:20" ht="15">
       <c r="A445" s="31"/>
       <c r="B445" s="32"/>
       <c r="C445" s="31"/>
@@ -45664,7 +45664,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="446" spans="1:20">
+    <row r="446" spans="1:20" ht="15">
       <c r="A446" s="31"/>
       <c r="B446" s="32"/>
       <c r="C446" s="31"/>
@@ -45702,7 +45702,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="447" spans="1:20">
+    <row r="447" spans="1:20" ht="15">
       <c r="A447" s="31"/>
       <c r="B447" s="32"/>
       <c r="C447" s="31"/>
@@ -45740,7 +45740,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="448" spans="1:20">
+    <row r="448" spans="1:20" ht="15">
       <c r="A448" s="31"/>
       <c r="B448" s="32"/>
       <c r="C448" s="31"/>
@@ -45778,7 +45778,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="449" spans="1:20">
+    <row r="449" spans="1:20" ht="15">
       <c r="A449" s="31"/>
       <c r="B449" s="32"/>
       <c r="C449" s="31"/>
@@ -45816,7 +45816,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="450" spans="1:20">
+    <row r="450" spans="1:20" ht="15">
       <c r="A450" s="31"/>
       <c r="B450" s="32"/>
       <c r="C450" s="31"/>
@@ -45854,7 +45854,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="451" spans="1:20">
+    <row r="451" spans="1:20" ht="15">
       <c r="A451" s="31"/>
       <c r="B451" s="32"/>
       <c r="C451" s="31"/>
@@ -45892,7 +45892,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="452" spans="1:20">
+    <row r="452" spans="1:20" ht="15">
       <c r="A452" s="31"/>
       <c r="B452" s="32"/>
       <c r="C452" s="31"/>
@@ -45930,7 +45930,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="453" spans="1:20">
+    <row r="453" spans="1:20" ht="15">
       <c r="A453" s="31"/>
       <c r="B453" s="32"/>
       <c r="C453" s="31"/>
@@ -45968,7 +45968,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="454" spans="1:20">
+    <row r="454" spans="1:20" ht="15">
       <c r="A454" s="31"/>
       <c r="B454" s="32"/>
       <c r="C454" s="31"/>
@@ -46006,7 +46006,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="455" spans="1:20">
+    <row r="455" spans="1:20" ht="15">
       <c r="A455" s="31"/>
       <c r="B455" s="32"/>
       <c r="C455" s="31"/>
@@ -46044,7 +46044,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="456" spans="1:20">
+    <row r="456" spans="1:20" ht="15">
       <c r="A456" s="31"/>
       <c r="B456" s="32"/>
       <c r="C456" s="31"/>
@@ -46082,7 +46082,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="457" spans="1:20">
+    <row r="457" spans="1:20" ht="15">
       <c r="A457" s="31"/>
       <c r="B457" s="32"/>
       <c r="C457" s="31"/>
@@ -46120,7 +46120,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="458" spans="1:20">
+    <row r="458" spans="1:20" ht="15">
       <c r="A458" s="31"/>
       <c r="B458" s="32"/>
       <c r="C458" s="31"/>
@@ -46158,7 +46158,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="459" spans="1:20">
+    <row r="459" spans="1:20" ht="15">
       <c r="A459" s="31"/>
       <c r="B459" s="32"/>
       <c r="C459" s="31"/>
@@ -46196,7 +46196,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="460" spans="1:20">
+    <row r="460" spans="1:20" ht="15">
       <c r="A460" s="31"/>
       <c r="B460" s="32"/>
       <c r="C460" s="31"/>
@@ -46234,7 +46234,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="461" spans="1:20">
+    <row r="461" spans="1:20" ht="15">
       <c r="A461" s="31"/>
       <c r="B461" s="32"/>
       <c r="C461" s="31"/>
@@ -46272,7 +46272,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="462" spans="1:20">
+    <row r="462" spans="1:20" ht="15">
       <c r="A462" s="31"/>
       <c r="B462" s="32"/>
       <c r="C462" s="31"/>
@@ -46310,7 +46310,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="463" spans="1:20">
+    <row r="463" spans="1:20" ht="15">
       <c r="A463" s="31"/>
       <c r="B463" s="32"/>
       <c r="C463" s="31"/>
@@ -46348,7 +46348,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="464" spans="1:20">
+    <row r="464" spans="1:20" ht="15">
       <c r="A464" s="31"/>
       <c r="B464" s="32"/>
       <c r="C464" s="31"/>
@@ -46386,7 +46386,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="465" spans="1:20">
+    <row r="465" spans="1:20" ht="15">
       <c r="A465" s="31"/>
       <c r="B465" s="32"/>
       <c r="C465" s="31"/>
@@ -46424,7 +46424,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="466" spans="1:20">
+    <row r="466" spans="1:20" ht="15">
       <c r="A466" s="31"/>
       <c r="B466" s="32"/>
       <c r="C466" s="31"/>
@@ -46462,7 +46462,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="467" spans="1:20">
+    <row r="467" spans="1:20" ht="15">
       <c r="A467" s="31"/>
       <c r="B467" s="32"/>
       <c r="C467" s="31"/>
@@ -46500,7 +46500,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="468" spans="1:20">
+    <row r="468" spans="1:20" ht="15">
       <c r="A468" s="31"/>
       <c r="B468" s="32"/>
       <c r="C468" s="31"/>
@@ -46538,7 +46538,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="469" spans="1:20">
+    <row r="469" spans="1:20" ht="15">
       <c r="A469" s="31"/>
       <c r="B469" s="32"/>
       <c r="C469" s="31"/>
@@ -46576,7 +46576,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="470" spans="1:20">
+    <row r="470" spans="1:20" ht="15">
       <c r="A470" s="31"/>
       <c r="B470" s="32"/>
       <c r="C470" s="31"/>
@@ -46614,7 +46614,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="471" spans="1:20">
+    <row r="471" spans="1:20" ht="15">
       <c r="A471" s="31"/>
       <c r="B471" s="32"/>
       <c r="C471" s="31"/>
@@ -46652,7 +46652,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="472" spans="1:20">
+    <row r="472" spans="1:20" ht="15">
       <c r="A472" s="31"/>
       <c r="B472" s="32"/>
       <c r="C472" s="31"/>
@@ -46690,7 +46690,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="473" spans="1:20">
+    <row r="473" spans="1:20" ht="15">
       <c r="A473" s="31"/>
       <c r="B473" s="32"/>
       <c r="C473" s="31"/>
@@ -46728,7 +46728,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="474" spans="1:20">
+    <row r="474" spans="1:20" ht="15">
       <c r="A474" s="31"/>
       <c r="B474" s="32"/>
       <c r="C474" s="31"/>
@@ -46766,7 +46766,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="475" spans="1:20">
+    <row r="475" spans="1:20" ht="15">
       <c r="A475" s="31"/>
       <c r="B475" s="32"/>
       <c r="C475" s="31"/>
@@ -46804,7 +46804,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="476" spans="1:20">
+    <row r="476" spans="1:20" ht="15">
       <c r="A476" s="31"/>
       <c r="B476" s="32"/>
       <c r="C476" s="31"/>
@@ -46842,7 +46842,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="477" spans="1:20">
+    <row r="477" spans="1:20" ht="15">
       <c r="A477" s="31"/>
       <c r="B477" s="32"/>
       <c r="C477" s="31"/>
@@ -46880,7 +46880,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="478" spans="1:20">
+    <row r="478" spans="1:20" ht="15">
       <c r="A478" s="31"/>
       <c r="B478" s="32"/>
       <c r="C478" s="31"/>
@@ -46918,7 +46918,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="479" spans="1:20">
+    <row r="479" spans="1:20" ht="15">
       <c r="A479" s="31"/>
       <c r="B479" s="32"/>
       <c r="C479" s="31"/>
@@ -46956,7 +46956,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="480" spans="1:20">
+    <row r="480" spans="1:20" ht="15">
       <c r="A480" s="31"/>
       <c r="B480" s="32"/>
       <c r="C480" s="31"/>
@@ -46994,7 +46994,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="481" spans="1:20">
+    <row r="481" spans="1:20" ht="15">
       <c r="A481" s="31"/>
       <c r="B481" s="32"/>
       <c r="C481" s="31"/>
@@ -47032,7 +47032,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="482" spans="1:20">
+    <row r="482" spans="1:20" ht="15">
       <c r="A482" s="31"/>
       <c r="B482" s="32"/>
       <c r="C482" s="31"/>
@@ -47070,7 +47070,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="483" spans="1:20">
+    <row r="483" spans="1:20" ht="15">
       <c r="A483" s="31"/>
       <c r="B483" s="32"/>
       <c r="C483" s="31"/>
@@ -47108,7 +47108,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="484" spans="1:20">
+    <row r="484" spans="1:20" ht="15">
       <c r="A484" s="31"/>
       <c r="B484" s="32"/>
       <c r="C484" s="31"/>
@@ -47146,7 +47146,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="485" spans="1:20">
+    <row r="485" spans="1:20" ht="15">
       <c r="A485" s="31"/>
       <c r="B485" s="32"/>
       <c r="C485" s="31"/>
@@ -47184,7 +47184,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="486" spans="1:20">
+    <row r="486" spans="1:20" ht="15">
       <c r="A486" s="31"/>
       <c r="B486" s="32"/>
       <c r="C486" s="31"/>
@@ -47222,7 +47222,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="487" spans="1:20">
+    <row r="487" spans="1:20" ht="15">
       <c r="A487" s="31"/>
       <c r="B487" s="32"/>
       <c r="C487" s="31"/>
@@ -47260,7 +47260,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="488" spans="1:20">
+    <row r="488" spans="1:20" ht="15">
       <c r="A488" s="31"/>
       <c r="B488" s="32"/>
       <c r="C488" s="31"/>
@@ -47298,7 +47298,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="489" spans="1:20">
+    <row r="489" spans="1:20" ht="15">
       <c r="A489" s="31"/>
       <c r="B489" s="32"/>
       <c r="C489" s="31"/>
@@ -47336,7 +47336,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="490" spans="1:20">
+    <row r="490" spans="1:20" ht="15">
       <c r="A490" s="31"/>
       <c r="B490" s="32"/>
       <c r="C490" s="31"/>
@@ -47374,7 +47374,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="491" spans="1:20">
+    <row r="491" spans="1:20" ht="15">
       <c r="A491" s="31"/>
       <c r="B491" s="32"/>
       <c r="C491" s="31"/>
@@ -47412,7 +47412,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="492" spans="1:20">
+    <row r="492" spans="1:20" ht="15">
       <c r="A492" s="31"/>
       <c r="B492" s="32"/>
       <c r="C492" s="31"/>
@@ -47450,7 +47450,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="493" spans="1:20">
+    <row r="493" spans="1:20" ht="15">
       <c r="A493" s="31"/>
       <c r="B493" s="32"/>
       <c r="C493" s="31"/>
@@ -47488,7 +47488,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="494" spans="1:20">
+    <row r="494" spans="1:20" ht="15">
       <c r="A494" s="31"/>
       <c r="B494" s="32"/>
       <c r="C494" s="31"/>
@@ -47526,7 +47526,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="495" spans="1:20">
+    <row r="495" spans="1:20" ht="15">
       <c r="A495" s="31"/>
       <c r="B495" s="32"/>
       <c r="C495" s="31"/>
@@ -47564,7 +47564,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="496" spans="1:20">
+    <row r="496" spans="1:20" ht="15">
       <c r="A496" s="31"/>
       <c r="B496" s="32"/>
       <c r="C496" s="31"/>
@@ -47602,7 +47602,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="497" spans="1:20">
+    <row r="497" spans="1:20" ht="15">
       <c r="A497" s="31"/>
       <c r="B497" s="32"/>
       <c r="C497" s="31"/>
@@ -47640,7 +47640,7 @@
         <v xml:space="preserve"> -&gt; </v>
       </c>
     </row>
-    <row r="498" spans="1:20">
+    <row r="498" spans="1:20" ht="15">
       <c r="A498" s="31"/>
       <c r="B498" s="32"/>
       <c r="C498" s="31"/>

--- a/public/data/GDM_Tracker_latest.xlsx
+++ b/public/data/GDM_Tracker_latest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nationalgridplc.sharepoint.com/sites/GRP-INT-GasBusinessEnablement-DataManagement/Public Folder/Gas Data Modernization Journey/Report Migration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3334" documentId="13_ncr:1_{52745E9B-3AA1-4770-AAD3-E6166BFC13AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA9446D7-8765-49AA-B397-8D6039EF1B4E}"/>
+  <xr:revisionPtr revIDLastSave="3384" documentId="13_ncr:1_{52745E9B-3AA1-4770-AAD3-E6166BFC13AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95950B0F-E148-4F88-8FED-DED77E15D9E0}"/>
   <bookViews>
     <workbookView minimized="1" xWindow="-21540" yWindow="4485" windowWidth="17280" windowHeight="8880" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -753,13 +753,13 @@
     <t>RPT_02_Cut Out Orders</t>
   </si>
   <si>
-    <t>QA</t>
-  </si>
-  <si>
     <t>Ready for Kushal's review</t>
   </si>
   <si>
     <t>RPT_02_Gas Trouble</t>
+  </si>
+  <si>
+    <t>QA</t>
   </si>
   <si>
     <t>PI2, S2, S3</t>
@@ -2575,7 +2575,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="140">
+  <dxfs count="141">
     <dxf>
       <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
     </dxf>
@@ -3052,6 +3052,17 @@
     </dxf>
     <dxf>
       <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7A4100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFC97A"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4352,7 +4363,7 @@
     <col min="31" max="31" width="15" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="36.28515625" customWidth="1"/>
     <col min="36" max="36" width="45.7109375" customWidth="1"/>
-    <col min="37" max="37" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="21.42578125" customWidth="1"/>
     <col min="38" max="38" width="41.5703125" customWidth="1"/>
     <col min="39" max="39" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="9.140625" bestFit="1" customWidth="1"/>
@@ -4480,7 +4491,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:40" ht="14.45" hidden="1">
+    <row r="2" spans="1:40" ht="14.45">
       <c r="A2" s="33" t="s">
         <v>40</v>
       </c>
@@ -4568,8 +4579,8 @@
       <c r="AJ2" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK2" s="72" t="str">
-        <f>IF($B2="","",IF(AND(LEFT($AJ2,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B2)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ2,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B2)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ2="Yes – needs DB Dev to fix",M2&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B2)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ2="Yes – needs PBI Dev to fix",S2&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B2)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ2="Yes – needs QA to fix",Y2&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B2)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B2)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B2)&gt;0,"",IF(AND(V2&lt;&gt;"",K2&lt;&gt;"",V2&lt;K2),"QA target is before DB Dev target",IF(AND(V2&lt;&gt;"",Q2&lt;&gt;"",V2&lt;Q2),"QA target is before PBI Dev target",IF(AND(AA2&lt;&gt;"",V2&lt;&gt;"",AA2&lt;V2),"DPO Approval target is before QA target",IF(AND(AG2&lt;&gt;"",AA2&lt;&gt;"",AG2&lt;AA2),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK2" s="72" t="str" cm="1">
+        <f t="array" ref="AK2">IF($B2="","",_xlfn.LET(_xlpm.nm,$B2,_xlpm.st,$C2,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M2,_xlpm.st="DB Dev",$M2,_xlpm.st="PBI Dev",$S2,_xlpm.st="QA",$Y2,_xlpm.st="DPO Approval",$AC2,_xlpm.st="Ready for Release in Prod",$AG2,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ2,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ2,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B2)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B2)&gt;0,"",IF(AND($V2&lt;&gt;"",$K2&lt;&gt;"",$V2&lt;$K2),"QA target is before DB Dev target",IF(AND($V2&lt;&gt;"",$Q2&lt;&gt;"",$V2&lt;$Q2),"QA target is before PBI Dev target",IF(AND($AA2&lt;&gt;"",$V2&lt;&gt;"",$AA2&lt;$V2),"DPO Approval target is before QA target",IF(AND($AG2&lt;&gt;"",$AA2&lt;&gt;"",$AG2&lt;$AA2),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v>Confirmed Deployed date is before DPO Approval target</v>
       </c>
       <c r="AL2" s="41" t="s">
@@ -4584,7 +4595,7 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:40" ht="14.45" hidden="1">
+    <row r="3" spans="1:40" ht="14.45">
       <c r="A3" s="33" t="s">
         <v>40</v>
       </c>
@@ -4672,9 +4683,9 @@
       <c r="AJ3" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK3" s="72" t="e">
-        <f>IF($B3="","",IF(AND(LEFT($AJ3,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B3)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ3,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B3)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ3="Yes – needs DB Dev to fix",M3&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B3)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ3="Yes – needs PBI Dev to fix",S3&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B3)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ3="Yes – needs QA to fix",Y3&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B3)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B3)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B3)&gt;0,"",IF(AND(V3&lt;&gt;"",K3&lt;&gt;"",V3&lt;K3),"QA target is before DB Dev target",IF(AND(V3&lt;&gt;"",Q3&lt;&gt;"",V3&lt;Q3),"QA target is before PBI Dev target",IF(AND(#REF!&lt;&gt;"",V3&lt;&gt;"",#REF!&lt;V3),"DPO Approval target is before QA target",IF(AND(AG3&lt;&gt;"",#REF!&lt;&gt;"",AG3&lt;#REF!),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
-        <v>#REF!</v>
+      <c r="AK3" s="72" t="str" cm="1">
+        <f t="array" ref="AK3">IF($B3="","",_xlfn.LET(_xlpm.nm,$B3,_xlpm.st,$C3,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M3,_xlpm.st="DB Dev",$M3,_xlpm.st="PBI Dev",$S3,_xlpm.st="QA",$Y3,_xlpm.st="DPO Approval",$AC3,_xlpm.st="Ready for Release in Prod",$AG3,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ3,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ3,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B3)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B3)&gt;0,"",IF(AND($V3&lt;&gt;"",$K3&lt;&gt;"",$V3&lt;$K3),"QA target is before DB Dev target",IF(AND($V3&lt;&gt;"",$Q3&lt;&gt;"",$V3&lt;$Q3),"QA target is before PBI Dev target",IF(AND($AA3&lt;&gt;"",$V3&lt;&gt;"",$AA3&lt;$V3),"DPO Approval target is before QA target",IF(AND($AG3&lt;&gt;"",$AA3&lt;&gt;"",$AG3&lt;$AA3),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v>Confirmed Deployed date is before DPO Approval target</v>
       </c>
       <c r="AL3" s="41" t="s">
         <v>54</v>
@@ -4688,7 +4699,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:40" ht="14.45" hidden="1">
+    <row r="4" spans="1:40" ht="14.45">
       <c r="A4" s="33" t="s">
         <v>40</v>
       </c>
@@ -4776,8 +4787,8 @@
       <c r="AJ4" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK4" s="72" t="str">
-        <f>IF($B4="","",IF(AND(LEFT($AJ4,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B4)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ4,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B4)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ4="Yes – needs DB Dev to fix",M4&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B4)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ4="Yes – needs PBI Dev to fix",S4&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B4)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ4="Yes – needs QA to fix",Y4&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B4)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B4)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B4)&gt;0,"",IF(AND(V4&lt;&gt;"",K4&lt;&gt;"",V4&lt;K4),"QA target is before DB Dev target",IF(AND(V4&lt;&gt;"",Q4&lt;&gt;"",V4&lt;Q4),"QA target is before PBI Dev target",IF(AND(AA4&lt;&gt;"",V4&lt;&gt;"",AA4&lt;V4),"DPO Approval target is before QA target",IF(AND(AG4&lt;&gt;"",AA4&lt;&gt;"",AG4&lt;AA4),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK4" s="72" t="str" cm="1">
+        <f t="array" ref="AK4">IF($B4="","",_xlfn.LET(_xlpm.nm,$B4,_xlpm.st,$C4,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M4,_xlpm.st="DB Dev",$M4,_xlpm.st="PBI Dev",$S4,_xlpm.st="QA",$Y4,_xlpm.st="DPO Approval",$AC4,_xlpm.st="Ready for Release in Prod",$AG4,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ4,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ4,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B4)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B4)&gt;0,"",IF(AND($V4&lt;&gt;"",$K4&lt;&gt;"",$V4&lt;$K4),"QA target is before DB Dev target",IF(AND($V4&lt;&gt;"",$Q4&lt;&gt;"",$V4&lt;$Q4),"QA target is before PBI Dev target",IF(AND($AA4&lt;&gt;"",$V4&lt;&gt;"",$AA4&lt;$V4),"DPO Approval target is before QA target",IF(AND($AG4&lt;&gt;"",$AA4&lt;&gt;"",$AG4&lt;$AA4),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v>Confirmed Deployed date is before DPO Approval target</v>
       </c>
       <c r="AL4" s="41" t="s">
@@ -4792,7 +4803,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:40" ht="14.45" hidden="1">
+    <row r="5" spans="1:40" ht="14.45">
       <c r="A5" s="33" t="s">
         <v>40</v>
       </c>
@@ -4880,8 +4891,8 @@
       <c r="AJ5" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK5" s="72" t="str">
-        <f>IF($B5="","",IF(AND(LEFT($AJ5,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B5)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ5,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B5)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ5="Yes – needs DB Dev to fix",M5&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B5)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ5="Yes – needs PBI Dev to fix",S5&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B5)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ5="Yes – needs QA to fix",Y5&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B5)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B5)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B5)&gt;0,"",IF(AND(V5&lt;&gt;"",K5&lt;&gt;"",V5&lt;K5),"QA target is before DB Dev target",IF(AND(V5&lt;&gt;"",Q5&lt;&gt;"",V5&lt;Q5),"QA target is before PBI Dev target",IF(AND(AA5&lt;&gt;"",V5&lt;&gt;"",AA5&lt;V5),"DPO Approval target is before QA target",IF(AND(AG5&lt;&gt;"",AA5&lt;&gt;"",AG5&lt;AA5),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK5" s="72" t="str" cm="1">
+        <f t="array" ref="AK5">IF($B5="","",_xlfn.LET(_xlpm.nm,$B5,_xlpm.st,$C5,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M5,_xlpm.st="DB Dev",$M5,_xlpm.st="PBI Dev",$S5,_xlpm.st="QA",$Y5,_xlpm.st="DPO Approval",$AC5,_xlpm.st="Ready for Release in Prod",$AG5,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ5,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ5,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B5)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B5)&gt;0,"",IF(AND($V5&lt;&gt;"",$K5&lt;&gt;"",$V5&lt;$K5),"QA target is before DB Dev target",IF(AND($V5&lt;&gt;"",$Q5&lt;&gt;"",$V5&lt;$Q5),"QA target is before PBI Dev target",IF(AND($AA5&lt;&gt;"",$V5&lt;&gt;"",$AA5&lt;$V5),"DPO Approval target is before QA target",IF(AND($AG5&lt;&gt;"",$AA5&lt;&gt;"",$AG5&lt;$AA5),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v>Confirmed Deployed date is before DPO Approval target</v>
       </c>
       <c r="AL5" s="41" t="s">
@@ -4896,7 +4907,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:40" ht="14.45" hidden="1">
+    <row r="6" spans="1:40" ht="14.45">
       <c r="A6" s="33" t="s">
         <v>40</v>
       </c>
@@ -4958,7 +4969,10 @@
       <c r="AH6" s="39"/>
       <c r="AI6" s="33"/>
       <c r="AJ6" s="40"/>
-      <c r="AK6" s="47"/>
+      <c r="AK6" s="47" t="str" cm="1">
+        <f t="array" ref="AK6">IF($B6="","",_xlfn.LET(_xlpm.nm,$B6,_xlpm.st,$C6,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M6,_xlpm.st="DB Dev",$M6,_xlpm.st="PBI Dev",$S6,_xlpm.st="QA",$Y6,_xlpm.st="DPO Approval",$AC6,_xlpm.st="Ready for Release in Prod",$AG6,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ6,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ6,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B6)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B6)&gt;0,"",IF(AND($V6&lt;&gt;"",$K6&lt;&gt;"",$V6&lt;$K6),"QA target is before DB Dev target",IF(AND($V6&lt;&gt;"",$Q6&lt;&gt;"",$V6&lt;$Q6),"QA target is before PBI Dev target",IF(AND($AA6&lt;&gt;"",$V6&lt;&gt;"",$AA6&lt;$V6),"DPO Approval target is before QA target",IF(AND($AG6&lt;&gt;"",$AA6&lt;&gt;"",$AG6&lt;$AA6),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL6" s="41"/>
       <c r="AM6" s="31" t="str" cm="1">
         <f t="array" ref="AM6">_xlfn.LET(_xlpm.rep,$B6,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -4969,7 +4983,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:40" ht="14.45" hidden="1">
+    <row r="7" spans="1:40" ht="14.45">
       <c r="A7" s="33" t="s">
         <v>40</v>
       </c>
@@ -5031,7 +5045,10 @@
       <c r="AH7" s="39"/>
       <c r="AI7" s="33"/>
       <c r="AJ7" s="40"/>
-      <c r="AK7" s="47"/>
+      <c r="AK7" s="47" t="str" cm="1">
+        <f t="array" ref="AK7">IF($B7="","",_xlfn.LET(_xlpm.nm,$B7,_xlpm.st,$C7,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M7,_xlpm.st="DB Dev",$M7,_xlpm.st="PBI Dev",$S7,_xlpm.st="QA",$Y7,_xlpm.st="DPO Approval",$AC7,_xlpm.st="Ready for Release in Prod",$AG7,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ7,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ7,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B7)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B7)&gt;0,"",IF(AND($V7&lt;&gt;"",$K7&lt;&gt;"",$V7&lt;$K7),"QA target is before DB Dev target",IF(AND($V7&lt;&gt;"",$Q7&lt;&gt;"",$V7&lt;$Q7),"QA target is before PBI Dev target",IF(AND($AA7&lt;&gt;"",$V7&lt;&gt;"",$AA7&lt;$V7),"DPO Approval target is before QA target",IF(AND($AG7&lt;&gt;"",$AA7&lt;&gt;"",$AG7&lt;$AA7),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL7" s="41"/>
       <c r="AM7" s="31" t="str" cm="1">
         <f t="array" ref="AM7">_xlfn.LET(_xlpm.rep,$B7,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -5042,7 +5059,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:40" ht="14.45" hidden="1">
+    <row r="8" spans="1:40" ht="14.45">
       <c r="A8" s="33" t="s">
         <v>40</v>
       </c>
@@ -5104,7 +5121,10 @@
       <c r="AH8" s="39"/>
       <c r="AI8" s="33"/>
       <c r="AJ8" s="40"/>
-      <c r="AK8" s="47"/>
+      <c r="AK8" s="47" t="str" cm="1">
+        <f t="array" ref="AK8">IF($B8="","",_xlfn.LET(_xlpm.nm,$B8,_xlpm.st,$C8,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M8,_xlpm.st="DB Dev",$M8,_xlpm.st="PBI Dev",$S8,_xlpm.st="QA",$Y8,_xlpm.st="DPO Approval",$AC8,_xlpm.st="Ready for Release in Prod",$AG8,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ8,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ8,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B8)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B8)&gt;0,"",IF(AND($V8&lt;&gt;"",$K8&lt;&gt;"",$V8&lt;$K8),"QA target is before DB Dev target",IF(AND($V8&lt;&gt;"",$Q8&lt;&gt;"",$V8&lt;$Q8),"QA target is before PBI Dev target",IF(AND($AA8&lt;&gt;"",$V8&lt;&gt;"",$AA8&lt;$V8),"DPO Approval target is before QA target",IF(AND($AG8&lt;&gt;"",$AA8&lt;&gt;"",$AG8&lt;$AA8),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL8" s="41"/>
       <c r="AM8" s="31" t="str" cm="1">
         <f t="array" ref="AM8">_xlfn.LET(_xlpm.rep,$B8,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -5115,7 +5135,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:40" ht="14.45" hidden="1">
+    <row r="9" spans="1:40" ht="14.45">
       <c r="A9" s="33" t="s">
         <v>40</v>
       </c>
@@ -5177,7 +5197,10 @@
       <c r="AH9" s="39"/>
       <c r="AI9" s="33"/>
       <c r="AJ9" s="40"/>
-      <c r="AK9" s="47"/>
+      <c r="AK9" s="47" t="str" cm="1">
+        <f t="array" ref="AK9">IF($B9="","",_xlfn.LET(_xlpm.nm,$B9,_xlpm.st,$C9,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M9,_xlpm.st="DB Dev",$M9,_xlpm.st="PBI Dev",$S9,_xlpm.st="QA",$Y9,_xlpm.st="DPO Approval",$AC9,_xlpm.st="Ready for Release in Prod",$AG9,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ9,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ9,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B9)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B9)&gt;0,"",IF(AND($V9&lt;&gt;"",$K9&lt;&gt;"",$V9&lt;$K9),"QA target is before DB Dev target",IF(AND($V9&lt;&gt;"",$Q9&lt;&gt;"",$V9&lt;$Q9),"QA target is before PBI Dev target",IF(AND($AA9&lt;&gt;"",$V9&lt;&gt;"",$AA9&lt;$V9),"DPO Approval target is before QA target",IF(AND($AG9&lt;&gt;"",$AA9&lt;&gt;"",$AG9&lt;$AA9),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL9" s="41"/>
       <c r="AM9" s="31" t="str" cm="1">
         <f t="array" ref="AM9">_xlfn.LET(_xlpm.rep,$B9,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -5188,7 +5211,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:40" ht="14.45" hidden="1">
+    <row r="10" spans="1:40" ht="14.45">
       <c r="A10" s="33" t="s">
         <v>40</v>
       </c>
@@ -5276,8 +5299,8 @@
       <c r="AJ10" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK10" s="72" t="str">
-        <f>IF($B10="","",IF(AND(LEFT($AJ10,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B10)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ10,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B10)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ10="Yes – needs DB Dev to fix",M10&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B10)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ10="Yes – needs PBI Dev to fix",S10&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B10)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ10="Yes – needs QA to fix",Y10&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B10)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B10)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B10)&gt;0,"",IF(AND(V10&lt;&gt;"",K10&lt;&gt;"",V10&lt;K10),"QA target is before DB Dev target",IF(AND(V10&lt;&gt;"",Q10&lt;&gt;"",V10&lt;Q10),"QA target is before PBI Dev target",IF(AND(AA10&lt;&gt;"",V10&lt;&gt;"",AA10&lt;V10),"DPO Approval target is before QA target",IF(AND(AG10&lt;&gt;"",AA10&lt;&gt;"",AG10&lt;AA10),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK10" s="72" t="str" cm="1">
+        <f t="array" ref="AK10">IF($B10="","",_xlfn.LET(_xlpm.nm,$B10,_xlpm.st,$C10,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M10,_xlpm.st="DB Dev",$M10,_xlpm.st="PBI Dev",$S10,_xlpm.st="QA",$Y10,_xlpm.st="DPO Approval",$AC10,_xlpm.st="Ready for Release in Prod",$AG10,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ10,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ10,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B10)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B10)&gt;0,"",IF(AND($V10&lt;&gt;"",$K10&lt;&gt;"",$V10&lt;$K10),"QA target is before DB Dev target",IF(AND($V10&lt;&gt;"",$Q10&lt;&gt;"",$V10&lt;$Q10),"QA target is before PBI Dev target",IF(AND($AA10&lt;&gt;"",$V10&lt;&gt;"",$AA10&lt;$V10),"DPO Approval target is before QA target",IF(AND($AG10&lt;&gt;"",$AA10&lt;&gt;"",$AG10&lt;$AA10),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v>Confirmed Deployed date is before DPO Approval target</v>
       </c>
       <c r="AL10" s="41"/>
@@ -5290,7 +5313,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:40" ht="14.45" hidden="1">
+    <row r="11" spans="1:40" ht="14.45">
       <c r="A11" s="33" t="s">
         <v>40</v>
       </c>
@@ -5378,8 +5401,8 @@
       <c r="AJ11" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK11" s="72" t="str">
-        <f>IF($B11="","",IF(AND(LEFT($AJ11,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B11)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ11,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B11)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ11="Yes – needs DB Dev to fix",M11&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B11)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ11="Yes – needs PBI Dev to fix",S11&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B11)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ11="Yes – needs QA to fix",Y11&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B11)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B11)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B11)&gt;0,"",IF(AND(V11&lt;&gt;"",K11&lt;&gt;"",V11&lt;K11),"QA target is before DB Dev target",IF(AND(V11&lt;&gt;"",Q11&lt;&gt;"",V11&lt;Q11),"QA target is before PBI Dev target",IF(AND(AA11&lt;&gt;"",V11&lt;&gt;"",AA11&lt;V11),"DPO Approval target is before QA target",IF(AND(AG11&lt;&gt;"",AA11&lt;&gt;"",AG11&lt;AA11),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK11" s="72" t="str" cm="1">
+        <f t="array" ref="AK11">IF($B11="","",_xlfn.LET(_xlpm.nm,$B11,_xlpm.st,$C11,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M11,_xlpm.st="DB Dev",$M11,_xlpm.st="PBI Dev",$S11,_xlpm.st="QA",$Y11,_xlpm.st="DPO Approval",$AC11,_xlpm.st="Ready for Release in Prod",$AG11,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ11,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ11,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B11)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B11)&gt;0,"",IF(AND($V11&lt;&gt;"",$K11&lt;&gt;"",$V11&lt;$K11),"QA target is before DB Dev target",IF(AND($V11&lt;&gt;"",$Q11&lt;&gt;"",$V11&lt;$Q11),"QA target is before PBI Dev target",IF(AND($AA11&lt;&gt;"",$V11&lt;&gt;"",$AA11&lt;$V11),"DPO Approval target is before QA target",IF(AND($AG11&lt;&gt;"",$AA11&lt;&gt;"",$AG11&lt;$AA11),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v>Confirmed Deployed date is before DPO Approval target</v>
       </c>
       <c r="AL11" s="41"/>
@@ -5392,7 +5415,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:40" ht="14.45" hidden="1">
+    <row r="12" spans="1:40" ht="14.45">
       <c r="A12" s="33" t="s">
         <v>40</v>
       </c>
@@ -5494,7 +5517,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:40" ht="14.45" hidden="1">
+    <row r="13" spans="1:40" ht="14.45">
       <c r="A13" s="33" t="s">
         <v>40</v>
       </c>
@@ -5594,7 +5617,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:40" ht="14.45" hidden="1">
+    <row r="14" spans="1:40" ht="14.45">
       <c r="A14" s="33" t="s">
         <v>40</v>
       </c>
@@ -5696,7 +5719,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:40" ht="14.45" hidden="1">
+    <row r="15" spans="1:40" ht="14.45">
       <c r="A15" s="33" t="s">
         <v>40</v>
       </c>
@@ -5782,8 +5805,8 @@
       <c r="AJ15" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK15" s="72" t="str">
-        <f>IF($B15="","",IF(AND(LEFT($AJ15,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B15)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ15,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B15)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ15="Yes – needs DB Dev to fix",M15&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B15)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ15="Yes – needs PBI Dev to fix",S15&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B15)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ15="Yes – needs QA to fix",Y15&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B15)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B15)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B15)&gt;0,"",IF(AND(V15&lt;&gt;"",K15&lt;&gt;"",V15&lt;K15),"QA target is before DB Dev target",IF(AND(V15&lt;&gt;"",Q15&lt;&gt;"",V15&lt;Q15),"QA target is before PBI Dev target",IF(AND(AA15&lt;&gt;"",V15&lt;&gt;"",AA15&lt;V15),"DPO Approval target is before QA target",IF(AND(AG15&lt;&gt;"",AA15&lt;&gt;"",AG15&lt;AA15),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK15" s="72" t="str" cm="1">
+        <f t="array" ref="AK15">IF($B15="","",_xlfn.LET(_xlpm.nm,$B15,_xlpm.st,$C15,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M15,_xlpm.st="DB Dev",$M15,_xlpm.st="PBI Dev",$S15,_xlpm.st="QA",$Y15,_xlpm.st="DPO Approval",$AC15,_xlpm.st="Ready for Release in Prod",$AG15,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ15,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ15,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B15)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B15)&gt;0,"",IF(AND($V15&lt;&gt;"",$K15&lt;&gt;"",$V15&lt;$K15),"QA target is before DB Dev target",IF(AND($V15&lt;&gt;"",$Q15&lt;&gt;"",$V15&lt;$Q15),"QA target is before PBI Dev target",IF(AND($AA15&lt;&gt;"",$V15&lt;&gt;"",$AA15&lt;$V15),"DPO Approval target is before QA target",IF(AND($AG15&lt;&gt;"",$AA15&lt;&gt;"",$AG15&lt;$AA15),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL15" s="41" t="s">
@@ -5798,7 +5821,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:40" ht="14.45" hidden="1">
+    <row r="16" spans="1:40" ht="14.45">
       <c r="A16" s="33" t="s">
         <v>40</v>
       </c>
@@ -5871,7 +5894,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:40" ht="14.45" hidden="1">
+    <row r="17" spans="1:40" ht="14.45">
       <c r="A17" s="33" t="s">
         <v>40</v>
       </c>
@@ -5944,7 +5967,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:40" ht="14.45" hidden="1">
+    <row r="18" spans="1:40" ht="14.45">
       <c r="A18" s="33" t="s">
         <v>40</v>
       </c>
@@ -6017,7 +6040,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:40" ht="14.45" hidden="1">
+    <row r="19" spans="1:40" ht="14.45">
       <c r="A19" s="33" t="s">
         <v>40</v>
       </c>
@@ -6090,7 +6113,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:40" ht="14.45" hidden="1">
+    <row r="20" spans="1:40" ht="14.45">
       <c r="A20" s="33" t="s">
         <v>40</v>
       </c>
@@ -6188,7 +6211,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:40" ht="14.45" hidden="1">
+    <row r="21" spans="1:40" ht="14.45">
       <c r="A21" s="33" t="s">
         <v>40</v>
       </c>
@@ -6272,8 +6295,8 @@
       <c r="AJ21" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK21" s="72" t="str">
-        <f>IF($B21="","",IF(AND(LEFT($AJ21,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B21)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ21,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B21)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ21="Yes – needs DB Dev to fix",M21&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B21)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ21="Yes – needs PBI Dev to fix",S21&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B21)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ21="Yes – needs QA to fix",Y21&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B21)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B21)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B21)&gt;0,"",IF(AND(V21&lt;&gt;"",K21&lt;&gt;"",V21&lt;K21),"QA target is before DB Dev target",IF(AND(V21&lt;&gt;"",Q21&lt;&gt;"",V21&lt;Q21),"QA target is before PBI Dev target",IF(AND(AA21&lt;&gt;"",V21&lt;&gt;"",AA21&lt;V21),"DPO Approval target is before QA target",IF(AND(AG21&lt;&gt;"",AA21&lt;&gt;"",AG21&lt;AA21),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK21" s="72" t="str" cm="1">
+        <f t="array" ref="AK21">IF($B21="","",_xlfn.LET(_xlpm.nm,$B21,_xlpm.st,$C21,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M21,_xlpm.st="DB Dev",$M21,_xlpm.st="PBI Dev",$S21,_xlpm.st="QA",$Y21,_xlpm.st="DPO Approval",$AC21,_xlpm.st="Ready for Release in Prod",$AG21,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ21,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ21,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B21)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B21)&gt;0,"",IF(AND($V21&lt;&gt;"",$K21&lt;&gt;"",$V21&lt;$K21),"QA target is before DB Dev target",IF(AND($V21&lt;&gt;"",$Q21&lt;&gt;"",$V21&lt;$Q21),"QA target is before PBI Dev target",IF(AND($AA21&lt;&gt;"",$V21&lt;&gt;"",$AA21&lt;$V21),"DPO Approval target is before QA target",IF(AND($AG21&lt;&gt;"",$AA21&lt;&gt;"",$AG21&lt;$AA21),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v>Confirmed Deployed date is before DPO Approval target</v>
       </c>
       <c r="AL21" s="41" t="s">
@@ -6288,7 +6311,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:40" ht="14.45" hidden="1">
+    <row r="22" spans="1:40" ht="14.45">
       <c r="A22" s="33" t="s">
         <v>40</v>
       </c>
@@ -6384,7 +6407,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:40" ht="14.45" hidden="1">
+    <row r="23" spans="1:40" ht="14.45">
       <c r="A23" s="33" t="s">
         <v>40</v>
       </c>
@@ -6486,7 +6509,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:40" ht="14.45" hidden="1">
+    <row r="24" spans="1:40" ht="14.45">
       <c r="A24" s="33" t="s">
         <v>40</v>
       </c>
@@ -6584,7 +6607,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:40" ht="14.45" hidden="1">
+    <row r="25" spans="1:40" ht="14.45">
       <c r="A25" s="33" t="s">
         <v>40</v>
       </c>
@@ -6668,8 +6691,8 @@
       <c r="AJ25" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK25" s="72" t="str">
-        <f>IF($B25="","",IF(AND(LEFT($AJ25,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B25)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ25,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B25)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ25="Yes – needs DB Dev to fix",M25&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B25)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ25="Yes – needs PBI Dev to fix",S25&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B25)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ25="Yes – needs QA to fix",Y25&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B25)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B25)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B25)&gt;0,"",IF(AND(V25&lt;&gt;"",K25&lt;&gt;"",V25&lt;K25),"QA target is before DB Dev target",IF(AND(V25&lt;&gt;"",Q25&lt;&gt;"",V25&lt;Q25),"QA target is before PBI Dev target",IF(AND(AA25&lt;&gt;"",V25&lt;&gt;"",AA25&lt;V25),"DPO Approval target is before QA target",IF(AND(AG25&lt;&gt;"",AA25&lt;&gt;"",AG25&lt;AA25),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK25" s="72" t="str" cm="1">
+        <f t="array" ref="AK25">IF($B25="","",_xlfn.LET(_xlpm.nm,$B25,_xlpm.st,$C25,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M25,_xlpm.st="DB Dev",$M25,_xlpm.st="PBI Dev",$S25,_xlpm.st="QA",$Y25,_xlpm.st="DPO Approval",$AC25,_xlpm.st="Ready for Release in Prod",$AG25,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ25,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ25,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B25)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B25)&gt;0,"",IF(AND($V25&lt;&gt;"",$K25&lt;&gt;"",$V25&lt;$K25),"QA target is before DB Dev target",IF(AND($V25&lt;&gt;"",$Q25&lt;&gt;"",$V25&lt;$Q25),"QA target is before PBI Dev target",IF(AND($AA25&lt;&gt;"",$V25&lt;&gt;"",$AA25&lt;$V25),"DPO Approval target is before QA target",IF(AND($AG25&lt;&gt;"",$AA25&lt;&gt;"",$AG25&lt;$AA25),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL25" s="41" t="s">
@@ -6684,7 +6707,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:40" ht="14.45" hidden="1">
+    <row r="26" spans="1:40" ht="14.45">
       <c r="A26" s="33" t="s">
         <v>40</v>
       </c>
@@ -6786,7 +6809,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:40" ht="14.45" hidden="1">
+    <row r="27" spans="1:40" ht="14.45">
       <c r="A27" s="33" t="s">
         <v>40</v>
       </c>
@@ -6870,8 +6893,8 @@
       <c r="AJ27" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK27" s="72" t="str">
-        <f>IF($B27="","",IF(AND(LEFT($AJ27,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B27)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ27,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B27)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ27="Yes – needs DB Dev to fix",M27&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B27)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ27="Yes – needs PBI Dev to fix",S27&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B27)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ27="Yes – needs QA to fix",Y27&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B27)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B27)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B27)&gt;0,"",IF(AND(V27&lt;&gt;"",K27&lt;&gt;"",V27&lt;K27),"QA target is before DB Dev target",IF(AND(V27&lt;&gt;"",Q27&lt;&gt;"",V27&lt;Q27),"QA target is before PBI Dev target",IF(AND(AA27&lt;&gt;"",V27&lt;&gt;"",AA27&lt;V27),"DPO Approval target is before QA target",IF(AND(AG27&lt;&gt;"",AA27&lt;&gt;"",AG27&lt;AA27),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK27" s="72" t="str" cm="1">
+        <f t="array" ref="AK27">IF($B27="","",_xlfn.LET(_xlpm.nm,$B27,_xlpm.st,$C27,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M27,_xlpm.st="DB Dev",$M27,_xlpm.st="PBI Dev",$S27,_xlpm.st="QA",$Y27,_xlpm.st="DPO Approval",$AC27,_xlpm.st="Ready for Release in Prod",$AG27,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ27,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ27,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B27)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B27)&gt;0,"",IF(AND($V27&lt;&gt;"",$K27&lt;&gt;"",$V27&lt;$K27),"QA target is before DB Dev target",IF(AND($V27&lt;&gt;"",$Q27&lt;&gt;"",$V27&lt;$Q27),"QA target is before PBI Dev target",IF(AND($AA27&lt;&gt;"",$V27&lt;&gt;"",$AA27&lt;$V27),"DPO Approval target is before QA target",IF(AND($AG27&lt;&gt;"",$AA27&lt;&gt;"",$AG27&lt;$AA27),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v>Confirmed Deployed date is before DPO Approval target</v>
       </c>
       <c r="AL27" s="41"/>
@@ -6884,7 +6907,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:40" ht="14.45" hidden="1">
+    <row r="28" spans="1:40" ht="14.45">
       <c r="A28" s="33" t="s">
         <v>40</v>
       </c>
@@ -6966,8 +6989,8 @@
       <c r="AJ28" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK28" s="72" t="str">
-        <f>IF($B28="","",IF(AND(LEFT($AJ28,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B28)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ28,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B28)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ28="Yes – needs DB Dev to fix",M28&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B28)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ28="Yes – needs PBI Dev to fix",S28&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B28)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ28="Yes – needs QA to fix",Y28&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B28)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B28)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B28)&gt;0,"",IF(AND(V28&lt;&gt;"",K28&lt;&gt;"",V28&lt;K28),"QA target is before DB Dev target",IF(AND(V28&lt;&gt;"",Q28&lt;&gt;"",V28&lt;Q28),"QA target is before PBI Dev target",IF(AND(AA28&lt;&gt;"",V28&lt;&gt;"",AA28&lt;V28),"DPO Approval target is before QA target",IF(AND(AG28&lt;&gt;"",AA28&lt;&gt;"",AG28&lt;AA28),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK28" s="72" t="str" cm="1">
+        <f t="array" ref="AK28">IF($B28="","",_xlfn.LET(_xlpm.nm,$B28,_xlpm.st,$C28,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M28,_xlpm.st="DB Dev",$M28,_xlpm.st="PBI Dev",$S28,_xlpm.st="QA",$Y28,_xlpm.st="DPO Approval",$AC28,_xlpm.st="Ready for Release in Prod",$AG28,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ28,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ28,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B28)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B28)&gt;0,"",IF(AND($V28&lt;&gt;"",$K28&lt;&gt;"",$V28&lt;$K28),"QA target is before DB Dev target",IF(AND($V28&lt;&gt;"",$Q28&lt;&gt;"",$V28&lt;$Q28),"QA target is before PBI Dev target",IF(AND($AA28&lt;&gt;"",$V28&lt;&gt;"",$AA28&lt;$V28),"DPO Approval target is before QA target",IF(AND($AG28&lt;&gt;"",$AA28&lt;&gt;"",$AG28&lt;$AA28),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v>Confirmed Deployed date is before DPO Approval target</v>
       </c>
       <c r="AL28" s="41" t="s">
@@ -6982,7 +7005,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:40" ht="14.45" hidden="1">
+    <row r="29" spans="1:40" ht="14.45">
       <c r="A29" s="33" t="s">
         <v>126</v>
       </c>
@@ -7076,8 +7099,8 @@
       <c r="AJ29" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK29" s="72" t="str">
-        <f>IF($B29="","",IF(AND(LEFT($AJ29,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B29)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ29,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B29)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ29="Yes – needs DB Dev to fix",M29&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B29)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ29="Yes – needs PBI Dev to fix",S29&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B29)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ29="Yes – needs QA to fix",Y29&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B29)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B29)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B29)&gt;0,"",IF(AND(V29&lt;&gt;"",K29&lt;&gt;"",V29&lt;K29),"QA target is before DB Dev target",IF(AND(V29&lt;&gt;"",Q29&lt;&gt;"",V29&lt;Q29),"QA target is before PBI Dev target",IF(AND(AA29&lt;&gt;"",V29&lt;&gt;"",AA29&lt;V29),"DPO Approval target is before QA target",IF(AND(AG29&lt;&gt;"",AA29&lt;&gt;"",AG29&lt;AA29),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK29" s="72" t="str" cm="1">
+        <f t="array" ref="AK29">IF($B29="","",_xlfn.LET(_xlpm.nm,$B29,_xlpm.st,$C29,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M29,_xlpm.st="DB Dev",$M29,_xlpm.st="PBI Dev",$S29,_xlpm.st="QA",$Y29,_xlpm.st="DPO Approval",$AC29,_xlpm.st="Ready for Release in Prod",$AG29,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ29,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ29,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B29)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B29)&gt;0,"",IF(AND($V29&lt;&gt;"",$K29&lt;&gt;"",$V29&lt;$K29),"QA target is before DB Dev target",IF(AND($V29&lt;&gt;"",$Q29&lt;&gt;"",$V29&lt;$Q29),"QA target is before PBI Dev target",IF(AND($AA29&lt;&gt;"",$V29&lt;&gt;"",$AA29&lt;$V29),"DPO Approval target is before QA target",IF(AND($AG29&lt;&gt;"",$AA29&lt;&gt;"",$AG29&lt;$AA29),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL29" s="41" t="s">
@@ -7092,7 +7115,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:40" ht="14.45" hidden="1">
+    <row r="30" spans="1:40" ht="14.45">
       <c r="A30" s="33" t="s">
         <v>126</v>
       </c>
@@ -7186,8 +7209,8 @@
       <c r="AJ30" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK30" s="72" t="str">
-        <f>IF($B30="","",IF(AND(LEFT($AJ30,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B30)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ30,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B30)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ30="Yes – needs DB Dev to fix",M30&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B30)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ30="Yes – needs PBI Dev to fix",S30&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B30)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ30="Yes – needs QA to fix",Y30&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B30)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B30)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B30)&gt;0,"",IF(AND(V30&lt;&gt;"",K30&lt;&gt;"",V30&lt;K30),"QA target is before DB Dev target",IF(AND(V30&lt;&gt;"",Q30&lt;&gt;"",V30&lt;Q30),"QA target is before PBI Dev target",IF(AND(AA30&lt;&gt;"",V30&lt;&gt;"",AA30&lt;V30),"DPO Approval target is before QA target",IF(AND(AG30&lt;&gt;"",AA30&lt;&gt;"",AG30&lt;AA30),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK30" s="72" t="str" cm="1">
+        <f t="array" ref="AK30">IF($B30="","",_xlfn.LET(_xlpm.nm,$B30,_xlpm.st,$C30,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M30,_xlpm.st="DB Dev",$M30,_xlpm.st="PBI Dev",$S30,_xlpm.st="QA",$Y30,_xlpm.st="DPO Approval",$AC30,_xlpm.st="Ready for Release in Prod",$AG30,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ30,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ30,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B30)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B30)&gt;0,"",IF(AND($V30&lt;&gt;"",$K30&lt;&gt;"",$V30&lt;$K30),"QA target is before DB Dev target",IF(AND($V30&lt;&gt;"",$Q30&lt;&gt;"",$V30&lt;$Q30),"QA target is before PBI Dev target",IF(AND($AA30&lt;&gt;"",$V30&lt;&gt;"",$AA30&lt;$V30),"DPO Approval target is before QA target",IF(AND($AG30&lt;&gt;"",$AA30&lt;&gt;"",$AG30&lt;$AA30),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL30" s="41" t="s">
@@ -7202,7 +7225,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:40" ht="14.45" hidden="1">
+    <row r="31" spans="1:40" ht="14.45">
       <c r="A31" s="33" t="s">
         <v>126</v>
       </c>
@@ -7296,8 +7319,8 @@
       <c r="AJ31" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK31" s="72" t="str">
-        <f>IF($B31="","",IF(AND(LEFT($AJ31,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B31)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ31,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B31)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ31="Yes – needs DB Dev to fix",M31&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B31)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ31="Yes – needs PBI Dev to fix",S31&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B31)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ31="Yes – needs QA to fix",Y31&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B31)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B31)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B31)&gt;0,"",IF(AND(V31&lt;&gt;"",K31&lt;&gt;"",V31&lt;K31),"QA target is before DB Dev target",IF(AND(V31&lt;&gt;"",Q31&lt;&gt;"",V31&lt;Q31),"QA target is before PBI Dev target",IF(AND(AA31&lt;&gt;"",V31&lt;&gt;"",AA31&lt;V31),"DPO Approval target is before QA target",IF(AND(AG31&lt;&gt;"",AA31&lt;&gt;"",AG31&lt;AA31),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK31" s="72" t="str" cm="1">
+        <f t="array" ref="AK31">IF($B31="","",_xlfn.LET(_xlpm.nm,$B31,_xlpm.st,$C31,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M31,_xlpm.st="DB Dev",$M31,_xlpm.st="PBI Dev",$S31,_xlpm.st="QA",$Y31,_xlpm.st="DPO Approval",$AC31,_xlpm.st="Ready for Release in Prod",$AG31,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ31,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ31,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B31)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B31)&gt;0,"",IF(AND($V31&lt;&gt;"",$K31&lt;&gt;"",$V31&lt;$K31),"QA target is before DB Dev target",IF(AND($V31&lt;&gt;"",$Q31&lt;&gt;"",$V31&lt;$Q31),"QA target is before PBI Dev target",IF(AND($AA31&lt;&gt;"",$V31&lt;&gt;"",$AA31&lt;$V31),"DPO Approval target is before QA target",IF(AND($AG31&lt;&gt;"",$AA31&lt;&gt;"",$AG31&lt;$AA31),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL31" s="41" t="s">
@@ -7312,7 +7335,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:40" ht="14.45" hidden="1">
+    <row r="32" spans="1:40" ht="14.45">
       <c r="A32" s="33" t="s">
         <v>126</v>
       </c>
@@ -7404,8 +7427,8 @@
       <c r="AJ32" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK32" s="72" t="str">
-        <f>IF($B32="","",IF(AND(LEFT($AJ32,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B32)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ32,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B32)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ32="Yes – needs DB Dev to fix",M32&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B32)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ32="Yes – needs PBI Dev to fix",S32&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B32)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ32="Yes – needs QA to fix",Y32&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B32)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B32)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B32)&gt;0,"",IF(AND(V32&lt;&gt;"",K32&lt;&gt;"",V32&lt;K32),"QA target is before DB Dev target",IF(AND(V32&lt;&gt;"",Q32&lt;&gt;"",V32&lt;Q32),"QA target is before PBI Dev target",IF(AND(AA32&lt;&gt;"",V32&lt;&gt;"",AA32&lt;V32),"DPO Approval target is before QA target",IF(AND(AG32&lt;&gt;"",AA32&lt;&gt;"",AG32&lt;AA32),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK32" s="72" t="str" cm="1">
+        <f t="array" ref="AK32">IF($B32="","",_xlfn.LET(_xlpm.nm,$B32,_xlpm.st,$C32,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M32,_xlpm.st="DB Dev",$M32,_xlpm.st="PBI Dev",$S32,_xlpm.st="QA",$Y32,_xlpm.st="DPO Approval",$AC32,_xlpm.st="Ready for Release in Prod",$AG32,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ32,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ32,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B32)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B32)&gt;0,"",IF(AND($V32&lt;&gt;"",$K32&lt;&gt;"",$V32&lt;$K32),"QA target is before DB Dev target",IF(AND($V32&lt;&gt;"",$Q32&lt;&gt;"",$V32&lt;$Q32),"QA target is before PBI Dev target",IF(AND($AA32&lt;&gt;"",$V32&lt;&gt;"",$AA32&lt;$V32),"DPO Approval target is before QA target",IF(AND($AG32&lt;&gt;"",$AA32&lt;&gt;"",$AG32&lt;$AA32),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL32" s="41" t="s">
@@ -7420,7 +7443,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:40" ht="14.45" hidden="1">
+    <row r="33" spans="1:40" ht="14.45">
       <c r="A33" s="33" t="s">
         <v>126</v>
       </c>
@@ -7514,8 +7537,8 @@
       <c r="AJ33" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK33" s="72" t="str">
-        <f>IF($B33="","",IF(AND(LEFT($AJ33,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B33)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ33,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B33)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ33="Yes – needs DB Dev to fix",M33&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B33)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ33="Yes – needs PBI Dev to fix",S33&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B33)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ33="Yes – needs QA to fix",Y33&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B33)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B33)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B33)&gt;0,"",IF(AND(V33&lt;&gt;"",K33&lt;&gt;"",V33&lt;K33),"QA target is before DB Dev target",IF(AND(V33&lt;&gt;"",Q33&lt;&gt;"",V33&lt;Q33),"QA target is before PBI Dev target",IF(AND(AA33&lt;&gt;"",V33&lt;&gt;"",AA33&lt;V33),"DPO Approval target is before QA target",IF(AND(AG33&lt;&gt;"",AA33&lt;&gt;"",AG33&lt;AA33),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK33" s="72" t="str" cm="1">
+        <f t="array" ref="AK33">IF($B33="","",_xlfn.LET(_xlpm.nm,$B33,_xlpm.st,$C33,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M33,_xlpm.st="DB Dev",$M33,_xlpm.st="PBI Dev",$S33,_xlpm.st="QA",$Y33,_xlpm.st="DPO Approval",$AC33,_xlpm.st="Ready for Release in Prod",$AG33,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ33,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ33,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B33)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B33)&gt;0,"",IF(AND($V33&lt;&gt;"",$K33&lt;&gt;"",$V33&lt;$K33),"QA target is before DB Dev target",IF(AND($V33&lt;&gt;"",$Q33&lt;&gt;"",$V33&lt;$Q33),"QA target is before PBI Dev target",IF(AND($AA33&lt;&gt;"",$V33&lt;&gt;"",$AA33&lt;$V33),"DPO Approval target is before QA target",IF(AND($AG33&lt;&gt;"",$AA33&lt;&gt;"",$AG33&lt;$AA33),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL33" s="41" t="s">
@@ -7530,7 +7553,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:40" ht="14.45" hidden="1">
+    <row r="34" spans="1:40" ht="14.45">
       <c r="A34" s="33" t="s">
         <v>126</v>
       </c>
@@ -7624,8 +7647,8 @@
       <c r="AJ34" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK34" s="72" t="str">
-        <f>IF($B34="","",IF(AND(LEFT($AJ34,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B34)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ34,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B34)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ34="Yes – needs DB Dev to fix",M34&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B34)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ34="Yes – needs PBI Dev to fix",S34&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B34)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ34="Yes – needs QA to fix",Y34&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B34)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B34)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B34)&gt;0,"",IF(AND(V34&lt;&gt;"",K34&lt;&gt;"",V34&lt;K34),"QA target is before DB Dev target",IF(AND(V34&lt;&gt;"",Q34&lt;&gt;"",V34&lt;Q34),"QA target is before PBI Dev target",IF(AND(AA34&lt;&gt;"",V34&lt;&gt;"",AA34&lt;V34),"DPO Approval target is before QA target",IF(AND(AG34&lt;&gt;"",AA34&lt;&gt;"",AG34&lt;AA34),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK34" s="72" t="str" cm="1">
+        <f t="array" ref="AK34">IF($B34="","",_xlfn.LET(_xlpm.nm,$B34,_xlpm.st,$C34,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M34,_xlpm.st="DB Dev",$M34,_xlpm.st="PBI Dev",$S34,_xlpm.st="QA",$Y34,_xlpm.st="DPO Approval",$AC34,_xlpm.st="Ready for Release in Prod",$AG34,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ34,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ34,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B34)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B34)&gt;0,"",IF(AND($V34&lt;&gt;"",$K34&lt;&gt;"",$V34&lt;$K34),"QA target is before DB Dev target",IF(AND($V34&lt;&gt;"",$Q34&lt;&gt;"",$V34&lt;$Q34),"QA target is before PBI Dev target",IF(AND($AA34&lt;&gt;"",$V34&lt;&gt;"",$AA34&lt;$V34),"DPO Approval target is before QA target",IF(AND($AG34&lt;&gt;"",$AA34&lt;&gt;"",$AG34&lt;$AA34),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL34" s="41" t="s">
@@ -7640,7 +7663,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:40" ht="14.45" hidden="1">
+    <row r="35" spans="1:40" ht="14.45">
       <c r="A35" s="33" t="s">
         <v>126</v>
       </c>
@@ -7734,8 +7757,8 @@
       <c r="AJ35" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK35" s="72" t="str">
-        <f>IF($B35="","",IF(AND(LEFT($AJ35,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B35)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ35,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B35)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ35="Yes – needs DB Dev to fix",M35&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B35)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ35="Yes – needs PBI Dev to fix",S35&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B35)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ35="Yes – needs QA to fix",Y35&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B35)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B35)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B35)&gt;0,"",IF(AND(V35&lt;&gt;"",K35&lt;&gt;"",V35&lt;K35),"QA target is before DB Dev target",IF(AND(V35&lt;&gt;"",Q35&lt;&gt;"",V35&lt;Q35),"QA target is before PBI Dev target",IF(AND(AA35&lt;&gt;"",V35&lt;&gt;"",AA35&lt;V35),"DPO Approval target is before QA target",IF(AND(AG35&lt;&gt;"",AA35&lt;&gt;"",AG35&lt;AA35),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK35" s="72" t="str" cm="1">
+        <f t="array" ref="AK35">IF($B35="","",_xlfn.LET(_xlpm.nm,$B35,_xlpm.st,$C35,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M35,_xlpm.st="DB Dev",$M35,_xlpm.st="PBI Dev",$S35,_xlpm.st="QA",$Y35,_xlpm.st="DPO Approval",$AC35,_xlpm.st="Ready for Release in Prod",$AG35,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ35,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ35,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B35)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B35)&gt;0,"",IF(AND($V35&lt;&gt;"",$K35&lt;&gt;"",$V35&lt;$K35),"QA target is before DB Dev target",IF(AND($V35&lt;&gt;"",$Q35&lt;&gt;"",$V35&lt;$Q35),"QA target is before PBI Dev target",IF(AND($AA35&lt;&gt;"",$V35&lt;&gt;"",$AA35&lt;$V35),"DPO Approval target is before QA target",IF(AND($AG35&lt;&gt;"",$AA35&lt;&gt;"",$AG35&lt;$AA35),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL35" s="41" t="s">
@@ -7750,7 +7773,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:40" ht="14.45" hidden="1">
+    <row r="36" spans="1:40" ht="14.45">
       <c r="A36" s="33" t="s">
         <v>126</v>
       </c>
@@ -7844,8 +7867,8 @@
       <c r="AJ36" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK36" s="72" t="str">
-        <f>IF($B36="","",IF(AND(LEFT($AJ36,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B36)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ36,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B36)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ36="Yes – needs DB Dev to fix",M36&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B36)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ36="Yes – needs PBI Dev to fix",S36&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B36)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ36="Yes – needs QA to fix",Y36&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B36)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B36)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B36)&gt;0,"",IF(AND(V36&lt;&gt;"",K36&lt;&gt;"",V36&lt;K36),"QA target is before DB Dev target",IF(AND(V36&lt;&gt;"",Q36&lt;&gt;"",V36&lt;Q36),"QA target is before PBI Dev target",IF(AND(AA36&lt;&gt;"",V36&lt;&gt;"",AA36&lt;V36),"DPO Approval target is before QA target",IF(AND(AG36&lt;&gt;"",AA36&lt;&gt;"",AG36&lt;AA36),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK36" s="72" t="str" cm="1">
+        <f t="array" ref="AK36">IF($B36="","",_xlfn.LET(_xlpm.nm,$B36,_xlpm.st,$C36,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M36,_xlpm.st="DB Dev",$M36,_xlpm.st="PBI Dev",$S36,_xlpm.st="QA",$Y36,_xlpm.st="DPO Approval",$AC36,_xlpm.st="Ready for Release in Prod",$AG36,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ36,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ36,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B36)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B36)&gt;0,"",IF(AND($V36&lt;&gt;"",$K36&lt;&gt;"",$V36&lt;$K36),"QA target is before DB Dev target",IF(AND($V36&lt;&gt;"",$Q36&lt;&gt;"",$V36&lt;$Q36),"QA target is before PBI Dev target",IF(AND($AA36&lt;&gt;"",$V36&lt;&gt;"",$AA36&lt;$V36),"DPO Approval target is before QA target",IF(AND($AG36&lt;&gt;"",$AA36&lt;&gt;"",$AG36&lt;$AA36),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL36" s="41" t="s">
@@ -7860,7 +7883,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:40" ht="14.45" hidden="1">
+    <row r="37" spans="1:40" ht="14.45">
       <c r="A37" s="33" t="s">
         <v>126</v>
       </c>
@@ -7954,8 +7977,8 @@
       <c r="AJ37" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK37" s="72" t="str">
-        <f>IF($B37="","",IF(AND(LEFT($AJ37,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B37)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ37,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B37)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ37="Yes – needs DB Dev to fix",M37&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B37)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ37="Yes – needs PBI Dev to fix",S37&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B37)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ37="Yes – needs QA to fix",Y37&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B37)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B37)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B37)&gt;0,"",IF(AND(V37&lt;&gt;"",K37&lt;&gt;"",V37&lt;K37),"QA target is before DB Dev target",IF(AND(V37&lt;&gt;"",Q37&lt;&gt;"",V37&lt;Q37),"QA target is before PBI Dev target",IF(AND(AA37&lt;&gt;"",V37&lt;&gt;"",AA37&lt;V37),"DPO Approval target is before QA target",IF(AND(AG37&lt;&gt;"",AA37&lt;&gt;"",AG37&lt;AA37),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK37" s="72" t="str" cm="1">
+        <f t="array" ref="AK37">IF($B37="","",_xlfn.LET(_xlpm.nm,$B37,_xlpm.st,$C37,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M37,_xlpm.st="DB Dev",$M37,_xlpm.st="PBI Dev",$S37,_xlpm.st="QA",$Y37,_xlpm.st="DPO Approval",$AC37,_xlpm.st="Ready for Release in Prod",$AG37,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ37,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ37,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B37)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B37)&gt;0,"",IF(AND($V37&lt;&gt;"",$K37&lt;&gt;"",$V37&lt;$K37),"QA target is before DB Dev target",IF(AND($V37&lt;&gt;"",$Q37&lt;&gt;"",$V37&lt;$Q37),"QA target is before PBI Dev target",IF(AND($AA37&lt;&gt;"",$V37&lt;&gt;"",$AA37&lt;$V37),"DPO Approval target is before QA target",IF(AND($AG37&lt;&gt;"",$AA37&lt;&gt;"",$AG37&lt;$AA37),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL37" s="41" t="s">
@@ -7970,7 +7993,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:40" ht="14.45" hidden="1">
+    <row r="38" spans="1:40" ht="14.45">
       <c r="A38" s="33" t="s">
         <v>126</v>
       </c>
@@ -8064,8 +8087,8 @@
       <c r="AJ38" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK38" s="72" t="str">
-        <f>IF($B38="","",IF(AND(LEFT($AJ38,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B38)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ38,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B38)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ38="Yes – needs DB Dev to fix",M38&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B38)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ38="Yes – needs PBI Dev to fix",S38&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B38)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ38="Yes – needs QA to fix",Y38&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B38)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B38)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B38)&gt;0,"",IF(AND(V38&lt;&gt;"",K38&lt;&gt;"",V38&lt;K38),"QA target is before DB Dev target",IF(AND(V38&lt;&gt;"",Q38&lt;&gt;"",V38&lt;Q38),"QA target is before PBI Dev target",IF(AND(AA38&lt;&gt;"",V38&lt;&gt;"",AA38&lt;V38),"DPO Approval target is before QA target",IF(AND(AG38&lt;&gt;"",AA38&lt;&gt;"",AG38&lt;AA38),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK38" s="72" t="str" cm="1">
+        <f t="array" ref="AK38">IF($B38="","",_xlfn.LET(_xlpm.nm,$B38,_xlpm.st,$C38,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M38,_xlpm.st="DB Dev",$M38,_xlpm.st="PBI Dev",$S38,_xlpm.st="QA",$Y38,_xlpm.st="DPO Approval",$AC38,_xlpm.st="Ready for Release in Prod",$AG38,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ38,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ38,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B38)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B38)&gt;0,"",IF(AND($V38&lt;&gt;"",$K38&lt;&gt;"",$V38&lt;$K38),"QA target is before DB Dev target",IF(AND($V38&lt;&gt;"",$Q38&lt;&gt;"",$V38&lt;$Q38),"QA target is before PBI Dev target",IF(AND($AA38&lt;&gt;"",$V38&lt;&gt;"",$AA38&lt;$V38),"DPO Approval target is before QA target",IF(AND($AG38&lt;&gt;"",$AA38&lt;&gt;"",$AG38&lt;$AA38),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL38" s="41"/>
@@ -8078,7 +8101,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:40" ht="14.45" hidden="1">
+    <row r="39" spans="1:40" ht="14.45">
       <c r="A39" s="33" t="s">
         <v>126</v>
       </c>
@@ -8172,8 +8195,8 @@
       <c r="AJ39" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK39" s="72" t="str">
-        <f>IF($B39="","",IF(AND(LEFT($AJ39,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B39)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ39,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B39)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ39="Yes – needs DB Dev to fix",M39&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B39)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ39="Yes – needs PBI Dev to fix",S39&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B39)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ39="Yes – needs QA to fix",Y39&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B39)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B39)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B39)&gt;0,"",IF(AND(V39&lt;&gt;"",K39&lt;&gt;"",V39&lt;K39),"QA target is before DB Dev target",IF(AND(V39&lt;&gt;"",Q39&lt;&gt;"",V39&lt;Q39),"QA target is before PBI Dev target",IF(AND(AA39&lt;&gt;"",V39&lt;&gt;"",AA39&lt;V39),"DPO Approval target is before QA target",IF(AND(AG39&lt;&gt;"",AA39&lt;&gt;"",AG39&lt;AA39),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK39" s="72" t="str" cm="1">
+        <f t="array" ref="AK39">IF($B39="","",_xlfn.LET(_xlpm.nm,$B39,_xlpm.st,$C39,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M39,_xlpm.st="DB Dev",$M39,_xlpm.st="PBI Dev",$S39,_xlpm.st="QA",$Y39,_xlpm.st="DPO Approval",$AC39,_xlpm.st="Ready for Release in Prod",$AG39,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ39,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ39,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B39)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B39)&gt;0,"",IF(AND($V39&lt;&gt;"",$K39&lt;&gt;"",$V39&lt;$K39),"QA target is before DB Dev target",IF(AND($V39&lt;&gt;"",$Q39&lt;&gt;"",$V39&lt;$Q39),"QA target is before PBI Dev target",IF(AND($AA39&lt;&gt;"",$V39&lt;&gt;"",$AA39&lt;$V39),"DPO Approval target is before QA target",IF(AND($AG39&lt;&gt;"",$AA39&lt;&gt;"",$AG39&lt;$AA39),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL39" s="41" t="s">
@@ -8188,7 +8211,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:40" ht="14.45" hidden="1">
+    <row r="40" spans="1:40" ht="14.45">
       <c r="A40" s="33" t="s">
         <v>126</v>
       </c>
@@ -8282,8 +8305,8 @@
       <c r="AJ40" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK40" s="72" t="str">
-        <f>IF($B40="","",IF(AND(LEFT($AJ40,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B40)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ40,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B40)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ40="Yes – needs DB Dev to fix",M40&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B40)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ40="Yes – needs PBI Dev to fix",S40&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B40)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ40="Yes – needs QA to fix",Y40&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B40)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B40)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B40)&gt;0,"",IF(AND(V40&lt;&gt;"",K40&lt;&gt;"",V40&lt;K40),"QA target is before DB Dev target",IF(AND(V40&lt;&gt;"",Q40&lt;&gt;"",V40&lt;Q40),"QA target is before PBI Dev target",IF(AND(AA40&lt;&gt;"",V40&lt;&gt;"",AA40&lt;V40),"DPO Approval target is before QA target",IF(AND(AG40&lt;&gt;"",AA40&lt;&gt;"",AG40&lt;AA40),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK40" s="72" t="str" cm="1">
+        <f t="array" ref="AK40">IF($B40="","",_xlfn.LET(_xlpm.nm,$B40,_xlpm.st,$C40,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M40,_xlpm.st="DB Dev",$M40,_xlpm.st="PBI Dev",$S40,_xlpm.st="QA",$Y40,_xlpm.st="DPO Approval",$AC40,_xlpm.st="Ready for Release in Prod",$AG40,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ40,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ40,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B40)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B40)&gt;0,"",IF(AND($V40&lt;&gt;"",$K40&lt;&gt;"",$V40&lt;$K40),"QA target is before DB Dev target",IF(AND($V40&lt;&gt;"",$Q40&lt;&gt;"",$V40&lt;$Q40),"QA target is before PBI Dev target",IF(AND($AA40&lt;&gt;"",$V40&lt;&gt;"",$AA40&lt;$V40),"DPO Approval target is before QA target",IF(AND($AG40&lt;&gt;"",$AA40&lt;&gt;"",$AG40&lt;$AA40),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL40" s="41" t="s">
@@ -8298,7 +8321,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:40" ht="14.45" hidden="1">
+    <row r="41" spans="1:40" ht="14.45">
       <c r="A41" s="33" t="s">
         <v>126</v>
       </c>
@@ -8392,8 +8415,8 @@
       <c r="AJ41" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK41" s="72" t="str">
-        <f>IF($B41="","",IF(AND(LEFT($AJ41,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B41)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ41,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B41)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ41="Yes – needs DB Dev to fix",M41&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B41)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ41="Yes – needs PBI Dev to fix",S41&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B41)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ41="Yes – needs QA to fix",Y41&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B41)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B41)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B41)&gt;0,"",IF(AND(V41&lt;&gt;"",K42&lt;&gt;"",V41&lt;K42),"QA target is before DB Dev target",IF(AND(V41&lt;&gt;"",Q41&lt;&gt;"",V41&lt;Q41),"QA target is before PBI Dev target",IF(AND(AA41&lt;&gt;"",V41&lt;&gt;"",AA41&lt;V41),"DPO Approval target is before QA target",IF(AND(AG41&lt;&gt;"",AA41&lt;&gt;"",AG41&lt;AA41),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK41" s="72" t="str" cm="1">
+        <f t="array" ref="AK41">IF($B41="","",_xlfn.LET(_xlpm.nm,$B41,_xlpm.st,$C41,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M41,_xlpm.st="DB Dev",$M41,_xlpm.st="PBI Dev",$S41,_xlpm.st="QA",$Y41,_xlpm.st="DPO Approval",$AC41,_xlpm.st="Ready for Release in Prod",$AG41,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ41,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ41,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B41)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B41)&gt;0,"",IF(AND($V41&lt;&gt;"",$K41&lt;&gt;"",$V41&lt;$K41),"QA target is before DB Dev target",IF(AND($V41&lt;&gt;"",$Q41&lt;&gt;"",$V41&lt;$Q41),"QA target is before PBI Dev target",IF(AND($AA41&lt;&gt;"",$V41&lt;&gt;"",$AA41&lt;$V41),"DPO Approval target is before QA target",IF(AND($AG41&lt;&gt;"",$AA41&lt;&gt;"",$AG41&lt;$AA41),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL41" s="41" t="s">
@@ -8408,7 +8431,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:40" ht="14.45" hidden="1">
+    <row r="42" spans="1:40" ht="14.45">
       <c r="A42" s="33" t="s">
         <v>126</v>
       </c>
@@ -8502,8 +8525,8 @@
       <c r="AJ42" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK42" s="47" t="str">
-        <f>IF($B42="","",IF(AND(LEFT($AJ42,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B42)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ42,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B42)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ42="Yes – needs DB Dev to fix",M42&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B42)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ42="Yes – needs PBI Dev to fix",S42&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B42)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ42="Yes – needs QA to fix",Y42&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B42)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B42)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B42)&gt;0,"",IF(AND(V42&lt;&gt;"",K42&lt;&gt;"",V42&lt;K42),"QA target is before DB Dev target",IF(AND(V42&lt;&gt;"",Q42&lt;&gt;"",V42&lt;Q42),"QA target is before PBI Dev target",IF(AND(AA42&lt;&gt;"",V42&lt;&gt;"",AA42&lt;V42),"DPO Approval target is before QA target",IF(AND(AG42&lt;&gt;"",AA42&lt;&gt;"",AG42&lt;AA42),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK42" s="47" t="str" cm="1">
+        <f t="array" ref="AK42">IF($B42="","",_xlfn.LET(_xlpm.nm,$B42,_xlpm.st,$C42,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M42,_xlpm.st="DB Dev",$M42,_xlpm.st="PBI Dev",$S42,_xlpm.st="QA",$Y42,_xlpm.st="DPO Approval",$AC42,_xlpm.st="Ready for Release in Prod",$AG42,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ42,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ42,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B42)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B42)&gt;0,"",IF(AND($V42&lt;&gt;"",$K42&lt;&gt;"",$V42&lt;$K42),"QA target is before DB Dev target",IF(AND($V42&lt;&gt;"",$Q42&lt;&gt;"",$V42&lt;$Q42),"QA target is before PBI Dev target",IF(AND($AA42&lt;&gt;"",$V42&lt;&gt;"",$AA42&lt;$V42),"DPO Approval target is before QA target",IF(AND($AG42&lt;&gt;"",$AA42&lt;&gt;"",$AG42&lt;$AA42),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL42" s="45" t="s">
@@ -8518,7 +8541,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:40" ht="14.45" hidden="1">
+    <row r="43" spans="1:40" ht="14.45">
       <c r="A43" s="33" t="s">
         <v>126</v>
       </c>
@@ -8612,8 +8635,8 @@
       <c r="AJ43" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK43" s="72" t="str">
-        <f>IF($B43="","",IF(AND(LEFT($AJ43,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B43)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ43,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B43)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ43="Yes – needs DB Dev to fix",M43&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B43)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ43="Yes – needs PBI Dev to fix",S43&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B43)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ43="Yes – needs QA to fix",Y43&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B43)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B43)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B43)&gt;0,"",IF(AND(V43&lt;&gt;"",K43&lt;&gt;"",V43&lt;K43),"QA target is before DB Dev target",IF(AND(V43&lt;&gt;"",Q43&lt;&gt;"",V43&lt;Q43),"QA target is before PBI Dev target",IF(AND(AA43&lt;&gt;"",V43&lt;&gt;"",AA43&lt;V43),"DPO Approval target is before QA target",IF(AND(AG43&lt;&gt;"",AA43&lt;&gt;"",AG43&lt;AA43),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK43" s="72" t="str" cm="1">
+        <f t="array" ref="AK43">IF($B43="","",_xlfn.LET(_xlpm.nm,$B43,_xlpm.st,$C43,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M43,_xlpm.st="DB Dev",$M43,_xlpm.st="PBI Dev",$S43,_xlpm.st="QA",$Y43,_xlpm.st="DPO Approval",$AC43,_xlpm.st="Ready for Release in Prod",$AG43,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ43,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ43,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B43)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B43)&gt;0,"",IF(AND($V43&lt;&gt;"",$K43&lt;&gt;"",$V43&lt;$K43),"QA target is before DB Dev target",IF(AND($V43&lt;&gt;"",$Q43&lt;&gt;"",$V43&lt;$Q43),"QA target is before PBI Dev target",IF(AND($AA43&lt;&gt;"",$V43&lt;&gt;"",$AA43&lt;$V43),"DPO Approval target is before QA target",IF(AND($AG43&lt;&gt;"",$AA43&lt;&gt;"",$AG43&lt;$AA43),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL43" s="41" t="s">
@@ -8628,7 +8651,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:40" ht="43.15" hidden="1">
+    <row r="44" spans="1:40" ht="43.15">
       <c r="A44" s="33" t="s">
         <v>126</v>
       </c>
@@ -8722,8 +8745,8 @@
       <c r="AJ44" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK44" s="72" t="str">
-        <f>IF($B44="","",IF(AND(LEFT($AJ44,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B44)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ44,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B44)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ44="Yes – needs DB Dev to fix",M44&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B44)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ44="Yes – needs PBI Dev to fix",S44&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B44)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ44="Yes – needs QA to fix",Y44&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B44)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B44)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B44)&gt;0,"",IF(AND(V44&lt;&gt;"",K44&lt;&gt;"",V44&lt;K44),"QA target is before DB Dev target",IF(AND(V44&lt;&gt;"",Q44&lt;&gt;"",V44&lt;Q44),"QA target is before PBI Dev target",IF(AND(AA44&lt;&gt;"",V44&lt;&gt;"",AA44&lt;V44),"DPO Approval target is before QA target",IF(AND(AG44&lt;&gt;"",AA44&lt;&gt;"",AG44&lt;AA44),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK44" s="72" t="str" cm="1">
+        <f t="array" ref="AK44">IF($B44="","",_xlfn.LET(_xlpm.nm,$B44,_xlpm.st,$C44,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M44,_xlpm.st="DB Dev",$M44,_xlpm.st="PBI Dev",$S44,_xlpm.st="QA",$Y44,_xlpm.st="DPO Approval",$AC44,_xlpm.st="Ready for Release in Prod",$AG44,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ44,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ44,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B44)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B44)&gt;0,"",IF(AND($V44&lt;&gt;"",$K44&lt;&gt;"",$V44&lt;$K44),"QA target is before DB Dev target",IF(AND($V44&lt;&gt;"",$Q44&lt;&gt;"",$V44&lt;$Q44),"QA target is before PBI Dev target",IF(AND($AA44&lt;&gt;"",$V44&lt;&gt;"",$AA44&lt;$V44),"DPO Approval target is before QA target",IF(AND($AG44&lt;&gt;"",$AA44&lt;&gt;"",$AG44&lt;$AA44),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL44" s="115" t="s">
@@ -8746,7 +8769,7 @@
         <v>172</v>
       </c>
       <c r="C45" s="33" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D45" t="str" cm="1">
         <f t="array" aca="1" ref="D45" ca="1">IF(AND(C45="Ready for Release in Prod",LEFT($AJ45,3)&lt;&gt;"Yes"),IF(AG45&lt;&gt;"","Delivered","On track"),IF($B45="","",IF(LEFT($AJ45,3)="Yes","Blocked - "&amp;MID($AJ45,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B45)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B45)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B45)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C45="NOT STARTED",IF(H45="","No plan date set",IF(H45&lt;TODAY(),"Review - planned start passed","On track")),IF(C45="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B45,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B45,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L45&lt;&gt;"",L45,K45)),_xlpm.act,IF(AND(M45&lt;&gt;"",M45&gt;=_xlpm.sent),M45,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C45="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B45,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B45,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R45&lt;&gt;"",R45,Q45)),_xlpm.act,IF(AND(S45&lt;&gt;"",S45&gt;=_xlpm.sent),S45,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C45="QA",_xlfn.LET(_xlpm.tgt,IF(AM45&lt;&gt;"",AM45,IF(W45&lt;&gt;"",W45,V45)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B45,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y45&lt;&gt;"",Y45&gt;=_xlpm.sent),Y45,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C45="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN45&lt;&gt;"",AN45,IF(AB45&lt;&gt;"",AB45,AA45)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B45,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC45&lt;&gt;"",AC45&gt;=_xlpm.sent),AC45,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C45="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -8828,12 +8851,12 @@
       <c r="AJ45" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK45" s="72" t="str">
-        <f>IF($B45="","",IF(AND(LEFT($AJ45,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B45)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ45,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B45)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ45="Yes – needs DB Dev to fix",M45&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B45)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ45="Yes – needs PBI Dev to fix",S45&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B45)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ45="Yes – needs QA to fix",Y45&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B45)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B45)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B45)&gt;0,"",IF(AND(V45&lt;&gt;"",K45&lt;&gt;"",V45&lt;K45),"QA target is before DB Dev target",IF(AND(V45&lt;&gt;"",Q45&lt;&gt;"",V45&lt;Q45),"QA target is before PBI Dev target",IF(AND(AA45&lt;&gt;"",V45&lt;&gt;"",AA45&lt;V45),"DPO Approval target is before QA target",IF(AND(AG45&lt;&gt;"",AA45&lt;&gt;"",AG45&lt;AA45),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK45" s="72" t="str" cm="1">
+        <f t="array" ref="AK45">IF($B45="","",_xlfn.LET(_xlpm.nm,$B45,_xlpm.st,$C45,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M45,_xlpm.st="DB Dev",$M45,_xlpm.st="PBI Dev",$S45,_xlpm.st="QA",$Y45,_xlpm.st="DPO Approval",$AC45,_xlpm.st="Ready for Release in Prod",$AG45,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ45,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ45,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B45)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B45)&gt;0,"",IF(AND($V45&lt;&gt;"",$K45&lt;&gt;"",$V45&lt;$K45),"QA target is before DB Dev target",IF(AND($V45&lt;&gt;"",$Q45&lt;&gt;"",$V45&lt;$Q45),"QA target is before PBI Dev target",IF(AND($AA45&lt;&gt;"",$V45&lt;&gt;"",$AA45&lt;$V45),"DPO Approval target is before QA target",IF(AND($AG45&lt;&gt;"",$AA45&lt;&gt;"",$AG45&lt;$AA45),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL45" s="41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AM45" s="32" cm="1">
         <f t="array" ref="AM45">_xlfn.LET(_xlpm.rep,$B45,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -8844,15 +8867,15 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:40" ht="14.45" hidden="1">
+    <row r="46" spans="1:40" ht="14.45">
       <c r="A46" s="33" t="s">
         <v>126</v>
       </c>
       <c r="B46" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="C46" s="33" t="s">
         <v>175</v>
-      </c>
-      <c r="C46" s="33" t="s">
-        <v>173</v>
       </c>
       <c r="D46" t="str" cm="1">
         <f t="array" aca="1" ref="D46" ca="1">IF(AND(C46="Ready for Release in Prod",LEFT($AJ46,3)&lt;&gt;"Yes"),IF(AG46&lt;&gt;"","Delivered","On track"),IF($B46="","",IF(LEFT($AJ46,3)="Yes","Blocked - "&amp;MID($AJ46,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B46)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B46)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B46)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C46="NOT STARTED",IF(H46="","No plan date set",IF(H46&lt;TODAY(),"Review - planned start passed","On track")),IF(C46="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B46,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B46,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L46&lt;&gt;"",L46,K46)),_xlpm.act,IF(AND(M46&lt;&gt;"",M46&gt;=_xlpm.sent),M46,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C46="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B46,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B46,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R46&lt;&gt;"",R46,Q46)),_xlpm.act,IF(AND(S46&lt;&gt;"",S46&gt;=_xlpm.sent),S46,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C46="QA",_xlfn.LET(_xlpm.tgt,IF(AM46&lt;&gt;"",AM46,IF(W46&lt;&gt;"",W46,V46)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B46,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y46&lt;&gt;"",Y46&gt;=_xlpm.sent),Y46,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C46="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN46&lt;&gt;"",AN46,IF(AB46&lt;&gt;"",AB46,AA46)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B46,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC46&lt;&gt;"",AC46&gt;=_xlpm.sent),AC46,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C46="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -8939,7 +8962,7 @@
         <v/>
       </c>
       <c r="AL46" s="41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AM46" s="32" cm="1">
         <f t="array" ref="AM46">_xlfn.LET(_xlpm.rep,$B46,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -8958,7 +8981,7 @@
         <v>177</v>
       </c>
       <c r="C47" s="33" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D47" t="str" cm="1">
         <f t="array" aca="1" ref="D47" ca="1">IF(AND(C47="Ready for Release in Prod",LEFT($AJ47,3)&lt;&gt;"Yes"),IF(AG47&lt;&gt;"","Delivered","On track"),IF($B47="","",IF(LEFT($AJ47,3)="Yes","Blocked - "&amp;MID($AJ47,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B47)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B47)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B47)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C47="NOT STARTED",IF(H47="","No plan date set",IF(H47&lt;TODAY(),"Review - planned start passed","On track")),IF(C47="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B47,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B47,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L47&lt;&gt;"",L47,K47)),_xlpm.act,IF(AND(M47&lt;&gt;"",M47&gt;=_xlpm.sent),M47,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C47="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B47,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B47,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R47&lt;&gt;"",R47,Q47)),_xlpm.act,IF(AND(S47&lt;&gt;"",S47&gt;=_xlpm.sent),S47,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C47="QA",_xlfn.LET(_xlpm.tgt,IF(AM47&lt;&gt;"",AM47,IF(W47&lt;&gt;"",W47,V47)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B47,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y47&lt;&gt;"",Y47&gt;=_xlpm.sent),Y47,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C47="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN47&lt;&gt;"",AN47,IF(AB47&lt;&gt;"",AB47,AA47)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B47,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC47&lt;&gt;"",AC47&gt;=_xlpm.sent),AC47,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C47="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -9042,12 +9065,12 @@
       <c r="AJ47" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK47" s="72" t="str">
-        <f>IF($B47="","",IF(AND(LEFT($AJ47,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B47)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ47,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B47)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ47="Yes – needs DB Dev to fix",M47&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B47)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ47="Yes – needs PBI Dev to fix",S47&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B47)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ47="Yes – needs QA to fix",Y47&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B47)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B47)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B47)&gt;0,"",IF(AND(V47&lt;&gt;"",K47&lt;&gt;"",V47&lt;K47),"QA target is before DB Dev target",IF(AND(V47&lt;&gt;"",Q47&lt;&gt;"",V47&lt;Q47),"QA target is before PBI Dev target",IF(AND(AA47&lt;&gt;"",V47&lt;&gt;"",AA47&lt;V47),"DPO Approval target is before QA target",IF(AND(AG47&lt;&gt;"",AA47&lt;&gt;"",AG47&lt;AA47),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK47" s="72" t="str" cm="1">
+        <f t="array" ref="AK47">IF($B47="","",_xlfn.LET(_xlpm.nm,$B47,_xlpm.st,$C47,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M47,_xlpm.st="DB Dev",$M47,_xlpm.st="PBI Dev",$S47,_xlpm.st="QA",$Y47,_xlpm.st="DPO Approval",$AC47,_xlpm.st="Ready for Release in Prod",$AG47,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ47,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ47,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B47)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B47)&gt;0,"",IF(AND($V47&lt;&gt;"",$K47&lt;&gt;"",$V47&lt;$K47),"QA target is before DB Dev target",IF(AND($V47&lt;&gt;"",$Q47&lt;&gt;"",$V47&lt;$Q47),"QA target is before PBI Dev target",IF(AND($AA47&lt;&gt;"",$V47&lt;&gt;"",$AA47&lt;$V47),"DPO Approval target is before QA target",IF(AND($AG47&lt;&gt;"",$AA47&lt;&gt;"",$AG47&lt;$AA47),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL47" s="41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AM47" s="32" t="str" cm="1">
         <f t="array" ref="AM47">_xlfn.LET(_xlpm.rep,$B47,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -9058,7 +9081,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:40" ht="14.45" hidden="1">
+    <row r="48" spans="1:40" ht="14.45">
       <c r="A48" s="33" t="s">
         <v>126</v>
       </c>
@@ -9150,8 +9173,8 @@
       <c r="AJ48" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK48" s="72" t="str">
-        <f>IF($B48="","",IF(AND(LEFT($AJ48,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B48)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ48,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B48)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ48="Yes – needs DB Dev to fix",M48&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B48)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ48="Yes – needs PBI Dev to fix",S48&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B48)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ48="Yes – needs QA to fix",Y48&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B48)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B48)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B48)&gt;0,"",IF(AND(V48&lt;&gt;"",K48&lt;&gt;"",V48&lt;K48),"QA target is before DB Dev target",IF(AND(V48&lt;&gt;"",Q48&lt;&gt;"",V48&lt;Q48),"QA target is before PBI Dev target",IF(AND(AA48&lt;&gt;"",V48&lt;&gt;"",AA48&lt;V48),"DPO Approval target is before QA target",IF(AND(AG48&lt;&gt;"",AA48&lt;&gt;"",AG48&lt;AA48),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK48" s="72" t="str" cm="1">
+        <f t="array" ref="AK48">IF($B48="","",_xlfn.LET(_xlpm.nm,$B48,_xlpm.st,$C48,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M48,_xlpm.st="DB Dev",$M48,_xlpm.st="PBI Dev",$S48,_xlpm.st="QA",$Y48,_xlpm.st="DPO Approval",$AC48,_xlpm.st="Ready for Release in Prod",$AG48,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ48,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ48,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B48)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B48)&gt;0,"",IF(AND($V48&lt;&gt;"",$K48&lt;&gt;"",$V48&lt;$K48),"QA target is before DB Dev target",IF(AND($V48&lt;&gt;"",$Q48&lt;&gt;"",$V48&lt;$Q48),"QA target is before PBI Dev target",IF(AND($AA48&lt;&gt;"",$V48&lt;&gt;"",$AA48&lt;$V48),"DPO Approval target is before QA target",IF(AND($AG48&lt;&gt;"",$AA48&lt;&gt;"",$AG48&lt;$AA48),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL48" s="41" t="s">
@@ -9166,7 +9189,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:40" ht="14.45" hidden="1">
+    <row r="49" spans="1:40" ht="14.45">
       <c r="A49" s="33" t="s">
         <v>126</v>
       </c>
@@ -9256,8 +9279,8 @@
       <c r="AJ49" s="40" t="s">
         <v>183</v>
       </c>
-      <c r="AK49" s="72" t="str">
-        <f>IF($B49="","",IF(AND(LEFT($AJ49,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B49)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ49,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B49)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ49="Yes – needs DB Dev to fix",M49&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B49)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ49="Yes – needs PBI Dev to fix",S49&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B49)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ49="Yes – needs QA to fix",Y49&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B49)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B49)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B49)&gt;0,"",IF(AND(V49&lt;&gt;"",K49&lt;&gt;"",V49&lt;K49),"QA target is before DB Dev target",IF(AND(V49&lt;&gt;"",Q49&lt;&gt;"",V49&lt;Q49),"QA target is before PBI Dev target",IF(AND(AA49&lt;&gt;"",V49&lt;&gt;"",AA49&lt;V49),"DPO Approval target is before QA target",IF(AND(AG49&lt;&gt;"",AA49&lt;&gt;"",AG49&lt;AA49),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK49" s="72" t="str" cm="1">
+        <f t="array" ref="AK49">IF($B49="","",_xlfn.LET(_xlpm.nm,$B49,_xlpm.st,$C49,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M49,_xlpm.st="DB Dev",$M49,_xlpm.st="PBI Dev",$S49,_xlpm.st="QA",$Y49,_xlpm.st="DPO Approval",$AC49,_xlpm.st="Ready for Release in Prod",$AG49,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ49,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ49,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B49)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B49)&gt;0,"",IF(AND($V49&lt;&gt;"",$K49&lt;&gt;"",$V49&lt;$K49),"QA target is before DB Dev target",IF(AND($V49&lt;&gt;"",$Q49&lt;&gt;"",$V49&lt;$Q49),"QA target is before PBI Dev target",IF(AND($AA49&lt;&gt;"",$V49&lt;&gt;"",$AA49&lt;$V49),"DPO Approval target is before QA target",IF(AND($AG49&lt;&gt;"",$AA49&lt;&gt;"",$AG49&lt;$AA49),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL49" s="41"/>
@@ -9270,7 +9293,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:40" ht="15" hidden="1" customHeight="1">
+    <row r="50" spans="1:40" ht="15" customHeight="1">
       <c r="A50" s="33" t="s">
         <v>126</v>
       </c>
@@ -9363,7 +9386,7 @@
         <v>53</v>
       </c>
       <c r="AK50" s="72" t="str" cm="1">
-        <f t="array" ref="AK50">IF($B50="","",IF(AND(LEFT($AJ50,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B50)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ50,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B50)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ50="Yes – needs DB Dev to fix",M50&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B50)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ50="Yes – needs PBI Dev to fix",S50&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B50)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ50="Yes – needs QA to fix",Y50&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B50)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B50)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B50)&gt;0,"",IF(AND(V50&lt;&gt;"",K50&lt;&gt;"",V50&lt;K50),"QA target is before DB Dev target",IF(AND(V50&lt;&gt;"",Q50&lt;&gt;"",V50&lt;Q50),"QA target is before PBI Dev target",IF(AND(AA50&lt;&gt;"",V50&lt;&gt;"",AA50&lt;V50),"DPO Approval target is before QA target",IF(AND(AG50&lt;&gt;"",AA50&lt;&gt;"",AG50&lt;AA50),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <f t="array" ref="AK50">IF($B50="","",_xlfn.LET(_xlpm.nm,$B50,_xlpm.st,$C50,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M50,_xlpm.st="DB Dev",$M50,_xlpm.st="PBI Dev",$S50,_xlpm.st="QA",$Y50,_xlpm.st="DPO Approval",$AC50,_xlpm.st="Ready for Release in Prod",$AG50,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ50,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ50,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B50)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B50)&gt;0,"",IF(AND($V50&lt;&gt;"",$K50&lt;&gt;"",$V50&lt;$K50),"QA target is before DB Dev target",IF(AND($V50&lt;&gt;"",$Q50&lt;&gt;"",$V50&lt;$Q50),"QA target is before PBI Dev target",IF(AND($AA50&lt;&gt;"",$V50&lt;&gt;"",$AA50&lt;$V50),"DPO Approval target is before QA target",IF(AND($AG50&lt;&gt;"",$AA50&lt;&gt;"",$AG50&lt;$AA50),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL50" s="41"/>
@@ -9468,8 +9491,8 @@
       <c r="AJ51" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK51" s="72" t="str">
-        <f>IF($B51="","",IF(AND(LEFT($AJ51,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B51)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ51,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B51)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ51="Yes – needs DB Dev to fix",M51&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B51)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ51="Yes – needs PBI Dev to fix",S51&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B51)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ51="Yes – needs QA to fix",Y51&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B51)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B51)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B51)&gt;0,"",IF(AND(V51&lt;&gt;"",K51&lt;&gt;"",V51&lt;K51),"QA target is before DB Dev target",IF(AND(V51&lt;&gt;"",Q51&lt;&gt;"",V51&lt;Q51),"QA target is before PBI Dev target",IF(AND(AA51&lt;&gt;"",V51&lt;&gt;"",AA51&lt;V51),"DPO Approval target is before QA target",IF(AND(AG51&lt;&gt;"",AA51&lt;&gt;"",AG51&lt;AA51),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK51" s="72" t="str" cm="1">
+        <f t="array" ref="AK51">IF($B51="","",_xlfn.LET(_xlpm.nm,$B51,_xlpm.st,$C51,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M51,_xlpm.st="DB Dev",$M51,_xlpm.st="PBI Dev",$S51,_xlpm.st="QA",$Y51,_xlpm.st="DPO Approval",$AC51,_xlpm.st="Ready for Release in Prod",$AG51,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ51,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ51,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B51)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B51)&gt;0,"",IF(AND($V51&lt;&gt;"",$K51&lt;&gt;"",$V51&lt;$K51),"QA target is before DB Dev target",IF(AND($V51&lt;&gt;"",$Q51&lt;&gt;"",$V51&lt;$Q51),"QA target is before PBI Dev target",IF(AND($AA51&lt;&gt;"",$V51&lt;&gt;"",$AA51&lt;$V51),"DPO Approval target is before QA target",IF(AND($AG51&lt;&gt;"",$AA51&lt;&gt;"",$AG51&lt;$AA51),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL51" s="41" t="s">
@@ -9484,7 +9507,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:40" ht="16.899999999999999" hidden="1" customHeight="1">
+    <row r="52" spans="1:40" ht="16.899999999999999" customHeight="1">
       <c r="A52" s="33" t="s">
         <v>126</v>
       </c>
@@ -9574,9 +9597,9 @@
       <c r="AJ52" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="AK52" s="72" t="str">
-        <f>IF($B52="","",IF(AND(LEFT($AJ52,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B52)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ52,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B52)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ52="Yes – needs DB Dev to fix",M52&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B52)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ52="Yes – needs PBI Dev to fix",S52&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B52)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ52="Yes – needs QA to fix",Y52&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B52)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B52)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B52)&gt;0,"",IF(AND(V52&lt;&gt;"",K52&lt;&gt;"",V52&lt;K52),"QA target is before DB Dev target",IF(AND(V52&lt;&gt;"",Q52&lt;&gt;"",V52&lt;Q52),"QA target is before PBI Dev target",IF(AND(AA52&lt;&gt;"",V52&lt;&gt;"",AA52&lt;V52),"DPO Approval target is before QA target",IF(AND(AG52&lt;&gt;"",AA52&lt;&gt;"",AG52&lt;AA52),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
-        <v/>
+      <c r="AK52" s="72" t="str" cm="1">
+        <f t="array" ref="AK52">IF($B52="","",_xlfn.LET(_xlpm.nm,$B52,_xlpm.st,$C52,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M52,_xlpm.st="DB Dev",$M52,_xlpm.st="PBI Dev",$S52,_xlpm.st="QA",$Y52,_xlpm.st="DPO Approval",$AC52,_xlpm.st="Ready for Release in Prod",$AG52,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ52,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ52,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B52)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B52)&gt;0,"",IF(AND($V52&lt;&gt;"",$K52&lt;&gt;"",$V52&lt;$K52),"QA target is before DB Dev target",IF(AND($V52&lt;&gt;"",$Q52&lt;&gt;"",$V52&lt;$Q52),"QA target is before PBI Dev target",IF(AND($AA52&lt;&gt;"",$V52&lt;&gt;"",$AA52&lt;$V52),"DPO Approval target is before QA target",IF(AND($AG52&lt;&gt;"",$AA52&lt;&gt;"",$AG52&lt;$AA52),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v>Move status back to DB Dev</v>
       </c>
       <c r="AL52" s="79" t="s">
         <v>191</v>
@@ -9682,8 +9705,8 @@
       <c r="AJ53" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK53" s="72" t="str">
-        <f>IF($B53="","",IF(AND(LEFT($AJ53,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B53)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ53,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B53)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ53="Yes – needs DB Dev to fix",M53&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B53)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ53="Yes – needs PBI Dev to fix",S53&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B53)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ53="Yes – needs QA to fix",Y53&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B53)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B53)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B53)&gt;0,"",IF(AND(V53&lt;&gt;"",K53&lt;&gt;"",V53&lt;K53),"QA target is before DB Dev target",IF(AND(V53&lt;&gt;"",Q53&lt;&gt;"",V53&lt;Q53),"QA target is before PBI Dev target",IF(AND(AA53&lt;&gt;"",V53&lt;&gt;"",AA53&lt;V53),"DPO Approval target is before QA target",IF(AND(AG53&lt;&gt;"",AA53&lt;&gt;"",AG53&lt;AA53),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK53" s="72" t="str" cm="1">
+        <f t="array" ref="AK53">IF($B53="","",_xlfn.LET(_xlpm.nm,$B53,_xlpm.st,$C53,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M53,_xlpm.st="DB Dev",$M53,_xlpm.st="PBI Dev",$S53,_xlpm.st="QA",$Y53,_xlpm.st="DPO Approval",$AC53,_xlpm.st="Ready for Release in Prod",$AG53,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ53,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ53,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B53)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B53)&gt;0,"",IF(AND($V53&lt;&gt;"",$K53&lt;&gt;"",$V53&lt;$K53),"QA target is before DB Dev target",IF(AND($V53&lt;&gt;"",$Q53&lt;&gt;"",$V53&lt;$Q53),"QA target is before PBI Dev target",IF(AND($AA53&lt;&gt;"",$V53&lt;&gt;"",$AA53&lt;$V53),"DPO Approval target is before QA target",IF(AND($AG53&lt;&gt;"",$AA53&lt;&gt;"",$AG53&lt;$AA53),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL53" s="41"/>
@@ -9696,7 +9719,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:40" ht="14.45" hidden="1">
+    <row r="54" spans="1:40" ht="14.45">
       <c r="A54" s="33" t="s">
         <v>126</v>
       </c>
@@ -9788,8 +9811,8 @@
       <c r="AJ54" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK54" s="72" t="str">
-        <f>IF($B54="","",IF(AND(LEFT($AJ54,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B54)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ54,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B54)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ54="Yes – needs DB Dev to fix",M54&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B54)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ54="Yes – needs PBI Dev to fix",S54&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B54)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ54="Yes – needs QA to fix",Y54&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B54)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B54)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B54)&gt;0,"",IF(AND(V54&lt;&gt;"",K54&lt;&gt;"",V54&lt;K54),"QA target is before DB Dev target",IF(AND(V54&lt;&gt;"",Q54&lt;&gt;"",V54&lt;Q54),"QA target is before PBI Dev target",IF(AND(AA54&lt;&gt;"",V54&lt;&gt;"",AA54&lt;V54),"DPO Approval target is before QA target",IF(AND(AG54&lt;&gt;"",AA54&lt;&gt;"",AG54&lt;AA54),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK54" s="72" t="str" cm="1">
+        <f t="array" ref="AK54">IF($B54="","",_xlfn.LET(_xlpm.nm,$B54,_xlpm.st,$C54,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M54,_xlpm.st="DB Dev",$M54,_xlpm.st="PBI Dev",$S54,_xlpm.st="QA",$Y54,_xlpm.st="DPO Approval",$AC54,_xlpm.st="Ready for Release in Prod",$AG54,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ54,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ54,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B54)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B54)&gt;0,"",IF(AND($V54&lt;&gt;"",$K54&lt;&gt;"",$V54&lt;$K54),"QA target is before DB Dev target",IF(AND($V54&lt;&gt;"",$Q54&lt;&gt;"",$V54&lt;$Q54),"QA target is before PBI Dev target",IF(AND($AA54&lt;&gt;"",$V54&lt;&gt;"",$AA54&lt;$V54),"DPO Approval target is before QA target",IF(AND($AG54&lt;&gt;"",$AA54&lt;&gt;"",$AG54&lt;$AA54),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL54" s="41"/>
@@ -9802,7 +9825,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:40" ht="14.45" hidden="1">
+    <row r="55" spans="1:40" ht="14.45">
       <c r="A55" s="33" t="s">
         <v>126</v>
       </c>
@@ -9810,7 +9833,7 @@
         <v>195</v>
       </c>
       <c r="C55" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D55" t="str" cm="1">
         <f t="array" aca="1" ref="D55" ca="1">IF(AND(C55="Ready for Release in Prod",LEFT($AJ55,3)&lt;&gt;"Yes"),IF(AG55&lt;&gt;"","Delivered","On track"),IF($B55="","",IF(LEFT($AJ55,3)="Yes","Blocked - "&amp;MID($AJ55,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B55)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B55)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B55)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C55="NOT STARTED",IF(H55="","No plan date set",IF(H55&lt;TODAY(),"Review - planned start passed","On track")),IF(C55="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B55,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B55,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L55&lt;&gt;"",L55,K55)),_xlpm.act,IF(AND(M55&lt;&gt;"",M55&gt;=_xlpm.sent),M55,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C55="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B55,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B55,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R55&lt;&gt;"",R55,Q55)),_xlpm.act,IF(AND(S55&lt;&gt;"",S55&gt;=_xlpm.sent),S55,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C55="QA",_xlfn.LET(_xlpm.tgt,IF(AM55&lt;&gt;"",AM55,IF(W55&lt;&gt;"",W55,V55)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B55,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y55&lt;&gt;"",Y55&gt;=_xlpm.sent),Y55,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C55="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN55&lt;&gt;"",AN55,IF(AB55&lt;&gt;"",AB55,AA55)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B55,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC55&lt;&gt;"",AC55&gt;=_xlpm.sent),AC55,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C55="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -9892,8 +9915,8 @@
       <c r="AJ55" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK55" s="72" t="str">
-        <f>IF($B55="","",IF(AND(LEFT($AJ55,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B55)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ55,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B55)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ55="Yes – needs DB Dev to fix",M55&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B55)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ55="Yes – needs PBI Dev to fix",S55&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B55)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ55="Yes – needs QA to fix",Y55&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B55)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B55)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B55)&gt;0,"",IF(AND(V55&lt;&gt;"",K55&lt;&gt;"",V55&lt;K55),"QA target is before DB Dev target",IF(AND(V55&lt;&gt;"",Q55&lt;&gt;"",V55&lt;Q55),"QA target is before PBI Dev target",IF(AND(AA55&lt;&gt;"",V55&lt;&gt;"",AA55&lt;V55),"DPO Approval target is before QA target",IF(AND(AG55&lt;&gt;"",AA55&lt;&gt;"",AG55&lt;AA55),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK55" s="72" t="str" cm="1">
+        <f t="array" ref="AK55">IF($B55="","",_xlfn.LET(_xlpm.nm,$B55,_xlpm.st,$C55,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M55,_xlpm.st="DB Dev",$M55,_xlpm.st="PBI Dev",$S55,_xlpm.st="QA",$Y55,_xlpm.st="DPO Approval",$AC55,_xlpm.st="Ready for Release in Prod",$AG55,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ55,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ55,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B55)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B55)&gt;0,"",IF(AND($V55&lt;&gt;"",$K55&lt;&gt;"",$V55&lt;$K55),"QA target is before DB Dev target",IF(AND($V55&lt;&gt;"",$Q55&lt;&gt;"",$V55&lt;$Q55),"QA target is before PBI Dev target",IF(AND($AA55&lt;&gt;"",$V55&lt;&gt;"",$AA55&lt;$V55),"DPO Approval target is before QA target",IF(AND($AG55&lt;&gt;"",$AA55&lt;&gt;"",$AG55&lt;$AA55),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL55" s="41" t="s">
@@ -9908,7 +9931,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:40" ht="14.45" hidden="1">
+    <row r="56" spans="1:40" ht="14.45">
       <c r="A56" s="33" t="s">
         <v>126</v>
       </c>
@@ -9916,7 +9939,7 @@
         <v>201</v>
       </c>
       <c r="C56" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D56" t="str" cm="1">
         <f t="array" aca="1" ref="D56" ca="1">IF(AND(C56="Ready for Release in Prod",LEFT($AJ56,3)&lt;&gt;"Yes"),IF(AG56&lt;&gt;"","Delivered","On track"),IF($B56="","",IF(LEFT($AJ56,3)="Yes","Blocked - "&amp;MID($AJ56,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B56)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B56)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B56)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C56="NOT STARTED",IF(H56="","No plan date set",IF(H56&lt;TODAY(),"Review - planned start passed","On track")),IF(C56="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B56,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B56,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L56&lt;&gt;"",L56,K56)),_xlpm.act,IF(AND(M56&lt;&gt;"",M56&gt;=_xlpm.sent),M56,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C56="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B56,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B56,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R56&lt;&gt;"",R56,Q56)),_xlpm.act,IF(AND(S56&lt;&gt;"",S56&gt;=_xlpm.sent),S56,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C56="QA",_xlfn.LET(_xlpm.tgt,IF(AM56&lt;&gt;"",AM56,IF(W56&lt;&gt;"",W56,V56)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B56,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y56&lt;&gt;"",Y56&gt;=_xlpm.sent),Y56,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C56="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN56&lt;&gt;"",AN56,IF(AB56&lt;&gt;"",AB56,AA56)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B56,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC56&lt;&gt;"",AC56&gt;=_xlpm.sent),AC56,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C56="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -10000,8 +10023,8 @@
       <c r="AJ56" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK56" s="72" t="str">
-        <f>IF($B56="","",IF(AND(LEFT($AJ56,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B56)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ56,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B56)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ56="Yes – needs DB Dev to fix",M56&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B56)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ56="Yes – needs PBI Dev to fix",S56&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B56)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ56="Yes – needs QA to fix",Y56&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B56)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B56)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B56)&gt;0,"",IF(AND(V56&lt;&gt;"",K56&lt;&gt;"",V56&lt;K56),"QA target is before DB Dev target",IF(AND(V56&lt;&gt;"",Q56&lt;&gt;"",V56&lt;Q56),"QA target is before PBI Dev target",IF(AND(AA56&lt;&gt;"",V56&lt;&gt;"",AA56&lt;V56),"DPO Approval target is before QA target",IF(AND(AG56&lt;&gt;"",AA56&lt;&gt;"",AG56&lt;AA56),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK56" s="72" t="str" cm="1">
+        <f t="array" ref="AK56">IF($B56="","",_xlfn.LET(_xlpm.nm,$B56,_xlpm.st,$C56,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M56,_xlpm.st="DB Dev",$M56,_xlpm.st="PBI Dev",$S56,_xlpm.st="QA",$Y56,_xlpm.st="DPO Approval",$AC56,_xlpm.st="Ready for Release in Prod",$AG56,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ56,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ56,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B56)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B56)&gt;0,"",IF(AND($V56&lt;&gt;"",$K56&lt;&gt;"",$V56&lt;$K56),"QA target is before DB Dev target",IF(AND($V56&lt;&gt;"",$Q56&lt;&gt;"",$V56&lt;$Q56),"QA target is before PBI Dev target",IF(AND($AA56&lt;&gt;"",$V56&lt;&gt;"",$AA56&lt;$V56),"DPO Approval target is before QA target",IF(AND($AG56&lt;&gt;"",$AA56&lt;&gt;"",$AG56&lt;$AA56),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL56" s="41" t="s">
@@ -10016,7 +10039,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:40" ht="14.45" hidden="1">
+    <row r="57" spans="1:40" ht="14.45">
       <c r="A57" s="33" t="s">
         <v>126</v>
       </c>
@@ -10108,8 +10131,8 @@
       <c r="AJ57" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK57" s="72" t="str">
-        <f>IF($B57="","",IF(AND(LEFT($AJ57,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B57)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ57,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B57)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ57="Yes – needs DB Dev to fix",M57&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B57)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ57="Yes – needs PBI Dev to fix",S57&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B57)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ57="Yes – needs QA to fix",Y57&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B57)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B57)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B57)&gt;0,"",IF(AND(V57&lt;&gt;"",K57&lt;&gt;"",V57&lt;K57),"QA target is before DB Dev target",IF(AND(V57&lt;&gt;"",Q57&lt;&gt;"",V57&lt;Q57),"QA target is before PBI Dev target",IF(AND(AA57&lt;&gt;"",V57&lt;&gt;"",AA57&lt;V57),"DPO Approval target is before QA target",IF(AND(AG57&lt;&gt;"",AA57&lt;&gt;"",AG57&lt;AA57),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK57" s="72" t="str" cm="1">
+        <f t="array" ref="AK57">IF($B57="","",_xlfn.LET(_xlpm.nm,$B57,_xlpm.st,$C57,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M57,_xlpm.st="DB Dev",$M57,_xlpm.st="PBI Dev",$S57,_xlpm.st="QA",$Y57,_xlpm.st="DPO Approval",$AC57,_xlpm.st="Ready for Release in Prod",$AG57,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ57,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ57,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B57)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B57)&gt;0,"",IF(AND($V57&lt;&gt;"",$K57&lt;&gt;"",$V57&lt;$K57),"QA target is before DB Dev target",IF(AND($V57&lt;&gt;"",$Q57&lt;&gt;"",$V57&lt;$Q57),"QA target is before PBI Dev target",IF(AND($AA57&lt;&gt;"",$V57&lt;&gt;"",$AA57&lt;$V57),"DPO Approval target is before QA target",IF(AND($AG57&lt;&gt;"",$AA57&lt;&gt;"",$AG57&lt;$AA57),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL57" s="41" t="s">
@@ -10124,7 +10147,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:40" ht="14.45" hidden="1">
+    <row r="58" spans="1:40" ht="14.45">
       <c r="A58" s="33" t="s">
         <v>126</v>
       </c>
@@ -10206,8 +10229,8 @@
       <c r="AJ58" s="40" t="s">
         <v>183</v>
       </c>
-      <c r="AK58" s="72" t="str">
-        <f>IF($B58="","",IF(AND(LEFT($AJ58,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B58)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ58,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B58)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ58="Yes – needs DB Dev to fix",M58&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B58)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ58="Yes – needs PBI Dev to fix",S58&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B58)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ58="Yes – needs QA to fix",Y58&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B58)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B58)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B58)&gt;0,"",IF(AND(V58&lt;&gt;"",K58&lt;&gt;"",V58&lt;K58),"QA target is before DB Dev target",IF(AND(V58&lt;&gt;"",Q58&lt;&gt;"",V58&lt;Q58),"QA target is before PBI Dev target",IF(AND(AA58&lt;&gt;"",V58&lt;&gt;"",AA58&lt;V58),"DPO Approval target is before QA target",IF(AND(AG58&lt;&gt;"",AA58&lt;&gt;"",AG58&lt;AA58),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK58" s="72" t="str" cm="1">
+        <f t="array" ref="AK58">IF($B58="","",_xlfn.LET(_xlpm.nm,$B58,_xlpm.st,$C58,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M58,_xlpm.st="DB Dev",$M58,_xlpm.st="PBI Dev",$S58,_xlpm.st="QA",$Y58,_xlpm.st="DPO Approval",$AC58,_xlpm.st="Ready for Release in Prod",$AG58,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ58,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ58,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B58)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B58)&gt;0,"",IF(AND($V58&lt;&gt;"",$K58&lt;&gt;"",$V58&lt;$K58),"QA target is before DB Dev target",IF(AND($V58&lt;&gt;"",$Q58&lt;&gt;"",$V58&lt;$Q58),"QA target is before PBI Dev target",IF(AND($AA58&lt;&gt;"",$V58&lt;&gt;"",$AA58&lt;$V58),"DPO Approval target is before QA target",IF(AND($AG58&lt;&gt;"",$AA58&lt;&gt;"",$AG58&lt;$AA58),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v>Blocked - log it on Rework Log</v>
       </c>
       <c r="AL58" s="41" t="s">
@@ -10222,7 +10245,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:40" ht="14.45" hidden="1">
+    <row r="59" spans="1:40" ht="14.45">
       <c r="A59" s="33" t="s">
         <v>126</v>
       </c>
@@ -10308,8 +10331,8 @@
       <c r="AJ59" s="40" t="s">
         <v>210</v>
       </c>
-      <c r="AK59" s="72" t="str">
-        <f>IF($B59="","",IF(AND(LEFT($AJ59,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B59)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ59,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B59)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ59="Yes – needs DB Dev to fix",M59&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B59)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ59="Yes – needs PBI Dev to fix",S59&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B59)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ59="Yes – needs QA to fix",Y59&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B59)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B59)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B59)&gt;0,"",IF(AND(V59&lt;&gt;"",K59&lt;&gt;"",V59&lt;K59),"QA target is before DB Dev target",IF(AND(V59&lt;&gt;"",Q59&lt;&gt;"",V59&lt;Q59),"QA target is before PBI Dev target",IF(AND(AA59&lt;&gt;"",V59&lt;&gt;"",AA59&lt;V59),"DPO Approval target is before QA target",IF(AND(AG59&lt;&gt;"",AA59&lt;&gt;"",AG59&lt;AA59),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK59" s="72" t="str" cm="1">
+        <f t="array" ref="AK59">IF($B59="","",_xlfn.LET(_xlpm.nm,$B59,_xlpm.st,$C59,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M59,_xlpm.st="DB Dev",$M59,_xlpm.st="PBI Dev",$S59,_xlpm.st="QA",$Y59,_xlpm.st="DPO Approval",$AC59,_xlpm.st="Ready for Release in Prod",$AG59,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ59,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ59,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B59)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B59)&gt;0,"",IF(AND($V59&lt;&gt;"",$K59&lt;&gt;"",$V59&lt;$K59),"QA target is before DB Dev target",IF(AND($V59&lt;&gt;"",$Q59&lt;&gt;"",$V59&lt;$Q59),"QA target is before PBI Dev target",IF(AND($AA59&lt;&gt;"",$V59&lt;&gt;"",$AA59&lt;$V59),"DPO Approval target is before QA target",IF(AND($AG59&lt;&gt;"",$AA59&lt;&gt;"",$AG59&lt;$AA59),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL59" s="41"/>
@@ -10322,7 +10345,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:40" ht="14.45" hidden="1">
+    <row r="60" spans="1:40" ht="14.45">
       <c r="A60" s="33" t="s">
         <v>126</v>
       </c>
@@ -10330,7 +10353,7 @@
         <v>211</v>
       </c>
       <c r="C60" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D60" t="str" cm="1">
         <f t="array" aca="1" ref="D60" ca="1">IF(AND(C60="Ready for Release in Prod",LEFT($AJ60,3)&lt;&gt;"Yes"),IF(AG60&lt;&gt;"","Delivered","On track"),IF($B60="","",IF(LEFT($AJ60,3)="Yes","Blocked - "&amp;MID($AJ60,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B60)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B60)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B60)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C60="NOT STARTED",IF(H60="","No plan date set",IF(H60&lt;TODAY(),"Review - planned start passed","On track")),IF(C60="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B60,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B60,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L60&lt;&gt;"",L60,K60)),_xlpm.act,IF(AND(M60&lt;&gt;"",M60&gt;=_xlpm.sent),M60,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C60="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B60,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B60,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R60&lt;&gt;"",R60,Q60)),_xlpm.act,IF(AND(S60&lt;&gt;"",S60&gt;=_xlpm.sent),S60,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C60="QA",_xlfn.LET(_xlpm.tgt,IF(AM60&lt;&gt;"",AM60,IF(W60&lt;&gt;"",W60,V60)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B60,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y60&lt;&gt;"",Y60&gt;=_xlpm.sent),Y60,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C60="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN60&lt;&gt;"",AN60,IF(AB60&lt;&gt;"",AB60,AA60)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B60,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC60&lt;&gt;"",AC60&gt;=_xlpm.sent),AC60,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C60="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -10410,9 +10433,9 @@
       <c r="AJ60" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK60" s="72" t="str">
-        <f>IF($B60="","",IF(AND(LEFT($AJ60,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B60)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ60,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B60)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ60="Yes – needs DB Dev to fix",M60&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B60)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ60="Yes – needs PBI Dev to fix",S60&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B60)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ60="Yes – needs QA to fix",Y60&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B60)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B60)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B60)&gt;0,"",IF(AND(V60&lt;&gt;"",K60&lt;&gt;"",V60&lt;K60),"QA target is before DB Dev target",IF(AND(V60&lt;&gt;"",Q60&lt;&gt;"",V60&lt;Q60),"QA target is before PBI Dev target",IF(AND(AA60&lt;&gt;"",V60&lt;&gt;"",AA60&lt;V60),"DPO Approval target is before QA target",IF(AND(AG60&lt;&gt;"",AA60&lt;&gt;"",AG60&lt;AA60),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
-        <v>Open rework row - mark Blocked? or close it</v>
+      <c r="AK60" s="72" t="str" cm="1">
+        <f t="array" ref="AK60">IF($B60="","",_xlfn.LET(_xlpm.nm,$B60,_xlpm.st,$C60,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M60,_xlpm.st="DB Dev",$M60,_xlpm.st="PBI Dev",$S60,_xlpm.st="QA",$Y60,_xlpm.st="DPO Approval",$AC60,_xlpm.st="Ready for Release in Prod",$AG60,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ60,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ60,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B60)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B60)&gt;0,"",IF(AND($V60&lt;&gt;"",$K60&lt;&gt;"",$V60&lt;$K60),"QA target is before DB Dev target",IF(AND($V60&lt;&gt;"",$Q60&lt;&gt;"",$V60&lt;$Q60),"QA target is before PBI Dev target",IF(AND($AA60&lt;&gt;"",$V60&lt;&gt;"",$AA60&lt;$V60),"DPO Approval target is before QA target",IF(AND($AG60&lt;&gt;"",$AA60&lt;&gt;"",$AG60&lt;$AA60),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v>Move status back to DB Dev</v>
       </c>
       <c r="AL60" s="41"/>
       <c r="AM60" s="32" t="str" cm="1">
@@ -10424,7 +10447,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:40" ht="14.45" hidden="1">
+    <row r="61" spans="1:40" ht="14.45">
       <c r="A61" s="33" t="s">
         <v>126</v>
       </c>
@@ -10432,7 +10455,7 @@
         <v>213</v>
       </c>
       <c r="C61" s="33" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D61" t="str" cm="1">
         <f t="array" aca="1" ref="D61" ca="1">IF(AND(C61="Ready for Release in Prod",LEFT($AJ61,3)&lt;&gt;"Yes"),IF(AG61&lt;&gt;"","Delivered","On track"),IF($B61="","",IF(LEFT($AJ61,3)="Yes","Blocked - "&amp;MID($AJ61,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B61)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B61)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B61)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C61="NOT STARTED",IF(H61="","No plan date set",IF(H61&lt;TODAY(),"Review - planned start passed","On track")),IF(C61="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B61,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B61,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L61&lt;&gt;"",L61,K61)),_xlpm.act,IF(AND(M61&lt;&gt;"",M61&gt;=_xlpm.sent),M61,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C61="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B61,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B61,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R61&lt;&gt;"",R61,Q61)),_xlpm.act,IF(AND(S61&lt;&gt;"",S61&gt;=_xlpm.sent),S61,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C61="QA",_xlfn.LET(_xlpm.tgt,IF(AM61&lt;&gt;"",AM61,IF(W61&lt;&gt;"",W61,V61)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B61,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y61&lt;&gt;"",Y61&gt;=_xlpm.sent),Y61,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C61="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN61&lt;&gt;"",AN61,IF(AB61&lt;&gt;"",AB61,AA61)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B61,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC61&lt;&gt;"",AC61&gt;=_xlpm.sent),AC61,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C61="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -10514,8 +10537,8 @@
       <c r="AJ61" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK61" s="72" t="str">
-        <f>IF($B61="","",IF(AND(LEFT($AJ61,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B61)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ61,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B61)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ61="Yes – needs DB Dev to fix",M61&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B61)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ61="Yes – needs PBI Dev to fix",S61&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B61)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ61="Yes – needs QA to fix",Y61&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B61)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B61)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B61)&gt;0,"",IF(AND(V61&lt;&gt;"",K61&lt;&gt;"",V61&lt;K61),"QA target is before DB Dev target",IF(AND(V61&lt;&gt;"",Q61&lt;&gt;"",V61&lt;Q61),"QA target is before PBI Dev target",IF(AND(AA61&lt;&gt;"",V61&lt;&gt;"",AA61&lt;V61),"DPO Approval target is before QA target",IF(AND(AG61&lt;&gt;"",AA61&lt;&gt;"",AG61&lt;AA61),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK61" s="72" t="str" cm="1">
+        <f t="array" ref="AK61">IF($B61="","",_xlfn.LET(_xlpm.nm,$B61,_xlpm.st,$C61,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M61,_xlpm.st="DB Dev",$M61,_xlpm.st="PBI Dev",$S61,_xlpm.st="QA",$Y61,_xlpm.st="DPO Approval",$AC61,_xlpm.st="Ready for Release in Prod",$AG61,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ61,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ61,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B61)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B61)&gt;0,"",IF(AND($V61&lt;&gt;"",$K61&lt;&gt;"",$V61&lt;$K61),"QA target is before DB Dev target",IF(AND($V61&lt;&gt;"",$Q61&lt;&gt;"",$V61&lt;$Q61),"QA target is before PBI Dev target",IF(AND($AA61&lt;&gt;"",$V61&lt;&gt;"",$AA61&lt;$V61),"DPO Approval target is before QA target",IF(AND($AG61&lt;&gt;"",$AA61&lt;&gt;"",$AG61&lt;$AA61),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL61" s="41" t="s">
@@ -10530,7 +10553,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:40" ht="14.45" hidden="1">
+    <row r="62" spans="1:40" ht="14.45">
       <c r="A62" s="33" t="s">
         <v>126</v>
       </c>
@@ -10538,7 +10561,7 @@
         <v>215</v>
       </c>
       <c r="C62" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D62" t="str" cm="1">
         <f t="array" aca="1" ref="D62" ca="1">IF(AND(C62="Ready for Release in Prod",LEFT($AJ62,3)&lt;&gt;"Yes"),IF(AG62&lt;&gt;"","Delivered","On track"),IF($B62="","",IF(LEFT($AJ62,3)="Yes","Blocked - "&amp;MID($AJ62,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B62)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B62)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B62)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C62="NOT STARTED",IF(H62="","No plan date set",IF(H62&lt;TODAY(),"Review - planned start passed","On track")),IF(C62="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B62,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B62,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L62&lt;&gt;"",L62,K62)),_xlpm.act,IF(AND(M62&lt;&gt;"",M62&gt;=_xlpm.sent),M62,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C62="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B62,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B62,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R62&lt;&gt;"",R62,Q62)),_xlpm.act,IF(AND(S62&lt;&gt;"",S62&gt;=_xlpm.sent),S62,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C62="QA",_xlfn.LET(_xlpm.tgt,IF(AM62&lt;&gt;"",AM62,IF(W62&lt;&gt;"",W62,V62)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B62,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y62&lt;&gt;"",Y62&gt;=_xlpm.sent),Y62,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C62="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN62&lt;&gt;"",AN62,IF(AB62&lt;&gt;"",AB62,AA62)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B62,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC62&lt;&gt;"",AC62&gt;=_xlpm.sent),AC62,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C62="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -10614,8 +10637,8 @@
       <c r="AJ62" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK62" s="72" t="str">
-        <f>IF($B62="","",IF(AND(LEFT($AJ62,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B62)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ62,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B62)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ62="Yes – needs DB Dev to fix",M62&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B62)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ62="Yes – needs PBI Dev to fix",S62&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B62)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ62="Yes – needs QA to fix",Y62&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B62)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B62)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B62)&gt;0,"",IF(AND(V62&lt;&gt;"",K62&lt;&gt;"",V62&lt;K62),"QA target is before DB Dev target",IF(AND(V62&lt;&gt;"",Q62&lt;&gt;"",V62&lt;Q62),"QA target is before PBI Dev target",IF(AND(AA62&lt;&gt;"",V62&lt;&gt;"",AA62&lt;V62),"DPO Approval target is before QA target",IF(AND(AG62&lt;&gt;"",AA62&lt;&gt;"",AG62&lt;AA62),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK62" s="72" t="str" cm="1">
+        <f t="array" ref="AK62">IF($B62="","",_xlfn.LET(_xlpm.nm,$B62,_xlpm.st,$C62,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M62,_xlpm.st="DB Dev",$M62,_xlpm.st="PBI Dev",$S62,_xlpm.st="QA",$Y62,_xlpm.st="DPO Approval",$AC62,_xlpm.st="Ready for Release in Prod",$AG62,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ62,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ62,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B62)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B62)&gt;0,"",IF(AND($V62&lt;&gt;"",$K62&lt;&gt;"",$V62&lt;$K62),"QA target is before DB Dev target",IF(AND($V62&lt;&gt;"",$Q62&lt;&gt;"",$V62&lt;$Q62),"QA target is before PBI Dev target",IF(AND($AA62&lt;&gt;"",$V62&lt;&gt;"",$AA62&lt;$V62),"DPO Approval target is before QA target",IF(AND($AG62&lt;&gt;"",$AA62&lt;&gt;"",$AG62&lt;$AA62),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL62" s="41"/>
@@ -10628,7 +10651,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:40" ht="14.45" hidden="1">
+    <row r="63" spans="1:40" ht="14.45">
       <c r="A63" s="33" t="s">
         <v>126</v>
       </c>
@@ -10636,7 +10659,7 @@
         <v>217</v>
       </c>
       <c r="C63" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D63" t="str" cm="1">
         <f t="array" aca="1" ref="D63" ca="1">IF(AND(C63="Ready for Release in Prod",LEFT($AJ63,3)&lt;&gt;"Yes"),IF(AG63&lt;&gt;"","Delivered","On track"),IF($B63="","",IF(LEFT($AJ63,3)="Yes","Blocked - "&amp;MID($AJ63,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B63)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B63)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B63)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C63="NOT STARTED",IF(H63="","No plan date set",IF(H63&lt;TODAY(),"Review - planned start passed","On track")),IF(C63="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B63,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B63,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L63&lt;&gt;"",L63,K63)),_xlpm.act,IF(AND(M63&lt;&gt;"",M63&gt;=_xlpm.sent),M63,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C63="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B63,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B63,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R63&lt;&gt;"",R63,Q63)),_xlpm.act,IF(AND(S63&lt;&gt;"",S63&gt;=_xlpm.sent),S63,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C63="QA",_xlfn.LET(_xlpm.tgt,IF(AM63&lt;&gt;"",AM63,IF(W63&lt;&gt;"",W63,V63)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B63,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y63&lt;&gt;"",Y63&gt;=_xlpm.sent),Y63,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C63="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN63&lt;&gt;"",AN63,IF(AB63&lt;&gt;"",AB63,AA63)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B63,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC63&lt;&gt;"",AC63&gt;=_xlpm.sent),AC63,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C63="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -10712,8 +10735,8 @@
       <c r="AJ63" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK63" s="72" t="str">
-        <f>IF($B63="","",IF(AND(LEFT($AJ63,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B63)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ63,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B63)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ63="Yes – needs DB Dev to fix",M63&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B63)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ63="Yes – needs PBI Dev to fix",S63&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B63)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ63="Yes – needs QA to fix",Y63&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B63)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B63)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B63)&gt;0,"",IF(AND(V63&lt;&gt;"",K63&lt;&gt;"",V63&lt;K63),"QA target is before DB Dev target",IF(AND(V63&lt;&gt;"",Q63&lt;&gt;"",V63&lt;Q63),"QA target is before PBI Dev target",IF(AND(AA63&lt;&gt;"",V63&lt;&gt;"",AA63&lt;V63),"DPO Approval target is before QA target",IF(AND(AG63&lt;&gt;"",AA63&lt;&gt;"",AG63&lt;AA63),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK63" s="72" t="str" cm="1">
+        <f t="array" ref="AK63">IF($B63="","",_xlfn.LET(_xlpm.nm,$B63,_xlpm.st,$C63,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M63,_xlpm.st="DB Dev",$M63,_xlpm.st="PBI Dev",$S63,_xlpm.st="QA",$Y63,_xlpm.st="DPO Approval",$AC63,_xlpm.st="Ready for Release in Prod",$AG63,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ63,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ63,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B63)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B63)&gt;0,"",IF(AND($V63&lt;&gt;"",$K63&lt;&gt;"",$V63&lt;$K63),"QA target is before DB Dev target",IF(AND($V63&lt;&gt;"",$Q63&lt;&gt;"",$V63&lt;$Q63),"QA target is before PBI Dev target",IF(AND($AA63&lt;&gt;"",$V63&lt;&gt;"",$AA63&lt;$V63),"DPO Approval target is before QA target",IF(AND($AG63&lt;&gt;"",$AA63&lt;&gt;"",$AG63&lt;$AA63),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL63" s="41" t="s">
@@ -10728,7 +10751,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:40" s="119" customFormat="1" ht="14.45" hidden="1">
+    <row r="64" spans="1:40" s="119" customFormat="1" ht="14.45">
       <c r="A64" s="118" t="s">
         <v>126</v>
       </c>
@@ -10736,7 +10759,7 @@
         <v>220</v>
       </c>
       <c r="C64" s="118" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D64" s="119" t="str" cm="1">
         <f t="array" aca="1" ref="D64" ca="1">IF(AND(C64="Ready for Release in Prod",LEFT($AJ64,3)&lt;&gt;"Yes"),IF(AG64&lt;&gt;"","Delivered","On track"),IF($B64="","",IF(LEFT($AJ64,3)="Yes","Blocked - "&amp;MID($AJ64,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B64)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B64)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B64)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C64="NOT STARTED",IF(H64="","No plan date set",IF(H64&lt;TODAY(),"Review - planned start passed","On track")),IF(C64="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B64,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B64,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L64&lt;&gt;"",L64,K64)),_xlpm.act,IF(AND(M64&lt;&gt;"",M64&gt;=_xlpm.sent),M64,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C64="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B64,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B64,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R64&lt;&gt;"",R64,Q64)),_xlpm.act,IF(AND(S64&lt;&gt;"",S64&gt;=_xlpm.sent),S64,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C64="QA",_xlfn.LET(_xlpm.tgt,IF(AM64&lt;&gt;"",AM64,IF(W64&lt;&gt;"",W64,V64)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B64,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y64&lt;&gt;"",Y64&gt;=_xlpm.sent),Y64,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C64="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN64&lt;&gt;"",AN64,IF(AB64&lt;&gt;"",AB64,AA64)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B64,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC64&lt;&gt;"",AC64&gt;=_xlpm.sent),AC64,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C64="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -10814,8 +10837,8 @@
       <c r="AJ64" s="131" t="s">
         <v>53</v>
       </c>
-      <c r="AK64" s="132" t="str">
-        <f>IF($B64="","",IF(AND(LEFT($AJ64,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B64)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ64,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B64)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ64="Yes – needs DB Dev to fix",M64&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B64)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ64="Yes – needs PBI Dev to fix",S64&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B64)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ64="Yes – needs QA to fix",Y64&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B64)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B64)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B64)&gt;0,"",IF(AND(V64&lt;&gt;"",K64&lt;&gt;"",V64&lt;K64),"QA target is before DB Dev target",IF(AND(V64&lt;&gt;"",Q64&lt;&gt;"",V64&lt;Q64),"QA target is before PBI Dev target",IF(AND(AA64&lt;&gt;"",V64&lt;&gt;"",AA64&lt;V64),"DPO Approval target is before QA target",IF(AND(AG64&lt;&gt;"",AA64&lt;&gt;"",AG64&lt;AA64),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK64" s="132" t="str" cm="1">
+        <f t="array" ref="AK64">IF($B64="","",_xlfn.LET(_xlpm.nm,$B64,_xlpm.st,$C64,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M64,_xlpm.st="DB Dev",$M64,_xlpm.st="PBI Dev",$S64,_xlpm.st="QA",$Y64,_xlpm.st="DPO Approval",$AC64,_xlpm.st="Ready for Release in Prod",$AG64,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ64,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ64,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B64)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B64)&gt;0,"",IF(AND($V64&lt;&gt;"",$K64&lt;&gt;"",$V64&lt;$K64),"QA target is before DB Dev target",IF(AND($V64&lt;&gt;"",$Q64&lt;&gt;"",$V64&lt;$Q64),"QA target is before PBI Dev target",IF(AND($AA64&lt;&gt;"",$V64&lt;&gt;"",$AA64&lt;$V64),"DPO Approval target is before QA target",IF(AND($AG64&lt;&gt;"",$AA64&lt;&gt;"",$AG64&lt;$AA64),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL64" s="133"/>
@@ -10828,7 +10851,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:40" ht="14.45" hidden="1">
+    <row r="65" spans="1:40" ht="14.45">
       <c r="A65" s="33" t="s">
         <v>126</v>
       </c>
@@ -10836,7 +10859,7 @@
         <v>222</v>
       </c>
       <c r="C65" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D65" t="str" cm="1">
         <f t="array" aca="1" ref="D65" ca="1">IF(AND(C65="Ready for Release in Prod",LEFT($AJ65,3)&lt;&gt;"Yes"),IF(AG65&lt;&gt;"","Delivered","On track"),IF($B65="","",IF(LEFT($AJ65,3)="Yes","Blocked - "&amp;MID($AJ65,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B65)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B65)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B65)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C65="NOT STARTED",IF(H65="","No plan date set",IF(H65&lt;TODAY(),"Review - planned start passed","On track")),IF(C65="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B65,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B65,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L65&lt;&gt;"",L65,K65)),_xlpm.act,IF(AND(M65&lt;&gt;"",M65&gt;=_xlpm.sent),M65,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C65="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B65,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B65,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R65&lt;&gt;"",R65,Q65)),_xlpm.act,IF(AND(S65&lt;&gt;"",S65&gt;=_xlpm.sent),S65,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C65="QA",_xlfn.LET(_xlpm.tgt,IF(AM65&lt;&gt;"",AM65,IF(W65&lt;&gt;"",W65,V65)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B65,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y65&lt;&gt;"",Y65&gt;=_xlpm.sent),Y65,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C65="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN65&lt;&gt;"",AN65,IF(AB65&lt;&gt;"",AB65,AA65)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B65,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC65&lt;&gt;"",AC65&gt;=_xlpm.sent),AC65,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C65="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -10918,8 +10941,8 @@
       <c r="AJ65" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK65" s="72" t="str">
-        <f>IF($B65="","",IF(AND(LEFT($AJ65,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B65)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ65,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B65)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ65="Yes – needs DB Dev to fix",M65&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B65)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ65="Yes – needs PBI Dev to fix",R58&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B65)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ65="Yes – needs QA to fix",Y65&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B65)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B65)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B65)&gt;0,"",IF(AND(V65&lt;&gt;"",K65&lt;&gt;"",V65&lt;K65),"QA target is before DB Dev target",IF(AND(V65&lt;&gt;"",Q65&lt;&gt;"",V65&lt;Q65),"QA target is before PBI Dev target",IF(AND(AA65&lt;&gt;"",V65&lt;&gt;"",AA65&lt;V65),"DPO Approval target is before QA target",IF(AND(AG65&lt;&gt;"",AA65&lt;&gt;"",AG65&lt;AA65),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK65" s="72" t="str" cm="1">
+        <f t="array" ref="AK65">IF($B65="","",_xlfn.LET(_xlpm.nm,$B65,_xlpm.st,$C65,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M65,_xlpm.st="DB Dev",$M65,_xlpm.st="PBI Dev",$S65,_xlpm.st="QA",$Y65,_xlpm.st="DPO Approval",$AC65,_xlpm.st="Ready for Release in Prod",$AG65,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ65,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ65,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B65)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B65)&gt;0,"",IF(AND($V65&lt;&gt;"",$K65&lt;&gt;"",$V65&lt;$K65),"QA target is before DB Dev target",IF(AND($V65&lt;&gt;"",$Q65&lt;&gt;"",$V65&lt;$Q65),"QA target is before PBI Dev target",IF(AND($AA65&lt;&gt;"",$V65&lt;&gt;"",$AA65&lt;$V65),"DPO Approval target is before QA target",IF(AND($AG65&lt;&gt;"",$AA65&lt;&gt;"",$AG65&lt;$AA65),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL65" s="41"/>
@@ -10932,7 +10955,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:40" s="136" customFormat="1" ht="14.45" hidden="1">
+    <row r="66" spans="1:40" s="136" customFormat="1" ht="14.45">
       <c r="A66" s="157" t="s">
         <v>126</v>
       </c>
@@ -11010,8 +11033,8 @@
       <c r="AJ66" s="166" t="s">
         <v>53</v>
       </c>
-      <c r="AK66" s="167" t="str">
-        <f>IF($B66="","",IF(AND(LEFT($AJ66,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B66)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ66,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B66)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ66="Yes – needs DB Dev to fix",M66&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B66)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ66="Yes – needs PBI Dev to fix",S66&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B66)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ66="Yes – needs QA to fix",Y66&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B66)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B66)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B66)&gt;0,"",IF(AND(V66&lt;&gt;"",K66&lt;&gt;"",V66&lt;K66),"QA target is before DB Dev target",IF(AND(V66&lt;&gt;"",Q66&lt;&gt;"",V66&lt;Q66),"QA target is before PBI Dev target",IF(AND(AA66&lt;&gt;"",V66&lt;&gt;"",AA66&lt;V66),"DPO Approval target is before QA target",IF(AND(AG66&lt;&gt;"",AA66&lt;&gt;"",AG66&lt;AA66),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK66" s="167" t="str" cm="1">
+        <f t="array" ref="AK66">IF($B66="","",_xlfn.LET(_xlpm.nm,$B66,_xlpm.st,$C66,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M66,_xlpm.st="DB Dev",$M66,_xlpm.st="PBI Dev",$S66,_xlpm.st="QA",$Y66,_xlpm.st="DPO Approval",$AC66,_xlpm.st="Ready for Release in Prod",$AG66,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ66,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ66,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B66)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B66)&gt;0,"",IF(AND($V66&lt;&gt;"",$K66&lt;&gt;"",$V66&lt;$K66),"QA target is before DB Dev target",IF(AND($V66&lt;&gt;"",$Q66&lt;&gt;"",$V66&lt;$Q66),"QA target is before PBI Dev target",IF(AND($AA66&lt;&gt;"",$V66&lt;&gt;"",$AA66&lt;$V66),"DPO Approval target is before QA target",IF(AND($AG66&lt;&gt;"",$AA66&lt;&gt;"",$AG66&lt;$AA66),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL66" s="168"/>
@@ -11024,7 +11047,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:40" ht="14.45" hidden="1">
+    <row r="67" spans="1:40" ht="14.45">
       <c r="A67" s="33" t="s">
         <v>126</v>
       </c>
@@ -11032,7 +11055,7 @@
         <v>225</v>
       </c>
       <c r="C67" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D67" t="str" cm="1">
         <f t="array" aca="1" ref="D67" ca="1">IF(AND(C67="Ready for Release in Prod",LEFT($AJ67,3)&lt;&gt;"Yes"),IF(AG67&lt;&gt;"","Delivered","On track"),IF($B67="","",IF(LEFT($AJ67,3)="Yes","Blocked - "&amp;MID($AJ67,7,100)&amp;IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B67)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0,"",IF(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B67)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))=0," - unclaimed"," - promised "&amp;TEXT(SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B67)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498)),"m/d"))),IF(C67="NOT STARTED",IF(H67="","No plan date set",IF(H67&lt;TODAY(),"Review - planned start passed","On track")),IF(C67="DB Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B67,'Rework Log'!$D$3:$D$498,"DB Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B67,'Rework Log'!$D$3:$D$498,"DB Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(L67&lt;&gt;"",L67,K67)),_xlpm.act,IF(AND(M67&lt;&gt;"",M67&gt;=_xlpm.sent),M67,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C67="PBI Dev",_xlfn.LET(_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B67,'Rework Log'!$D$3:$D$498,"PBI Dev"),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,$B67,'Rework Log'!$D$3:$D$498,"PBI Dev",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.tgt,IF(_xlpm.expfix&gt;0,_xlpm.expfix,IF(R67&lt;&gt;"",R67,Q67)),_xlpm.act,IF(AND(S67&lt;&gt;"",S67&gt;=_xlpm.sent),S67,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C67="QA",_xlfn.LET(_xlpm.tgt,IF(AM67&lt;&gt;"",AM67,IF(W67&lt;&gt;"",W67,V67)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B67,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.act,IF(AND(Y67&lt;&gt;"",Y67&gt;=_xlpm.sent),Y67,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C67="DPO Approval",_xlfn.LET(_xlpm.tgt,IF(AN67&lt;&gt;"",AN67,IF(AB67&lt;&gt;"",AB67,AA67)),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,$B67,'Rework Log'!$C$3:$C$498,"DPO*"),_xlpm.act,IF(AND(AC67&lt;&gt;"",AC67&gt;=_xlpm.sent),AC67,""),IF(_xlpm.tgt="","No target set",IF(AND(_xlpm.tgt&lt;TODAY(),_xlpm.act=""),"Overdue","On track"))),IF(C67="RELEASED IN PROD","Delivered","")))))))))</f>
@@ -11112,8 +11135,8 @@
       <c r="AJ67" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK67" s="72" t="str">
-        <f>IF($B67="","",IF(AND(LEFT($AJ67,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B67)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ67,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B67)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ67="Yes – needs DB Dev to fix",M67&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B67)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ67="Yes – needs PBI Dev to fix",S67&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B67)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ67="Yes – needs QA to fix",Y67&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B67)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B67)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B67)&gt;0,"",IF(AND(V67&lt;&gt;"",K67&lt;&gt;"",V67&lt;K67),"QA target is before DB Dev target",IF(AND(V67&lt;&gt;"",Q67&lt;&gt;"",V67&lt;Q67),"QA target is before PBI Dev target",IF(AND(AA67&lt;&gt;"",V67&lt;&gt;"",AA67&lt;V67),"DPO Approval target is before QA target",IF(AND(AG67&lt;&gt;"",AA67&lt;&gt;"",AG67&lt;AA67),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK67" s="72" t="str" cm="1">
+        <f t="array" ref="AK67">IF($B67="","",_xlfn.LET(_xlpm.nm,$B67,_xlpm.st,$C67,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M67,_xlpm.st="DB Dev",$M67,_xlpm.st="PBI Dev",$S67,_xlpm.st="QA",$Y67,_xlpm.st="DPO Approval",$AC67,_xlpm.st="Ready for Release in Prod",$AG67,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ67,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ67,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B67)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B67)&gt;0,"",IF(AND($V67&lt;&gt;"",$K67&lt;&gt;"",$V67&lt;$K67),"QA target is before DB Dev target",IF(AND($V67&lt;&gt;"",$Q67&lt;&gt;"",$V67&lt;$Q67),"QA target is before PBI Dev target",IF(AND($AA67&lt;&gt;"",$V67&lt;&gt;"",$AA67&lt;$V67),"DPO Approval target is before QA target",IF(AND($AG67&lt;&gt;"",$AA67&lt;&gt;"",$AG67&lt;$AA67),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL67" s="41"/>
@@ -11126,7 +11149,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:40" s="81" customFormat="1" ht="14.45" hidden="1">
+    <row r="68" spans="1:40" s="81" customFormat="1" ht="14.45">
       <c r="A68" s="80" t="s">
         <v>126</v>
       </c>
@@ -11206,8 +11229,8 @@
       <c r="AJ68" s="93" t="s">
         <v>53</v>
       </c>
-      <c r="AK68" s="94" t="str">
-        <f>IF($B68="","",IF(AND(LEFT($AJ68,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B68)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ68,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B68)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ68="Yes – needs DB Dev to fix",M68&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B68)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ68="Yes – needs PBI Dev to fix",S68&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B68)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ68="Yes – needs QA to fix",Y68&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B68)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B68)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B68)&gt;0,"",IF(AND(V68&lt;&gt;"",K68&lt;&gt;"",V68&lt;K68),"QA target is before DB Dev target",IF(AND(V68&lt;&gt;"",Q68&lt;&gt;"",V68&lt;Q68),"QA target is before PBI Dev target",IF(AND(AA68&lt;&gt;"",V68&lt;&gt;"",AA68&lt;V68),"DPO Approval target is before QA target",IF(AND(AG68&lt;&gt;"",AA68&lt;&gt;"",AG68&lt;AA68),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK68" s="94" t="str" cm="1">
+        <f t="array" ref="AK68">IF($B68="","",_xlfn.LET(_xlpm.nm,$B68,_xlpm.st,$C68,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M68,_xlpm.st="DB Dev",$M68,_xlpm.st="PBI Dev",$S68,_xlpm.st="QA",$Y68,_xlpm.st="DPO Approval",$AC68,_xlpm.st="Ready for Release in Prod",$AG68,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ68,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ68,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B68)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B68)&gt;0,"",IF(AND($V68&lt;&gt;"",$K68&lt;&gt;"",$V68&lt;$K68),"QA target is before DB Dev target",IF(AND($V68&lt;&gt;"",$Q68&lt;&gt;"",$V68&lt;$Q68),"QA target is before PBI Dev target",IF(AND($AA68&lt;&gt;"",$V68&lt;&gt;"",$AA68&lt;$V68),"DPO Approval target is before QA target",IF(AND($AG68&lt;&gt;"",$AA68&lt;&gt;"",$AG68&lt;$AA68),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL68" s="95" t="s">
@@ -11222,7 +11245,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:40" s="98" customFormat="1" ht="14.45" hidden="1">
+    <row r="69" spans="1:40" s="98" customFormat="1" ht="14.45">
       <c r="A69" s="97" t="s">
         <v>126</v>
       </c>
@@ -11298,8 +11321,8 @@
       <c r="AJ69" s="110" t="s">
         <v>53</v>
       </c>
-      <c r="AK69" s="111" t="str">
-        <f>IF($B69="","",IF(AND(LEFT($AJ69,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B69)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ69,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B69)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ69="Yes – needs DB Dev to fix",M69&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B69)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ69="Yes – needs PBI Dev to fix",S69&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B69)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ69="Yes – needs QA to fix",Y69&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B69)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B69)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B69)&gt;0,"",IF(AND(V69&lt;&gt;"",K69&lt;&gt;"",V69&lt;K69),"QA target is before DB Dev target",IF(AND(V69&lt;&gt;"",Q69&lt;&gt;"",V69&lt;Q69),"QA target is before PBI Dev target",IF(AND(AA69&lt;&gt;"",V69&lt;&gt;"",AA69&lt;V69),"DPO Approval target is before QA target",IF(AND(AG69&lt;&gt;"",AA69&lt;&gt;"",AG69&lt;AA69),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK69" s="111" t="str" cm="1">
+        <f t="array" ref="AK69">IF($B69="","",_xlfn.LET(_xlpm.nm,$B69,_xlpm.st,$C69,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M69,_xlpm.st="DB Dev",$M69,_xlpm.st="PBI Dev",$S69,_xlpm.st="QA",$Y69,_xlpm.st="DPO Approval",$AC69,_xlpm.st="Ready for Release in Prod",$AG69,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ69,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ69,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B69)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B69)&gt;0,"",IF(AND($V69&lt;&gt;"",$K69&lt;&gt;"",$V69&lt;$K69),"QA target is before DB Dev target",IF(AND($V69&lt;&gt;"",$Q69&lt;&gt;"",$V69&lt;$Q69),"QA target is before PBI Dev target",IF(AND($AA69&lt;&gt;"",$V69&lt;&gt;"",$AA69&lt;$V69),"DPO Approval target is before QA target",IF(AND($AG69&lt;&gt;"",$AA69&lt;&gt;"",$AG69&lt;$AA69),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL69" s="112" t="s">
@@ -11314,7 +11337,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:40" ht="14.45" hidden="1">
+    <row r="70" spans="1:40" ht="14.45">
       <c r="A70" s="33" t="s">
         <v>126</v>
       </c>
@@ -11398,8 +11421,8 @@
       <c r="AJ70" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK70" s="72" t="str">
-        <f>IF($B70="","",IF(AND(LEFT($AJ70,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B70)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ70,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B70)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ70="Yes – needs DB Dev to fix",M70&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B70)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ70="Yes – needs PBI Dev to fix",S70&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B70)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ70="Yes – needs QA to fix",Y70&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B70)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B70)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B70)&gt;0,"",IF(AND(V70&lt;&gt;"",K70&lt;&gt;"",V70&lt;K70),"QA target is before DB Dev target",IF(AND(V70&lt;&gt;"",Q70&lt;&gt;"",V70&lt;Q70),"QA target is before PBI Dev target",IF(AND(AA70&lt;&gt;"",V70&lt;&gt;"",AA70&lt;V70),"DPO Approval target is before QA target",IF(AND(AG70&lt;&gt;"",AA70&lt;&gt;"",AG70&lt;AA70),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK70" s="72" t="str" cm="1">
+        <f t="array" ref="AK70">IF($B70="","",_xlfn.LET(_xlpm.nm,$B70,_xlpm.st,$C70,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M70,_xlpm.st="DB Dev",$M70,_xlpm.st="PBI Dev",$S70,_xlpm.st="QA",$Y70,_xlpm.st="DPO Approval",$AC70,_xlpm.st="Ready for Release in Prod",$AG70,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ70,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ70,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B70)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B70)&gt;0,"",IF(AND($V70&lt;&gt;"",$K70&lt;&gt;"",$V70&lt;$K70),"QA target is before DB Dev target",IF(AND($V70&lt;&gt;"",$Q70&lt;&gt;"",$V70&lt;$Q70),"QA target is before PBI Dev target",IF(AND($AA70&lt;&gt;"",$V70&lt;&gt;"",$AA70&lt;$V70),"DPO Approval target is before QA target",IF(AND($AG70&lt;&gt;"",$AA70&lt;&gt;"",$AG70&lt;$AA70),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL70" s="41"/>
@@ -11412,7 +11435,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:40" ht="14.45" hidden="1">
+    <row r="71" spans="1:40" ht="14.45">
       <c r="A71" s="33" t="s">
         <v>126</v>
       </c>
@@ -11498,9 +11521,9 @@
       <c r="AJ71" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK71" s="72" t="str">
-        <f>IF($B71="","",IF(AND(LEFT($AJ71,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B71)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ71,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B71)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ71="Yes – needs DB Dev to fix",M71&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B71)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ71="Yes – needs PBI Dev to fix",S71&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B71)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ71="Yes – needs QA to fix",Y71&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B71)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B71)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B71)&gt;0,"",IF(AND(V71&lt;&gt;"",K71&lt;&gt;"",V71&lt;K71),"QA target is before DB Dev target",IF(AND(V71&lt;&gt;"",Q71&lt;&gt;"",V71&lt;Q71),"QA target is before PBI Dev target",IF(AND(AA71&lt;&gt;"",V71&lt;&gt;"",AA71&lt;V71),"DPO Approval target is before QA target",IF(AND(AG71&lt;&gt;"",AA71&lt;&gt;"",AG71&lt;AA71),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
-        <v/>
+      <c r="AK71" s="72" t="str" cm="1">
+        <f t="array" ref="AK71">IF($B71="","",_xlfn.LET(_xlpm.nm,$B71,_xlpm.st,$C71,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M71,_xlpm.st="DB Dev",$M71,_xlpm.st="PBI Dev",$S71,_xlpm.st="QA",$Y71,_xlpm.st="DPO Approval",$AC71,_xlpm.st="Ready for Release in Prod",$AG71,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ71,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ71,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B71)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B71)&gt;0,"",IF(AND($V71&lt;&gt;"",$K71&lt;&gt;"",$V71&lt;$K71),"QA target is before DB Dev target",IF(AND($V71&lt;&gt;"",$Q71&lt;&gt;"",$V71&lt;$Q71),"QA target is before PBI Dev target",IF(AND($AA71&lt;&gt;"",$V71&lt;&gt;"",$AA71&lt;$V71),"DPO Approval target is before QA target",IF(AND($AG71&lt;&gt;"",$AA71&lt;&gt;"",$AG71&lt;$AA71),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v>Move status to PBI Dev</v>
       </c>
       <c r="AL71" s="41" t="s">
         <v>238</v>
@@ -11514,7 +11537,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:40" ht="17.25" hidden="1" customHeight="1">
+    <row r="72" spans="1:40" ht="17.25" customHeight="1">
       <c r="A72" s="33" t="s">
         <v>126</v>
       </c>
@@ -11608,8 +11631,8 @@
       <c r="AJ72" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AK72" s="72" t="str">
-        <f>IF($B72="","",IF(AND(LEFT($AJ72,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B72)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ72,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B72)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ72="Yes – needs DB Dev to fix",M72&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B72)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ72="Yes – needs PBI Dev to fix",S72&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B72)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ72="Yes – needs QA to fix",Y72&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B72)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B72)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B72)&gt;0,"",IF(AND(V72&lt;&gt;"",K72&lt;&gt;"",V72&lt;K72),"QA target is before DB Dev target",IF(AND(V72&lt;&gt;"",Q72&lt;&gt;"",V72&lt;Q72),"QA target is before PBI Dev target",IF(AND(AA72&lt;&gt;"",V72&lt;&gt;"",AA72&lt;V72),"DPO Approval target is before QA target",IF(AND(AG72&lt;&gt;"",AA72&lt;&gt;"",AG72&lt;AA72),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK72" s="72" t="str" cm="1">
+        <f t="array" ref="AK72">IF($B72="","",_xlfn.LET(_xlpm.nm,$B72,_xlpm.st,$C72,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M72,_xlpm.st="DB Dev",$M72,_xlpm.st="PBI Dev",$S72,_xlpm.st="QA",$Y72,_xlpm.st="DPO Approval",$AC72,_xlpm.st="Ready for Release in Prod",$AG72,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ72,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ72,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B72)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B72)&gt;0,"",IF(AND($V72&lt;&gt;"",$K72&lt;&gt;"",$V72&lt;$K72),"QA target is before DB Dev target",IF(AND($V72&lt;&gt;"",$Q72&lt;&gt;"",$V72&lt;$Q72),"QA target is before PBI Dev target",IF(AND($AA72&lt;&gt;"",$V72&lt;&gt;"",$AA72&lt;$V72),"DPO Approval target is before QA target",IF(AND($AG72&lt;&gt;"",$AA72&lt;&gt;"",$AG72&lt;$AA72),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL72" s="41"/>
@@ -11622,7 +11645,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:40" ht="14.45" hidden="1">
+    <row r="73" spans="1:40" ht="14.45">
       <c r="A73" s="76" t="s">
         <v>126</v>
       </c>
@@ -11702,8 +11725,8 @@
       <c r="AH73" s="31"/>
       <c r="AI73" s="31"/>
       <c r="AJ73" s="31"/>
-      <c r="AK73" s="31" t="str">
-        <f>IF($B73="","",IF(AND(LEFT($AJ73,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B73)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ73,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B73)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ73="Yes – needs DB Dev to fix",M73&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B73)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ73="Yes – needs PBI Dev to fix",S73&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B73)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ73="Yes – needs QA to fix",Y73&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B73)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B73)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B73)&gt;0,"",IF(AND(V73&lt;&gt;"",K73&lt;&gt;"",V73&lt;K73),"QA target is before DB Dev target",IF(AND(V73&lt;&gt;"",Q73&lt;&gt;"",V73&lt;Q73),"QA target is before PBI Dev target",IF(AND(AA73&lt;&gt;"",V73&lt;&gt;"",AA73&lt;V73),"DPO Approval target is before QA target",IF(AND(AG73&lt;&gt;"",AA73&lt;&gt;"",AG73&lt;AA73),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK73" s="31" t="str" cm="1">
+        <f t="array" ref="AK73">IF($B73="","",_xlfn.LET(_xlpm.nm,$B73,_xlpm.st,$C73,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M73,_xlpm.st="DB Dev",$M73,_xlpm.st="PBI Dev",$S73,_xlpm.st="QA",$Y73,_xlpm.st="DPO Approval",$AC73,_xlpm.st="Ready for Release in Prod",$AG73,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ73,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ73,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B73)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B73)&gt;0,"",IF(AND($V73&lt;&gt;"",$K73&lt;&gt;"",$V73&lt;$K73),"QA target is before DB Dev target",IF(AND($V73&lt;&gt;"",$Q73&lt;&gt;"",$V73&lt;$Q73),"QA target is before PBI Dev target",IF(AND($AA73&lt;&gt;"",$V73&lt;&gt;"",$AA73&lt;$V73),"DPO Approval target is before QA target",IF(AND($AG73&lt;&gt;"",$AA73&lt;&gt;"",$AG73&lt;$AA73),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL73" s="31"/>
@@ -11716,7 +11739,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:40" ht="14.45" hidden="1">
+    <row r="74" spans="1:40" ht="14.45">
       <c r="A74" s="31" t="s">
         <v>126</v>
       </c>
@@ -11794,8 +11817,8 @@
       <c r="AH74" s="31"/>
       <c r="AI74" s="31"/>
       <c r="AJ74" s="31"/>
-      <c r="AK74" s="31" t="str">
-        <f>IF($B74="","",IF(AND(LEFT($AJ74,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B74)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ74,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B74)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ74="Yes – needs DB Dev to fix",M74&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B74)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ74="Yes – needs PBI Dev to fix",S74&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B74)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ74="Yes – needs QA to fix",Y74&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B74)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B74)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B74)&gt;0,"",IF(AND(V74&lt;&gt;"",K74&lt;&gt;"",V74&lt;K74),"QA target is before DB Dev target",IF(AND(V74&lt;&gt;"",Q74&lt;&gt;"",V74&lt;Q74),"QA target is before PBI Dev target",IF(AND(AA74&lt;&gt;"",V74&lt;&gt;"",AA74&lt;V74),"DPO Approval target is before QA target",IF(AND(AG74&lt;&gt;"",AA74&lt;&gt;"",AG74&lt;AA74),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK74" s="31" t="str" cm="1">
+        <f t="array" ref="AK74">IF($B74="","",_xlfn.LET(_xlpm.nm,$B74,_xlpm.st,$C74,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M74,_xlpm.st="DB Dev",$M74,_xlpm.st="PBI Dev",$S74,_xlpm.st="QA",$Y74,_xlpm.st="DPO Approval",$AC74,_xlpm.st="Ready for Release in Prod",$AG74,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ74,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ74,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B74)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B74)&gt;0,"",IF(AND($V74&lt;&gt;"",$K74&lt;&gt;"",$V74&lt;$K74),"QA target is before DB Dev target",IF(AND($V74&lt;&gt;"",$Q74&lt;&gt;"",$V74&lt;$Q74),"QA target is before PBI Dev target",IF(AND($AA74&lt;&gt;"",$V74&lt;&gt;"",$AA74&lt;$V74),"DPO Approval target is before QA target",IF(AND($AG74&lt;&gt;"",$AA74&lt;&gt;"",$AG74&lt;$AA74),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL74" s="31"/>
@@ -11808,7 +11831,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:40" s="136" customFormat="1" ht="14.45" hidden="1">
+    <row r="75" spans="1:40" s="136" customFormat="1" ht="14.45">
       <c r="A75" s="135" t="s">
         <v>126</v>
       </c>
@@ -11878,8 +11901,8 @@
       <c r="AH75" s="135"/>
       <c r="AI75" s="135"/>
       <c r="AJ75" s="135"/>
-      <c r="AK75" s="135" t="str">
-        <f>IF($B75="","",IF(AND(LEFT($AJ75,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B75)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ75,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B75)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ75="Yes – needs DB Dev to fix",M75&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B75)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ75="Yes – needs PBI Dev to fix",S75&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B75)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ75="Yes – needs QA to fix",Y75&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B75)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B75)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B75)&gt;0,"",IF(AND(V75&lt;&gt;"",K75&lt;&gt;"",V75&lt;K75),"QA target is before DB Dev target",IF(AND(V75&lt;&gt;"",Q75&lt;&gt;"",V75&lt;Q75),"QA target is before PBI Dev target",IF(AND(AA75&lt;&gt;"",V75&lt;&gt;"",AA75&lt;V75),"DPO Approval target is before QA target",IF(AND(AG75&lt;&gt;"",AA75&lt;&gt;"",AG75&lt;AA75),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK75" s="135" t="str" cm="1">
+        <f t="array" ref="AK75">IF($B75="","",_xlfn.LET(_xlpm.nm,$B75,_xlpm.st,$C75,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M75,_xlpm.st="DB Dev",$M75,_xlpm.st="PBI Dev",$S75,_xlpm.st="QA",$Y75,_xlpm.st="DPO Approval",$AC75,_xlpm.st="Ready for Release in Prod",$AG75,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ75,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ75,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B75)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B75)&gt;0,"",IF(AND($V75&lt;&gt;"",$K75&lt;&gt;"",$V75&lt;$K75),"QA target is before DB Dev target",IF(AND($V75&lt;&gt;"",$Q75&lt;&gt;"",$V75&lt;$Q75),"QA target is before PBI Dev target",IF(AND($AA75&lt;&gt;"",$V75&lt;&gt;"",$AA75&lt;$V75),"DPO Approval target is before QA target",IF(AND($AG75&lt;&gt;"",$AA75&lt;&gt;"",$AG75&lt;$AA75),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL75" s="135"/>
@@ -11892,7 +11915,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:40" s="136" customFormat="1" ht="14.45" hidden="1">
+    <row r="76" spans="1:40" s="136" customFormat="1" ht="14.45">
       <c r="A76" s="135" t="s">
         <v>126</v>
       </c>
@@ -11962,8 +11985,8 @@
       <c r="AH76" s="135"/>
       <c r="AI76" s="135"/>
       <c r="AJ76" s="135"/>
-      <c r="AK76" s="135" t="str">
-        <f>IF($B76="","",IF(AND(LEFT($AJ76,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B76)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ76,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B76)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ76="Yes – needs DB Dev to fix",M76&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B76)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ76="Yes – needs PBI Dev to fix",S76&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B76)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ76="Yes – needs QA to fix",Y76&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B76)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B76)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B76)&gt;0,"",IF(AND(V76&lt;&gt;"",K76&lt;&gt;"",V76&lt;K76),"QA target is before DB Dev target",IF(AND(V76&lt;&gt;"",Q76&lt;&gt;"",V76&lt;Q76),"QA target is before PBI Dev target",IF(AND(AA76&lt;&gt;"",V76&lt;&gt;"",AA76&lt;V76),"DPO Approval target is before QA target",IF(AND(AG76&lt;&gt;"",AA76&lt;&gt;"",AG76&lt;AA76),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK76" s="135" t="str" cm="1">
+        <f t="array" ref="AK76">IF($B76="","",_xlfn.LET(_xlpm.nm,$B76,_xlpm.st,$C76,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M76,_xlpm.st="DB Dev",$M76,_xlpm.st="PBI Dev",$S76,_xlpm.st="QA",$Y76,_xlpm.st="DPO Approval",$AC76,_xlpm.st="Ready for Release in Prod",$AG76,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ76,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ76,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B76)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B76)&gt;0,"",IF(AND($V76&lt;&gt;"",$K76&lt;&gt;"",$V76&lt;$K76),"QA target is before DB Dev target",IF(AND($V76&lt;&gt;"",$Q76&lt;&gt;"",$V76&lt;$Q76),"QA target is before PBI Dev target",IF(AND($AA76&lt;&gt;"",$V76&lt;&gt;"",$AA76&lt;$V76),"DPO Approval target is before QA target",IF(AND($AG76&lt;&gt;"",$AA76&lt;&gt;"",$AG76&lt;$AA76),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL76" s="135"/>
@@ -11976,7 +11999,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:40" s="136" customFormat="1" ht="14.45" hidden="1">
+    <row r="77" spans="1:40" s="136" customFormat="1" ht="14.45">
       <c r="A77" s="135" t="s">
         <v>126</v>
       </c>
@@ -12046,8 +12069,8 @@
       <c r="AH77" s="135"/>
       <c r="AI77" s="135"/>
       <c r="AJ77" s="135"/>
-      <c r="AK77" s="135" t="str">
-        <f>IF($B77="","",IF(AND(LEFT($AJ77,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B77)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ77,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B77)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ77="Yes – needs DB Dev to fix",M77&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B77)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ77="Yes – needs PBI Dev to fix",S77&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B77)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ77="Yes – needs QA to fix",Y77&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B77)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B77)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B77)&gt;0,"",IF(AND(V77&lt;&gt;"",K77&lt;&gt;"",V77&lt;K77),"QA target is before DB Dev target",IF(AND(V77&lt;&gt;"",Q77&lt;&gt;"",V77&lt;Q77),"QA target is before PBI Dev target",IF(AND(AA77&lt;&gt;"",V77&lt;&gt;"",AA77&lt;V77),"DPO Approval target is before QA target",IF(AND(AG77&lt;&gt;"",AA77&lt;&gt;"",AG77&lt;AA77),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK77" s="135" t="str" cm="1">
+        <f t="array" ref="AK77">IF($B77="","",_xlfn.LET(_xlpm.nm,$B77,_xlpm.st,$C77,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M77,_xlpm.st="DB Dev",$M77,_xlpm.st="PBI Dev",$S77,_xlpm.st="QA",$Y77,_xlpm.st="DPO Approval",$AC77,_xlpm.st="Ready for Release in Prod",$AG77,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ77,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ77,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B77)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B77)&gt;0,"",IF(AND($V77&lt;&gt;"",$K77&lt;&gt;"",$V77&lt;$K77),"QA target is before DB Dev target",IF(AND($V77&lt;&gt;"",$Q77&lt;&gt;"",$V77&lt;$Q77),"QA target is before PBI Dev target",IF(AND($AA77&lt;&gt;"",$V77&lt;&gt;"",$AA77&lt;$V77),"DPO Approval target is before QA target",IF(AND($AG77&lt;&gt;"",$AA77&lt;&gt;"",$AG77&lt;$AA77),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL77" s="135"/>
@@ -12060,7 +12083,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:40" s="147" customFormat="1" ht="14.45" hidden="1">
+    <row r="78" spans="1:40" s="147" customFormat="1" ht="14.45">
       <c r="A78" s="146" t="s">
         <v>126</v>
       </c>
@@ -12134,8 +12157,8 @@
       <c r="AH78" s="146"/>
       <c r="AI78" s="146"/>
       <c r="AJ78" s="146"/>
-      <c r="AK78" s="146" t="str">
-        <f>IF($B78="","",IF(AND(LEFT($AJ78,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B78)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ78,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B78)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ78="Yes – needs DB Dev to fix",M78&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B78)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ78="Yes – needs PBI Dev to fix",S78&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B78)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ78="Yes – needs QA to fix",Y78&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B78)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B78)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B78)&gt;0,"",IF(AND(V78&lt;&gt;"",K78&lt;&gt;"",V78&lt;K78),"QA target is before DB Dev target",IF(AND(V78&lt;&gt;"",Q78&lt;&gt;"",V78&lt;Q78),"QA target is before PBI Dev target",IF(AND(AA78&lt;&gt;"",V78&lt;&gt;"",AA78&lt;V78),"DPO Approval target is before QA target",IF(AND(AG78&lt;&gt;"",AA78&lt;&gt;"",AG78&lt;AA78),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK78" s="146" t="str" cm="1">
+        <f t="array" ref="AK78">IF($B78="","",_xlfn.LET(_xlpm.nm,$B78,_xlpm.st,$C78,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M78,_xlpm.st="DB Dev",$M78,_xlpm.st="PBI Dev",$S78,_xlpm.st="QA",$Y78,_xlpm.st="DPO Approval",$AC78,_xlpm.st="Ready for Release in Prod",$AG78,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ78,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ78,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B78)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B78)&gt;0,"",IF(AND($V78&lt;&gt;"",$K78&lt;&gt;"",$V78&lt;$K78),"QA target is before DB Dev target",IF(AND($V78&lt;&gt;"",$Q78&lt;&gt;"",$V78&lt;$Q78),"QA target is before PBI Dev target",IF(AND($AA78&lt;&gt;"",$V78&lt;&gt;"",$AA78&lt;$V78),"DPO Approval target is before QA target",IF(AND($AG78&lt;&gt;"",$AA78&lt;&gt;"",$AG78&lt;$AA78),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL78" s="146"/>
@@ -12148,7 +12171,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:40" ht="14.45" hidden="1">
+    <row r="79" spans="1:40" ht="14.45">
       <c r="A79" s="31" t="s">
         <v>126</v>
       </c>
@@ -12228,8 +12251,8 @@
       <c r="AH79" s="31"/>
       <c r="AI79" s="31"/>
       <c r="AJ79" s="31"/>
-      <c r="AK79" s="31" t="str">
-        <f>IF($B79="","",IF(AND(LEFT($AJ79,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B79)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ79,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B79)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ79="Yes – needs DB Dev to fix",M79&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B79)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ79="Yes – needs PBI Dev to fix",S79&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B79)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ79="Yes – needs QA to fix",Y79&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B79)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B79)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B79)&gt;0,"",IF(AND(V79&lt;&gt;"",K79&lt;&gt;"",V79&lt;K79),"QA target is before DB Dev target",IF(AND(V79&lt;&gt;"",Q79&lt;&gt;"",V79&lt;Q79),"QA target is before PBI Dev target",IF(AND(AA79&lt;&gt;"",V79&lt;&gt;"",AA79&lt;V79),"DPO Approval target is before QA target",IF(AND(AG79&lt;&gt;"",AA79&lt;&gt;"",AG79&lt;AA79),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK79" s="31" t="str" cm="1">
+        <f t="array" ref="AK79">IF($B79="","",_xlfn.LET(_xlpm.nm,$B79,_xlpm.st,$C79,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M79,_xlpm.st="DB Dev",$M79,_xlpm.st="PBI Dev",$S79,_xlpm.st="QA",$Y79,_xlpm.st="DPO Approval",$AC79,_xlpm.st="Ready for Release in Prod",$AG79,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ79,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ79,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B79)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B79)&gt;0,"",IF(AND($V79&lt;&gt;"",$K79&lt;&gt;"",$V79&lt;$K79),"QA target is before DB Dev target",IF(AND($V79&lt;&gt;"",$Q79&lt;&gt;"",$V79&lt;$Q79),"QA target is before PBI Dev target",IF(AND($AA79&lt;&gt;"",$V79&lt;&gt;"",$AA79&lt;$V79),"DPO Approval target is before QA target",IF(AND($AG79&lt;&gt;"",$AA79&lt;&gt;"",$AG79&lt;$AA79),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL79" s="31"/>
@@ -12242,7 +12265,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:40" ht="14.45" hidden="1">
+    <row r="80" spans="1:40" ht="14.45">
       <c r="A80" s="31" t="s">
         <v>126</v>
       </c>
@@ -12322,9 +12345,9 @@
       <c r="AH80" s="31"/>
       <c r="AI80" s="31"/>
       <c r="AJ80" s="31"/>
-      <c r="AK80" s="31" t="str">
-        <f>IF($B80="","",IF(AND(LEFT($AJ80,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B80)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ80,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B80)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ80="Yes – needs DB Dev to fix",M80&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B80)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ80="Yes – needs PBI Dev to fix",S80&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B80)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ80="Yes – needs QA to fix",Y80&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B80)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B80)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B80)&gt;0,"",IF(AND(V80&lt;&gt;"",K80&lt;&gt;"",V80&lt;K80),"QA target is before DB Dev target",IF(AND(V80&lt;&gt;"",Q80&lt;&gt;"",V80&lt;Q80),"QA target is before PBI Dev target",IF(AND(AA80&lt;&gt;"",V80&lt;&gt;"",AA80&lt;V80),"DPO Approval target is before QA target",IF(AND(AG80&lt;&gt;"",AA80&lt;&gt;"",AG80&lt;AA80),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
-        <v/>
+      <c r="AK80" s="31" t="str" cm="1">
+        <f t="array" ref="AK80">IF($B80="","",_xlfn.LET(_xlpm.nm,$B80,_xlpm.st,$C80,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M80,_xlpm.st="DB Dev",$M80,_xlpm.st="PBI Dev",$S80,_xlpm.st="QA",$Y80,_xlpm.st="DPO Approval",$AC80,_xlpm.st="Ready for Release in Prod",$AG80,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ80,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ80,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B80)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B80)&gt;0,"",IF(AND($V80&lt;&gt;"",$K80&lt;&gt;"",$V80&lt;$K80),"QA target is before DB Dev target",IF(AND($V80&lt;&gt;"",$Q80&lt;&gt;"",$V80&lt;$Q80),"QA target is before PBI Dev target",IF(AND($AA80&lt;&gt;"",$V80&lt;&gt;"",$AA80&lt;$V80),"DPO Approval target is before QA target",IF(AND($AG80&lt;&gt;"",$AA80&lt;&gt;"",$AG80&lt;$AA80),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v>Move status to PBI Dev</v>
       </c>
       <c r="AL80" s="31"/>
       <c r="AM80" s="32" t="str" cm="1">
@@ -12336,7 +12359,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:40" s="147" customFormat="1" ht="14.45" hidden="1">
+    <row r="81" spans="1:40" s="147" customFormat="1" ht="14.45">
       <c r="A81" s="146" t="s">
         <v>126</v>
       </c>
@@ -12410,8 +12433,8 @@
       <c r="AH81" s="146"/>
       <c r="AI81" s="146"/>
       <c r="AJ81" s="146"/>
-      <c r="AK81" s="146" t="str">
-        <f>IF($B81="","",IF(AND(LEFT($AJ81,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B81)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ81,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B81)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ81="Yes – needs DB Dev to fix",M81&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B81)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ81="Yes – needs PBI Dev to fix",S81&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B81)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ81="Yes – needs QA to fix",Y81&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B81)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B81)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B81)&gt;0,"",IF(AND(V81&lt;&gt;"",K81&lt;&gt;"",V81&lt;K81),"QA target is before DB Dev target",IF(AND(V81&lt;&gt;"",Q81&lt;&gt;"",V81&lt;Q81),"QA target is before PBI Dev target",IF(AND(AA81&lt;&gt;"",V81&lt;&gt;"",AA81&lt;V81),"DPO Approval target is before QA target",IF(AND(AG81&lt;&gt;"",AA81&lt;&gt;"",AG81&lt;AA81),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK81" s="146" t="str" cm="1">
+        <f t="array" ref="AK81">IF($B81="","",_xlfn.LET(_xlpm.nm,$B81,_xlpm.st,$C81,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M81,_xlpm.st="DB Dev",$M81,_xlpm.st="PBI Dev",$S81,_xlpm.st="QA",$Y81,_xlpm.st="DPO Approval",$AC81,_xlpm.st="Ready for Release in Prod",$AG81,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ81,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ81,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B81)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B81)&gt;0,"",IF(AND($V81&lt;&gt;"",$K81&lt;&gt;"",$V81&lt;$K81),"QA target is before DB Dev target",IF(AND($V81&lt;&gt;"",$Q81&lt;&gt;"",$V81&lt;$Q81),"QA target is before PBI Dev target",IF(AND($AA81&lt;&gt;"",$V81&lt;&gt;"",$AA81&lt;$V81),"DPO Approval target is before QA target",IF(AND($AG81&lt;&gt;"",$AA81&lt;&gt;"",$AG81&lt;$AA81),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL81" s="146"/>
@@ -12424,7 +12447,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:40" ht="14.45" hidden="1">
+    <row r="82" spans="1:40" ht="14.45">
       <c r="A82" s="31" t="s">
         <v>126</v>
       </c>
@@ -12502,8 +12525,8 @@
       <c r="AH82" s="31"/>
       <c r="AI82" s="31"/>
       <c r="AJ82" s="31"/>
-      <c r="AK82" s="31" t="str">
-        <f>IF($B82="","",IF(AND(LEFT($AJ82,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B82)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ82,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B82)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ82="Yes – needs DB Dev to fix",M82&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B82)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ82="Yes – needs PBI Dev to fix",S82&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B82)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ82="Yes – needs QA to fix",Y82&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B82)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B82)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B82)&gt;0,"",IF(AND(V82&lt;&gt;"",K82&lt;&gt;"",V82&lt;K82),"QA target is before DB Dev target",IF(AND(V82&lt;&gt;"",Q82&lt;&gt;"",V82&lt;Q82),"QA target is before PBI Dev target",IF(AND(AA82&lt;&gt;"",V82&lt;&gt;"",AA82&lt;V82),"DPO Approval target is before QA target",IF(AND(AG82&lt;&gt;"",AA82&lt;&gt;"",AG82&lt;AA82),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK82" s="31" t="str" cm="1">
+        <f t="array" ref="AK82">IF($B82="","",_xlfn.LET(_xlpm.nm,$B82,_xlpm.st,$C82,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M82,_xlpm.st="DB Dev",$M82,_xlpm.st="PBI Dev",$S82,_xlpm.st="QA",$Y82,_xlpm.st="DPO Approval",$AC82,_xlpm.st="Ready for Release in Prod",$AG82,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ82,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ82,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B82)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B82)&gt;0,"",IF(AND($V82&lt;&gt;"",$K82&lt;&gt;"",$V82&lt;$K82),"QA target is before DB Dev target",IF(AND($V82&lt;&gt;"",$Q82&lt;&gt;"",$V82&lt;$Q82),"QA target is before PBI Dev target",IF(AND($AA82&lt;&gt;"",$V82&lt;&gt;"",$AA82&lt;$V82),"DPO Approval target is before QA target",IF(AND($AG82&lt;&gt;"",$AA82&lt;&gt;"",$AG82&lt;$AA82),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL82" s="31"/>
@@ -12516,7 +12539,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:40" ht="14.45" hidden="1">
+    <row r="83" spans="1:40" ht="14.45">
       <c r="A83" s="31" t="s">
         <v>126</v>
       </c>
@@ -12596,8 +12619,8 @@
       <c r="AH83" s="31"/>
       <c r="AI83" s="31"/>
       <c r="AJ83" s="31"/>
-      <c r="AK83" s="31" t="str">
-        <f>IF($B83="","",IF(AND(LEFT($AJ83,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B83)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ83,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B83)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ83="Yes – needs DB Dev to fix",M83&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B83)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ83="Yes – needs PBI Dev to fix",S83&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B83)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ83="Yes – needs QA to fix",Y83&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B83)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B83)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B83)&gt;0,"",IF(AND(V83&lt;&gt;"",K83&lt;&gt;"",V83&lt;K83),"QA target is before DB Dev target",IF(AND(V83&lt;&gt;"",Q83&lt;&gt;"",V83&lt;Q83),"QA target is before PBI Dev target",IF(AND(AA83&lt;&gt;"",V83&lt;&gt;"",AA83&lt;V83),"DPO Approval target is before QA target",IF(AND(AG83&lt;&gt;"",AA83&lt;&gt;"",AG83&lt;AA83),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK83" s="31" t="str" cm="1">
+        <f t="array" ref="AK83">IF($B83="","",_xlfn.LET(_xlpm.nm,$B83,_xlpm.st,$C83,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M83,_xlpm.st="DB Dev",$M83,_xlpm.st="PBI Dev",$S83,_xlpm.st="QA",$Y83,_xlpm.st="DPO Approval",$AC83,_xlpm.st="Ready for Release in Prod",$AG83,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ83,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ83,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B83)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B83)&gt;0,"",IF(AND($V83&lt;&gt;"",$K83&lt;&gt;"",$V83&lt;$K83),"QA target is before DB Dev target",IF(AND($V83&lt;&gt;"",$Q83&lt;&gt;"",$V83&lt;$Q83),"QA target is before PBI Dev target",IF(AND($AA83&lt;&gt;"",$V83&lt;&gt;"",$AA83&lt;$V83),"DPO Approval target is before QA target",IF(AND($AG83&lt;&gt;"",$AA83&lt;&gt;"",$AG83&lt;$AA83),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL83" s="31"/>
@@ -12610,7 +12633,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:40" ht="14.45" hidden="1">
+    <row r="84" spans="1:40" ht="14.45">
       <c r="A84" s="31" t="s">
         <v>126</v>
       </c>
@@ -12686,8 +12709,8 @@
       <c r="AH84" s="31"/>
       <c r="AI84" s="31"/>
       <c r="AJ84" s="31"/>
-      <c r="AK84" s="31" t="str">
-        <f>IF($B84="","",IF(AND(LEFT($AJ84,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B84)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ84,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B84)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ84="Yes – needs DB Dev to fix",M84&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B84)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ84="Yes – needs PBI Dev to fix",S84&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B84)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ84="Yes – needs QA to fix",Y84&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B84)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B84)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B84)&gt;0,"",IF(AND(V84&lt;&gt;"",K84&lt;&gt;"",V84&lt;K84),"QA target is before DB Dev target",IF(AND(V84&lt;&gt;"",Q84&lt;&gt;"",V84&lt;Q84),"QA target is before PBI Dev target",IF(AND(AA84&lt;&gt;"",V84&lt;&gt;"",AA84&lt;V84),"DPO Approval target is before QA target",IF(AND(AG84&lt;&gt;"",AA84&lt;&gt;"",AG84&lt;AA84),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK84" s="31" t="str" cm="1">
+        <f t="array" ref="AK84">IF($B84="","",_xlfn.LET(_xlpm.nm,$B84,_xlpm.st,$C84,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M84,_xlpm.st="DB Dev",$M84,_xlpm.st="PBI Dev",$S84,_xlpm.st="QA",$Y84,_xlpm.st="DPO Approval",$AC84,_xlpm.st="Ready for Release in Prod",$AG84,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ84,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ84,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B84)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B84)&gt;0,"",IF(AND($V84&lt;&gt;"",$K84&lt;&gt;"",$V84&lt;$K84),"QA target is before DB Dev target",IF(AND($V84&lt;&gt;"",$Q84&lt;&gt;"",$V84&lt;$Q84),"QA target is before PBI Dev target",IF(AND($AA84&lt;&gt;"",$V84&lt;&gt;"",$AA84&lt;$V84),"DPO Approval target is before QA target",IF(AND($AG84&lt;&gt;"",$AA84&lt;&gt;"",$AG84&lt;$AA84),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL84" s="31"/>
@@ -12700,7 +12723,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:40" ht="14.45" hidden="1">
+    <row r="85" spans="1:40" ht="14.45">
       <c r="A85" s="31" t="s">
         <v>126</v>
       </c>
@@ -12774,8 +12797,8 @@
       <c r="AH85" s="31"/>
       <c r="AI85" s="31"/>
       <c r="AJ85" s="31"/>
-      <c r="AK85" s="31" t="str">
-        <f>IF($B85="","",IF(AND(LEFT($AJ85,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B85)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ85,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B85)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ85="Yes – needs DB Dev to fix",M85&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B85)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ85="Yes – needs PBI Dev to fix",S85&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B85)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ85="Yes – needs QA to fix",Y85&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B85)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B85)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B85)&gt;0,"",IF(AND(V85&lt;&gt;"",K85&lt;&gt;"",V85&lt;K85),"QA target is before DB Dev target",IF(AND(V85&lt;&gt;"",Q85&lt;&gt;"",V85&lt;Q85),"QA target is before PBI Dev target",IF(AND(AA85&lt;&gt;"",V85&lt;&gt;"",AA85&lt;V85),"DPO Approval target is before QA target",IF(AND(AG85&lt;&gt;"",AA85&lt;&gt;"",AG85&lt;AA85),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK85" s="31" t="str" cm="1">
+        <f t="array" ref="AK85">IF($B85="","",_xlfn.LET(_xlpm.nm,$B85,_xlpm.st,$C85,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M85,_xlpm.st="DB Dev",$M85,_xlpm.st="PBI Dev",$S85,_xlpm.st="QA",$Y85,_xlpm.st="DPO Approval",$AC85,_xlpm.st="Ready for Release in Prod",$AG85,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ85,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ85,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B85)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B85)&gt;0,"",IF(AND($V85&lt;&gt;"",$K85&lt;&gt;"",$V85&lt;$K85),"QA target is before DB Dev target",IF(AND($V85&lt;&gt;"",$Q85&lt;&gt;"",$V85&lt;$Q85),"QA target is before PBI Dev target",IF(AND($AA85&lt;&gt;"",$V85&lt;&gt;"",$AA85&lt;$V85),"DPO Approval target is before QA target",IF(AND($AG85&lt;&gt;"",$AA85&lt;&gt;"",$AG85&lt;$AA85),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL85" s="31"/>
@@ -12788,7 +12811,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:40" ht="14.45" hidden="1">
+    <row r="86" spans="1:40" ht="14.45">
       <c r="A86" s="31" t="s">
         <v>126</v>
       </c>
@@ -12860,8 +12883,8 @@
       <c r="AH86" s="31"/>
       <c r="AI86" s="31"/>
       <c r="AJ86" s="31"/>
-      <c r="AK86" s="31" t="str">
-        <f>IF($B86="","",IF(AND(LEFT($AJ86,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B86)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ86,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B86)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ86="Yes – needs DB Dev to fix",M86&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B86)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ86="Yes – needs PBI Dev to fix",S86&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B86)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ86="Yes – needs QA to fix",Y86&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B86)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B86)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B86)&gt;0,"",IF(AND(V86&lt;&gt;"",K86&lt;&gt;"",V86&lt;K86),"QA target is before DB Dev target",IF(AND(V86&lt;&gt;"",Q86&lt;&gt;"",V86&lt;Q86),"QA target is before PBI Dev target",IF(AND(AA86&lt;&gt;"",V86&lt;&gt;"",AA86&lt;V86),"DPO Approval target is before QA target",IF(AND(AG86&lt;&gt;"",AA86&lt;&gt;"",AG86&lt;AA86),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK86" s="31" t="str" cm="1">
+        <f t="array" ref="AK86">IF($B86="","",_xlfn.LET(_xlpm.nm,$B86,_xlpm.st,$C86,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M86,_xlpm.st="DB Dev",$M86,_xlpm.st="PBI Dev",$S86,_xlpm.st="QA",$Y86,_xlpm.st="DPO Approval",$AC86,_xlpm.st="Ready for Release in Prod",$AG86,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ86,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ86,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B86)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B86)&gt;0,"",IF(AND($V86&lt;&gt;"",$K86&lt;&gt;"",$V86&lt;$K86),"QA target is before DB Dev target",IF(AND($V86&lt;&gt;"",$Q86&lt;&gt;"",$V86&lt;$Q86),"QA target is before PBI Dev target",IF(AND($AA86&lt;&gt;"",$V86&lt;&gt;"",$AA86&lt;$V86),"DPO Approval target is before QA target",IF(AND($AG86&lt;&gt;"",$AA86&lt;&gt;"",$AG86&lt;$AA86),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL86" s="31"/>
@@ -12874,7 +12897,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:40" ht="14.45" hidden="1">
+    <row r="87" spans="1:40" ht="14.45">
       <c r="A87" s="31" t="s">
         <v>126</v>
       </c>
@@ -12946,8 +12969,8 @@
       <c r="AH87" s="31"/>
       <c r="AI87" s="31"/>
       <c r="AJ87" s="31"/>
-      <c r="AK87" s="31" t="str">
-        <f>IF($B87="","",IF(AND(LEFT($AJ87,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B87)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ87,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B87)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ87="Yes – needs DB Dev to fix",M87&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B87)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ87="Yes – needs PBI Dev to fix",S87&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B87)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ87="Yes – needs QA to fix",Y87&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B87)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B87)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B87)&gt;0,"",IF(AND(V87&lt;&gt;"",K87&lt;&gt;"",V87&lt;K87),"QA target is before DB Dev target",IF(AND(V87&lt;&gt;"",Q87&lt;&gt;"",V87&lt;Q87),"QA target is before PBI Dev target",IF(AND(AA87&lt;&gt;"",V87&lt;&gt;"",AA87&lt;V87),"DPO Approval target is before QA target",IF(AND(AG87&lt;&gt;"",AA87&lt;&gt;"",AG87&lt;AA87),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK87" s="31" t="str" cm="1">
+        <f t="array" ref="AK87">IF($B87="","",_xlfn.LET(_xlpm.nm,$B87,_xlpm.st,$C87,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M87,_xlpm.st="DB Dev",$M87,_xlpm.st="PBI Dev",$S87,_xlpm.st="QA",$Y87,_xlpm.st="DPO Approval",$AC87,_xlpm.st="Ready for Release in Prod",$AG87,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ87,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ87,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B87)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B87)&gt;0,"",IF(AND($V87&lt;&gt;"",$K87&lt;&gt;"",$V87&lt;$K87),"QA target is before DB Dev target",IF(AND($V87&lt;&gt;"",$Q87&lt;&gt;"",$V87&lt;$Q87),"QA target is before PBI Dev target",IF(AND($AA87&lt;&gt;"",$V87&lt;&gt;"",$AA87&lt;$V87),"DPO Approval target is before QA target",IF(AND($AG87&lt;&gt;"",$AA87&lt;&gt;"",$AG87&lt;$AA87),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL87" s="31"/>
@@ -12960,7 +12983,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:40" ht="14.45" hidden="1">
+    <row r="88" spans="1:40" ht="14.45">
       <c r="A88" s="31" t="s">
         <v>126</v>
       </c>
@@ -13032,8 +13055,8 @@
       <c r="AH88" s="31"/>
       <c r="AI88" s="31"/>
       <c r="AJ88" s="31"/>
-      <c r="AK88" s="31" t="str">
-        <f>IF($B88="","",IF(AND(LEFT($AJ88,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B88)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ88,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B88)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ88="Yes – needs DB Dev to fix",M88&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B88)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ88="Yes – needs PBI Dev to fix",S88&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B88)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ88="Yes – needs QA to fix",Y88&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B88)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B88)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B88)&gt;0,"",IF(AND(V88&lt;&gt;"",K88&lt;&gt;"",V88&lt;K88),"QA target is before DB Dev target",IF(AND(V88&lt;&gt;"",Q88&lt;&gt;"",V88&lt;Q88),"QA target is before PBI Dev target",IF(AND(AA88&lt;&gt;"",V88&lt;&gt;"",AA88&lt;V88),"DPO Approval target is before QA target",IF(AND(AG88&lt;&gt;"",AA88&lt;&gt;"",AG88&lt;AA88),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK88" s="31" t="str" cm="1">
+        <f t="array" ref="AK88">IF($B88="","",_xlfn.LET(_xlpm.nm,$B88,_xlpm.st,$C88,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M88,_xlpm.st="DB Dev",$M88,_xlpm.st="PBI Dev",$S88,_xlpm.st="QA",$Y88,_xlpm.st="DPO Approval",$AC88,_xlpm.st="Ready for Release in Prod",$AG88,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ88,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ88,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B88)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B88)&gt;0,"",IF(AND($V88&lt;&gt;"",$K88&lt;&gt;"",$V88&lt;$K88),"QA target is before DB Dev target",IF(AND($V88&lt;&gt;"",$Q88&lt;&gt;"",$V88&lt;$Q88),"QA target is before PBI Dev target",IF(AND($AA88&lt;&gt;"",$V88&lt;&gt;"",$AA88&lt;$V88),"DPO Approval target is before QA target",IF(AND($AG88&lt;&gt;"",$AA88&lt;&gt;"",$AG88&lt;$AA88),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL88" s="31"/>
@@ -13046,7 +13069,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:40" ht="14.45" hidden="1">
+    <row r="89" spans="1:40" ht="14.45">
       <c r="A89" s="31" t="s">
         <v>126</v>
       </c>
@@ -13122,9 +13145,9 @@
       <c r="AH89" s="31"/>
       <c r="AI89" s="31"/>
       <c r="AJ89" s="31"/>
-      <c r="AK89" s="31" t="str">
-        <f>IF($B89="","",IF(AND(LEFT($AJ89,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B89)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ89,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B89)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ89="Yes – needs DB Dev to fix",M89&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B89)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ89="Yes – needs PBI Dev to fix",S89&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B89)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ89="Yes – needs QA to fix",Y89&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B89)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B89)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B89)&gt;0,"",IF(AND(V89&lt;&gt;"",K89&lt;&gt;"",V89&lt;K89),"QA target is before DB Dev target",IF(AND(V89&lt;&gt;"",Q89&lt;&gt;"",V89&lt;Q89),"QA target is before PBI Dev target",IF(AND(AA89&lt;&gt;"",V89&lt;&gt;"",AA89&lt;V89),"DPO Approval target is before QA target",IF(AND(AG89&lt;&gt;"",AA89&lt;&gt;"",AG89&lt;AA89),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
-        <v/>
+      <c r="AK89" s="31" t="str" cm="1">
+        <f t="array" ref="AK89">IF($B89="","",_xlfn.LET(_xlpm.nm,$B89,_xlpm.st,$C89,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M89,_xlpm.st="DB Dev",$M89,_xlpm.st="PBI Dev",$S89,_xlpm.st="QA",$Y89,_xlpm.st="DPO Approval",$AC89,_xlpm.st="Ready for Release in Prod",$AG89,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ89,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ89,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B89)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B89)&gt;0,"",IF(AND($V89&lt;&gt;"",$K89&lt;&gt;"",$V89&lt;$K89),"QA target is before DB Dev target",IF(AND($V89&lt;&gt;"",$Q89&lt;&gt;"",$V89&lt;$Q89),"QA target is before PBI Dev target",IF(AND($AA89&lt;&gt;"",$V89&lt;&gt;"",$AA89&lt;$V89),"DPO Approval target is before QA target",IF(AND($AG89&lt;&gt;"",$AA89&lt;&gt;"",$AG89&lt;$AA89),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v>Move status to PBI Dev</v>
       </c>
       <c r="AL89" s="31"/>
       <c r="AM89" s="32" t="str" cm="1">
@@ -13136,7 +13159,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:40" ht="14.45" hidden="1">
+    <row r="90" spans="1:40" ht="14.45">
       <c r="A90" s="31" t="s">
         <v>126</v>
       </c>
@@ -13206,8 +13229,8 @@
       <c r="AH90" s="31"/>
       <c r="AI90" s="31"/>
       <c r="AJ90" s="31"/>
-      <c r="AK90" s="31" t="str">
-        <f>IF($B90="","",IF(AND(LEFT($AJ90,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B90)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ90,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B90)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ90="Yes – needs DB Dev to fix",M90&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B90)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ90="Yes – needs PBI Dev to fix",S90&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B90)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ90="Yes – needs QA to fix",Y90&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B90)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B90)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B90)&gt;0,"",IF(AND(V90&lt;&gt;"",K90&lt;&gt;"",V90&lt;K90),"QA target is before DB Dev target",IF(AND(V90&lt;&gt;"",Q90&lt;&gt;"",V90&lt;Q90),"QA target is before PBI Dev target",IF(AND(AA90&lt;&gt;"",V90&lt;&gt;"",AA90&lt;V90),"DPO Approval target is before QA target",IF(AND(AG90&lt;&gt;"",AA90&lt;&gt;"",AG90&lt;AA90),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK90" s="31" t="str" cm="1">
+        <f t="array" ref="AK90">IF($B90="","",_xlfn.LET(_xlpm.nm,$B90,_xlpm.st,$C90,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M90,_xlpm.st="DB Dev",$M90,_xlpm.st="PBI Dev",$S90,_xlpm.st="QA",$Y90,_xlpm.st="DPO Approval",$AC90,_xlpm.st="Ready for Release in Prod",$AG90,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ90,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ90,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B90)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B90)&gt;0,"",IF(AND($V90&lt;&gt;"",$K90&lt;&gt;"",$V90&lt;$K90),"QA target is before DB Dev target",IF(AND($V90&lt;&gt;"",$Q90&lt;&gt;"",$V90&lt;$Q90),"QA target is before PBI Dev target",IF(AND($AA90&lt;&gt;"",$V90&lt;&gt;"",$AA90&lt;$V90),"DPO Approval target is before QA target",IF(AND($AG90&lt;&gt;"",$AA90&lt;&gt;"",$AG90&lt;$AA90),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL90" s="31"/>
@@ -13220,7 +13243,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:40" ht="14.45" hidden="1">
+    <row r="91" spans="1:40" ht="14.45">
       <c r="A91" s="31" t="s">
         <v>126</v>
       </c>
@@ -13298,9 +13321,9 @@
       <c r="AH91" s="31"/>
       <c r="AI91" s="31"/>
       <c r="AJ91" s="31"/>
-      <c r="AK91" s="31" t="str">
-        <f>IF($B91="","",IF(AND(LEFT($AJ91,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B91)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ91,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B91)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ91="Yes – needs DB Dev to fix",M91&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B91)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ91="Yes – needs PBI Dev to fix",S91&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B91)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ91="Yes – needs QA to fix",Y91&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B91)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B91)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B91)&gt;0,"",IF(AND(V91&lt;&gt;"",K91&lt;&gt;"",V91&lt;K91),"QA target is before DB Dev target",IF(AND(V91&lt;&gt;"",Q91&lt;&gt;"",V91&lt;Q91),"QA target is before PBI Dev target",IF(AND(AA91&lt;&gt;"",V91&lt;&gt;"",AA91&lt;V91),"DPO Approval target is before QA target",IF(AND(AG91&lt;&gt;"",AA91&lt;&gt;"",AG91&lt;AA91),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
-        <v/>
+      <c r="AK91" s="31" t="str" cm="1">
+        <f t="array" ref="AK91">IF($B91="","",_xlfn.LET(_xlpm.nm,$B91,_xlpm.st,$C91,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M91,_xlpm.st="DB Dev",$M91,_xlpm.st="PBI Dev",$S91,_xlpm.st="QA",$Y91,_xlpm.st="DPO Approval",$AC91,_xlpm.st="Ready for Release in Prod",$AG91,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ91,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ91,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B91)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B91)&gt;0,"",IF(AND($V91&lt;&gt;"",$K91&lt;&gt;"",$V91&lt;$K91),"QA target is before DB Dev target",IF(AND($V91&lt;&gt;"",$Q91&lt;&gt;"",$V91&lt;$Q91),"QA target is before PBI Dev target",IF(AND($AA91&lt;&gt;"",$V91&lt;&gt;"",$AA91&lt;$V91),"DPO Approval target is before QA target",IF(AND($AG91&lt;&gt;"",$AA91&lt;&gt;"",$AG91&lt;$AA91),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v>Move status to PBI Dev</v>
       </c>
       <c r="AL91" s="31" t="s">
         <v>274</v>
@@ -13314,7 +13337,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:40" ht="14.45" hidden="1">
+    <row r="92" spans="1:40" ht="14.45">
       <c r="A92" s="31" t="s">
         <v>126</v>
       </c>
@@ -13390,9 +13413,9 @@
       <c r="AH92" s="31"/>
       <c r="AI92" s="31"/>
       <c r="AJ92" s="31"/>
-      <c r="AK92" s="31" t="str">
-        <f>IF($B92="","",IF(AND(LEFT($AJ92,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B92)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ92,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B92)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ92="Yes – needs DB Dev to fix",M92&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B92)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ92="Yes – needs PBI Dev to fix",S92&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B92)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ92="Yes – needs QA to fix",Y92&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B92)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B92)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B92)&gt;0,"",IF(AND(V92&lt;&gt;"",K92&lt;&gt;"",V92&lt;K92),"QA target is before DB Dev target",IF(AND(V92&lt;&gt;"",Q92&lt;&gt;"",V92&lt;Q92),"QA target is before PBI Dev target",IF(AND(AA92&lt;&gt;"",V92&lt;&gt;"",AA92&lt;V92),"DPO Approval target is before QA target",IF(AND(AG92&lt;&gt;"",AA92&lt;&gt;"",AG92&lt;AA92),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
-        <v/>
+      <c r="AK92" s="31" t="str" cm="1">
+        <f t="array" ref="AK92">IF($B92="","",_xlfn.LET(_xlpm.nm,$B92,_xlpm.st,$C92,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M92,_xlpm.st="DB Dev",$M92,_xlpm.st="PBI Dev",$S92,_xlpm.st="QA",$Y92,_xlpm.st="DPO Approval",$AC92,_xlpm.st="Ready for Release in Prod",$AG92,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ92,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ92,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B92)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B92)&gt;0,"",IF(AND($V92&lt;&gt;"",$K92&lt;&gt;"",$V92&lt;$K92),"QA target is before DB Dev target",IF(AND($V92&lt;&gt;"",$Q92&lt;&gt;"",$V92&lt;$Q92),"QA target is before PBI Dev target",IF(AND($AA92&lt;&gt;"",$V92&lt;&gt;"",$AA92&lt;$V92),"DPO Approval target is before QA target",IF(AND($AG92&lt;&gt;"",$AA92&lt;&gt;"",$AG92&lt;$AA92),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v>Move status to PBI Dev</v>
       </c>
       <c r="AL92" s="31" t="s">
         <v>276</v>
@@ -13406,7 +13429,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:40" ht="14.45" hidden="1">
+    <row r="93" spans="1:40" ht="14.45">
       <c r="A93" s="31" t="s">
         <v>126</v>
       </c>
@@ -13476,8 +13499,8 @@
       <c r="AH93" s="31"/>
       <c r="AI93" s="31"/>
       <c r="AJ93" s="31"/>
-      <c r="AK93" s="31" t="str">
-        <f>IF($B93="","",IF(AND(LEFT($AJ93,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B93)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ93,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B93)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ93="Yes – needs DB Dev to fix",M93&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B93)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ93="Yes – needs PBI Dev to fix",S93&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B93)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ93="Yes – needs QA to fix",Y93&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B93)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B93)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B93)&gt;0,"",IF(AND(V93&lt;&gt;"",K93&lt;&gt;"",V93&lt;K93),"QA target is before DB Dev target",IF(AND(V93&lt;&gt;"",Q93&lt;&gt;"",V93&lt;Q93),"QA target is before PBI Dev target",IF(AND(AA93&lt;&gt;"",V93&lt;&gt;"",AA93&lt;V93),"DPO Approval target is before QA target",IF(AND(AG93&lt;&gt;"",AA93&lt;&gt;"",AG93&lt;AA93),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK93" s="31" t="str" cm="1">
+        <f t="array" ref="AK93">IF($B93="","",_xlfn.LET(_xlpm.nm,$B93,_xlpm.st,$C93,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M93,_xlpm.st="DB Dev",$M93,_xlpm.st="PBI Dev",$S93,_xlpm.st="QA",$Y93,_xlpm.st="DPO Approval",$AC93,_xlpm.st="Ready for Release in Prod",$AG93,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ93,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ93,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B93)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B93)&gt;0,"",IF(AND($V93&lt;&gt;"",$K93&lt;&gt;"",$V93&lt;$K93),"QA target is before DB Dev target",IF(AND($V93&lt;&gt;"",$Q93&lt;&gt;"",$V93&lt;$Q93),"QA target is before PBI Dev target",IF(AND($AA93&lt;&gt;"",$V93&lt;&gt;"",$AA93&lt;$V93),"DPO Approval target is before QA target",IF(AND($AG93&lt;&gt;"",$AA93&lt;&gt;"",$AG93&lt;$AA93),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL93" s="31"/>
@@ -13490,7 +13513,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:40" ht="14.45" hidden="1">
+    <row r="94" spans="1:40" ht="14.45">
       <c r="A94" s="31" t="s">
         <v>126</v>
       </c>
@@ -13560,8 +13583,8 @@
       <c r="AH94" s="31"/>
       <c r="AI94" s="31"/>
       <c r="AJ94" s="31"/>
-      <c r="AK94" s="31" t="str">
-        <f>IF($B94="","",IF(AND(LEFT($AJ94,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B94)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ94,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B94)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ94="Yes – needs DB Dev to fix",M94&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B94)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ94="Yes – needs PBI Dev to fix",S94&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B94)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ94="Yes – needs QA to fix",Y94&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B94)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B94)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B94)&gt;0,"",IF(AND(V94&lt;&gt;"",K94&lt;&gt;"",V94&lt;K94),"QA target is before DB Dev target",IF(AND(V94&lt;&gt;"",Q94&lt;&gt;"",V94&lt;Q94),"QA target is before PBI Dev target",IF(AND(AA94&lt;&gt;"",V94&lt;&gt;"",AA94&lt;V94),"DPO Approval target is before QA target",IF(AND(AG94&lt;&gt;"",AA94&lt;&gt;"",AG94&lt;AA94),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK94" s="31" t="str" cm="1">
+        <f t="array" ref="AK94">IF($B94="","",_xlfn.LET(_xlpm.nm,$B94,_xlpm.st,$C94,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M94,_xlpm.st="DB Dev",$M94,_xlpm.st="PBI Dev",$S94,_xlpm.st="QA",$Y94,_xlpm.st="DPO Approval",$AC94,_xlpm.st="Ready for Release in Prod",$AG94,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ94,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ94,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B94)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B94)&gt;0,"",IF(AND($V94&lt;&gt;"",$K94&lt;&gt;"",$V94&lt;$K94),"QA target is before DB Dev target",IF(AND($V94&lt;&gt;"",$Q94&lt;&gt;"",$V94&lt;$Q94),"QA target is before PBI Dev target",IF(AND($AA94&lt;&gt;"",$V94&lt;&gt;"",$AA94&lt;$V94),"DPO Approval target is before QA target",IF(AND($AG94&lt;&gt;"",$AA94&lt;&gt;"",$AG94&lt;$AA94),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL94" s="31"/>
@@ -13574,7 +13597,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:40" ht="14.45" hidden="1">
+    <row r="95" spans="1:40" ht="14.45">
       <c r="A95" s="31" t="s">
         <v>126</v>
       </c>
@@ -13646,8 +13669,8 @@
       <c r="AH95" s="31"/>
       <c r="AI95" s="31"/>
       <c r="AJ95" s="31"/>
-      <c r="AK95" s="31" t="str">
-        <f>IF($B95="","",IF(AND(LEFT($AJ95,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B95)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ95,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B95)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ95="Yes – needs DB Dev to fix",M95&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B95)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ95="Yes – needs PBI Dev to fix",S95&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B95)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ95="Yes – needs QA to fix",Y95&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B95)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B95)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B95)&gt;0,"",IF(AND(V95&lt;&gt;"",K95&lt;&gt;"",V95&lt;K95),"QA target is before DB Dev target",IF(AND(V95&lt;&gt;"",Q95&lt;&gt;"",V95&lt;Q95),"QA target is before PBI Dev target",IF(AND(AA95&lt;&gt;"",V95&lt;&gt;"",AA95&lt;V95),"DPO Approval target is before QA target",IF(AND(AG95&lt;&gt;"",AA95&lt;&gt;"",AG95&lt;AA95),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK95" s="31" t="str" cm="1">
+        <f t="array" ref="AK95">IF($B95="","",_xlfn.LET(_xlpm.nm,$B95,_xlpm.st,$C95,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M95,_xlpm.st="DB Dev",$M95,_xlpm.st="PBI Dev",$S95,_xlpm.st="QA",$Y95,_xlpm.st="DPO Approval",$AC95,_xlpm.st="Ready for Release in Prod",$AG95,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ95,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ95,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B95)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B95)&gt;0,"",IF(AND($V95&lt;&gt;"",$K95&lt;&gt;"",$V95&lt;$K95),"QA target is before DB Dev target",IF(AND($V95&lt;&gt;"",$Q95&lt;&gt;"",$V95&lt;$Q95),"QA target is before PBI Dev target",IF(AND($AA95&lt;&gt;"",$V95&lt;&gt;"",$AA95&lt;$V95),"DPO Approval target is before QA target",IF(AND($AG95&lt;&gt;"",$AA95&lt;&gt;"",$AG95&lt;$AA95),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL95" s="31"/>
@@ -13660,7 +13683,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:40" ht="14.45" hidden="1">
+    <row r="96" spans="1:40" ht="14.45">
       <c r="A96" s="31" t="s">
         <v>126</v>
       </c>
@@ -13732,8 +13755,8 @@
       <c r="AH96" s="31"/>
       <c r="AI96" s="31"/>
       <c r="AJ96" s="31"/>
-      <c r="AK96" s="31" t="str">
-        <f>IF($B96="","",IF(AND(LEFT($AJ96,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B96)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ96,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B96)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ96="Yes – needs DB Dev to fix",M96&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B96)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ96="Yes – needs PBI Dev to fix",S96&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B96)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ96="Yes – needs QA to fix",Y96&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B96)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B96)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B96)&gt;0,"",IF(AND(V96&lt;&gt;"",K96&lt;&gt;"",V96&lt;K96),"QA target is before DB Dev target",IF(AND(V96&lt;&gt;"",Q96&lt;&gt;"",V96&lt;Q96),"QA target is before PBI Dev target",IF(AND(AA96&lt;&gt;"",V96&lt;&gt;"",AA96&lt;V96),"DPO Approval target is before QA target",IF(AND(AG96&lt;&gt;"",AA96&lt;&gt;"",AG96&lt;AA96),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK96" s="31" t="str" cm="1">
+        <f t="array" ref="AK96">IF($B96="","",_xlfn.LET(_xlpm.nm,$B96,_xlpm.st,$C96,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M96,_xlpm.st="DB Dev",$M96,_xlpm.st="PBI Dev",$S96,_xlpm.st="QA",$Y96,_xlpm.st="DPO Approval",$AC96,_xlpm.st="Ready for Release in Prod",$AG96,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ96,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ96,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B96)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B96)&gt;0,"",IF(AND($V96&lt;&gt;"",$K96&lt;&gt;"",$V96&lt;$K96),"QA target is before DB Dev target",IF(AND($V96&lt;&gt;"",$Q96&lt;&gt;"",$V96&lt;$Q96),"QA target is before PBI Dev target",IF(AND($AA96&lt;&gt;"",$V96&lt;&gt;"",$AA96&lt;$V96),"DPO Approval target is before QA target",IF(AND($AG96&lt;&gt;"",$AA96&lt;&gt;"",$AG96&lt;$AA96),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL96" s="31"/>
@@ -13746,7 +13769,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:40" ht="14.45" hidden="1">
+    <row r="97" spans="1:40" ht="14.45">
       <c r="A97" s="31" t="s">
         <v>126</v>
       </c>
@@ -13816,8 +13839,8 @@
       <c r="AH97" s="31"/>
       <c r="AI97" s="31"/>
       <c r="AJ97" s="31"/>
-      <c r="AK97" s="31" t="str">
-        <f>IF($B97="","",IF(AND(LEFT($AJ97,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B97)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ97,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B97)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ97="Yes – needs DB Dev to fix",M97&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B97)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ97="Yes – needs PBI Dev to fix",S97&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B97)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ97="Yes – needs QA to fix",Y97&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B97)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B97)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B97)&gt;0,"",IF(AND(V97&lt;&gt;"",K97&lt;&gt;"",V97&lt;K97),"QA target is before DB Dev target",IF(AND(V97&lt;&gt;"",Q97&lt;&gt;"",V97&lt;Q97),"QA target is before PBI Dev target",IF(AND(AA97&lt;&gt;"",V97&lt;&gt;"",AA97&lt;V97),"DPO Approval target is before QA target",IF(AND(AG97&lt;&gt;"",AA97&lt;&gt;"",AG97&lt;AA97),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK97" s="31" t="str" cm="1">
+        <f t="array" ref="AK97">IF($B97="","",_xlfn.LET(_xlpm.nm,$B97,_xlpm.st,$C97,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M97,_xlpm.st="DB Dev",$M97,_xlpm.st="PBI Dev",$S97,_xlpm.st="QA",$Y97,_xlpm.st="DPO Approval",$AC97,_xlpm.st="Ready for Release in Prod",$AG97,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ97,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ97,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B97)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B97)&gt;0,"",IF(AND($V97&lt;&gt;"",$K97&lt;&gt;"",$V97&lt;$K97),"QA target is before DB Dev target",IF(AND($V97&lt;&gt;"",$Q97&lt;&gt;"",$V97&lt;$Q97),"QA target is before PBI Dev target",IF(AND($AA97&lt;&gt;"",$V97&lt;&gt;"",$AA97&lt;$V97),"DPO Approval target is before QA target",IF(AND($AG97&lt;&gt;"",$AA97&lt;&gt;"",$AG97&lt;$AA97),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL97" s="31"/>
@@ -13830,7 +13853,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:40" ht="14.45" hidden="1">
+    <row r="98" spans="1:40" ht="14.45">
       <c r="A98" s="31" t="s">
         <v>126</v>
       </c>
@@ -13900,8 +13923,8 @@
       <c r="AH98" s="31"/>
       <c r="AI98" s="31"/>
       <c r="AJ98" s="31"/>
-      <c r="AK98" s="31" t="str">
-        <f>IF($B98="","",IF(AND(LEFT($AJ98,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B98)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ98,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B98)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ98="Yes – needs DB Dev to fix",M98&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B98)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ98="Yes – needs PBI Dev to fix",S98&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B98)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ98="Yes – needs QA to fix",Y98&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B98)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B98)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B98)&gt;0,"",IF(AND(V98&lt;&gt;"",K98&lt;&gt;"",V98&lt;K98),"QA target is before DB Dev target",IF(AND(V98&lt;&gt;"",Q98&lt;&gt;"",V98&lt;Q98),"QA target is before PBI Dev target",IF(AND(AA98&lt;&gt;"",V98&lt;&gt;"",AA98&lt;V98),"DPO Approval target is before QA target",IF(AND(AG98&lt;&gt;"",AA98&lt;&gt;"",AG98&lt;AA98),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK98" s="31" t="str" cm="1">
+        <f t="array" ref="AK98">IF($B98="","",_xlfn.LET(_xlpm.nm,$B98,_xlpm.st,$C98,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M98,_xlpm.st="DB Dev",$M98,_xlpm.st="PBI Dev",$S98,_xlpm.st="QA",$Y98,_xlpm.st="DPO Approval",$AC98,_xlpm.st="Ready for Release in Prod",$AG98,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ98,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ98,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B98)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B98)&gt;0,"",IF(AND($V98&lt;&gt;"",$K98&lt;&gt;"",$V98&lt;$K98),"QA target is before DB Dev target",IF(AND($V98&lt;&gt;"",$Q98&lt;&gt;"",$V98&lt;$Q98),"QA target is before PBI Dev target",IF(AND($AA98&lt;&gt;"",$V98&lt;&gt;"",$AA98&lt;$V98),"DPO Approval target is before QA target",IF(AND($AG98&lt;&gt;"",$AA98&lt;&gt;"",$AG98&lt;$AA98),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL98" s="31"/>
@@ -13914,7 +13937,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="1:40" ht="14.45" hidden="1">
+    <row r="99" spans="1:40" ht="14.45">
       <c r="A99" s="31" t="s">
         <v>126</v>
       </c>
@@ -13986,8 +14009,8 @@
       <c r="AH99" s="31"/>
       <c r="AI99" s="31"/>
       <c r="AJ99" s="31"/>
-      <c r="AK99" s="31" t="str">
-        <f>IF($B99="","",IF(AND(LEFT($AJ99,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B99)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ99,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B99)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ99="Yes – needs DB Dev to fix",M99&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B99)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ99="Yes – needs PBI Dev to fix",S99&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B99)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ99="Yes – needs QA to fix",Y99&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B99)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B99)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B99)&gt;0,"",IF(AND(V99&lt;&gt;"",K99&lt;&gt;"",V99&lt;K99),"QA target is before DB Dev target",IF(AND(V99&lt;&gt;"",Q99&lt;&gt;"",V99&lt;Q99),"QA target is before PBI Dev target",IF(AND(AA99&lt;&gt;"",V99&lt;&gt;"",AA99&lt;V99),"DPO Approval target is before QA target",IF(AND(AG99&lt;&gt;"",AA99&lt;&gt;"",AG99&lt;AA99),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK99" s="31" t="str" cm="1">
+        <f t="array" ref="AK99">IF($B99="","",_xlfn.LET(_xlpm.nm,$B99,_xlpm.st,$C99,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M99,_xlpm.st="DB Dev",$M99,_xlpm.st="PBI Dev",$S99,_xlpm.st="QA",$Y99,_xlpm.st="DPO Approval",$AC99,_xlpm.st="Ready for Release in Prod",$AG99,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ99,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ99,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B99)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B99)&gt;0,"",IF(AND($V99&lt;&gt;"",$K99&lt;&gt;"",$V99&lt;$K99),"QA target is before DB Dev target",IF(AND($V99&lt;&gt;"",$Q99&lt;&gt;"",$V99&lt;$Q99),"QA target is before PBI Dev target",IF(AND($AA99&lt;&gt;"",$V99&lt;&gt;"",$AA99&lt;$V99),"DPO Approval target is before QA target",IF(AND($AG99&lt;&gt;"",$AA99&lt;&gt;"",$AG99&lt;$AA99),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL99" s="31"/>
@@ -14000,7 +14023,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:40" ht="14.45" hidden="1">
+    <row r="100" spans="1:40" ht="14.45">
       <c r="A100" s="31" t="s">
         <v>126</v>
       </c>
@@ -14070,8 +14093,8 @@
       <c r="AH100" s="31"/>
       <c r="AI100" s="31"/>
       <c r="AJ100" s="31"/>
-      <c r="AK100" s="31" t="str">
-        <f>IF($B100="","",IF(AND(LEFT($AJ100,3)="Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B100)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))=0),"Blocked - log it on Rework Log",IF(AND(LEFT($AJ100,3)&lt;&gt;"Yes",SUMPRODUCT(('Rework Log'!$A$3:$A$498=$B100)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))&gt;0),"Open rework row - mark Blocked? or close it",IF(AND($AJ100="Yes – needs DB Dev to fix",M100&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B100)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old DB Dev completion date to Rework Log (col H)",IF(AND($AJ100="Yes – needs PBI Dev to fix",S100&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B100)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old PBI Dev completion date to Rework Log (col H)",IF(AND($AJ100="Yes – needs QA to fix",Y100&lt;&gt;"",SUMPRODUCT(MAX((('Rework Log'!$A$3:$A$498=$B100)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test"))*'Rework Log'!$I$3:$I$498))&gt;0),"Move old QA completion date to Rework Log (col H)",IF(COUNTIF($B$2:$B$527,$B100)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B100)&gt;0,"",IF(AND(V100&lt;&gt;"",K100&lt;&gt;"",V100&lt;K100),"QA target is before DB Dev target",IF(AND(V100&lt;&gt;"",Q100&lt;&gt;"",V100&lt;Q100),"QA target is before PBI Dev target",IF(AND(AA100&lt;&gt;"",V100&lt;&gt;"",AA100&lt;V100),"DPO Approval target is before QA target",IF(AND(AG100&lt;&gt;"",AA100&lt;&gt;"",AG100&lt;AA100),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+      <c r="AK100" s="31" t="str" cm="1">
+        <f t="array" ref="AK100">IF($B100="","",_xlfn.LET(_xlpm.nm,$B100,_xlpm.st,$C100,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M100,_xlpm.st="DB Dev",$M100,_xlpm.st="PBI Dev",$S100,_xlpm.st="QA",$Y100,_xlpm.st="DPO Approval",$AC100,_xlpm.st="Ready for Release in Prod",$AG100,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ100,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ100,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B100)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B100)&gt;0,"",IF(AND($V100&lt;&gt;"",$K100&lt;&gt;"",$V100&lt;$K100),"QA target is before DB Dev target",IF(AND($V100&lt;&gt;"",$Q100&lt;&gt;"",$V100&lt;$Q100),"QA target is before PBI Dev target",IF(AND($AA100&lt;&gt;"",$V100&lt;&gt;"",$AA100&lt;$V100),"DPO Approval target is before QA target",IF(AND($AG100&lt;&gt;"",$AA100&lt;&gt;"",$AG100&lt;$AA100),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
         <v/>
       </c>
       <c r="AL100" s="31"/>
@@ -14084,7 +14107,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:40" ht="14.45" hidden="1">
+    <row r="101" spans="1:40" ht="14.45">
       <c r="A101" s="31" t="s">
         <v>294</v>
       </c>
@@ -14154,7 +14177,10 @@
       <c r="AH101" s="31"/>
       <c r="AI101" s="31"/>
       <c r="AJ101" s="31"/>
-      <c r="AK101" s="31"/>
+      <c r="AK101" s="31" t="str" cm="1">
+        <f t="array" ref="AK101">IF($B101="","",_xlfn.LET(_xlpm.nm,$B101,_xlpm.st,$C101,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M101,_xlpm.st="DB Dev",$M101,_xlpm.st="PBI Dev",$S101,_xlpm.st="QA",$Y101,_xlpm.st="DPO Approval",$AC101,_xlpm.st="Ready for Release in Prod",$AG101,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ101,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ101,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B101)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B101)&gt;0,"",IF(AND($V101&lt;&gt;"",$K101&lt;&gt;"",$V101&lt;$K101),"QA target is before DB Dev target",IF(AND($V101&lt;&gt;"",$Q101&lt;&gt;"",$V101&lt;$Q101),"QA target is before PBI Dev target",IF(AND($AA101&lt;&gt;"",$V101&lt;&gt;"",$AA101&lt;$V101),"DPO Approval target is before QA target",IF(AND($AG101&lt;&gt;"",$AA101&lt;&gt;"",$AG101&lt;$AA101),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL101" s="31"/>
       <c r="AM101" s="31" t="str" cm="1">
         <f t="array" ref="AM101">_xlfn.LET(_xlpm.rep,$B101,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -14165,7 +14191,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:40" ht="14.45" hidden="1">
+    <row r="102" spans="1:40" ht="14.45">
       <c r="A102" s="31" t="s">
         <v>294</v>
       </c>
@@ -14235,7 +14261,10 @@
       <c r="AH102" s="31"/>
       <c r="AI102" s="31"/>
       <c r="AJ102" s="31"/>
-      <c r="AK102" s="31"/>
+      <c r="AK102" s="31" t="str" cm="1">
+        <f t="array" ref="AK102">IF($B102="","",_xlfn.LET(_xlpm.nm,$B102,_xlpm.st,$C102,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M102,_xlpm.st="DB Dev",$M102,_xlpm.st="PBI Dev",$S102,_xlpm.st="QA",$Y102,_xlpm.st="DPO Approval",$AC102,_xlpm.st="Ready for Release in Prod",$AG102,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ102,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ102,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B102)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B102)&gt;0,"",IF(AND($V102&lt;&gt;"",$K102&lt;&gt;"",$V102&lt;$K102),"QA target is before DB Dev target",IF(AND($V102&lt;&gt;"",$Q102&lt;&gt;"",$V102&lt;$Q102),"QA target is before PBI Dev target",IF(AND($AA102&lt;&gt;"",$V102&lt;&gt;"",$AA102&lt;$V102),"DPO Approval target is before QA target",IF(AND($AG102&lt;&gt;"",$AA102&lt;&gt;"",$AG102&lt;$AA102),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL102" s="31"/>
       <c r="AM102" s="31" t="str" cm="1">
         <f t="array" ref="AM102">_xlfn.LET(_xlpm.rep,$B102,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -14246,7 +14275,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:40" ht="14.45" hidden="1">
+    <row r="103" spans="1:40" ht="14.45">
       <c r="A103" s="31" t="s">
         <v>294</v>
       </c>
@@ -14316,7 +14345,10 @@
       <c r="AH103" s="31"/>
       <c r="AI103" s="31"/>
       <c r="AJ103" s="31"/>
-      <c r="AK103" s="31"/>
+      <c r="AK103" s="31" t="str" cm="1">
+        <f t="array" ref="AK103">IF($B103="","",_xlfn.LET(_xlpm.nm,$B103,_xlpm.st,$C103,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M103,_xlpm.st="DB Dev",$M103,_xlpm.st="PBI Dev",$S103,_xlpm.st="QA",$Y103,_xlpm.st="DPO Approval",$AC103,_xlpm.st="Ready for Release in Prod",$AG103,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ103,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ103,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B103)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B103)&gt;0,"",IF(AND($V103&lt;&gt;"",$K103&lt;&gt;"",$V103&lt;$K103),"QA target is before DB Dev target",IF(AND($V103&lt;&gt;"",$Q103&lt;&gt;"",$V103&lt;$Q103),"QA target is before PBI Dev target",IF(AND($AA103&lt;&gt;"",$V103&lt;&gt;"",$AA103&lt;$V103),"DPO Approval target is before QA target",IF(AND($AG103&lt;&gt;"",$AA103&lt;&gt;"",$AG103&lt;$AA103),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL103" s="31"/>
       <c r="AM103" s="31" t="str" cm="1">
         <f t="array" ref="AM103">_xlfn.LET(_xlpm.rep,$B103,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -14327,7 +14359,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:40" ht="14.45" hidden="1">
+    <row r="104" spans="1:40" ht="14.45">
       <c r="A104" s="31" t="s">
         <v>304</v>
       </c>
@@ -14397,7 +14429,10 @@
       <c r="AH104" s="31"/>
       <c r="AI104" s="31"/>
       <c r="AJ104" s="31"/>
-      <c r="AK104" s="31"/>
+      <c r="AK104" s="31" t="str" cm="1">
+        <f t="array" ref="AK104">IF($B104="","",_xlfn.LET(_xlpm.nm,$B104,_xlpm.st,$C104,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M104,_xlpm.st="DB Dev",$M104,_xlpm.st="PBI Dev",$S104,_xlpm.st="QA",$Y104,_xlpm.st="DPO Approval",$AC104,_xlpm.st="Ready for Release in Prod",$AG104,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ104,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ104,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B104)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B104)&gt;0,"",IF(AND($V104&lt;&gt;"",$K104&lt;&gt;"",$V104&lt;$K104),"QA target is before DB Dev target",IF(AND($V104&lt;&gt;"",$Q104&lt;&gt;"",$V104&lt;$Q104),"QA target is before PBI Dev target",IF(AND($AA104&lt;&gt;"",$V104&lt;&gt;"",$AA104&lt;$V104),"DPO Approval target is before QA target",IF(AND($AG104&lt;&gt;"",$AA104&lt;&gt;"",$AG104&lt;$AA104),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL104" s="31"/>
       <c r="AM104" s="31" t="str" cm="1">
         <f t="array" ref="AM104">_xlfn.LET(_xlpm.rep,$B104,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -14408,7 +14443,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:40" ht="14.45" hidden="1">
+    <row r="105" spans="1:40" ht="14.45">
       <c r="A105" s="31" t="s">
         <v>294</v>
       </c>
@@ -14478,7 +14513,10 @@
       <c r="AH105" s="31"/>
       <c r="AI105" s="31"/>
       <c r="AJ105" s="31"/>
-      <c r="AK105" s="31"/>
+      <c r="AK105" s="31" t="str" cm="1">
+        <f t="array" ref="AK105">IF($B105="","",_xlfn.LET(_xlpm.nm,$B105,_xlpm.st,$C105,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M105,_xlpm.st="DB Dev",$M105,_xlpm.st="PBI Dev",$S105,_xlpm.st="QA",$Y105,_xlpm.st="DPO Approval",$AC105,_xlpm.st="Ready for Release in Prod",$AG105,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ105,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ105,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B105)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B105)&gt;0,"",IF(AND($V105&lt;&gt;"",$K105&lt;&gt;"",$V105&lt;$K105),"QA target is before DB Dev target",IF(AND($V105&lt;&gt;"",$Q105&lt;&gt;"",$V105&lt;$Q105),"QA target is before PBI Dev target",IF(AND($AA105&lt;&gt;"",$V105&lt;&gt;"",$AA105&lt;$V105),"DPO Approval target is before QA target",IF(AND($AG105&lt;&gt;"",$AA105&lt;&gt;"",$AG105&lt;$AA105),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL105" s="31"/>
       <c r="AM105" s="31" t="str" cm="1">
         <f t="array" ref="AM105">_xlfn.LET(_xlpm.rep,$B105,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -14489,7 +14527,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:40" ht="14.45" hidden="1">
+    <row r="106" spans="1:40" ht="14.45">
       <c r="A106" s="31" t="s">
         <v>294</v>
       </c>
@@ -14559,7 +14597,10 @@
       <c r="AH106" s="31"/>
       <c r="AI106" s="31"/>
       <c r="AJ106" s="31"/>
-      <c r="AK106" s="31"/>
+      <c r="AK106" s="31" t="str" cm="1">
+        <f t="array" ref="AK106">IF($B106="","",_xlfn.LET(_xlpm.nm,$B106,_xlpm.st,$C106,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M106,_xlpm.st="DB Dev",$M106,_xlpm.st="PBI Dev",$S106,_xlpm.st="QA",$Y106,_xlpm.st="DPO Approval",$AC106,_xlpm.st="Ready for Release in Prod",$AG106,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ106,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ106,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B106)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B106)&gt;0,"",IF(AND($V106&lt;&gt;"",$K106&lt;&gt;"",$V106&lt;$K106),"QA target is before DB Dev target",IF(AND($V106&lt;&gt;"",$Q106&lt;&gt;"",$V106&lt;$Q106),"QA target is before PBI Dev target",IF(AND($AA106&lt;&gt;"",$V106&lt;&gt;"",$AA106&lt;$V106),"DPO Approval target is before QA target",IF(AND($AG106&lt;&gt;"",$AA106&lt;&gt;"",$AG106&lt;$AA106),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL106" s="31"/>
       <c r="AM106" s="31" t="str" cm="1">
         <f t="array" ref="AM106">_xlfn.LET(_xlpm.rep,$B106,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -14570,7 +14611,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" spans="1:40" ht="14.45" hidden="1">
+    <row r="107" spans="1:40" ht="14.45">
       <c r="A107" s="31" t="s">
         <v>294</v>
       </c>
@@ -14640,7 +14681,10 @@
       <c r="AH107" s="31"/>
       <c r="AI107" s="31"/>
       <c r="AJ107" s="31"/>
-      <c r="AK107" s="31"/>
+      <c r="AK107" s="31" t="str" cm="1">
+        <f t="array" ref="AK107">IF($B107="","",_xlfn.LET(_xlpm.nm,$B107,_xlpm.st,$C107,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M107,_xlpm.st="DB Dev",$M107,_xlpm.st="PBI Dev",$S107,_xlpm.st="QA",$Y107,_xlpm.st="DPO Approval",$AC107,_xlpm.st="Ready for Release in Prod",$AG107,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ107,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ107,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B107)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B107)&gt;0,"",IF(AND($V107&lt;&gt;"",$K107&lt;&gt;"",$V107&lt;$K107),"QA target is before DB Dev target",IF(AND($V107&lt;&gt;"",$Q107&lt;&gt;"",$V107&lt;$Q107),"QA target is before PBI Dev target",IF(AND($AA107&lt;&gt;"",$V107&lt;&gt;"",$AA107&lt;$V107),"DPO Approval target is before QA target",IF(AND($AG107&lt;&gt;"",$AA107&lt;&gt;"",$AG107&lt;$AA107),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL107" s="31"/>
       <c r="AM107" s="31" t="str" cm="1">
         <f t="array" ref="AM107">_xlfn.LET(_xlpm.rep,$B107,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -14651,7 +14695,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:40" ht="14.45" hidden="1">
+    <row r="108" spans="1:40" ht="14.45">
       <c r="A108" s="31" t="s">
         <v>294</v>
       </c>
@@ -14721,7 +14765,10 @@
       <c r="AH108" s="31"/>
       <c r="AI108" s="31"/>
       <c r="AJ108" s="31"/>
-      <c r="AK108" s="31"/>
+      <c r="AK108" s="31" t="str" cm="1">
+        <f t="array" ref="AK108">IF($B108="","",_xlfn.LET(_xlpm.nm,$B108,_xlpm.st,$C108,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M108,_xlpm.st="DB Dev",$M108,_xlpm.st="PBI Dev",$S108,_xlpm.st="QA",$Y108,_xlpm.st="DPO Approval",$AC108,_xlpm.st="Ready for Release in Prod",$AG108,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ108,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ108,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B108)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B108)&gt;0,"",IF(AND($V108&lt;&gt;"",$K108&lt;&gt;"",$V108&lt;$K108),"QA target is before DB Dev target",IF(AND($V108&lt;&gt;"",$Q108&lt;&gt;"",$V108&lt;$Q108),"QA target is before PBI Dev target",IF(AND($AA108&lt;&gt;"",$V108&lt;&gt;"",$AA108&lt;$V108),"DPO Approval target is before QA target",IF(AND($AG108&lt;&gt;"",$AA108&lt;&gt;"",$AG108&lt;$AA108),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL108" s="31"/>
       <c r="AM108" s="31" t="str" cm="1">
         <f t="array" ref="AM108">_xlfn.LET(_xlpm.rep,$B108,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -14732,7 +14779,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:40" ht="14.45" hidden="1">
+    <row r="109" spans="1:40" ht="14.45">
       <c r="A109" s="31" t="s">
         <v>304</v>
       </c>
@@ -14802,7 +14849,10 @@
       <c r="AH109" s="31"/>
       <c r="AI109" s="31"/>
       <c r="AJ109" s="31"/>
-      <c r="AK109" s="31"/>
+      <c r="AK109" s="31" t="str" cm="1">
+        <f t="array" ref="AK109">IF($B109="","",_xlfn.LET(_xlpm.nm,$B109,_xlpm.st,$C109,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M109,_xlpm.st="DB Dev",$M109,_xlpm.st="PBI Dev",$S109,_xlpm.st="QA",$Y109,_xlpm.st="DPO Approval",$AC109,_xlpm.st="Ready for Release in Prod",$AG109,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ109,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ109,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B109)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B109)&gt;0,"",IF(AND($V109&lt;&gt;"",$K109&lt;&gt;"",$V109&lt;$K109),"QA target is before DB Dev target",IF(AND($V109&lt;&gt;"",$Q109&lt;&gt;"",$V109&lt;$Q109),"QA target is before PBI Dev target",IF(AND($AA109&lt;&gt;"",$V109&lt;&gt;"",$AA109&lt;$V109),"DPO Approval target is before QA target",IF(AND($AG109&lt;&gt;"",$AA109&lt;&gt;"",$AG109&lt;$AA109),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL109" s="31"/>
       <c r="AM109" s="31" t="str" cm="1">
         <f t="array" ref="AM109">_xlfn.LET(_xlpm.rep,$B109,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -14813,7 +14863,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:40" ht="14.45" hidden="1">
+    <row r="110" spans="1:40" ht="14.45">
       <c r="A110" s="31" t="s">
         <v>294</v>
       </c>
@@ -14883,7 +14933,10 @@
       <c r="AH110" s="31"/>
       <c r="AI110" s="31"/>
       <c r="AJ110" s="31"/>
-      <c r="AK110" s="31"/>
+      <c r="AK110" s="31" t="str" cm="1">
+        <f t="array" ref="AK110">IF($B110="","",_xlfn.LET(_xlpm.nm,$B110,_xlpm.st,$C110,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M110,_xlpm.st="DB Dev",$M110,_xlpm.st="PBI Dev",$S110,_xlpm.st="QA",$Y110,_xlpm.st="DPO Approval",$AC110,_xlpm.st="Ready for Release in Prod",$AG110,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ110,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ110,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B110)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B110)&gt;0,"",IF(AND($V110&lt;&gt;"",$K110&lt;&gt;"",$V110&lt;$K110),"QA target is before DB Dev target",IF(AND($V110&lt;&gt;"",$Q110&lt;&gt;"",$V110&lt;$Q110),"QA target is before PBI Dev target",IF(AND($AA110&lt;&gt;"",$V110&lt;&gt;"",$AA110&lt;$V110),"DPO Approval target is before QA target",IF(AND($AG110&lt;&gt;"",$AA110&lt;&gt;"",$AG110&lt;$AA110),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL110" s="31"/>
       <c r="AM110" s="31" t="str" cm="1">
         <f t="array" ref="AM110">_xlfn.LET(_xlpm.rep,$B110,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -14894,7 +14947,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:40" ht="14.45" hidden="1">
+    <row r="111" spans="1:40" ht="14.45">
       <c r="A111" s="31" t="s">
         <v>304</v>
       </c>
@@ -14964,7 +15017,10 @@
       <c r="AH111" s="31"/>
       <c r="AI111" s="31"/>
       <c r="AJ111" s="31"/>
-      <c r="AK111" s="31"/>
+      <c r="AK111" s="31" t="str" cm="1">
+        <f t="array" ref="AK111">IF($B111="","",_xlfn.LET(_xlpm.nm,$B111,_xlpm.st,$C111,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M111,_xlpm.st="DB Dev",$M111,_xlpm.st="PBI Dev",$S111,_xlpm.st="QA",$Y111,_xlpm.st="DPO Approval",$AC111,_xlpm.st="Ready for Release in Prod",$AG111,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ111,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ111,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B111)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B111)&gt;0,"",IF(AND($V111&lt;&gt;"",$K111&lt;&gt;"",$V111&lt;$K111),"QA target is before DB Dev target",IF(AND($V111&lt;&gt;"",$Q111&lt;&gt;"",$V111&lt;$Q111),"QA target is before PBI Dev target",IF(AND($AA111&lt;&gt;"",$V111&lt;&gt;"",$AA111&lt;$V111),"DPO Approval target is before QA target",IF(AND($AG111&lt;&gt;"",$AA111&lt;&gt;"",$AG111&lt;$AA111),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL111" s="31"/>
       <c r="AM111" s="31" t="str" cm="1">
         <f t="array" ref="AM111">_xlfn.LET(_xlpm.rep,$B111,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -14975,7 +15031,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" spans="1:40" ht="14.45" hidden="1">
+    <row r="112" spans="1:40" ht="14.45">
       <c r="A112" s="31" t="s">
         <v>304</v>
       </c>
@@ -15045,7 +15101,10 @@
       <c r="AH112" s="31"/>
       <c r="AI112" s="31"/>
       <c r="AJ112" s="31"/>
-      <c r="AK112" s="31"/>
+      <c r="AK112" s="31" t="str" cm="1">
+        <f t="array" ref="AK112">IF($B112="","",_xlfn.LET(_xlpm.nm,$B112,_xlpm.st,$C112,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M112,_xlpm.st="DB Dev",$M112,_xlpm.st="PBI Dev",$S112,_xlpm.st="QA",$Y112,_xlpm.st="DPO Approval",$AC112,_xlpm.st="Ready for Release in Prod",$AG112,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ112,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ112,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B112)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B112)&gt;0,"",IF(AND($V112&lt;&gt;"",$K112&lt;&gt;"",$V112&lt;$K112),"QA target is before DB Dev target",IF(AND($V112&lt;&gt;"",$Q112&lt;&gt;"",$V112&lt;$Q112),"QA target is before PBI Dev target",IF(AND($AA112&lt;&gt;"",$V112&lt;&gt;"",$AA112&lt;$V112),"DPO Approval target is before QA target",IF(AND($AG112&lt;&gt;"",$AA112&lt;&gt;"",$AG112&lt;$AA112),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL112" s="31"/>
       <c r="AM112" s="31" t="str" cm="1">
         <f t="array" ref="AM112">_xlfn.LET(_xlpm.rep,$B112,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -15056,7 +15115,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:40" ht="14.45" hidden="1">
+    <row r="113" spans="1:40" ht="14.45">
       <c r="A113" s="31" t="s">
         <v>304</v>
       </c>
@@ -15126,7 +15185,10 @@
       <c r="AH113" s="31"/>
       <c r="AI113" s="31"/>
       <c r="AJ113" s="31"/>
-      <c r="AK113" s="31"/>
+      <c r="AK113" s="31" t="str" cm="1">
+        <f t="array" ref="AK113">IF($B113="","",_xlfn.LET(_xlpm.nm,$B113,_xlpm.st,$C113,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M113,_xlpm.st="DB Dev",$M113,_xlpm.st="PBI Dev",$S113,_xlpm.st="QA",$Y113,_xlpm.st="DPO Approval",$AC113,_xlpm.st="Ready for Release in Prod",$AG113,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ113,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ113,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B113)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B113)&gt;0,"",IF(AND($V113&lt;&gt;"",$K113&lt;&gt;"",$V113&lt;$K113),"QA target is before DB Dev target",IF(AND($V113&lt;&gt;"",$Q113&lt;&gt;"",$V113&lt;$Q113),"QA target is before PBI Dev target",IF(AND($AA113&lt;&gt;"",$V113&lt;&gt;"",$AA113&lt;$V113),"DPO Approval target is before QA target",IF(AND($AG113&lt;&gt;"",$AA113&lt;&gt;"",$AG113&lt;$AA113),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL113" s="31"/>
       <c r="AM113" s="31" t="str" cm="1">
         <f t="array" ref="AM113">_xlfn.LET(_xlpm.rep,$B113,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -15137,7 +15199,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:40" ht="14.45" hidden="1">
+    <row r="114" spans="1:40" ht="14.45">
       <c r="A114" s="31" t="s">
         <v>304</v>
       </c>
@@ -15207,7 +15269,10 @@
       <c r="AH114" s="31"/>
       <c r="AI114" s="31"/>
       <c r="AJ114" s="31"/>
-      <c r="AK114" s="31"/>
+      <c r="AK114" s="31" t="str" cm="1">
+        <f t="array" ref="AK114">IF($B114="","",_xlfn.LET(_xlpm.nm,$B114,_xlpm.st,$C114,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M114,_xlpm.st="DB Dev",$M114,_xlpm.st="PBI Dev",$S114,_xlpm.st="QA",$Y114,_xlpm.st="DPO Approval",$AC114,_xlpm.st="Ready for Release in Prod",$AG114,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ114,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ114,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B114)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B114)&gt;0,"",IF(AND($V114&lt;&gt;"",$K114&lt;&gt;"",$V114&lt;$K114),"QA target is before DB Dev target",IF(AND($V114&lt;&gt;"",$Q114&lt;&gt;"",$V114&lt;$Q114),"QA target is before PBI Dev target",IF(AND($AA114&lt;&gt;"",$V114&lt;&gt;"",$AA114&lt;$V114),"DPO Approval target is before QA target",IF(AND($AG114&lt;&gt;"",$AA114&lt;&gt;"",$AG114&lt;$AA114),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL114" s="31"/>
       <c r="AM114" s="31" t="str" cm="1">
         <f t="array" ref="AM114">_xlfn.LET(_xlpm.rep,$B114,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -15218,7 +15283,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:40" ht="21" hidden="1" customHeight="1">
+    <row r="115" spans="1:40" ht="21" customHeight="1">
       <c r="A115" s="31" t="s">
         <v>304</v>
       </c>
@@ -15288,7 +15353,10 @@
       <c r="AH115" s="31"/>
       <c r="AI115" s="31"/>
       <c r="AJ115" s="31"/>
-      <c r="AK115" s="31"/>
+      <c r="AK115" s="31" t="str" cm="1">
+        <f t="array" ref="AK115">IF($B115="","",_xlfn.LET(_xlpm.nm,$B115,_xlpm.st,$C115,_xlpm.ou,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498="")),_xlpm.ob,SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")),_xlpm.oto,IF(SUMPRODUCT(('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""))=0,"",INDEX('Rework Log'!$D$3:$D$498,MATCH(1,('Rework Log'!$A$3:$A$498=_xlpm.nm)*('Rework Log'!$G$3:$G$498&lt;&gt;"Yes")*('Rework Log'!$G$3:$G$498&lt;&gt;"Did not pass re-test")*('Rework Log'!$J$3:$J$498=""),0))),_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.nm),_xlpm.act,_xlfn.IFS(_xlpm.st="NOT STARTED",$M115,_xlpm.st="DB Dev",$M115,_xlpm.st="PBI Dev",$S115,_xlpm.st="QA",$Y115,_xlpm.st="DPO Approval",$AC115,_xlpm.st="Ready for Release in Prod",$AG115,TRUE,""),_xlpm.nxt,_xlfn.IFS(_xlpm.st="NOT STARTED","PBI Dev",_xlpm.st="DB Dev","PBI Dev",_xlpm.st="PBI Dev","QA",_xlpm.st="QA","DPO Approval",_xlpm.st="DPO Approval","Ready for Release in Prod",_xlpm.st="Ready for Release in Prod","RELEASED IN PROD",TRUE,""),IF(AND(_xlpm.ou&gt;0,_xlpm.st&lt;&gt;_xlpm.oto),"Move status back to "&amp;_xlpm.oto,IF(AND(_xlpm.ob=0,LEFT($AJ115,3)="Yes"),"Blocked - log it on Rework Log",IF(AND(_xlpm.ob&gt;0,LEFT($AJ115,3)&lt;&gt;"Yes"),"Open rework row - mark Blocked or close it",IF(AND(_xlpm.ob=0,_xlpm.act&lt;&gt;"",_xlpm.act&gt;=_xlpm.sent,_xlpm.nxt&lt;&gt;""),"Move status to "&amp;_xlpm.nxt,IF(COUNTIF($B$2:$B$527,$B115)&gt;1,"Duplicate name - check row",IF(COUNTIF('Rework Log'!$A$3:$A$498,$B115)&gt;0,"",IF(AND($V115&lt;&gt;"",$K115&lt;&gt;"",$V115&lt;$K115),"QA target is before DB Dev target",IF(AND($V115&lt;&gt;"",$Q115&lt;&gt;"",$V115&lt;$Q115),"QA target is before PBI Dev target",IF(AND($AA115&lt;&gt;"",$V115&lt;&gt;"",$AA115&lt;$V115),"DPO Approval target is before QA target",IF(AND($AG115&lt;&gt;"",$AA115&lt;&gt;"",$AG115&lt;$AA115),"Confirmed Deployed date is before DPO Approval target",""))))))))))))</f>
+        <v/>
+      </c>
       <c r="AL115" s="31"/>
       <c r="AM115" s="31" t="str" cm="1">
         <f t="array" ref="AM115">_xlfn.LET(_xlpm.rep,$B115,_xlpm.sent,_xlfn.MAXIFS('Rework Log'!$B$3:$B$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA"),_xlpm.fixdate,_xlfn.MAXIFS('Rework Log'!$J$3:$J$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.expfix,_xlfn.MAXIFS('Rework Log'!$I$3:$I$498,'Rework Log'!$A$3:$A$498,_xlpm.rep,'Rework Log'!$C$3:$C$498,"QA",'Rework Log'!$B$3:$B$498,_xlpm.sent),_xlpm.base,IF(_xlpm.fixdate&gt;0,_xlpm.fixdate,_xlpm.expfix),IF(OR(_xlpm.rep="",_xlpm.sent=0,_xlpm.base=0),"",WORKDAY(_xlpm.base,3)))</f>
@@ -26427,336 +26495,341 @@
   <sheetProtection formatColumns="0" formatRows="0" sort="0" autoFilter="0"/>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="D2:D527">
-    <cfRule type="expression" dxfId="139" priority="42">
+    <cfRule type="expression" dxfId="140" priority="42">
       <formula>ISNUMBER(SEARCH("Blocked",$D2))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="138" priority="43">
+    <cfRule type="expression" dxfId="139" priority="43">
       <formula>ISNUMBER(SEARCH("overdue",$D2))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="137" priority="44">
+    <cfRule type="expression" dxfId="138" priority="44">
       <formula>ISNUMBER(SEARCH("no target",$D2))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="136" priority="45">
+    <cfRule type="expression" dxfId="137" priority="45">
       <formula>ISNUMBER(SEARCH("Review",$D2))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="135" priority="46">
+    <cfRule type="expression" dxfId="136" priority="46">
       <formula>OR($D2="On track",$D2="Delivered")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:O115">
-    <cfRule type="expression" dxfId="134" priority="20">
+    <cfRule type="expression" dxfId="135" priority="20">
       <formula>$AJ2="Yes – needs DB Dev to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J116:O192">
-    <cfRule type="expression" dxfId="133" priority="25">
+    <cfRule type="expression" dxfId="134" priority="25">
       <formula>$AH116="Yes – needs DB Dev to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K41">
-    <cfRule type="expression" dxfId="132" priority="601">
+    <cfRule type="expression" dxfId="133" priority="601">
       <formula>AND($B41&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="131" priority="602">
+    <cfRule type="expression" dxfId="132" priority="602">
       <formula>$AJ41="Yes – needs DB Dev to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K42">
-    <cfRule type="expression" dxfId="130" priority="603">
+    <cfRule type="expression" dxfId="131" priority="603">
       <formula>AND($B41&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="129" priority="604">
+    <cfRule type="expression" dxfId="130" priority="604">
       <formula>$AJ41="Yes – needs DB Dev to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K73:L100">
-    <cfRule type="expression" dxfId="128" priority="117">
+    <cfRule type="expression" dxfId="129" priority="117">
       <formula>$AF73="Yes – needs DB Dev to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K101:L115">
-    <cfRule type="expression" dxfId="127" priority="347">
+    <cfRule type="expression" dxfId="128" priority="347">
       <formula>$AA101="Yes – needs DB Dev to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K116:L527">
-    <cfRule type="expression" dxfId="126" priority="574">
+    <cfRule type="expression" dxfId="127" priority="574">
       <formula>$X116="Yes – needs DB Dev to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M73">
-    <cfRule type="expression" dxfId="125" priority="24">
+    <cfRule type="expression" dxfId="126" priority="24">
       <formula>$AF73="Yes – needs DB Dev to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M79">
-    <cfRule type="expression" dxfId="124" priority="11">
+    <cfRule type="expression" dxfId="125" priority="11">
       <formula>$AF79="Yes – needs DB Dev to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M73:P100">
-    <cfRule type="expression" dxfId="123" priority="302">
+    <cfRule type="expression" dxfId="124" priority="302">
       <formula>$AD73="Yes – needs PBI Dev to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M101:P115">
-    <cfRule type="expression" dxfId="122" priority="349">
+    <cfRule type="expression" dxfId="123" priority="349">
       <formula>$AA101="Yes – needs PBI Dev to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M116:P527">
-    <cfRule type="expression" dxfId="121" priority="575">
+    <cfRule type="expression" dxfId="122" priority="575">
       <formula>$X116="Yes – needs PBI Dev to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O101:O113">
-    <cfRule type="expression" dxfId="120" priority="23">
+    <cfRule type="expression" dxfId="121" priority="23">
       <formula>$AD101="Yes – needs PBI Dev to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q73:Q100">
-    <cfRule type="expression" dxfId="119" priority="18">
+    <cfRule type="expression" dxfId="120" priority="18">
       <formula>$AJ73="Yes – needs DB Dev to fix"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="118" priority="19">
+    <cfRule type="expression" dxfId="119" priority="19">
       <formula>$AF73="Yes – needs DB Dev to fix"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="117" priority="121">
+    <cfRule type="expression" dxfId="118" priority="121">
       <formula>$AF73="Yes – needs PBI Dev to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q101:R115 V101:V115 X101:X115">
-    <cfRule type="expression" dxfId="116" priority="17">
+    <cfRule type="expression" dxfId="117" priority="17">
       <formula>$AA101="Yes – needs QA to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q116:R527">
-    <cfRule type="expression" dxfId="115" priority="576">
+    <cfRule type="expression" dxfId="116" priority="576">
       <formula>$X116="Yes – needs QA to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U10:V19 X10:X19 J29 M29:P29 J32:J33 M32:P33 K40:K41 M40:P41 Q65 T65:U65 V101:V115 X101:X115 Q2:U64 Q66:U115">
-    <cfRule type="expression" dxfId="114" priority="32">
+    <cfRule type="expression" dxfId="115" priority="32">
       <formula>$AJ2="Yes – needs PBI Dev to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R58">
-    <cfRule type="expression" dxfId="113" priority="317">
+    <cfRule type="expression" dxfId="114" priority="317">
       <formula>AND($B65&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="112" priority="319">
+    <cfRule type="expression" dxfId="113" priority="319">
       <formula>$AJ65="Yes – needs PBI Dev to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R73:U100 T96:T101">
-    <cfRule type="expression" dxfId="111" priority="123">
+    <cfRule type="expression" dxfId="112" priority="123">
       <formula>$AF73="Yes – needs QA to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S101:U115">
-    <cfRule type="expression" dxfId="110" priority="363">
+    <cfRule type="expression" dxfId="111" priority="363">
       <formula>$AA101="Yes – needs DPO Approval to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S116:U527">
-    <cfRule type="expression" dxfId="109" priority="577">
+    <cfRule type="expression" dxfId="110" priority="577">
       <formula>$X116="Yes – needs DPO Approval to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U101:V527 X101:X527">
-    <cfRule type="expression" dxfId="108" priority="50">
+    <cfRule type="expression" dxfId="109" priority="50">
       <formula>$V101="Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U73:Y100">
-    <cfRule type="expression" dxfId="107" priority="125">
+    <cfRule type="expression" dxfId="108" priority="125">
       <formula>$AF73="Yes – needs DPO Approval to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X116:X527">
-    <cfRule type="expression" dxfId="106" priority="578">
+    <cfRule type="expression" dxfId="107" priority="578">
       <formula>LEFT($X116,3)="Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X73:Z100">
-    <cfRule type="expression" dxfId="105" priority="477">
+    <cfRule type="expression" dxfId="106" priority="477">
       <formula>$Y73="Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z116:AA527">
-    <cfRule type="expression" dxfId="104" priority="55">
+    <cfRule type="expression" dxfId="105" priority="55">
       <formula>ISNUMBER(SEARCH("Move old",$Z116))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="55">
+    <cfRule type="expression" dxfId="104" priority="55">
       <formula>ISNUMBER(SEARCH("log it",$Z116))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="102" priority="55">
+    <cfRule type="expression" dxfId="103" priority="55">
       <formula>ISNUMBER(SEARCH("Open rework",$Z116))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="56">
+    <cfRule type="expression" dxfId="102" priority="56">
       <formula>ISNUMBER(SEARCH("Duplicate",$Z116))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="57">
+    <cfRule type="expression" dxfId="101" priority="57">
       <formula>$Z116&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z116:AC527 G2:V40 N3:N44 L41:V42 T65:V65 G41:J42 Z2:AL2 Z3 Z4:AL41 Z42:AK42 Z43:AL44 Z45:AK47 Z101:AE115 AB3:AL3 A2:F87 G65:Q65 Z48:AL72 Z73:AH100 W2:Y527 G43:V64 G66:V73 A74:V527">
-    <cfRule type="expression" dxfId="99" priority="58">
+    <cfRule type="expression" dxfId="100" priority="58">
       <formula>AND($B2&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA3">
-    <cfRule type="expression" dxfId="98" priority="605">
+    <cfRule type="expression" dxfId="99" priority="605">
       <formula>AND($B3&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="606">
+    <cfRule type="expression" dxfId="98" priority="606">
       <formula>$AJ3="Yes – needs DPO Approval to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA101:AA115 U2:Z115">
-    <cfRule type="expression" dxfId="96" priority="15">
+    <cfRule type="expression" dxfId="97" priority="15">
       <formula>$AJ2="Yes – needs QA to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA101:AA115">
-    <cfRule type="expression" dxfId="95" priority="12">
+    <cfRule type="expression" dxfId="96" priority="12">
       <formula>$AJ101="Yes – needs PBI Dev to fix"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="94" priority="13">
+    <cfRule type="expression" dxfId="95" priority="13">
       <formula>$AA101="Yes – needs QA to fix"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="93" priority="14">
+    <cfRule type="expression" dxfId="94" priority="14">
       <formula>$V101="Yes"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="371">
+    <cfRule type="expression" dxfId="93" priority="371">
       <formula>LEFT($AA101,3)="Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AE2 AB3:AE3 AA4:AE100">
-    <cfRule type="expression" dxfId="91" priority="99">
+    <cfRule type="expression" dxfId="92" priority="99">
       <formula>$AJ2="Yes – needs DPO Approval to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB101:AC115">
-    <cfRule type="expression" dxfId="90" priority="379">
+    <cfRule type="expression" dxfId="91" priority="379">
       <formula>ISNUMBER(SEARCH("Open rework",$AB101))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="380">
+    <cfRule type="expression" dxfId="90" priority="380">
       <formula>ISNUMBER(SEARCH("Move old",$AB101))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="381">
+    <cfRule type="expression" dxfId="89" priority="381">
       <formula>ISNUMBER(SEARCH("log it",$AB101))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="87" priority="382">
+    <cfRule type="expression" dxfId="88" priority="382">
       <formula>ISNUMBER(SEARCH("Duplicate",$AB101))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="383">
+    <cfRule type="expression" dxfId="87" priority="383">
       <formula>$AB101&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF2:AF115">
-    <cfRule type="expression" dxfId="85" priority="71">
+    <cfRule type="expression" dxfId="86" priority="71">
       <formula>$AF2="Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF73:AF100">
-    <cfRule type="expression" dxfId="84" priority="129">
+    <cfRule type="expression" dxfId="85" priority="129">
       <formula>LEFT($AF73,3)="Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AG73:AG100">
-    <cfRule type="expression" dxfId="83" priority="135">
+    <cfRule type="expression" dxfId="84" priority="135">
       <formula>ISNUMBER(SEARCH("Open rework",$AG73))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="136">
+    <cfRule type="expression" dxfId="83" priority="136">
       <formula>ISNUMBER(SEARCH("Move old",$AG73))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="137">
+    <cfRule type="expression" dxfId="82" priority="137">
       <formula>ISNUMBER(SEARCH("log it",$AG73))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="138">
+    <cfRule type="expression" dxfId="81" priority="138">
       <formula>ISNUMBER(SEARCH("Duplicate",$AG73))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="79" priority="139">
+    <cfRule type="expression" dxfId="80" priority="139">
       <formula>$AG73&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AJ2:AJ115">
-    <cfRule type="expression" dxfId="78" priority="73">
+    <cfRule type="expression" dxfId="79" priority="73">
       <formula>LEFT($AJ2,3)="Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK2:AK115">
-    <cfRule type="expression" dxfId="77" priority="79">
+    <cfRule type="expression" dxfId="78" priority="79">
       <formula>ISNUMBER(SEARCH("log it",$AK2))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="80">
+    <cfRule type="expression" dxfId="77" priority="80">
       <formula>ISNUMBER(SEARCH("Open rework",$AK2))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="75" priority="81">
+    <cfRule type="expression" dxfId="76" priority="81">
       <formula>ISNUMBER(SEARCH("Move old",$AK2))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="82">
+    <cfRule type="expression" dxfId="75" priority="82">
       <formula>ISNUMBER(SEARCH("Duplicate",$AK2))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="83">
+    <cfRule type="expression" dxfId="74" priority="83">
       <formula>$AK2&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL45:AL47">
-    <cfRule type="expression" dxfId="72" priority="22">
+    <cfRule type="expression" dxfId="73" priority="22">
       <formula>AND($B49&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D88">
-    <cfRule type="expression" dxfId="71" priority="618">
+    <cfRule type="expression" dxfId="72" priority="618">
       <formula>AND($B50&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R60">
-    <cfRule type="expression" dxfId="70" priority="9">
+    <cfRule type="expression" dxfId="71" priority="9">
       <formula>AND($B67&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="10">
+    <cfRule type="expression" dxfId="70" priority="10">
       <formula>$AJ67="Yes – needs PBI Dev to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R60:S60">
-    <cfRule type="expression" dxfId="68" priority="7">
+    <cfRule type="expression" dxfId="69" priority="7">
       <formula>AND($B67&lt;&gt;"",MOD(ROW(),2)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="8">
+    <cfRule type="expression" dxfId="68" priority="8">
       <formula>$AJ67="Yes – needs PBI Dev to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N70">
-    <cfRule type="expression" dxfId="66" priority="6">
+    <cfRule type="expression" dxfId="67" priority="6">
       <formula>$AD70="Yes – needs PBI Dev to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N58">
-    <cfRule type="expression" dxfId="65" priority="5">
+    <cfRule type="expression" dxfId="66" priority="5">
       <formula>$AD58="Yes – needs PBI Dev to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M91">
-    <cfRule type="expression" dxfId="64" priority="4">
+    <cfRule type="expression" dxfId="65" priority="4">
       <formula>$AF91="Yes – needs DB Dev to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M80">
-    <cfRule type="expression" dxfId="63" priority="3">
+    <cfRule type="expression" dxfId="64" priority="3">
       <formula>$AF80="Yes – needs DB Dev to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N82">
-    <cfRule type="expression" dxfId="62" priority="2">
+    <cfRule type="expression" dxfId="63" priority="2">
       <formula>$AD82="Yes – needs PBI Dev to fix"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M83">
-    <cfRule type="expression" dxfId="61" priority="1">
+    <cfRule type="expression" dxfId="62" priority="1">
       <formula>$AF83="Yes – needs DB Dev to fix"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C115">
+    <cfRule type="expression" dxfId="61" priority="619">
+      <formula>LEFT($AK2,4)="Move"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
@@ -26789,7 +26862,7 @@
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="10">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="11">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Confirmed Deployed?" prompt="Confirmed live in production? Yes/No." xr:uid="{00000000-0002-0000-0100-000007000000}">
           <x14:formula1>
             <xm:f>'Data Validation'!$E$3:$E$4</xm:f>
@@ -26818,7 +26891,7 @@
           <x14:formula1>
             <xm:f>'Data Validation'!$F$3:$F$9</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C527</xm:sqref>
+          <xm:sqref>C116:C527</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="PO" prompt="Pick from the list, or type a new PO name." xr:uid="{00000000-0002-0000-0100-000003000000}">
           <x14:formula1>
@@ -26849,6 +26922,12 @@
             <xm:f>'Data Validation'!$E$3:$E$4</xm:f>
           </x14:formula1>
           <xm:sqref>AF73:AF100</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Update as you go" prompt="If this report is no longer at this stage, change it now. Move it forward as soon as your completion date is in, and move it back to the stage that owes a fix when it is sent back." xr:uid="{336805B9-9197-4DFE-8185-FF4B11254704}">
+          <x14:formula1>
+            <xm:f>'Data Validation'!$F$3:$F$9</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C115</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -27348,7 +27427,7 @@
         <v>46230</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D3" s="33" t="s">
         <v>182</v>
@@ -27407,7 +27486,7 @@
         <v>46237</v>
       </c>
       <c r="C4" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D4" s="31" t="s">
         <v>182</v>
@@ -27470,7 +27549,7 @@
         <v>46238</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D5" s="31" t="s">
         <v>182</v>
@@ -27529,7 +27608,7 @@
         <v>46234</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D6" s="31" t="s">
         <v>182</v>
@@ -27588,7 +27667,7 @@
         <v>46239</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D7" s="31" t="s">
         <v>182</v>
@@ -27647,7 +27726,7 @@
         <v>46246</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D8" s="31" t="s">
         <v>182</v>
@@ -27706,7 +27785,7 @@
         <v>46251</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D9" s="31" t="s">
         <v>182</v>
@@ -27765,7 +27844,7 @@
         <v>46237</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D10" s="31" t="s">
         <v>182</v>
@@ -27824,7 +27903,7 @@
         <v>46254</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D11" s="31" t="s">
         <v>182</v>
@@ -27883,7 +27962,7 @@
         <v>46254</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D12" s="31" t="s">
         <v>182</v>
@@ -27942,7 +28021,7 @@
         <v>46258</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D13" s="31" t="s">
         <v>182</v>
@@ -28001,7 +28080,7 @@
         <v>46258</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D14" s="31" t="s">
         <v>188</v>
@@ -28060,7 +28139,7 @@
         <v>46258</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D15" s="31" t="s">
         <v>188</v>
@@ -28119,7 +28198,7 @@
         <v>46258</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D16" s="31" t="s">
         <v>182</v>
@@ -28178,7 +28257,7 @@
         <v>46260</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D17" s="31" t="s">
         <v>188</v>
@@ -28210,7 +28289,7 @@
         <v>46261</v>
       </c>
       <c r="C18" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D18" s="31" t="s">
         <v>182</v>
@@ -28271,7 +28350,7 @@
         <v>46262</v>
       </c>
       <c r="C19" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D19" s="31" t="s">
         <v>188</v>
@@ -28330,7 +28409,7 @@
         <v>46265</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D20" s="31" t="s">
         <v>188</v>
@@ -28389,13 +28468,13 @@
     </row>
     <row r="21" spans="1:20" ht="15">
       <c r="A21" s="31" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B21" s="32">
         <v>46265</v>
       </c>
       <c r="C21" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D21" s="31" t="s">
         <v>182</v>
@@ -28458,7 +28537,7 @@
         <v>46265</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D22" s="31" t="s">
         <v>182</v>
@@ -28519,7 +28598,7 @@
         <v>46266</v>
       </c>
       <c r="C23" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D23" s="31" t="s">
         <v>188</v>
@@ -28584,7 +28663,7 @@
         <v>46266</v>
       </c>
       <c r="C24" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D24" s="31" t="s">
         <v>188</v>
@@ -28649,7 +28728,7 @@
         <v>46267</v>
       </c>
       <c r="C25" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D25" s="31" t="s">
         <v>188</v>
@@ -28714,7 +28793,7 @@
         <v>46267</v>
       </c>
       <c r="C26" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D26" s="31" t="s">
         <v>188</v>
@@ -28771,7 +28850,7 @@
         <v>46267</v>
       </c>
       <c r="C27" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D27" s="31" t="s">
         <v>182</v>
@@ -28832,7 +28911,7 @@
         <v>46267</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D28" s="31" t="s">
         <v>188</v>
@@ -28895,7 +28974,7 @@
         <v>46267</v>
       </c>
       <c r="C29" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D29" s="31" t="s">
         <v>188</v>
@@ -28958,7 +29037,7 @@
         <v>46267</v>
       </c>
       <c r="C30" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D30" s="31" t="s">
         <v>188</v>
@@ -29021,7 +29100,7 @@
         <v>46267</v>
       </c>
       <c r="C31" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D31" s="31" t="s">
         <v>182</v>
@@ -29082,7 +29161,7 @@
         <v>46268</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D32" s="31" t="s">
         <v>182</v>
@@ -29145,7 +29224,7 @@
         <v>46267</v>
       </c>
       <c r="C33" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D33" s="31" t="s">
         <v>182</v>
@@ -29204,7 +29283,7 @@
         <v>46273</v>
       </c>
       <c r="C34" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D34" s="31" t="s">
         <v>182</v>
@@ -29267,7 +29346,7 @@
         <v>46274</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D35" s="31" t="s">
         <v>188</v>
@@ -29332,7 +29411,7 @@
         <v>46275</v>
       </c>
       <c r="C36" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D36" s="31" t="s">
         <v>182</v>
@@ -29393,7 +29472,7 @@
         <v>46275</v>
       </c>
       <c r="C37" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D37" s="31" t="s">
         <v>182</v>
@@ -29447,7 +29526,7 @@
         <v>46279</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D38" s="31" t="s">
         <v>182</v>
@@ -29504,7 +29583,7 @@
         <v>46279</v>
       </c>
       <c r="C39" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D39" s="31" t="s">
         <v>188</v>
@@ -29569,7 +29648,7 @@
         <v>46280</v>
       </c>
       <c r="C40" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D40" s="31" t="s">
         <v>182</v>
@@ -29626,7 +29705,7 @@
         <v>46281</v>
       </c>
       <c r="C41" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D41" s="31" t="s">
         <v>188</v>
@@ -29680,7 +29759,7 @@
         <v>46282</v>
       </c>
       <c r="C42" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D42" s="31" t="s">
         <v>182</v>
@@ -29730,7 +29809,7 @@
       <c r="A43" s="31"/>
       <c r="B43" s="32"/>
       <c r="C43" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D43" s="31"/>
       <c r="E43" s="31"/>
@@ -29772,7 +29851,7 @@
       <c r="A44" s="31"/>
       <c r="B44" s="32"/>
       <c r="C44" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D44" s="31"/>
       <c r="E44" s="31"/>
@@ -29814,7 +29893,7 @@
       <c r="A45" s="31"/>
       <c r="B45" s="32"/>
       <c r="C45" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D45" s="31"/>
       <c r="E45" s="31"/>
@@ -29856,7 +29935,7 @@
       <c r="A46" s="31"/>
       <c r="B46" s="32"/>
       <c r="C46" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D46" s="31"/>
       <c r="E46" s="31"/>
@@ -29898,7 +29977,7 @@
       <c r="A47" s="31"/>
       <c r="B47" s="32"/>
       <c r="C47" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D47" s="31"/>
       <c r="E47" s="31"/>
@@ -29940,7 +30019,7 @@
       <c r="A48" s="31"/>
       <c r="B48" s="32"/>
       <c r="C48" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D48" s="31"/>
       <c r="E48" s="31"/>
@@ -29982,7 +30061,7 @@
       <c r="A49" s="31"/>
       <c r="B49" s="32"/>
       <c r="C49" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D49" s="31"/>
       <c r="E49" s="31"/>
@@ -30024,7 +30103,7 @@
       <c r="A50" s="31"/>
       <c r="B50" s="32"/>
       <c r="C50" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D50" s="31"/>
       <c r="E50" s="31"/>
@@ -30066,7 +30145,7 @@
       <c r="A51" s="31"/>
       <c r="B51" s="32"/>
       <c r="C51" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D51" s="31"/>
       <c r="E51" s="31"/>
@@ -30108,7 +30187,7 @@
       <c r="A52" s="31"/>
       <c r="B52" s="32"/>
       <c r="C52" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D52" s="31"/>
       <c r="E52" s="31"/>
@@ -30150,7 +30229,7 @@
       <c r="A53" s="31"/>
       <c r="B53" s="32"/>
       <c r="C53" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D53" s="31"/>
       <c r="E53" s="31"/>
@@ -30192,7 +30271,7 @@
       <c r="A54" s="31"/>
       <c r="B54" s="32"/>
       <c r="C54" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D54" s="31"/>
       <c r="E54" s="31"/>
@@ -30234,7 +30313,7 @@
       <c r="A55" s="31"/>
       <c r="B55" s="32"/>
       <c r="C55" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D55" s="31"/>
       <c r="E55" s="31"/>
@@ -30276,7 +30355,7 @@
       <c r="A56" s="31"/>
       <c r="B56" s="32"/>
       <c r="C56" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D56" s="31"/>
       <c r="E56" s="31"/>
@@ -30318,7 +30397,7 @@
       <c r="A57" s="31"/>
       <c r="B57" s="32"/>
       <c r="C57" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D57" s="31"/>
       <c r="E57" s="31"/>
@@ -30360,7 +30439,7 @@
       <c r="A58" s="31"/>
       <c r="B58" s="32"/>
       <c r="C58" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D58" s="31"/>
       <c r="E58" s="31"/>
@@ -30402,7 +30481,7 @@
       <c r="A59" s="31"/>
       <c r="B59" s="32"/>
       <c r="C59" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D59" s="31"/>
       <c r="E59" s="31"/>
@@ -30444,7 +30523,7 @@
       <c r="A60" s="31"/>
       <c r="B60" s="32"/>
       <c r="C60" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D60" s="31"/>
       <c r="E60" s="31"/>
@@ -30486,7 +30565,7 @@
       <c r="A61" s="31"/>
       <c r="B61" s="32"/>
       <c r="C61" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D61" s="31"/>
       <c r="E61" s="31"/>
@@ -30528,7 +30607,7 @@
       <c r="A62" s="31"/>
       <c r="B62" s="32"/>
       <c r="C62" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D62" s="31"/>
       <c r="E62" s="31"/>
@@ -30570,7 +30649,7 @@
       <c r="A63" s="31"/>
       <c r="B63" s="32"/>
       <c r="C63" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D63" s="31"/>
       <c r="E63" s="31"/>
@@ -30612,7 +30691,7 @@
       <c r="A64" s="31"/>
       <c r="B64" s="32"/>
       <c r="C64" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D64" s="31"/>
       <c r="E64" s="31"/>
@@ -30654,7 +30733,7 @@
       <c r="A65" s="31"/>
       <c r="B65" s="32"/>
       <c r="C65" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D65" s="31"/>
       <c r="E65" s="31"/>
@@ -30696,7 +30775,7 @@
       <c r="A66" s="31"/>
       <c r="B66" s="32"/>
       <c r="C66" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D66" s="31"/>
       <c r="E66" s="31"/>
@@ -30738,7 +30817,7 @@
       <c r="A67" s="31"/>
       <c r="B67" s="32"/>
       <c r="C67" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D67" s="31"/>
       <c r="E67" s="31"/>
@@ -30780,7 +30859,7 @@
       <c r="A68" s="31"/>
       <c r="B68" s="32"/>
       <c r="C68" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D68" s="31"/>
       <c r="E68" s="31"/>
@@ -30822,7 +30901,7 @@
       <c r="A69" s="31"/>
       <c r="B69" s="32"/>
       <c r="C69" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D69" s="31"/>
       <c r="E69" s="31"/>
@@ -30864,7 +30943,7 @@
       <c r="A70" s="31"/>
       <c r="B70" s="32"/>
       <c r="C70" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D70" s="31"/>
       <c r="E70" s="31"/>
@@ -30906,7 +30985,7 @@
       <c r="A71" s="31"/>
       <c r="B71" s="32"/>
       <c r="C71" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D71" s="31"/>
       <c r="E71" s="31"/>
@@ -30948,7 +31027,7 @@
       <c r="A72" s="31"/>
       <c r="B72" s="32"/>
       <c r="C72" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D72" s="31"/>
       <c r="E72" s="31"/>
@@ -30990,7 +31069,7 @@
       <c r="A73" s="31"/>
       <c r="B73" s="32"/>
       <c r="C73" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D73" s="31"/>
       <c r="E73" s="31"/>
@@ -31032,7 +31111,7 @@
       <c r="A74" s="31"/>
       <c r="B74" s="32"/>
       <c r="C74" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D74" s="31"/>
       <c r="E74" s="31"/>
@@ -31074,7 +31153,7 @@
       <c r="A75" s="31"/>
       <c r="B75" s="32"/>
       <c r="C75" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D75" s="31"/>
       <c r="E75" s="31"/>
@@ -31116,7 +31195,7 @@
       <c r="A76" s="31"/>
       <c r="B76" s="32"/>
       <c r="C76" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D76" s="31"/>
       <c r="E76" s="31"/>
@@ -31158,7 +31237,7 @@
       <c r="A77" s="31"/>
       <c r="B77" s="32"/>
       <c r="C77" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D77" s="31"/>
       <c r="E77" s="31"/>
@@ -31200,7 +31279,7 @@
       <c r="A78" s="31"/>
       <c r="B78" s="32"/>
       <c r="C78" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D78" s="31"/>
       <c r="E78" s="31"/>
@@ -31242,7 +31321,7 @@
       <c r="A79" s="31"/>
       <c r="B79" s="32"/>
       <c r="C79" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D79" s="31"/>
       <c r="E79" s="31"/>
@@ -31284,7 +31363,7 @@
       <c r="A80" s="31"/>
       <c r="B80" s="32"/>
       <c r="C80" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D80" s="31"/>
       <c r="E80" s="31"/>
@@ -31326,7 +31405,7 @@
       <c r="A81" s="31"/>
       <c r="B81" s="32"/>
       <c r="C81" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D81" s="31"/>
       <c r="E81" s="31"/>
@@ -31368,7 +31447,7 @@
       <c r="A82" s="31"/>
       <c r="B82" s="32"/>
       <c r="C82" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D82" s="31"/>
       <c r="E82" s="31"/>
@@ -31410,7 +31489,7 @@
       <c r="A83" s="31"/>
       <c r="B83" s="32"/>
       <c r="C83" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D83" s="31"/>
       <c r="E83" s="31"/>
@@ -31452,7 +31531,7 @@
       <c r="A84" s="31"/>
       <c r="B84" s="32"/>
       <c r="C84" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D84" s="31"/>
       <c r="E84" s="31"/>
@@ -31494,7 +31573,7 @@
       <c r="A85" s="31"/>
       <c r="B85" s="32"/>
       <c r="C85" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D85" s="31"/>
       <c r="E85" s="31"/>
@@ -31536,7 +31615,7 @@
       <c r="A86" s="31"/>
       <c r="B86" s="32"/>
       <c r="C86" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D86" s="31"/>
       <c r="E86" s="31"/>
@@ -31578,7 +31657,7 @@
       <c r="A87" s="31"/>
       <c r="B87" s="32"/>
       <c r="C87" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D87" s="31"/>
       <c r="E87" s="31"/>
@@ -31620,7 +31699,7 @@
       <c r="A88" s="31"/>
       <c r="B88" s="32"/>
       <c r="C88" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D88" s="31"/>
       <c r="E88" s="31"/>
@@ -31662,7 +31741,7 @@
       <c r="A89" s="31"/>
       <c r="B89" s="32"/>
       <c r="C89" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D89" s="31"/>
       <c r="E89" s="31"/>
@@ -31704,7 +31783,7 @@
       <c r="A90" s="31"/>
       <c r="B90" s="32"/>
       <c r="C90" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D90" s="31"/>
       <c r="E90" s="31"/>
@@ -31746,7 +31825,7 @@
       <c r="A91" s="31"/>
       <c r="B91" s="32"/>
       <c r="C91" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D91" s="31"/>
       <c r="E91" s="31"/>
@@ -31788,7 +31867,7 @@
       <c r="A92" s="31"/>
       <c r="B92" s="32"/>
       <c r="C92" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D92" s="31"/>
       <c r="E92" s="31"/>
@@ -31830,7 +31909,7 @@
       <c r="A93" s="31"/>
       <c r="B93" s="32"/>
       <c r="C93" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D93" s="31"/>
       <c r="E93" s="31"/>
@@ -31872,7 +31951,7 @@
       <c r="A94" s="31"/>
       <c r="B94" s="32"/>
       <c r="C94" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D94" s="31"/>
       <c r="E94" s="31"/>
@@ -31914,7 +31993,7 @@
       <c r="A95" s="31"/>
       <c r="B95" s="32"/>
       <c r="C95" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D95" s="31"/>
       <c r="E95" s="31"/>
@@ -31956,7 +32035,7 @@
       <c r="A96" s="31"/>
       <c r="B96" s="32"/>
       <c r="C96" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D96" s="31"/>
       <c r="E96" s="31"/>
@@ -31998,7 +32077,7 @@
       <c r="A97" s="31"/>
       <c r="B97" s="32"/>
       <c r="C97" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D97" s="31"/>
       <c r="E97" s="31"/>
@@ -32040,7 +32119,7 @@
       <c r="A98" s="31"/>
       <c r="B98" s="32"/>
       <c r="C98" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D98" s="31"/>
       <c r="E98" s="31"/>
@@ -32082,7 +32161,7 @@
       <c r="A99" s="31"/>
       <c r="B99" s="32"/>
       <c r="C99" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D99" s="31"/>
       <c r="E99" s="31"/>
@@ -32124,7 +32203,7 @@
       <c r="A100" s="31"/>
       <c r="B100" s="32"/>
       <c r="C100" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D100" s="31"/>
       <c r="E100" s="31"/>
@@ -32166,7 +32245,7 @@
       <c r="A101" s="31"/>
       <c r="B101" s="32"/>
       <c r="C101" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D101" s="31"/>
       <c r="E101" s="31"/>
@@ -32208,7 +32287,7 @@
       <c r="A102" s="31"/>
       <c r="B102" s="32"/>
       <c r="C102" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D102" s="31"/>
       <c r="E102" s="31"/>
@@ -32250,7 +32329,7 @@
       <c r="A103" s="31"/>
       <c r="B103" s="32"/>
       <c r="C103" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D103" s="31"/>
       <c r="E103" s="31"/>
@@ -32292,7 +32371,7 @@
       <c r="A104" s="31"/>
       <c r="B104" s="32"/>
       <c r="C104" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D104" s="31"/>
       <c r="E104" s="31"/>
@@ -32334,7 +32413,7 @@
       <c r="A105" s="31"/>
       <c r="B105" s="32"/>
       <c r="C105" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D105" s="31"/>
       <c r="E105" s="31"/>
@@ -32376,7 +32455,7 @@
       <c r="A106" s="31"/>
       <c r="B106" s="32"/>
       <c r="C106" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D106" s="31"/>
       <c r="E106" s="31"/>
@@ -32418,7 +32497,7 @@
       <c r="A107" s="31"/>
       <c r="B107" s="32"/>
       <c r="C107" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D107" s="31"/>
       <c r="E107" s="31"/>
@@ -32460,7 +32539,7 @@
       <c r="A108" s="31"/>
       <c r="B108" s="32"/>
       <c r="C108" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D108" s="31"/>
       <c r="E108" s="31"/>
@@ -32502,7 +32581,7 @@
       <c r="A109" s="31"/>
       <c r="B109" s="32"/>
       <c r="C109" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D109" s="31"/>
       <c r="E109" s="31"/>
@@ -32544,7 +32623,7 @@
       <c r="A110" s="31"/>
       <c r="B110" s="32"/>
       <c r="C110" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D110" s="31"/>
       <c r="E110" s="31"/>
@@ -32586,7 +32665,7 @@
       <c r="A111" s="31"/>
       <c r="B111" s="32"/>
       <c r="C111" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D111" s="31"/>
       <c r="E111" s="31"/>
@@ -32628,7 +32707,7 @@
       <c r="A112" s="31"/>
       <c r="B112" s="32"/>
       <c r="C112" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D112" s="31"/>
       <c r="E112" s="31"/>
@@ -32670,7 +32749,7 @@
       <c r="A113" s="31"/>
       <c r="B113" s="32"/>
       <c r="C113" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D113" s="31"/>
       <c r="E113" s="31"/>
@@ -32712,7 +32791,7 @@
       <c r="A114" s="31"/>
       <c r="B114" s="32"/>
       <c r="C114" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D114" s="31"/>
       <c r="E114" s="31"/>
@@ -32754,7 +32833,7 @@
       <c r="A115" s="31"/>
       <c r="B115" s="32"/>
       <c r="C115" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D115" s="31"/>
       <c r="E115" s="31"/>
@@ -32796,7 +32875,7 @@
       <c r="A116" s="31"/>
       <c r="B116" s="32"/>
       <c r="C116" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D116" s="31"/>
       <c r="E116" s="31"/>
@@ -32838,7 +32917,7 @@
       <c r="A117" s="31"/>
       <c r="B117" s="32"/>
       <c r="C117" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D117" s="31"/>
       <c r="E117" s="31"/>
@@ -32880,7 +32959,7 @@
       <c r="A118" s="31"/>
       <c r="B118" s="32"/>
       <c r="C118" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D118" s="31"/>
       <c r="E118" s="31"/>
@@ -32922,7 +33001,7 @@
       <c r="A119" s="31"/>
       <c r="B119" s="32"/>
       <c r="C119" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D119" s="31"/>
       <c r="E119" s="31"/>
@@ -32964,7 +33043,7 @@
       <c r="A120" s="31"/>
       <c r="B120" s="32"/>
       <c r="C120" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D120" s="31"/>
       <c r="E120" s="31"/>
@@ -33006,7 +33085,7 @@
       <c r="A121" s="31"/>
       <c r="B121" s="32"/>
       <c r="C121" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D121" s="31"/>
       <c r="E121" s="31"/>
@@ -33048,7 +33127,7 @@
       <c r="A122" s="31"/>
       <c r="B122" s="32"/>
       <c r="C122" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D122" s="31"/>
       <c r="E122" s="31"/>
@@ -33090,7 +33169,7 @@
       <c r="A123" s="31"/>
       <c r="B123" s="32"/>
       <c r="C123" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D123" s="31"/>
       <c r="E123" s="31"/>
@@ -33132,7 +33211,7 @@
       <c r="A124" s="31"/>
       <c r="B124" s="32"/>
       <c r="C124" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D124" s="31"/>
       <c r="E124" s="31"/>
@@ -33174,7 +33253,7 @@
       <c r="A125" s="31"/>
       <c r="B125" s="32"/>
       <c r="C125" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D125" s="31"/>
       <c r="E125" s="31"/>
@@ -33216,7 +33295,7 @@
       <c r="A126" s="31"/>
       <c r="B126" s="32"/>
       <c r="C126" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D126" s="31"/>
       <c r="E126" s="31"/>
@@ -33258,7 +33337,7 @@
       <c r="A127" s="31"/>
       <c r="B127" s="32"/>
       <c r="C127" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D127" s="31"/>
       <c r="E127" s="31"/>
@@ -33300,7 +33379,7 @@
       <c r="A128" s="31"/>
       <c r="B128" s="32"/>
       <c r="C128" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D128" s="31"/>
       <c r="E128" s="31"/>
@@ -33342,7 +33421,7 @@
       <c r="A129" s="31"/>
       <c r="B129" s="32"/>
       <c r="C129" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D129" s="31"/>
       <c r="E129" s="31"/>
@@ -33384,7 +33463,7 @@
       <c r="A130" s="31"/>
       <c r="B130" s="32"/>
       <c r="C130" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D130" s="31"/>
       <c r="E130" s="31"/>
@@ -33426,7 +33505,7 @@
       <c r="A131" s="31"/>
       <c r="B131" s="32"/>
       <c r="C131" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D131" s="31"/>
       <c r="E131" s="31"/>
@@ -33468,7 +33547,7 @@
       <c r="A132" s="31"/>
       <c r="B132" s="32"/>
       <c r="C132" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D132" s="31"/>
       <c r="E132" s="31"/>
@@ -33510,7 +33589,7 @@
       <c r="A133" s="31"/>
       <c r="B133" s="32"/>
       <c r="C133" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D133" s="31"/>
       <c r="E133" s="31"/>
@@ -33552,7 +33631,7 @@
       <c r="A134" s="31"/>
       <c r="B134" s="32"/>
       <c r="C134" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D134" s="31"/>
       <c r="E134" s="31"/>
@@ -33594,7 +33673,7 @@
       <c r="A135" s="31"/>
       <c r="B135" s="32"/>
       <c r="C135" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D135" s="31"/>
       <c r="E135" s="31"/>
@@ -33636,7 +33715,7 @@
       <c r="A136" s="31"/>
       <c r="B136" s="32"/>
       <c r="C136" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D136" s="31"/>
       <c r="E136" s="31"/>
@@ -33678,7 +33757,7 @@
       <c r="A137" s="31"/>
       <c r="B137" s="32"/>
       <c r="C137" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D137" s="31"/>
       <c r="E137" s="31"/>
@@ -33720,7 +33799,7 @@
       <c r="A138" s="31"/>
       <c r="B138" s="32"/>
       <c r="C138" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D138" s="31"/>
       <c r="E138" s="31"/>
@@ -33762,7 +33841,7 @@
       <c r="A139" s="31"/>
       <c r="B139" s="32"/>
       <c r="C139" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D139" s="31"/>
       <c r="E139" s="31"/>
@@ -33804,7 +33883,7 @@
       <c r="A140" s="31"/>
       <c r="B140" s="32"/>
       <c r="C140" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D140" s="31"/>
       <c r="E140" s="31"/>
@@ -33846,7 +33925,7 @@
       <c r="A141" s="31"/>
       <c r="B141" s="32"/>
       <c r="C141" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D141" s="31"/>
       <c r="E141" s="31"/>
@@ -33888,7 +33967,7 @@
       <c r="A142" s="31"/>
       <c r="B142" s="32"/>
       <c r="C142" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D142" s="31"/>
       <c r="E142" s="31"/>
@@ -33930,7 +34009,7 @@
       <c r="A143" s="31"/>
       <c r="B143" s="32"/>
       <c r="C143" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D143" s="31"/>
       <c r="E143" s="31"/>
@@ -33972,7 +34051,7 @@
       <c r="A144" s="31"/>
       <c r="B144" s="32"/>
       <c r="C144" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D144" s="31"/>
       <c r="E144" s="31"/>
@@ -34014,7 +34093,7 @@
       <c r="A145" s="31"/>
       <c r="B145" s="32"/>
       <c r="C145" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D145" s="31"/>
       <c r="E145" s="31"/>
@@ -34056,7 +34135,7 @@
       <c r="A146" s="31"/>
       <c r="B146" s="32"/>
       <c r="C146" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D146" s="31"/>
       <c r="E146" s="31"/>
@@ -34098,7 +34177,7 @@
       <c r="A147" s="31"/>
       <c r="B147" s="32"/>
       <c r="C147" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D147" s="31"/>
       <c r="E147" s="31"/>
@@ -34140,7 +34219,7 @@
       <c r="A148" s="31"/>
       <c r="B148" s="32"/>
       <c r="C148" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D148" s="31"/>
       <c r="E148" s="31"/>
@@ -34182,7 +34261,7 @@
       <c r="A149" s="31"/>
       <c r="B149" s="32"/>
       <c r="C149" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D149" s="31"/>
       <c r="E149" s="31"/>
@@ -34224,7 +34303,7 @@
       <c r="A150" s="31"/>
       <c r="B150" s="32"/>
       <c r="C150" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D150" s="31"/>
       <c r="E150" s="31"/>
@@ -34266,7 +34345,7 @@
       <c r="A151" s="31"/>
       <c r="B151" s="32"/>
       <c r="C151" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D151" s="31"/>
       <c r="E151" s="31"/>
@@ -34308,7 +34387,7 @@
       <c r="A152" s="31"/>
       <c r="B152" s="32"/>
       <c r="C152" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D152" s="31"/>
       <c r="E152" s="31"/>
@@ -34350,7 +34429,7 @@
       <c r="A153" s="31"/>
       <c r="B153" s="32"/>
       <c r="C153" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D153" s="31"/>
       <c r="E153" s="31"/>
@@ -34392,7 +34471,7 @@
       <c r="A154" s="31"/>
       <c r="B154" s="32"/>
       <c r="C154" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D154" s="31"/>
       <c r="E154" s="31"/>
@@ -34434,7 +34513,7 @@
       <c r="A155" s="31"/>
       <c r="B155" s="32"/>
       <c r="C155" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D155" s="31"/>
       <c r="E155" s="31"/>
@@ -34476,7 +34555,7 @@
       <c r="A156" s="31"/>
       <c r="B156" s="32"/>
       <c r="C156" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D156" s="31"/>
       <c r="E156" s="31"/>
@@ -34518,7 +34597,7 @@
       <c r="A157" s="31"/>
       <c r="B157" s="32"/>
       <c r="C157" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D157" s="31"/>
       <c r="E157" s="31"/>
@@ -34560,7 +34639,7 @@
       <c r="A158" s="31"/>
       <c r="B158" s="32"/>
       <c r="C158" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D158" s="31"/>
       <c r="E158" s="31"/>
@@ -34602,7 +34681,7 @@
       <c r="A159" s="31"/>
       <c r="B159" s="32"/>
       <c r="C159" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D159" s="31"/>
       <c r="E159" s="31"/>
@@ -34644,7 +34723,7 @@
       <c r="A160" s="31"/>
       <c r="B160" s="32"/>
       <c r="C160" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D160" s="31"/>
       <c r="E160" s="31"/>
@@ -34686,7 +34765,7 @@
       <c r="A161" s="31"/>
       <c r="B161" s="32"/>
       <c r="C161" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D161" s="31"/>
       <c r="E161" s="31"/>
@@ -34728,7 +34807,7 @@
       <c r="A162" s="31"/>
       <c r="B162" s="32"/>
       <c r="C162" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D162" s="31"/>
       <c r="E162" s="31"/>
@@ -34770,7 +34849,7 @@
       <c r="A163" s="31"/>
       <c r="B163" s="32"/>
       <c r="C163" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D163" s="31"/>
       <c r="E163" s="31"/>
@@ -34812,7 +34891,7 @@
       <c r="A164" s="31"/>
       <c r="B164" s="32"/>
       <c r="C164" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D164" s="31"/>
       <c r="E164" s="31"/>
@@ -34854,7 +34933,7 @@
       <c r="A165" s="31"/>
       <c r="B165" s="32"/>
       <c r="C165" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D165" s="31"/>
       <c r="E165" s="31"/>
@@ -34896,7 +34975,7 @@
       <c r="A166" s="31"/>
       <c r="B166" s="32"/>
       <c r="C166" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D166" s="31"/>
       <c r="E166" s="31"/>
@@ -34938,7 +35017,7 @@
       <c r="A167" s="31"/>
       <c r="B167" s="32"/>
       <c r="C167" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D167" s="31"/>
       <c r="E167" s="31"/>
@@ -34980,7 +35059,7 @@
       <c r="A168" s="31"/>
       <c r="B168" s="32"/>
       <c r="C168" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D168" s="31"/>
       <c r="E168" s="31"/>
@@ -35022,7 +35101,7 @@
       <c r="A169" s="31"/>
       <c r="B169" s="32"/>
       <c r="C169" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D169" s="31"/>
       <c r="E169" s="31"/>
@@ -35064,7 +35143,7 @@
       <c r="A170" s="31"/>
       <c r="B170" s="32"/>
       <c r="C170" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D170" s="31"/>
       <c r="E170" s="31"/>
@@ -35106,7 +35185,7 @@
       <c r="A171" s="31"/>
       <c r="B171" s="32"/>
       <c r="C171" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D171" s="31"/>
       <c r="E171" s="31"/>
@@ -35148,7 +35227,7 @@
       <c r="A172" s="31"/>
       <c r="B172" s="32"/>
       <c r="C172" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D172" s="31"/>
       <c r="E172" s="31"/>
@@ -35190,7 +35269,7 @@
       <c r="A173" s="31"/>
       <c r="B173" s="32"/>
       <c r="C173" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D173" s="31"/>
       <c r="E173" s="31"/>
@@ -35232,7 +35311,7 @@
       <c r="A174" s="31"/>
       <c r="B174" s="32"/>
       <c r="C174" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D174" s="31"/>
       <c r="E174" s="31"/>
@@ -35274,7 +35353,7 @@
       <c r="A175" s="31"/>
       <c r="B175" s="32"/>
       <c r="C175" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D175" s="31"/>
       <c r="E175" s="31"/>
@@ -35316,7 +35395,7 @@
       <c r="A176" s="31"/>
       <c r="B176" s="32"/>
       <c r="C176" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D176" s="31"/>
       <c r="E176" s="31"/>
@@ -35358,7 +35437,7 @@
       <c r="A177" s="31"/>
       <c r="B177" s="32"/>
       <c r="C177" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D177" s="31"/>
       <c r="E177" s="31"/>
@@ -35400,7 +35479,7 @@
       <c r="A178" s="31"/>
       <c r="B178" s="32"/>
       <c r="C178" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D178" s="31"/>
       <c r="E178" s="31"/>
@@ -35442,7 +35521,7 @@
       <c r="A179" s="31"/>
       <c r="B179" s="32"/>
       <c r="C179" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D179" s="31"/>
       <c r="E179" s="31"/>
@@ -35484,7 +35563,7 @@
       <c r="A180" s="31"/>
       <c r="B180" s="32"/>
       <c r="C180" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D180" s="31"/>
       <c r="E180" s="31"/>
@@ -35526,7 +35605,7 @@
       <c r="A181" s="31"/>
       <c r="B181" s="32"/>
       <c r="C181" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D181" s="31"/>
       <c r="E181" s="31"/>
@@ -35568,7 +35647,7 @@
       <c r="A182" s="31"/>
       <c r="B182" s="32"/>
       <c r="C182" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D182" s="31"/>
       <c r="E182" s="31"/>
@@ -35610,7 +35689,7 @@
       <c r="A183" s="31"/>
       <c r="B183" s="32"/>
       <c r="C183" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D183" s="31"/>
       <c r="E183" s="31"/>
@@ -35652,7 +35731,7 @@
       <c r="A184" s="31"/>
       <c r="B184" s="32"/>
       <c r="C184" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D184" s="31"/>
       <c r="E184" s="31"/>
@@ -35694,7 +35773,7 @@
       <c r="A185" s="31"/>
       <c r="B185" s="32"/>
       <c r="C185" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D185" s="31"/>
       <c r="E185" s="31"/>
@@ -35736,7 +35815,7 @@
       <c r="A186" s="31"/>
       <c r="B186" s="32"/>
       <c r="C186" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D186" s="31"/>
       <c r="E186" s="31"/>
@@ -35778,7 +35857,7 @@
       <c r="A187" s="31"/>
       <c r="B187" s="32"/>
       <c r="C187" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D187" s="31"/>
       <c r="E187" s="31"/>
@@ -35820,7 +35899,7 @@
       <c r="A188" s="31"/>
       <c r="B188" s="32"/>
       <c r="C188" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D188" s="31"/>
       <c r="E188" s="31"/>
@@ -35862,7 +35941,7 @@
       <c r="A189" s="31"/>
       <c r="B189" s="32"/>
       <c r="C189" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D189" s="31"/>
       <c r="E189" s="31"/>
@@ -35904,7 +35983,7 @@
       <c r="A190" s="31"/>
       <c r="B190" s="32"/>
       <c r="C190" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D190" s="31"/>
       <c r="E190" s="31"/>
@@ -35946,7 +36025,7 @@
       <c r="A191" s="31"/>
       <c r="B191" s="32"/>
       <c r="C191" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D191" s="31"/>
       <c r="E191" s="31"/>
@@ -35988,7 +36067,7 @@
       <c r="A192" s="31"/>
       <c r="B192" s="32"/>
       <c r="C192" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D192" s="31"/>
       <c r="E192" s="31"/>
@@ -36030,7 +36109,7 @@
       <c r="A193" s="31"/>
       <c r="B193" s="32"/>
       <c r="C193" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D193" s="31"/>
       <c r="E193" s="31"/>
@@ -36072,7 +36151,7 @@
       <c r="A194" s="31"/>
       <c r="B194" s="32"/>
       <c r="C194" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D194" s="31"/>
       <c r="E194" s="31"/>
@@ -36114,7 +36193,7 @@
       <c r="A195" s="31"/>
       <c r="B195" s="32"/>
       <c r="C195" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D195" s="31"/>
       <c r="E195" s="31"/>
@@ -36156,7 +36235,7 @@
       <c r="A196" s="31"/>
       <c r="B196" s="32"/>
       <c r="C196" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D196" s="31"/>
       <c r="E196" s="31"/>
@@ -36198,7 +36277,7 @@
       <c r="A197" s="31"/>
       <c r="B197" s="32"/>
       <c r="C197" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D197" s="31"/>
       <c r="E197" s="31"/>
@@ -36240,7 +36319,7 @@
       <c r="A198" s="31"/>
       <c r="B198" s="32"/>
       <c r="C198" s="31" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D198" s="31"/>
       <c r="E198" s="31"/>
@@ -48237,7 +48316,7 @@
         <v>40</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>41</v>
@@ -48365,7 +48444,7 @@
         <v>40</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>55</v>
@@ -48493,7 +48572,7 @@
         <v>40</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>424</v>
@@ -48621,7 +48700,7 @@
         <v>40</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>58</v>
@@ -48749,7 +48828,7 @@
         <v>40</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>64</v>
@@ -48877,7 +48956,7 @@
         <v>40</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>69</v>
@@ -49005,7 +49084,7 @@
         <v>40</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>70</v>
@@ -49133,7 +49212,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C40" s="9" t="s">
         <v>71</v>
@@ -49261,7 +49340,7 @@
         <v>40</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>73</v>
@@ -49383,7 +49462,7 @@
         <v>40</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C50" s="9" t="s">
         <v>97</v>
@@ -49505,7 +49584,7 @@
         <v>40</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C55" s="9" t="s">
         <v>98</v>
@@ -49627,7 +49706,7 @@
         <v>40</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C60" s="9" t="s">
         <v>99</v>
@@ -49749,7 +49828,7 @@
         <v>40</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C65" s="9" t="s">
         <v>100</v>
@@ -49875,7 +49954,7 @@
         <v>40</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C70" s="9" t="s">
         <v>74</v>
@@ -49997,7 +50076,7 @@
         <v>40</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C75" s="9" t="s">
         <v>80</v>
@@ -50119,7 +50198,7 @@
         <v>40</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C80" s="9" t="s">
         <v>83</v>
@@ -50241,7 +50320,7 @@
         <v>40</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C85" s="9" t="s">
         <v>87</v>
@@ -50363,7 +50442,7 @@
         <v>40</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C90" s="9" t="s">
         <v>90</v>
@@ -50495,7 +50574,7 @@
         <v>40</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C95" s="9" t="s">
         <v>93</v>
@@ -50627,7 +50706,7 @@
         <v>40</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C100" s="9" t="s">
         <v>101</v>
@@ -50755,7 +50834,7 @@
         <v>40</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C105" s="9" t="s">
         <v>105</v>
@@ -50883,7 +50962,7 @@
         <v>40</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C110" s="9" t="s">
         <v>108</v>
@@ -51011,7 +51090,7 @@
         <v>40</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C115" s="9" t="s">
         <v>109</v>
@@ -51143,7 +51222,7 @@
         <v>40</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C120" s="9" t="s">
         <v>113</v>
@@ -51225,7 +51304,7 @@
         <v>40</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C123" s="9" t="s">
         <v>116</v>
@@ -51353,7 +51432,7 @@
         <v>40</v>
       </c>
       <c r="B128" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C128" s="9" t="s">
         <v>117</v>
@@ -51481,7 +51560,7 @@
         <v>40</v>
       </c>
       <c r="B133" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C133" s="9" t="s">
         <v>121</v>
@@ -51613,7 +51692,7 @@
         <v>40</v>
       </c>
       <c r="B138" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C138" s="9" t="s">
         <v>123</v>
@@ -51739,7 +51818,7 @@
         <v>126</v>
       </c>
       <c r="B143" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C143" s="9" t="s">
         <v>127</v>
@@ -51821,7 +51900,7 @@
         <v>126</v>
       </c>
       <c r="B146" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C146" s="9" t="s">
         <v>134</v>
@@ -51903,7 +51982,7 @@
         <v>126</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C149" s="9" t="s">
         <v>136</v>
@@ -51985,7 +52064,7 @@
         <v>126</v>
       </c>
       <c r="B152" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C152" s="9" t="s">
         <v>138</v>
@@ -52067,7 +52146,7 @@
         <v>126</v>
       </c>
       <c r="B155" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C155" s="9" t="s">
         <v>140</v>
@@ -52197,7 +52276,7 @@
         <v>126</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>148</v>
@@ -52279,7 +52358,7 @@
         <v>126</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C163" s="3" t="s">
         <v>149</v>
@@ -52361,7 +52440,7 @@
         <v>126</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C166" s="3" t="s">
         <v>152</v>
@@ -52443,7 +52522,7 @@
         <v>126</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C169" s="3" t="s">
         <v>155</v>
@@ -52525,7 +52604,7 @@
         <v>126</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C172" s="3" t="s">
         <v>156</v>
@@ -52607,7 +52686,7 @@
         <v>126</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C175" s="3" t="s">
         <v>158</v>
@@ -52689,7 +52768,7 @@
         <v>126</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C178" s="3" t="s">
         <v>160</v>
@@ -52759,7 +52838,7 @@
         <v>126</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C181" s="3" t="s">
         <v>163</v>
@@ -52782,7 +52861,7 @@
         <v>182</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D182" s="3" t="s">
         <v>84</v>
@@ -52802,7 +52881,7 @@
         <v>188</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D183" s="3" t="s">
         <v>84</v>
@@ -52819,10 +52898,10 @@
         <v>126</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D184" s="3" t="s">
         <v>84</v>
@@ -53087,7 +53166,7 @@
         <v>210</v>
       </c>
       <c r="J5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L5" t="s">
         <v>448</v>
@@ -53107,7 +53186,7 @@
         <v>84</v>
       </c>
       <c r="F6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G6" t="s">
         <v>84</v>
